--- a/All_perf.xlsx
+++ b/All_perf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ttdkoc/Documents/dev/workspaces/python/copt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60CD728B-BD31-754B-A824-61B40E39458F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918BE3DF-5DF5-4943-91DA-9F177CA705BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20440" activeTab="8" xr2:uid="{544C10BC-9448-4CAA-97CB-C174D9523FCA}"/>
   </bookViews>
@@ -17,11 +17,13 @@
     <sheet name="Durations" sheetId="2" r:id="rId2"/>
     <sheet name="strict channel" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
-    <sheet name="NetworkingEXX" sheetId="5" r:id="rId5"/>
-    <sheet name="NetworkingLESS" sheetId="7" r:id="rId6"/>
-    <sheet name="TestInstances" sheetId="8" r:id="rId7"/>
-    <sheet name="OvGap" sheetId="9" r:id="rId8"/>
-    <sheet name="IntraGap" sheetId="10" r:id="rId9"/>
+    <sheet name="Sheet3" sheetId="12" r:id="rId5"/>
+    <sheet name="NetworkingEXX" sheetId="5" r:id="rId6"/>
+    <sheet name="NetworkingLESS" sheetId="7" r:id="rId7"/>
+    <sheet name="TestInstances" sheetId="8" r:id="rId8"/>
+    <sheet name="OV over DM" sheetId="13" r:id="rId9"/>
+    <sheet name="OvGap" sheetId="9" r:id="rId10"/>
+    <sheet name="IntraGap" sheetId="10" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="49">
   <si>
     <t>Exact</t>
   </si>
@@ -149,6 +151,54 @@
   <si>
     <t>Objective Value Gap To Algorithm-C(%)</t>
   </si>
+  <si>
+    <t>OV-S Diff</t>
+  </si>
+  <si>
+    <t>SA+Greed With Alg-C</t>
+  </si>
+  <si>
+    <t>Agg+Grdy
+Alg-A</t>
+  </si>
+  <si>
+    <t>Agg+Grdy
+Alg-B</t>
+  </si>
+  <si>
+    <t>Agg+Grdy
+Alg-C</t>
+  </si>
+  <si>
+    <t>SimA+Grdy Alg-C</t>
+  </si>
+  <si>
+    <t>SimAnn+Grdy
+Alg-C</t>
+  </si>
+  <si>
+    <t>Obj. Value Gap To 
+SimAnn+Grdy Alg-C(\%)</t>
+  </si>
+  <si>
+    <t>OV/DM</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Exact (CPLEX Solver)</t>
+  </si>
+  <si>
+    <t>Agg+ Grdy(A)</t>
+  </si>
+  <si>
+    <t>Agg+Grdy(B)</t>
+  </si>
+  <si>
+    <t>SA+Agg+
+Grdy©</t>
+  </si>
 </sst>
 </file>
 
@@ -156,7 +206,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="176" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -380,7 +430,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -406,21 +456,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -432,32 +474,50 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -465,17 +525,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -16851,27 +16910,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="F1" s="19" t="s">
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="F1" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="J1" s="19" t="s">
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="J1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="N1" s="19" t="s">
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="N1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="O1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
+      <c r="O1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
     </row>
     <row r="2" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B2">
@@ -18784,6 +18843,3377 @@
 </oddHeader>
   </headerFooter>
   <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4BCCACE-EA30-D046-B0A4-6BE1833C0F15}">
+  <dimension ref="A1:V43"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="5" max="5" width="2.6640625" customWidth="1"/>
+    <col min="13" max="15" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="2.83203125" customWidth="1"/>
+    <col min="18" max="18" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="33"/>
+      <c r="V1" s="33"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A2" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="L2" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="S2" s="50"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="50"/>
+      <c r="V2" s="50"/>
+    </row>
+    <row r="3" spans="1:22" ht="32" x14ac:dyDescent="0.2">
+      <c r="A3" s="49"/>
+      <c r="B3" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="27"/>
+      <c r="F3" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="49"/>
+      <c r="M3" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="O3" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="P3" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="S3" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="T3" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="U3" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="V3" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="23">
+        <f>NetworkingLESS!N5</f>
+        <v>0.24545454545454545</v>
+      </c>
+      <c r="C4" s="23">
+        <f>NetworkingLESS!V5</f>
+        <v>0.24545454545454545</v>
+      </c>
+      <c r="D4" s="24">
+        <f>NetworkingLESS!AD5</f>
+        <v>0.24545454545454545</v>
+      </c>
+      <c r="E4" s="24"/>
+      <c r="F4" s="20">
+        <f>NetworkingLESS!E5</f>
+        <v>0.02</v>
+      </c>
+      <c r="G4" s="20">
+        <f>NetworkingLESS!K5</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="20">
+        <f>NetworkingLESS!S5</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="20">
+        <f>NetworkingLESS!AA5</f>
+        <v>0.03</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4" s="2">
+        <f>NetworkingLESS!N5</f>
+        <v>0.24545454545454545</v>
+      </c>
+      <c r="N4" s="2">
+        <f>NetworkingLESS!V5</f>
+        <v>0.24545454545454545</v>
+      </c>
+      <c r="O4" s="43">
+        <f>NetworkingLESS!AD5</f>
+        <v>0.24545454545454545</v>
+      </c>
+      <c r="P4" s="43">
+        <f>NetworkingLESS!AK4</f>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="20">
+        <f>NetworkingLESS!E5</f>
+        <v>0.02</v>
+      </c>
+      <c r="S4" s="20">
+        <f>NetworkingLESS!K5</f>
+        <v>0</v>
+      </c>
+      <c r="T4" s="20">
+        <f>NetworkingLESS!S5</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="20">
+        <f>NetworkingLESS!AA5</f>
+        <v>0.03</v>
+      </c>
+      <c r="V4" s="20">
+        <f>NetworkingLESS!AH5</f>
+        <v>3.4000000000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" s="23">
+        <f>NetworkingLESS!N6</f>
+        <v>0.60356652949245537</v>
+      </c>
+      <c r="C5" s="23">
+        <f>NetworkingLESS!V6</f>
+        <v>0.60356652949245537</v>
+      </c>
+      <c r="D5" s="24">
+        <f>NetworkingLESS!AD6</f>
+        <v>0.19204389574759945</v>
+      </c>
+      <c r="E5" s="24"/>
+      <c r="F5" s="20">
+        <f>NetworkingLESS!E6</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G5" s="20">
+        <f>NetworkingLESS!K6</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="20">
+        <f>NetworkingLESS!S6</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="20">
+        <f>NetworkingLESS!AA6</f>
+        <v>0.06</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5" s="2">
+        <f>NetworkingLESS!N6</f>
+        <v>0.60356652949245537</v>
+      </c>
+      <c r="N5" s="2">
+        <f>NetworkingLESS!V6</f>
+        <v>0.60356652949245537</v>
+      </c>
+      <c r="O5" s="43">
+        <f>NetworkingLESS!AD6</f>
+        <v>0.19204389574759945</v>
+      </c>
+      <c r="P5" s="43">
+        <f>NetworkingLESS!AK5</f>
+        <v>1.8552875695732839E-2</v>
+      </c>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="20">
+        <f>NetworkingLESS!E6</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="S5" s="20">
+        <f>NetworkingLESS!K6</f>
+        <v>0</v>
+      </c>
+      <c r="T5" s="20">
+        <f>NetworkingLESS!S6</f>
+        <v>0</v>
+      </c>
+      <c r="U5" s="20">
+        <f>NetworkingLESS!AA6</f>
+        <v>0.06</v>
+      </c>
+      <c r="V5" s="20">
+        <f>NetworkingLESS!AH6</f>
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" s="23">
+        <f>NetworkingLESS!N7</f>
+        <v>0.51855181431840469</v>
+      </c>
+      <c r="C6" s="23">
+        <f>NetworkingLESS!V7</f>
+        <v>0.40209218698921217</v>
+      </c>
+      <c r="D6" s="24">
+        <f>NetworkingLESS!AD7</f>
+        <v>0.1443690748610657</v>
+      </c>
+      <c r="E6" s="24"/>
+      <c r="F6" s="20">
+        <f>NetworkingLESS!E7</f>
+        <v>0.1</v>
+      </c>
+      <c r="G6" s="20">
+        <f>NetworkingLESS!K7</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="20">
+        <f>NetworkingLESS!S7</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="20">
+        <f>NetworkingLESS!AA7</f>
+        <v>0.1</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6" s="2">
+        <f>NetworkingLESS!N7</f>
+        <v>0.51855181431840469</v>
+      </c>
+      <c r="N6" s="2">
+        <f>NetworkingLESS!V7</f>
+        <v>0.40209218698921217</v>
+      </c>
+      <c r="O6" s="43">
+        <f>NetworkingLESS!AD7</f>
+        <v>0.1443690748610657</v>
+      </c>
+      <c r="P6" s="43">
+        <f>NetworkingLESS!AK6</f>
+        <v>4.8010973936899862E-2</v>
+      </c>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="20">
+        <f>NetworkingLESS!E7</f>
+        <v>0.1</v>
+      </c>
+      <c r="S6" s="20">
+        <f>NetworkingLESS!K7</f>
+        <v>0</v>
+      </c>
+      <c r="T6" s="20">
+        <f>NetworkingLESS!S7</f>
+        <v>0</v>
+      </c>
+      <c r="U6" s="20">
+        <f>NetworkingLESS!AA7</f>
+        <v>0.1</v>
+      </c>
+      <c r="V6" s="20">
+        <f>NetworkingLESS!AH7</f>
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" s="23">
+        <f>NetworkingLESS!N8</f>
+        <v>0.62927627095543137</v>
+      </c>
+      <c r="C7" s="23">
+        <f>NetworkingLESS!V8</f>
+        <v>0.46388169551587843</v>
+      </c>
+      <c r="D7" s="24">
+        <f>NetworkingLESS!AD8</f>
+        <v>0.26298214529099084</v>
+      </c>
+      <c r="E7" s="24"/>
+      <c r="F7" s="20">
+        <f>NetworkingLESS!E8</f>
+        <v>0.27</v>
+      </c>
+      <c r="G7" s="20">
+        <f>NetworkingLESS!K8</f>
+        <v>0.02</v>
+      </c>
+      <c r="H7" s="20">
+        <f>NetworkingLESS!S8</f>
+        <v>0.05</v>
+      </c>
+      <c r="I7" s="20">
+        <f>NetworkingLESS!AA8</f>
+        <v>0.33</v>
+      </c>
+      <c r="L7">
+        <v>4</v>
+      </c>
+      <c r="M7" s="2">
+        <f>NetworkingLESS!N8</f>
+        <v>0.62927627095543137</v>
+      </c>
+      <c r="N7" s="2">
+        <f>NetworkingLESS!V8</f>
+        <v>0.46388169551587843</v>
+      </c>
+      <c r="O7" s="43">
+        <f>NetworkingLESS!AD8</f>
+        <v>0.26298214529099084</v>
+      </c>
+      <c r="P7" s="43">
+        <f>NetworkingLESS!AK7</f>
+        <v>4.1189931350114416E-2</v>
+      </c>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="20">
+        <f>NetworkingLESS!E8</f>
+        <v>0.27</v>
+      </c>
+      <c r="S7" s="20">
+        <f>NetworkingLESS!K8</f>
+        <v>0.02</v>
+      </c>
+      <c r="T7" s="20">
+        <f>NetworkingLESS!S8</f>
+        <v>0.05</v>
+      </c>
+      <c r="U7" s="20">
+        <f>NetworkingLESS!AA8</f>
+        <v>0.33</v>
+      </c>
+      <c r="V7" s="20">
+        <f>NetworkingLESS!AH8</f>
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" s="23">
+        <f>NetworkingLESS!N9</f>
+        <v>0.68208098307816278</v>
+      </c>
+      <c r="C8" s="23">
+        <f>NetworkingLESS!V9</f>
+        <v>0.5952659145850121</v>
+      </c>
+      <c r="D8" s="24">
+        <f>NetworkingLESS!AD9</f>
+        <v>0.17913980660757453</v>
+      </c>
+      <c r="E8" s="24"/>
+      <c r="F8" s="20">
+        <f>NetworkingLESS!E9</f>
+        <v>0.41</v>
+      </c>
+      <c r="G8" s="20">
+        <f>NetworkingLESS!K9</f>
+        <v>0.05</v>
+      </c>
+      <c r="H8" s="20">
+        <f>NetworkingLESS!S9</f>
+        <v>0.09</v>
+      </c>
+      <c r="I8" s="20">
+        <f>NetworkingLESS!AA9</f>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="L8">
+        <v>5</v>
+      </c>
+      <c r="M8" s="2">
+        <f>NetworkingLESS!N9</f>
+        <v>0.68208098307816278</v>
+      </c>
+      <c r="N8" s="2">
+        <f>NetworkingLESS!V9</f>
+        <v>0.5952659145850121</v>
+      </c>
+      <c r="O8" s="43">
+        <f>NetworkingLESS!AD9</f>
+        <v>0.17913980660757453</v>
+      </c>
+      <c r="P8" s="43">
+        <f>NetworkingLESS!AK8</f>
+        <v>6.484257871064468E-2</v>
+      </c>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="20">
+        <f>NetworkingLESS!E9</f>
+        <v>0.41</v>
+      </c>
+      <c r="S8" s="20">
+        <f>NetworkingLESS!K9</f>
+        <v>0.05</v>
+      </c>
+      <c r="T8" s="20">
+        <f>NetworkingLESS!S9</f>
+        <v>0.09</v>
+      </c>
+      <c r="U8" s="20">
+        <f>NetworkingLESS!AA9</f>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="V8" s="20">
+        <f>NetworkingLESS!AH9</f>
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" s="23">
+        <f>NetworkingLESS!N10</f>
+        <v>0.31385668008840178</v>
+      </c>
+      <c r="C9" s="23">
+        <f>NetworkingLESS!V10</f>
+        <v>0.31343283582089554</v>
+      </c>
+      <c r="D9" s="24">
+        <f>NetworkingLESS!AD10</f>
+        <v>0.19297024007750296</v>
+      </c>
+      <c r="E9" s="24"/>
+      <c r="F9" s="20">
+        <f>NetworkingLESS!E10</f>
+        <v>0.63</v>
+      </c>
+      <c r="G9" s="20">
+        <f>NetworkingLESS!K10</f>
+        <v>0.1</v>
+      </c>
+      <c r="H9" s="20">
+        <f>NetworkingLESS!S10</f>
+        <v>0.19</v>
+      </c>
+      <c r="I9" s="20">
+        <f>NetworkingLESS!AA10</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L9">
+        <v>6</v>
+      </c>
+      <c r="M9" s="2">
+        <f>NetworkingLESS!N10</f>
+        <v>0.31385668008840178</v>
+      </c>
+      <c r="N9" s="2">
+        <f>NetworkingLESS!V10</f>
+        <v>0.31343283582089554</v>
+      </c>
+      <c r="O9" s="43">
+        <f>NetworkingLESS!AD10</f>
+        <v>0.19297024007750296</v>
+      </c>
+      <c r="P9" s="43">
+        <f>NetworkingLESS!AK9</f>
+        <v>7.2058823529411759E-2</v>
+      </c>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="20">
+        <f>NetworkingLESS!E10</f>
+        <v>0.63</v>
+      </c>
+      <c r="S9" s="20">
+        <f>NetworkingLESS!K10</f>
+        <v>0.1</v>
+      </c>
+      <c r="T9" s="20">
+        <f>NetworkingLESS!S10</f>
+        <v>0.19</v>
+      </c>
+      <c r="U9" s="20">
+        <f>NetworkingLESS!AA10</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="V9" s="20">
+        <f>NetworkingLESS!AH10</f>
+        <v>10.149999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" s="23">
+        <f>NetworkingLESS!N11</f>
+        <v>0.70056198747867648</v>
+      </c>
+      <c r="C10" s="23">
+        <f>NetworkingLESS!V11</f>
+        <v>0.52568776356693192</v>
+      </c>
+      <c r="D10" s="24">
+        <f>NetworkingLESS!AD11</f>
+        <v>0.18213070322038741</v>
+      </c>
+      <c r="E10" s="24"/>
+      <c r="F10" s="20">
+        <f>NetworkingLESS!E11</f>
+        <v>1.29</v>
+      </c>
+      <c r="G10" s="20">
+        <f>NetworkingLESS!K11</f>
+        <v>0.15</v>
+      </c>
+      <c r="H10" s="20">
+        <f>NetworkingLESS!S11</f>
+        <v>0.24</v>
+      </c>
+      <c r="I10" s="20">
+        <f>NetworkingLESS!AA11</f>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="L10">
+        <v>7</v>
+      </c>
+      <c r="M10" s="2">
+        <f>NetworkingLESS!N11</f>
+        <v>0.70056198747867648</v>
+      </c>
+      <c r="N10" s="2">
+        <f>NetworkingLESS!V11</f>
+        <v>0.52568776356693192</v>
+      </c>
+      <c r="O10" s="43">
+        <f>NetworkingLESS!AD11</f>
+        <v>0.18213070322038741</v>
+      </c>
+      <c r="P10" s="43">
+        <f>NetworkingLESS!AK10</f>
+        <v>3.4997426659804425E-2</v>
+      </c>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="20">
+        <f>NetworkingLESS!E11</f>
+        <v>1.29</v>
+      </c>
+      <c r="S10" s="20">
+        <f>NetworkingLESS!K11</f>
+        <v>0.15</v>
+      </c>
+      <c r="T10" s="20">
+        <f>NetworkingLESS!S11</f>
+        <v>0.24</v>
+      </c>
+      <c r="U10" s="20">
+        <f>NetworkingLESS!AA11</f>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="V10" s="20">
+        <f>NetworkingLESS!AH11</f>
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" s="23">
+        <f>NetworkingLESS!N12</f>
+        <v>0.70038217385671719</v>
+      </c>
+      <c r="C11" s="23">
+        <f>NetworkingLESS!V12</f>
+        <v>0.68401023448633247</v>
+      </c>
+      <c r="D11" s="24">
+        <f>NetworkingLESS!AD12</f>
+        <v>0.24333894718659585</v>
+      </c>
+      <c r="E11" s="24"/>
+      <c r="F11" s="20">
+        <f>NetworkingLESS!E12</f>
+        <v>4.26</v>
+      </c>
+      <c r="G11" s="20">
+        <f>NetworkingLESS!K12</f>
+        <v>0.6</v>
+      </c>
+      <c r="H11" s="20">
+        <f>NetworkingLESS!S12</f>
+        <v>0.97</v>
+      </c>
+      <c r="I11" s="20">
+        <f>NetworkingLESS!AA12</f>
+        <v>8.75</v>
+      </c>
+      <c r="L11">
+        <v>8</v>
+      </c>
+      <c r="M11" s="2">
+        <f>NetworkingLESS!N12</f>
+        <v>0.70038217385671719</v>
+      </c>
+      <c r="N11" s="2">
+        <f>NetworkingLESS!V12</f>
+        <v>0.68401023448633247</v>
+      </c>
+      <c r="O11" s="43">
+        <f>NetworkingLESS!AD12</f>
+        <v>0.24333894718659585</v>
+      </c>
+      <c r="P11" s="43">
+        <f>NetworkingLESS!AK11</f>
+        <v>8.3155096421118263E-2</v>
+      </c>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="20">
+        <f>NetworkingLESS!E12</f>
+        <v>4.26</v>
+      </c>
+      <c r="S11" s="20">
+        <f>NetworkingLESS!K12</f>
+        <v>0.6</v>
+      </c>
+      <c r="T11" s="20">
+        <f>NetworkingLESS!S12</f>
+        <v>0.97</v>
+      </c>
+      <c r="U11" s="20">
+        <f>NetworkingLESS!AA12</f>
+        <v>8.75</v>
+      </c>
+      <c r="V11" s="20">
+        <f>NetworkingLESS!AH12</f>
+        <v>79.099999999999994</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" s="23">
+        <f>NetworkingLESS!N13</f>
+        <v>0.66356532099803756</v>
+      </c>
+      <c r="C12" s="23">
+        <f>NetworkingLESS!V13</f>
+        <v>0.66393327726380713</v>
+      </c>
+      <c r="D12" s="24">
+        <f>NetworkingLESS!AD13</f>
+        <v>0.17018102447034322</v>
+      </c>
+      <c r="E12" s="24"/>
+      <c r="F12" s="20">
+        <f>NetworkingLESS!E13</f>
+        <v>11.3</v>
+      </c>
+      <c r="G12" s="20">
+        <f>NetworkingLESS!K13</f>
+        <v>1.36</v>
+      </c>
+      <c r="H12" s="20">
+        <f>NetworkingLESS!S13</f>
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="I12" s="20">
+        <f>NetworkingLESS!AA13</f>
+        <v>20.100000000000001</v>
+      </c>
+      <c r="L12">
+        <v>9</v>
+      </c>
+      <c r="M12" s="2">
+        <f>NetworkingLESS!N13</f>
+        <v>0.66356532099803756</v>
+      </c>
+      <c r="N12" s="2">
+        <f>NetworkingLESS!V13</f>
+        <v>0.66393327726380713</v>
+      </c>
+      <c r="O12" s="43">
+        <f>NetworkingLESS!AD13</f>
+        <v>0.17018102447034322</v>
+      </c>
+      <c r="P12" s="43">
+        <f>NetworkingLESS!AK12</f>
+        <v>5.1598868592650171E-2</v>
+      </c>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="20">
+        <f>NetworkingLESS!E13</f>
+        <v>11.3</v>
+      </c>
+      <c r="S12" s="20">
+        <f>NetworkingLESS!K13</f>
+        <v>1.36</v>
+      </c>
+      <c r="T12" s="20">
+        <f>NetworkingLESS!S13</f>
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="U12" s="20">
+        <f>NetworkingLESS!AA13</f>
+        <v>20.100000000000001</v>
+      </c>
+      <c r="V12" s="20">
+        <f>NetworkingLESS!AH13</f>
+        <v>189.75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" s="23">
+        <f>NetworkingLESS!N14</f>
+        <v>0.63726798561345743</v>
+      </c>
+      <c r="C13" s="23">
+        <f>NetworkingLESS!V14</f>
+        <v>0.63810788608092273</v>
+      </c>
+      <c r="D13" s="24">
+        <f>NetworkingLESS!AD14</f>
+        <v>0.20905404045159803</v>
+      </c>
+      <c r="E13" s="24"/>
+      <c r="F13" s="20">
+        <f>NetworkingLESS!E14</f>
+        <v>24.03</v>
+      </c>
+      <c r="G13" s="20">
+        <f>NetworkingLESS!K14</f>
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="H13" s="20">
+        <f>NetworkingLESS!S14</f>
+        <v>3.88</v>
+      </c>
+      <c r="I13" s="20">
+        <f>NetworkingLESS!AA14</f>
+        <v>37.33</v>
+      </c>
+      <c r="L13">
+        <v>10</v>
+      </c>
+      <c r="M13" s="2">
+        <f>NetworkingLESS!N14</f>
+        <v>0.63726798561345743</v>
+      </c>
+      <c r="N13" s="2">
+        <f>NetworkingLESS!V14</f>
+        <v>0.63810788608092273</v>
+      </c>
+      <c r="O13" s="43">
+        <f>NetworkingLESS!AD14</f>
+        <v>0.20905404045159803</v>
+      </c>
+      <c r="P13" s="43">
+        <f>NetworkingLESS!AK13</f>
+        <v>7.5707627458047974E-2</v>
+      </c>
+      <c r="Q13" s="24"/>
+      <c r="R13" s="20">
+        <f>NetworkingLESS!E14</f>
+        <v>24.03</v>
+      </c>
+      <c r="S13" s="20">
+        <f>NetworkingLESS!K14</f>
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="T13" s="20">
+        <f>NetworkingLESS!S14</f>
+        <v>3.88</v>
+      </c>
+      <c r="U13" s="20">
+        <f>NetworkingLESS!AA14</f>
+        <v>37.33</v>
+      </c>
+      <c r="V13" s="20">
+        <f>NetworkingLESS!AH14</f>
+        <v>331.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" s="23">
+        <f>NetworkingLESS!N15</f>
+        <v>0.70677433427903735</v>
+      </c>
+      <c r="C14" s="23">
+        <f>NetworkingLESS!V15</f>
+        <v>0.70766909437496006</v>
+      </c>
+      <c r="D14" s="24">
+        <f>NetworkingLESS!AD15</f>
+        <v>0.15677475109274661</v>
+      </c>
+      <c r="E14" s="24"/>
+      <c r="F14" s="20">
+        <f>NetworkingLESS!E15</f>
+        <v>43.93</v>
+      </c>
+      <c r="G14" s="20">
+        <f>NetworkingLESS!K15</f>
+        <v>3.8</v>
+      </c>
+      <c r="H14" s="20">
+        <f>NetworkingLESS!S15</f>
+        <v>6.13</v>
+      </c>
+      <c r="I14" s="20">
+        <f>NetworkingLESS!AA15</f>
+        <v>60.39</v>
+      </c>
+      <c r="L14">
+        <v>11</v>
+      </c>
+      <c r="M14" s="2">
+        <f>NetworkingLESS!N15</f>
+        <v>0.70677433427903735</v>
+      </c>
+      <c r="N14" s="2">
+        <f>NetworkingLESS!V15</f>
+        <v>0.70766909437496006</v>
+      </c>
+      <c r="O14" s="43">
+        <f>NetworkingLESS!AD15</f>
+        <v>0.15677475109274661</v>
+      </c>
+      <c r="P14" s="43">
+        <f>NetworkingLESS!AK14</f>
+        <v>5.439979045782152E-2</v>
+      </c>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="20">
+        <f>NetworkingLESS!E15</f>
+        <v>43.93</v>
+      </c>
+      <c r="S14" s="20">
+        <f>NetworkingLESS!K15</f>
+        <v>3.8</v>
+      </c>
+      <c r="T14" s="20">
+        <f>NetworkingLESS!S15</f>
+        <v>6.13</v>
+      </c>
+      <c r="U14" s="20">
+        <f>NetworkingLESS!AA15</f>
+        <v>60.39</v>
+      </c>
+      <c r="V14" s="20">
+        <f>NetworkingLESS!AH15</f>
+        <v>541.70000000000005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" s="23">
+        <f>NetworkingLESS!N16</f>
+        <v>0.75607481107934316</v>
+      </c>
+      <c r="C15" s="23">
+        <f>NetworkingLESS!V16</f>
+        <v>0.75674874395053215</v>
+      </c>
+      <c r="D15" s="24">
+        <f>NetworkingLESS!AD16</f>
+        <v>0.20066237973625439</v>
+      </c>
+      <c r="E15" s="24"/>
+      <c r="F15" s="20">
+        <f>NetworkingLESS!E16</f>
+        <v>309.95999999999998</v>
+      </c>
+      <c r="G15" s="20">
+        <f>NetworkingLESS!K16</f>
+        <v>15.53</v>
+      </c>
+      <c r="H15" s="20">
+        <f>NetworkingLESS!S16</f>
+        <v>25.1</v>
+      </c>
+      <c r="I15" s="20">
+        <f>NetworkingLESS!AA16</f>
+        <v>290.14</v>
+      </c>
+      <c r="L15">
+        <v>12</v>
+      </c>
+      <c r="M15" s="2">
+        <f>NetworkingLESS!N16</f>
+        <v>0.75607481107934316</v>
+      </c>
+      <c r="N15" s="2">
+        <f>NetworkingLESS!V16</f>
+        <v>0.75674874395053215</v>
+      </c>
+      <c r="O15" s="43">
+        <f>NetworkingLESS!AD16</f>
+        <v>0.20066237973625439</v>
+      </c>
+      <c r="P15" s="43">
+        <f>NetworkingLESS!AK15</f>
+        <v>2.8799974805926904E-2</v>
+      </c>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="20">
+        <f>NetworkingLESS!E16</f>
+        <v>309.95999999999998</v>
+      </c>
+      <c r="S15" s="20">
+        <f>NetworkingLESS!K16</f>
+        <v>15.53</v>
+      </c>
+      <c r="T15" s="20">
+        <f>NetworkingLESS!S16</f>
+        <v>25.1</v>
+      </c>
+      <c r="U15" s="20">
+        <f>NetworkingLESS!AA16</f>
+        <v>290.14</v>
+      </c>
+      <c r="V15" s="20">
+        <f>NetworkingLESS!AH16</f>
+        <v>2601.5499999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" s="23">
+        <f>NetworkingLESS!N17</f>
+        <v>0.7320626048674691</v>
+      </c>
+      <c r="C16" s="23">
+        <f>NetworkingLESS!V17</f>
+        <v>0.73310925639185764</v>
+      </c>
+      <c r="D16" s="24">
+        <f>NetworkingLESS!AD17</f>
+        <v>0.23946739464697092</v>
+      </c>
+      <c r="E16" s="24"/>
+      <c r="F16" s="20">
+        <f>NetworkingLESS!E17</f>
+        <v>1732.32</v>
+      </c>
+      <c r="G16" s="20">
+        <f>NetworkingLESS!K17</f>
+        <v>35.65</v>
+      </c>
+      <c r="H16" s="20">
+        <f>NetworkingLESS!S17</f>
+        <v>57.41</v>
+      </c>
+      <c r="I16" s="20">
+        <f>NetworkingLESS!AA17</f>
+        <v>749.64</v>
+      </c>
+      <c r="L16">
+        <v>13</v>
+      </c>
+      <c r="M16" s="2">
+        <f>NetworkingLESS!N17</f>
+        <v>0.7320626048674691</v>
+      </c>
+      <c r="N16" s="2">
+        <f>NetworkingLESS!V17</f>
+        <v>0.73310925639185764</v>
+      </c>
+      <c r="O16" s="43">
+        <f>NetworkingLESS!AD17</f>
+        <v>0.23946739464697092</v>
+      </c>
+      <c r="P16" s="43">
+        <f>NetworkingLESS!AK16</f>
+        <v>4.1799978422821522E-2</v>
+      </c>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="20">
+        <f>NetworkingLESS!E17</f>
+        <v>1732.32</v>
+      </c>
+      <c r="S16" s="20">
+        <f>NetworkingLESS!K17</f>
+        <v>35.65</v>
+      </c>
+      <c r="T16" s="20">
+        <f>NetworkingLESS!S17</f>
+        <v>57.41</v>
+      </c>
+      <c r="U16" s="20">
+        <f>NetworkingLESS!AA17</f>
+        <v>749.64</v>
+      </c>
+      <c r="V16" s="20">
+        <f>NetworkingLESS!AH17</f>
+        <v>6781.25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" s="23">
+        <f>NetworkingLESS!N18</f>
+        <v>0.76867450216613709</v>
+      </c>
+      <c r="C17" s="23">
+        <f>NetworkingLESS!V18</f>
+        <v>0.76054204679719239</v>
+      </c>
+      <c r="D17" s="24">
+        <f>NetworkingLESS!AD18</f>
+        <v>0.26318025605196571</v>
+      </c>
+      <c r="E17" s="24"/>
+      <c r="F17" s="20">
+        <f>NetworkingLESS!E18</f>
+        <v>9234.91</v>
+      </c>
+      <c r="G17" s="20">
+        <f>NetworkingLESS!K18</f>
+        <v>66.44</v>
+      </c>
+      <c r="H17" s="20">
+        <f>NetworkingLESS!S18</f>
+        <v>104.96</v>
+      </c>
+      <c r="I17" s="20">
+        <f>NetworkingLESS!AA18</f>
+        <v>1209.1400000000001</v>
+      </c>
+      <c r="L17">
+        <v>14</v>
+      </c>
+      <c r="M17" s="2">
+        <f>NetworkingLESS!N18</f>
+        <v>0.76867450216613709</v>
+      </c>
+      <c r="N17" s="2">
+        <f>NetworkingLESS!V18</f>
+        <v>0.76054204679719239</v>
+      </c>
+      <c r="O17" s="43">
+        <f>NetworkingLESS!AD18</f>
+        <v>0.26318025605196571</v>
+      </c>
+      <c r="P17" s="43">
+        <f>NetworkingLESS!AK17</f>
+        <v>9.4420679730028642E-2</v>
+      </c>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="20">
+        <f>NetworkingLESS!E18</f>
+        <v>9234.91</v>
+      </c>
+      <c r="S17" s="20">
+        <f>NetworkingLESS!K18</f>
+        <v>66.44</v>
+      </c>
+      <c r="T17" s="20">
+        <f>NetworkingLESS!S18</f>
+        <v>104.96</v>
+      </c>
+      <c r="U17" s="20">
+        <f>NetworkingLESS!AA18</f>
+        <v>1209.1400000000001</v>
+      </c>
+      <c r="V17" s="20">
+        <f>NetworkingLESS!AH18</f>
+        <v>11609.75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A18" s="22">
+        <v>15</v>
+      </c>
+      <c r="B18" s="23">
+        <f>NetworkingLESS!N19</f>
+        <v>0.68917968979685051</v>
+      </c>
+      <c r="C18" s="23">
+        <f>NetworkingLESS!V19</f>
+        <v>0.68987193993093321</v>
+      </c>
+      <c r="D18" s="24">
+        <f>NetworkingLESS!AD19</f>
+        <v>0.19108570481753034</v>
+      </c>
+      <c r="E18" s="24"/>
+      <c r="F18" s="20">
+        <f>NetworkingLESS!E19</f>
+        <v>50792.01</v>
+      </c>
+      <c r="G18" s="20">
+        <f>NetworkingLESS!K19</f>
+        <v>109.15</v>
+      </c>
+      <c r="H18" s="20">
+        <f>NetworkingLESS!S19</f>
+        <v>168.04</v>
+      </c>
+      <c r="I18" s="20">
+        <f>NetworkingLESS!AA19</f>
+        <v>1668.64</v>
+      </c>
+      <c r="L18" s="22">
+        <v>15</v>
+      </c>
+      <c r="M18" s="2">
+        <f>NetworkingLESS!N19</f>
+        <v>0.68917968979685051</v>
+      </c>
+      <c r="N18" s="2">
+        <f>NetworkingLESS!V19</f>
+        <v>0.68987193993093321</v>
+      </c>
+      <c r="O18" s="43">
+        <f>NetworkingLESS!AD19</f>
+        <v>0.19108570481753034</v>
+      </c>
+      <c r="P18" s="43">
+        <f>NetworkingLESS!AK18</f>
+        <v>4.7400011734366317E-2</v>
+      </c>
+      <c r="Q18" s="24"/>
+      <c r="R18" s="20">
+        <f>NetworkingLESS!E19</f>
+        <v>50792.01</v>
+      </c>
+      <c r="S18" s="20">
+        <f>NetworkingLESS!K19</f>
+        <v>109.15</v>
+      </c>
+      <c r="T18" s="20">
+        <f>NetworkingLESS!S19</f>
+        <v>168.04</v>
+      </c>
+      <c r="U18" s="20">
+        <f>NetworkingLESS!AA19</f>
+        <v>1668.64</v>
+      </c>
+      <c r="V18" s="20">
+        <f>NetworkingLESS!AH19</f>
+        <v>14829.849999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="29">
+        <f t="shared" ref="B19:I19" si="0">AVERAGE(B4:B18)</f>
+        <v>0.62315534890154178</v>
+      </c>
+      <c r="C19" s="29">
+        <f t="shared" si="0"/>
+        <v>0.58555826338009809</v>
+      </c>
+      <c r="D19" s="29">
+        <f t="shared" si="0"/>
+        <v>0.2048556606475781</v>
+      </c>
+      <c r="E19" s="29"/>
+      <c r="F19" s="30">
+        <f t="shared" si="0"/>
+        <v>4143.7006666666666</v>
+      </c>
+      <c r="G19" s="30">
+        <f t="shared" si="0"/>
+        <v>15.685333333333334</v>
+      </c>
+      <c r="H19" s="30">
+        <f t="shared" si="0"/>
+        <v>24.616</v>
+      </c>
+      <c r="I19" s="30">
+        <f t="shared" si="0"/>
+        <v>269.90400000000005</v>
+      </c>
+      <c r="L19" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="M19" s="44">
+        <f t="shared" ref="M19:O19" si="1">AVERAGE(M4:M18)</f>
+        <v>0.62315534890154178</v>
+      </c>
+      <c r="N19" s="44">
+        <f t="shared" si="1"/>
+        <v>0.58555826338009809</v>
+      </c>
+      <c r="O19" s="44">
+        <f t="shared" si="1"/>
+        <v>0.2048556606475781</v>
+      </c>
+      <c r="P19" s="44">
+        <f>AVERAGE(P4:P18)</f>
+        <v>5.0462309167025966E-2</v>
+      </c>
+      <c r="Q19" s="29"/>
+      <c r="R19" s="30">
+        <f t="shared" ref="R19:V19" si="2">AVERAGE(R4:R18)</f>
+        <v>4143.7006666666666</v>
+      </c>
+      <c r="S19" s="30">
+        <f t="shared" si="2"/>
+        <v>15.685333333333334</v>
+      </c>
+      <c r="T19" s="30">
+        <f t="shared" si="2"/>
+        <v>24.616</v>
+      </c>
+      <c r="U19" s="30">
+        <f t="shared" si="2"/>
+        <v>269.90400000000005</v>
+      </c>
+      <c r="V19" s="30">
+        <f t="shared" si="2"/>
+        <v>2467.8599999999997</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="33"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A26" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="52"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="50"/>
+      <c r="H26" s="50"/>
+      <c r="I26" s="50"/>
+    </row>
+    <row r="27" spans="1:22" ht="32" x14ac:dyDescent="0.2">
+      <c r="A27" s="49"/>
+      <c r="B27" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" s="27"/>
+      <c r="F27" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="G27" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="H27" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="26" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>1</v>
+      </c>
+      <c r="B28" s="23">
+        <f>NetworkingLESS!N5</f>
+        <v>0.24545454545454545</v>
+      </c>
+      <c r="C28" s="23">
+        <f>NetworkingLESS!V5</f>
+        <v>0.24545454545454545</v>
+      </c>
+      <c r="D28" s="24">
+        <f>NetworkingLESS!AD5</f>
+        <v>0.24545454545454545</v>
+      </c>
+      <c r="E28" s="24"/>
+      <c r="F28" s="20">
+        <f>NetworkingLESS!E5</f>
+        <v>0.02</v>
+      </c>
+      <c r="G28" s="20">
+        <f>NetworkingLESS!K5</f>
+        <v>0</v>
+      </c>
+      <c r="H28" s="20">
+        <f>NetworkingLESS!S5</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="20">
+        <f>NetworkingLESS!AA5</f>
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29" s="23">
+        <f>NetworkingLESS!N6</f>
+        <v>0.60356652949245537</v>
+      </c>
+      <c r="C29" s="23">
+        <f>NetworkingLESS!V6</f>
+        <v>0.60356652949245537</v>
+      </c>
+      <c r="D29" s="24">
+        <f>NetworkingLESS!AD6</f>
+        <v>0.19204389574759945</v>
+      </c>
+      <c r="E29" s="24"/>
+      <c r="F29" s="20">
+        <f>NetworkingLESS!E6</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G29" s="20">
+        <f>NetworkingLESS!K6</f>
+        <v>0</v>
+      </c>
+      <c r="H29" s="20">
+        <f>NetworkingLESS!S6</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="20">
+        <f>NetworkingLESS!AA6</f>
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>3</v>
+      </c>
+      <c r="B30" s="23">
+        <f>NetworkingLESS!N7</f>
+        <v>0.51855181431840469</v>
+      </c>
+      <c r="C30" s="23">
+        <f>NetworkingLESS!V7</f>
+        <v>0.40209218698921217</v>
+      </c>
+      <c r="D30" s="24">
+        <f>NetworkingLESS!AD7</f>
+        <v>0.1443690748610657</v>
+      </c>
+      <c r="E30" s="24"/>
+      <c r="F30" s="20">
+        <f>NetworkingLESS!E7</f>
+        <v>0.1</v>
+      </c>
+      <c r="G30" s="20">
+        <f>NetworkingLESS!K7</f>
+        <v>0</v>
+      </c>
+      <c r="H30" s="20">
+        <f>NetworkingLESS!S7</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="20">
+        <f>NetworkingLESS!AA7</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31" s="23">
+        <f>NetworkingLESS!N8</f>
+        <v>0.62927627095543137</v>
+      </c>
+      <c r="C31" s="23">
+        <f>NetworkingLESS!V8</f>
+        <v>0.46388169551587843</v>
+      </c>
+      <c r="D31" s="24">
+        <f>NetworkingLESS!AD8</f>
+        <v>0.26298214529099084</v>
+      </c>
+      <c r="E31" s="24"/>
+      <c r="F31" s="20">
+        <f>NetworkingLESS!E8</f>
+        <v>0.27</v>
+      </c>
+      <c r="G31" s="20">
+        <f>NetworkingLESS!K8</f>
+        <v>0.02</v>
+      </c>
+      <c r="H31" s="20">
+        <f>NetworkingLESS!S8</f>
+        <v>0.05</v>
+      </c>
+      <c r="I31" s="20">
+        <f>NetworkingLESS!AA8</f>
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>5</v>
+      </c>
+      <c r="B32" s="23">
+        <f>NetworkingLESS!N9</f>
+        <v>0.68208098307816278</v>
+      </c>
+      <c r="C32" s="23">
+        <f>NetworkingLESS!V9</f>
+        <v>0.5952659145850121</v>
+      </c>
+      <c r="D32" s="24">
+        <f>NetworkingLESS!AD9</f>
+        <v>0.17913980660757453</v>
+      </c>
+      <c r="E32" s="24"/>
+      <c r="F32" s="20">
+        <f>NetworkingLESS!E9</f>
+        <v>0.41</v>
+      </c>
+      <c r="G32" s="20">
+        <f>NetworkingLESS!K9</f>
+        <v>0.05</v>
+      </c>
+      <c r="H32" s="20">
+        <f>NetworkingLESS!S9</f>
+        <v>0.09</v>
+      </c>
+      <c r="I32" s="20">
+        <f>NetworkingLESS!AA9</f>
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>6</v>
+      </c>
+      <c r="B33" s="23">
+        <f>NetworkingLESS!N10</f>
+        <v>0.31385668008840178</v>
+      </c>
+      <c r="C33" s="23">
+        <f>NetworkingLESS!V10</f>
+        <v>0.31343283582089554</v>
+      </c>
+      <c r="D33" s="24">
+        <f>NetworkingLESS!AD10</f>
+        <v>0.19297024007750296</v>
+      </c>
+      <c r="E33" s="24"/>
+      <c r="F33" s="20">
+        <f>NetworkingLESS!E10</f>
+        <v>0.63</v>
+      </c>
+      <c r="G33" s="20">
+        <f>NetworkingLESS!K10</f>
+        <v>0.1</v>
+      </c>
+      <c r="H33" s="20">
+        <f>NetworkingLESS!S10</f>
+        <v>0.19</v>
+      </c>
+      <c r="I33" s="20">
+        <f>NetworkingLESS!AA10</f>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>7</v>
+      </c>
+      <c r="B34" s="23">
+        <f>NetworkingLESS!N11</f>
+        <v>0.70056198747867648</v>
+      </c>
+      <c r="C34" s="23">
+        <f>NetworkingLESS!V11</f>
+        <v>0.52568776356693192</v>
+      </c>
+      <c r="D34" s="24">
+        <f>NetworkingLESS!AD11</f>
+        <v>0.18213070322038741</v>
+      </c>
+      <c r="E34" s="24"/>
+      <c r="F34" s="20">
+        <f>NetworkingLESS!E11</f>
+        <v>1.29</v>
+      </c>
+      <c r="G34" s="20">
+        <f>NetworkingLESS!K11</f>
+        <v>0.15</v>
+      </c>
+      <c r="H34" s="20">
+        <f>NetworkingLESS!S11</f>
+        <v>0.24</v>
+      </c>
+      <c r="I34" s="20">
+        <f>NetworkingLESS!AA11</f>
+        <v>2.2400000000000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>8</v>
+      </c>
+      <c r="B35" s="23">
+        <f>NetworkingLESS!N12</f>
+        <v>0.70038217385671719</v>
+      </c>
+      <c r="C35" s="23">
+        <f>NetworkingLESS!V12</f>
+        <v>0.68401023448633247</v>
+      </c>
+      <c r="D35" s="24">
+        <f>NetworkingLESS!AD12</f>
+        <v>0.24333894718659585</v>
+      </c>
+      <c r="E35" s="24"/>
+      <c r="F35" s="20">
+        <f>NetworkingLESS!E12</f>
+        <v>4.26</v>
+      </c>
+      <c r="G35" s="20">
+        <f>NetworkingLESS!K12</f>
+        <v>0.6</v>
+      </c>
+      <c r="H35" s="20">
+        <f>NetworkingLESS!S12</f>
+        <v>0.97</v>
+      </c>
+      <c r="I35" s="20">
+        <f>NetworkingLESS!AA12</f>
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>9</v>
+      </c>
+      <c r="B36" s="23">
+        <f>NetworkingLESS!N13</f>
+        <v>0.66356532099803756</v>
+      </c>
+      <c r="C36" s="23">
+        <f>NetworkingLESS!V13</f>
+        <v>0.66393327726380713</v>
+      </c>
+      <c r="D36" s="24">
+        <f>NetworkingLESS!AD13</f>
+        <v>0.17018102447034322</v>
+      </c>
+      <c r="E36" s="24"/>
+      <c r="F36" s="20">
+        <f>NetworkingLESS!E13</f>
+        <v>11.3</v>
+      </c>
+      <c r="G36" s="20">
+        <f>NetworkingLESS!K13</f>
+        <v>1.36</v>
+      </c>
+      <c r="H36" s="20">
+        <f>NetworkingLESS!S13</f>
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="I36" s="20">
+        <f>NetworkingLESS!AA13</f>
+        <v>20.100000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>10</v>
+      </c>
+      <c r="B37" s="23">
+        <f>NetworkingLESS!N14</f>
+        <v>0.63726798561345743</v>
+      </c>
+      <c r="C37" s="23">
+        <f>NetworkingLESS!V14</f>
+        <v>0.63810788608092273</v>
+      </c>
+      <c r="D37" s="24">
+        <f>NetworkingLESS!AD14</f>
+        <v>0.20905404045159803</v>
+      </c>
+      <c r="E37" s="24"/>
+      <c r="F37" s="20">
+        <f>NetworkingLESS!E14</f>
+        <v>24.03</v>
+      </c>
+      <c r="G37" s="20">
+        <f>NetworkingLESS!K14</f>
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="H37" s="20">
+        <f>NetworkingLESS!S14</f>
+        <v>3.88</v>
+      </c>
+      <c r="I37" s="20">
+        <f>NetworkingLESS!AA14</f>
+        <v>37.33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>11</v>
+      </c>
+      <c r="B38" s="23">
+        <f>NetworkingLESS!N15</f>
+        <v>0.70677433427903735</v>
+      </c>
+      <c r="C38" s="23">
+        <f>NetworkingLESS!V15</f>
+        <v>0.70766909437496006</v>
+      </c>
+      <c r="D38" s="24">
+        <f>NetworkingLESS!AD15</f>
+        <v>0.15677475109274661</v>
+      </c>
+      <c r="E38" s="24"/>
+      <c r="F38" s="20">
+        <f>NetworkingLESS!E15</f>
+        <v>43.93</v>
+      </c>
+      <c r="G38" s="20">
+        <f>NetworkingLESS!K15</f>
+        <v>3.8</v>
+      </c>
+      <c r="H38" s="20">
+        <f>NetworkingLESS!S15</f>
+        <v>6.13</v>
+      </c>
+      <c r="I38" s="20">
+        <f>NetworkingLESS!AA15</f>
+        <v>60.39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>12</v>
+      </c>
+      <c r="B39" s="23">
+        <f>NetworkingLESS!N16</f>
+        <v>0.75607481107934316</v>
+      </c>
+      <c r="C39" s="23">
+        <f>NetworkingLESS!V16</f>
+        <v>0.75674874395053215</v>
+      </c>
+      <c r="D39" s="24">
+        <f>NetworkingLESS!AD16</f>
+        <v>0.20066237973625439</v>
+      </c>
+      <c r="E39" s="24"/>
+      <c r="F39" s="20">
+        <f>NetworkingLESS!E16</f>
+        <v>309.95999999999998</v>
+      </c>
+      <c r="G39" s="20">
+        <f>NetworkingLESS!K16</f>
+        <v>15.53</v>
+      </c>
+      <c r="H39" s="20">
+        <f>NetworkingLESS!S16</f>
+        <v>25.1</v>
+      </c>
+      <c r="I39" s="20">
+        <f>NetworkingLESS!AA16</f>
+        <v>290.14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>13</v>
+      </c>
+      <c r="B40" s="23">
+        <f>NetworkingLESS!N17</f>
+        <v>0.7320626048674691</v>
+      </c>
+      <c r="C40" s="23">
+        <f>NetworkingLESS!V17</f>
+        <v>0.73310925639185764</v>
+      </c>
+      <c r="D40" s="24">
+        <f>NetworkingLESS!AD17</f>
+        <v>0.23946739464697092</v>
+      </c>
+      <c r="E40" s="24"/>
+      <c r="F40" s="20">
+        <f>NetworkingLESS!E17</f>
+        <v>1732.32</v>
+      </c>
+      <c r="G40" s="20">
+        <f>NetworkingLESS!K17</f>
+        <v>35.65</v>
+      </c>
+      <c r="H40" s="20">
+        <f>NetworkingLESS!S17</f>
+        <v>57.41</v>
+      </c>
+      <c r="I40" s="20">
+        <f>NetworkingLESS!AA17</f>
+        <v>749.64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>14</v>
+      </c>
+      <c r="B41" s="23">
+        <f>NetworkingLESS!N18</f>
+        <v>0.76867450216613709</v>
+      </c>
+      <c r="C41" s="23">
+        <f>NetworkingLESS!V18</f>
+        <v>0.76054204679719239</v>
+      </c>
+      <c r="D41" s="24">
+        <f>NetworkingLESS!AD18</f>
+        <v>0.26318025605196571</v>
+      </c>
+      <c r="E41" s="24"/>
+      <c r="F41" s="20">
+        <f>NetworkingLESS!E18</f>
+        <v>9234.91</v>
+      </c>
+      <c r="G41" s="20">
+        <f>NetworkingLESS!K18</f>
+        <v>66.44</v>
+      </c>
+      <c r="H41" s="20">
+        <f>NetworkingLESS!S18</f>
+        <v>104.96</v>
+      </c>
+      <c r="I41" s="20">
+        <f>NetworkingLESS!AA18</f>
+        <v>1209.1400000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A42" s="22">
+        <v>15</v>
+      </c>
+      <c r="B42" s="23">
+        <f>NetworkingLESS!N19</f>
+        <v>0.68917968979685051</v>
+      </c>
+      <c r="C42" s="23">
+        <f>NetworkingLESS!V19</f>
+        <v>0.68987193993093321</v>
+      </c>
+      <c r="D42" s="24">
+        <f>NetworkingLESS!AD19</f>
+        <v>0.19108570481753034</v>
+      </c>
+      <c r="E42" s="24"/>
+      <c r="F42" s="20">
+        <f>NetworkingLESS!E19</f>
+        <v>50792.01</v>
+      </c>
+      <c r="G42" s="20">
+        <f>NetworkingLESS!K19</f>
+        <v>109.15</v>
+      </c>
+      <c r="H42" s="20">
+        <f>NetworkingLESS!S19</f>
+        <v>168.04</v>
+      </c>
+      <c r="I42" s="20">
+        <f>NetworkingLESS!AA19</f>
+        <v>1668.64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B43" s="29">
+        <f t="shared" ref="B43:D43" si="3">AVERAGE(B28:B42)</f>
+        <v>0.62315534890154178</v>
+      </c>
+      <c r="C43" s="29">
+        <f t="shared" si="3"/>
+        <v>0.58555826338009809</v>
+      </c>
+      <c r="D43" s="29">
+        <f t="shared" si="3"/>
+        <v>0.2048556606475781</v>
+      </c>
+      <c r="E43" s="29"/>
+      <c r="F43" s="30">
+        <f t="shared" ref="F43:I43" si="4">AVERAGE(F28:F42)</f>
+        <v>4143.7006666666666</v>
+      </c>
+      <c r="G43" s="30">
+        <f t="shared" si="4"/>
+        <v>15.685333333333334</v>
+      </c>
+      <c r="H43" s="30">
+        <f t="shared" si="4"/>
+        <v>24.616</v>
+      </c>
+      <c r="I43" s="30">
+        <f t="shared" si="4"/>
+        <v>269.90400000000005</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="R2:V2"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="F2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D29F935A-7EB1-C14F-935D-FC60577D8149}">
+  <dimension ref="A1:S26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="3.33203125" customWidth="1"/>
+    <col min="11" max="11" width="7.1640625" customWidth="1"/>
+    <col min="12" max="14" width="8.1640625" customWidth="1"/>
+    <col min="15" max="15" width="2.83203125" customWidth="1"/>
+    <col min="16" max="18" width="8.1640625" customWidth="1"/>
+    <col min="19" max="19" width="11.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+    </row>
+    <row r="2" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="51"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="K2" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+    </row>
+    <row r="3" spans="1:19" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="54"/>
+      <c r="B3" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="54"/>
+      <c r="L3" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q3" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="R3" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="S3" s="27" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4" s="38">
+        <v>1</v>
+      </c>
+      <c r="B4" s="35">
+        <f>NetworkingLESS!O5</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="35">
+        <f>NetworkingLESS!W5</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="25"/>
+      <c r="E4" s="40">
+        <f>NetworkingLESS!K5</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="20">
+        <f>NetworkingLESS!S5</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="20">
+        <f>NetworkingLESS!AA5</f>
+        <v>0.03</v>
+      </c>
+      <c r="K4" s="38">
+        <v>1</v>
+      </c>
+      <c r="L4" s="42">
+        <f>NetworkingLESS!P5</f>
+        <v>0.23119092627599244</v>
+      </c>
+      <c r="M4" s="42">
+        <f>NetworkingLESS!X5</f>
+        <v>0.23119092627599244</v>
+      </c>
+      <c r="N4" s="42">
+        <f>NetworkingLESS!AE4</f>
+        <v>0</v>
+      </c>
+      <c r="O4" s="25"/>
+      <c r="P4" s="40">
+        <f>NetworkingLESS!K5</f>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="20">
+        <f>NetworkingLESS!S5</f>
+        <v>0</v>
+      </c>
+      <c r="R4" s="20">
+        <f>NetworkingLESS!AA5</f>
+        <v>0.03</v>
+      </c>
+      <c r="S4" s="20">
+        <f>NetworkingLESS!AH5</f>
+        <v>3.4000000000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A5" s="9">
+        <v>2</v>
+      </c>
+      <c r="B5" s="35">
+        <f>NetworkingLESS!O6</f>
+        <v>0.50933786078098475</v>
+      </c>
+      <c r="C5" s="35">
+        <f>NetworkingLESS!W6</f>
+        <v>0.50933786078098475</v>
+      </c>
+      <c r="D5" s="25"/>
+      <c r="E5" s="40">
+        <f>NetworkingLESS!K6</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="20">
+        <f>NetworkingLESS!S6</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="20">
+        <f>NetworkingLESS!AA6</f>
+        <v>0.06</v>
+      </c>
+      <c r="K5" s="9">
+        <v>2</v>
+      </c>
+      <c r="L5" s="42">
+        <f>NetworkingLESS!P6</f>
+        <v>0.58357348703170031</v>
+      </c>
+      <c r="M5" s="42">
+        <f>NetworkingLESS!X6</f>
+        <v>0.58357348703170031</v>
+      </c>
+      <c r="N5" s="42">
+        <f>NetworkingLESS!AE5</f>
+        <v>0.23119092627599244</v>
+      </c>
+      <c r="O5" s="25"/>
+      <c r="P5" s="40">
+        <f>NetworkingLESS!K6</f>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="20">
+        <f>NetworkingLESS!S6</f>
+        <v>0</v>
+      </c>
+      <c r="R5" s="20">
+        <f>NetworkingLESS!AA6</f>
+        <v>0.06</v>
+      </c>
+      <c r="S5" s="20">
+        <f>NetworkingLESS!AH6</f>
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6" s="9">
+        <v>3</v>
+      </c>
+      <c r="B6" s="35">
+        <f>NetworkingLESS!O7</f>
+        <v>0.43731792349204834</v>
+      </c>
+      <c r="C6" s="35">
+        <f>NetworkingLESS!W7</f>
+        <v>0.30120827164621045</v>
+      </c>
+      <c r="D6" s="25"/>
+      <c r="E6" s="40">
+        <f>NetworkingLESS!K7</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="20">
+        <f>NetworkingLESS!S7</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="20">
+        <f>NetworkingLESS!AA7</f>
+        <v>0.1</v>
+      </c>
+      <c r="K6" s="9">
+        <v>3</v>
+      </c>
+      <c r="L6" s="42">
+        <f>NetworkingLESS!P7</f>
+        <v>0.49786907603136721</v>
+      </c>
+      <c r="M6" s="42">
+        <f>NetworkingLESS!X7</f>
+        <v>0.37640640981929763</v>
+      </c>
+      <c r="N6" s="42">
+        <f>NetworkingLESS!AE6</f>
+        <v>0.15129682997118155</v>
+      </c>
+      <c r="O6" s="25"/>
+      <c r="P6" s="40">
+        <f>NetworkingLESS!K7</f>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="20">
+        <f>NetworkingLESS!S7</f>
+        <v>0</v>
+      </c>
+      <c r="R6" s="20">
+        <f>NetworkingLESS!AA7</f>
+        <v>0.1</v>
+      </c>
+      <c r="S6" s="20">
+        <f>NetworkingLESS!AH7</f>
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7" s="9">
+        <v>4</v>
+      </c>
+      <c r="B7" s="35">
+        <f>NetworkingLESS!O8</f>
+        <v>0.49699491447064265</v>
+      </c>
+      <c r="C7" s="35">
+        <f>NetworkingLESS!W8</f>
+        <v>0.27258437355524734</v>
+      </c>
+      <c r="D7" s="25"/>
+      <c r="E7" s="40">
+        <f>NetworkingLESS!K8</f>
+        <v>0.02</v>
+      </c>
+      <c r="F7" s="20">
+        <f>NetworkingLESS!S8</f>
+        <v>0.05</v>
+      </c>
+      <c r="G7" s="20">
+        <f>NetworkingLESS!AA8</f>
+        <v>0.33</v>
+      </c>
+      <c r="K7" s="9">
+        <v>4</v>
+      </c>
+      <c r="L7" s="42">
+        <f>NetworkingLESS!P8</f>
+        <v>0.60357077791947533</v>
+      </c>
+      <c r="M7" s="42">
+        <f>NetworkingLESS!X8</f>
+        <v>0.42670796137730005</v>
+      </c>
+      <c r="N7" s="42">
+        <f>NetworkingLESS!AE7</f>
+        <v>0.10761166041595636</v>
+      </c>
+      <c r="O7" s="25"/>
+      <c r="P7" s="40">
+        <f>NetworkingLESS!K8</f>
+        <v>0.02</v>
+      </c>
+      <c r="Q7" s="20">
+        <f>NetworkingLESS!S8</f>
+        <v>0.05</v>
+      </c>
+      <c r="R7" s="20">
+        <f>NetworkingLESS!AA8</f>
+        <v>0.33</v>
+      </c>
+      <c r="S7" s="20">
+        <f>NetworkingLESS!AH8</f>
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A8" s="9">
+        <v>5</v>
+      </c>
+      <c r="B8" s="35">
+        <f>NetworkingLESS!O9</f>
+        <v>0.61270016565433461</v>
+      </c>
+      <c r="C8" s="35">
+        <f>NetworkingLESS!W9</f>
+        <v>0.50693907601693355</v>
+      </c>
+      <c r="D8" s="25"/>
+      <c r="E8" s="40">
+        <f>NetworkingLESS!K9</f>
+        <v>0.05</v>
+      </c>
+      <c r="F8" s="20">
+        <f>NetworkingLESS!S9</f>
+        <v>0.09</v>
+      </c>
+      <c r="G8" s="20">
+        <f>NetworkingLESS!AA9</f>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="K8" s="9">
+        <v>5</v>
+      </c>
+      <c r="L8" s="42">
+        <f>NetworkingLESS!P9</f>
+        <v>0.65739313548835288</v>
+      </c>
+      <c r="M8" s="42">
+        <f>NetworkingLESS!X9</f>
+        <v>0.56383648481427606</v>
+      </c>
+      <c r="N8" s="42">
+        <f>NetworkingLESS!AE8</f>
+        <v>0.21187830205866279</v>
+      </c>
+      <c r="O8" s="25"/>
+      <c r="P8" s="40">
+        <f>NetworkingLESS!K9</f>
+        <v>0.05</v>
+      </c>
+      <c r="Q8" s="20">
+        <f>NetworkingLESS!S9</f>
+        <v>0.09</v>
+      </c>
+      <c r="R8" s="20">
+        <f>NetworkingLESS!AA9</f>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="S8" s="20">
+        <f>NetworkingLESS!AH9</f>
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A9" s="9">
+        <v>6</v>
+      </c>
+      <c r="B9" s="35">
+        <f>NetworkingLESS!O10</f>
+        <v>0.14979179952732866</v>
+      </c>
+      <c r="C9" s="35">
+        <f>NetworkingLESS!W10</f>
+        <v>0.14926660914581535</v>
+      </c>
+      <c r="D9" s="25"/>
+      <c r="E9" s="40">
+        <f>NetworkingLESS!K10</f>
+        <v>0.1</v>
+      </c>
+      <c r="F9" s="20">
+        <f>NetworkingLESS!S10</f>
+        <v>0.19</v>
+      </c>
+      <c r="G9" s="20">
+        <f>NetworkingLESS!AA10</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="K9" s="9">
+        <v>6</v>
+      </c>
+      <c r="L9" s="42">
+        <f>NetworkingLESS!P10</f>
+        <v>0.28897254901960784</v>
+      </c>
+      <c r="M9" s="42">
+        <f>NetworkingLESS!X10</f>
+        <v>0.28853333333333331</v>
+      </c>
+      <c r="N9" s="42">
+        <f>NetworkingLESS!AE9</f>
+        <v>0.11539630506046067</v>
+      </c>
+      <c r="O9" s="25"/>
+      <c r="P9" s="40">
+        <f>NetworkingLESS!K10</f>
+        <v>0.1</v>
+      </c>
+      <c r="Q9" s="20">
+        <f>NetworkingLESS!S10</f>
+        <v>0.19</v>
+      </c>
+      <c r="R9" s="20">
+        <f>NetworkingLESS!AA10</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="S9" s="20">
+        <f>NetworkingLESS!AH10</f>
+        <v>10.149999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A10" s="9">
+        <v>7</v>
+      </c>
+      <c r="B10" s="35">
+        <f>NetworkingLESS!O11</f>
+        <v>0.63388035997882475</v>
+      </c>
+      <c r="C10" s="35">
+        <f>NetworkingLESS!W11</f>
+        <v>0.4200635256749603</v>
+      </c>
+      <c r="D10" s="25"/>
+      <c r="E10" s="40">
+        <f>NetworkingLESS!K11</f>
+        <v>0.15</v>
+      </c>
+      <c r="F10" s="20">
+        <f>NetworkingLESS!S11</f>
+        <v>0.24</v>
+      </c>
+      <c r="G10" s="20">
+        <f>NetworkingLESS!AA11</f>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="K10" s="9">
+        <v>7</v>
+      </c>
+      <c r="L10" s="42">
+        <f>NetworkingLESS!P11</f>
+        <v>0.67340385341896492</v>
+      </c>
+      <c r="M10" s="42">
+        <f>NetworkingLESS!X11</f>
+        <v>0.48266905931242915</v>
+      </c>
+      <c r="N10" s="42">
+        <f>NetworkingLESS!AE10</f>
+        <v>0.16370196078431373</v>
+      </c>
+      <c r="O10" s="25"/>
+      <c r="P10" s="40">
+        <f>NetworkingLESS!K11</f>
+        <v>0.15</v>
+      </c>
+      <c r="Q10" s="20">
+        <f>NetworkingLESS!S11</f>
+        <v>0.24</v>
+      </c>
+      <c r="R10" s="20">
+        <f>NetworkingLESS!AA11</f>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="S10" s="20">
+        <f>NetworkingLESS!AH11</f>
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A11" s="9">
+        <v>8</v>
+      </c>
+      <c r="B11" s="35">
+        <f>NetworkingLESS!O12</f>
+        <v>0.60402636685309896</v>
+      </c>
+      <c r="C11" s="35">
+        <f>NetworkingLESS!W12</f>
+        <v>0.58238928204542861</v>
+      </c>
+      <c r="D11" s="25"/>
+      <c r="E11" s="40">
+        <f>NetworkingLESS!K12</f>
+        <v>0.6</v>
+      </c>
+      <c r="F11" s="20">
+        <f>NetworkingLESS!S12</f>
+        <v>0.97</v>
+      </c>
+      <c r="G11" s="20">
+        <f>NetworkingLESS!AA12</f>
+        <v>8.75</v>
+      </c>
+      <c r="K11" s="9">
+        <v>8</v>
+      </c>
+      <c r="L11" s="42">
+        <f>NetworkingLESS!P12</f>
+        <v>0.68408111692288431</v>
+      </c>
+      <c r="M11" s="42">
+        <f>NetworkingLESS!X12</f>
+        <v>0.66681844311513572</v>
+      </c>
+      <c r="N11" s="42">
+        <f>NetworkingLESS!AE11</f>
+        <v>0.10795239894219871</v>
+      </c>
+      <c r="O11" s="25"/>
+      <c r="P11" s="40">
+        <f>NetworkingLESS!K12</f>
+        <v>0.6</v>
+      </c>
+      <c r="Q11" s="20">
+        <f>NetworkingLESS!S12</f>
+        <v>0.97</v>
+      </c>
+      <c r="R11" s="20">
+        <f>NetworkingLESS!AA12</f>
+        <v>8.75</v>
+      </c>
+      <c r="S11" s="20">
+        <f>NetworkingLESS!AH12</f>
+        <v>79.099999999999994</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A12" s="9">
+        <v>9</v>
+      </c>
+      <c r="B12" s="35">
+        <f>NetworkingLESS!O13</f>
+        <v>0.59456858794145684</v>
+      </c>
+      <c r="C12" s="35">
+        <f>NetworkingLESS!W13</f>
+        <v>0.59501200545373378</v>
+      </c>
+      <c r="D12" s="25"/>
+      <c r="E12" s="40">
+        <f>NetworkingLESS!K13</f>
+        <v>1.36</v>
+      </c>
+      <c r="F12" s="20">
+        <f>NetworkingLESS!S13</f>
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="G12" s="20">
+        <f>NetworkingLESS!AA13</f>
+        <v>20.100000000000001</v>
+      </c>
+      <c r="K12" s="9">
+        <v>9</v>
+      </c>
+      <c r="L12" s="42">
+        <f>NetworkingLESS!P13</f>
+        <v>0.63600837895403894</v>
+      </c>
+      <c r="M12" s="42">
+        <f>NetworkingLESS!X13</f>
+        <v>0.63640647405543815</v>
+      </c>
+      <c r="N12" s="42">
+        <f>NetworkingLESS!AE12</f>
+        <v>0.2021719209775921</v>
+      </c>
+      <c r="O12" s="25"/>
+      <c r="P12" s="40">
+        <f>NetworkingLESS!K13</f>
+        <v>1.36</v>
+      </c>
+      <c r="Q12" s="20">
+        <f>NetworkingLESS!S13</f>
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="R12" s="20">
+        <f>NetworkingLESS!AA13</f>
+        <v>20.100000000000001</v>
+      </c>
+      <c r="S12" s="20">
+        <f>NetworkingLESS!AH13</f>
+        <v>189.75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A13" s="9">
+        <v>10</v>
+      </c>
+      <c r="B13" s="35">
+        <f>NetworkingLESS!O14</f>
+        <v>0.5413946932687439</v>
+      </c>
+      <c r="C13" s="35">
+        <f>NetworkingLESS!W14</f>
+        <v>0.54245658688780329</v>
+      </c>
+      <c r="D13" s="25"/>
+      <c r="E13" s="40">
+        <f>NetworkingLESS!K14</f>
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="F13" s="20">
+        <f>NetworkingLESS!S14</f>
+        <v>3.88</v>
+      </c>
+      <c r="G13" s="20">
+        <f>NetworkingLESS!AA14</f>
+        <v>37.33</v>
+      </c>
+      <c r="K13" s="9">
+        <v>10</v>
+      </c>
+      <c r="L13" s="42">
+        <f>NetworkingLESS!P14</f>
+        <v>0.61640023899512164</v>
+      </c>
+      <c r="M13" s="42">
+        <f>NetworkingLESS!X14</f>
+        <v>0.61728845841278857</v>
+      </c>
+      <c r="N13" s="42">
+        <f>NetworkingLESS!AE13</f>
+        <v>0.1022115943167185</v>
+      </c>
+      <c r="O13" s="25"/>
+      <c r="P13" s="40">
+        <f>NetworkingLESS!K14</f>
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="Q13" s="20">
+        <f>NetworkingLESS!S14</f>
+        <v>3.88</v>
+      </c>
+      <c r="R13" s="20">
+        <f>NetworkingLESS!AA14</f>
+        <v>37.33</v>
+      </c>
+      <c r="S13" s="20">
+        <f>NetworkingLESS!AH14</f>
+        <v>331.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A14" s="9">
+        <v>11</v>
+      </c>
+      <c r="B14" s="35">
+        <f>NetworkingLESS!O15</f>
+        <v>0.6522570142426859</v>
+      </c>
+      <c r="C14" s="35">
+        <f>NetworkingLESS!W15</f>
+        <v>0.65331813058980936</v>
+      </c>
+      <c r="D14" s="25"/>
+      <c r="E14" s="40">
+        <f>NetworkingLESS!K15</f>
+        <v>3.8</v>
+      </c>
+      <c r="F14" s="20">
+        <f>NetworkingLESS!S15</f>
+        <v>6.13</v>
+      </c>
+      <c r="G14" s="20">
+        <f>NetworkingLESS!AA15</f>
+        <v>60.39</v>
+      </c>
+      <c r="K14" s="9">
+        <v>11</v>
+      </c>
+      <c r="L14" s="42">
+        <f>NetworkingLESS!P15</f>
+        <v>0.69807901759231528</v>
+      </c>
+      <c r="M14" s="42">
+        <f>NetworkingLESS!X15</f>
+        <v>0.69900031091265258</v>
+      </c>
+      <c r="N14" s="42">
+        <f>NetworkingLESS!AE14</f>
+        <v>0.16355141256647338</v>
+      </c>
+      <c r="O14" s="25"/>
+      <c r="P14" s="40">
+        <f>NetworkingLESS!K15</f>
+        <v>3.8</v>
+      </c>
+      <c r="Q14" s="20">
+        <f>NetworkingLESS!S15</f>
+        <v>6.13</v>
+      </c>
+      <c r="R14" s="20">
+        <f>NetworkingLESS!AA15</f>
+        <v>60.39</v>
+      </c>
+      <c r="S14" s="20">
+        <f>NetworkingLESS!AH15</f>
+        <v>541.70000000000005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A15" s="9">
+        <v>12</v>
+      </c>
+      <c r="B15" s="35">
+        <f>NetworkingLESS!O16</f>
+        <v>0.69484084980239957</v>
+      </c>
+      <c r="C15" s="35">
+        <f>NetworkingLESS!W16</f>
+        <v>0.69568396396855958</v>
+      </c>
+      <c r="D15" s="25"/>
+      <c r="E15" s="40">
+        <f>NetworkingLESS!K16</f>
+        <v>15.53</v>
+      </c>
+      <c r="F15" s="20">
+        <f>NetworkingLESS!S16</f>
+        <v>25.1</v>
+      </c>
+      <c r="G15" s="20">
+        <f>NetworkingLESS!AA16</f>
+        <v>290.14</v>
+      </c>
+      <c r="K15" s="9">
+        <v>12</v>
+      </c>
+      <c r="L15" s="42">
+        <f>NetworkingLESS!P16</f>
+        <v>0.74543395593003559</v>
+      </c>
+      <c r="M15" s="42">
+        <f>NetworkingLESS!X16</f>
+        <v>0.74613728806947743</v>
+      </c>
+      <c r="N15" s="42">
+        <f>NetworkingLESS!AE15</f>
+        <v>0.13176974152286161</v>
+      </c>
+      <c r="O15" s="25"/>
+      <c r="P15" s="40">
+        <f>NetworkingLESS!K16</f>
+        <v>15.53</v>
+      </c>
+      <c r="Q15" s="20">
+        <f>NetworkingLESS!S16</f>
+        <v>25.1</v>
+      </c>
+      <c r="R15" s="20">
+        <f>NetworkingLESS!AA16</f>
+        <v>290.14</v>
+      </c>
+      <c r="S15" s="20">
+        <f>NetworkingLESS!AH16</f>
+        <v>2601.5499999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A16" s="9">
+        <v>13</v>
+      </c>
+      <c r="B16" s="35">
+        <f>NetworkingLESS!O17</f>
+        <v>0.64769768811140194</v>
+      </c>
+      <c r="C16" s="35">
+        <f>NetworkingLESS!W17</f>
+        <v>0.64907389672760296</v>
+      </c>
+      <c r="D16" s="25"/>
+      <c r="E16" s="40">
+        <f>NetworkingLESS!K17</f>
+        <v>35.65</v>
+      </c>
+      <c r="F16" s="20">
+        <f>NetworkingLESS!S17</f>
+        <v>57.41</v>
+      </c>
+      <c r="G16" s="20">
+        <f>NetworkingLESS!AA17</f>
+        <v>749.64</v>
+      </c>
+      <c r="K16" s="9">
+        <v>13</v>
+      </c>
+      <c r="L16" s="42">
+        <f>NetworkingLESS!P17</f>
+        <v>0.70412597865789006</v>
+      </c>
+      <c r="M16" s="42">
+        <f>NetworkingLESS!X17</f>
+        <v>0.70528175982576902</v>
+      </c>
+      <c r="N16" s="42">
+        <f>NetworkingLESS!AE16</f>
+        <v>0.16579252529336042</v>
+      </c>
+      <c r="O16" s="25"/>
+      <c r="P16" s="40">
+        <f>NetworkingLESS!K17</f>
+        <v>35.65</v>
+      </c>
+      <c r="Q16" s="20">
+        <f>NetworkingLESS!S17</f>
+        <v>57.41</v>
+      </c>
+      <c r="R16" s="20">
+        <f>NetworkingLESS!AA17</f>
+        <v>749.64</v>
+      </c>
+      <c r="S16" s="20">
+        <f>NetworkingLESS!AH17</f>
+        <v>6781.25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A17" s="9">
+        <v>14</v>
+      </c>
+      <c r="B17" s="35">
+        <f>NetworkingLESS!O18</f>
+        <v>0.68604872530373229</v>
+      </c>
+      <c r="C17" s="35">
+        <f>NetworkingLESS!W18</f>
+        <v>0.67501148663614552</v>
+      </c>
+      <c r="D17" s="25"/>
+      <c r="E17" s="40">
+        <f>NetworkingLESS!K18</f>
+        <v>66.44</v>
+      </c>
+      <c r="F17" s="20">
+        <f>NetworkingLESS!S18</f>
+        <v>104.96</v>
+      </c>
+      <c r="G17" s="20">
+        <f>NetworkingLESS!AA18</f>
+        <v>1209.1400000000001</v>
+      </c>
+      <c r="K17" s="9">
+        <v>14</v>
+      </c>
+      <c r="L17" s="42">
+        <f>NetworkingLESS!P18</f>
+        <v>0.75716407654483664</v>
+      </c>
+      <c r="M17" s="42">
+        <f>NetworkingLESS!X18</f>
+        <v>0.74862696183864064</v>
+      </c>
+      <c r="N17" s="42">
+        <f>NetworkingLESS!AE17</f>
+        <v>0.16017008302895094</v>
+      </c>
+      <c r="O17" s="25"/>
+      <c r="P17" s="40">
+        <f>NetworkingLESS!K18</f>
+        <v>66.44</v>
+      </c>
+      <c r="Q17" s="20">
+        <f>NetworkingLESS!S18</f>
+        <v>104.96</v>
+      </c>
+      <c r="R17" s="20">
+        <f>NetworkingLESS!AA18</f>
+        <v>1209.1400000000001</v>
+      </c>
+      <c r="S17" s="20">
+        <f>NetworkingLESS!AH18</f>
+        <v>11609.75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A18" s="9">
+        <v>15</v>
+      </c>
+      <c r="B18" s="35">
+        <f>NetworkingLESS!O19</f>
+        <v>0.61575619066907861</v>
+      </c>
+      <c r="C18" s="35">
+        <f>NetworkingLESS!W19</f>
+        <v>0.61661196752727665</v>
+      </c>
+      <c r="D18" s="25"/>
+      <c r="E18" s="40">
+        <f>NetworkingLESS!K19</f>
+        <v>109.15</v>
+      </c>
+      <c r="F18" s="20">
+        <f>NetworkingLESS!S19</f>
+        <v>168.04</v>
+      </c>
+      <c r="G18" s="20">
+        <f>NetworkingLESS!AA19</f>
+        <v>1668.64</v>
+      </c>
+      <c r="K18" s="9">
+        <v>15</v>
+      </c>
+      <c r="L18" s="42">
+        <f>NetworkingLESS!P19</f>
+        <v>0.67047690055471298</v>
+      </c>
+      <c r="M18" s="42">
+        <f>NetworkingLESS!X19</f>
+        <v>0.6712108050078206</v>
+      </c>
+      <c r="N18" s="42">
+        <f>NetworkingLESS!AE18</f>
+        <v>0.22651716037752964</v>
+      </c>
+      <c r="O18" s="25"/>
+      <c r="P18" s="40">
+        <f>NetworkingLESS!K19</f>
+        <v>109.15</v>
+      </c>
+      <c r="Q18" s="20">
+        <f>NetworkingLESS!S19</f>
+        <v>168.04</v>
+      </c>
+      <c r="R18" s="20">
+        <f>NetworkingLESS!AA19</f>
+        <v>1668.64</v>
+      </c>
+      <c r="S18" s="20">
+        <f>NetworkingLESS!AH19</f>
+        <v>14829.849999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="37">
+        <f>AVERAGE(B4:B18)</f>
+        <v>0.52510754267311743</v>
+      </c>
+      <c r="C19" s="37">
+        <f>AVERAGE(C4:C18)</f>
+        <v>0.47793046911043408</v>
+      </c>
+      <c r="D19" s="37"/>
+      <c r="E19" s="39">
+        <f>AVERAGE(E4:E18)</f>
+        <v>15.685333333333334</v>
+      </c>
+      <c r="F19" s="39">
+        <f>AVERAGE(F4:F18)</f>
+        <v>24.616</v>
+      </c>
+      <c r="G19" s="39">
+        <f>AVERAGE(G4:G18)</f>
+        <v>269.90400000000005</v>
+      </c>
+      <c r="K19" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="L19" s="45">
+        <f>AVERAGE(L4:L18)</f>
+        <v>0.60318289795581981</v>
+      </c>
+      <c r="M19" s="45">
+        <f>AVERAGE(M4:M18)</f>
+        <v>0.56291254421347015</v>
+      </c>
+      <c r="N19" s="45">
+        <f>AVERAGE(N4:N18)</f>
+        <v>0.1494141881061502</v>
+      </c>
+      <c r="O19" s="37"/>
+      <c r="P19" s="39">
+        <f>AVERAGE(P4:P18)</f>
+        <v>15.685333333333334</v>
+      </c>
+      <c r="Q19" s="39">
+        <f>AVERAGE(Q4:Q18)</f>
+        <v>24.616</v>
+      </c>
+      <c r="R19" s="39">
+        <f>AVERAGE(R4:R18)</f>
+        <v>269.90400000000005</v>
+      </c>
+      <c r="S19" s="39">
+        <f>AVERAGE(S4:S18)</f>
+        <v>2467.8599999999997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A20" s="9">
+        <v>16</v>
+      </c>
+      <c r="B20" s="35">
+        <f>NetworkingLESS!O20</f>
+        <v>0.52836154506374644</v>
+      </c>
+      <c r="C20" s="35">
+        <f>NetworkingLESS!W20</f>
+        <v>0.50870988212878476</v>
+      </c>
+      <c r="D20" s="35"/>
+      <c r="E20" s="40">
+        <f>NetworkingLESS!K20</f>
+        <v>163.15</v>
+      </c>
+      <c r="F20" s="20">
+        <f>NetworkingLESS!S20</f>
+        <v>253.59</v>
+      </c>
+      <c r="G20" s="20">
+        <f>NetworkingLESS!AA20</f>
+        <v>2128.14</v>
+      </c>
+      <c r="K20" s="9">
+        <v>16</v>
+      </c>
+      <c r="L20" s="42">
+        <f>NetworkingLESS!P20</f>
+        <v>0.60366517616572668</v>
+      </c>
+      <c r="M20" s="42">
+        <f>NetworkingLESS!X20</f>
+        <v>0.58715117420964946</v>
+      </c>
+      <c r="N20" s="42">
+        <f>NetworkingLESS!AE20</f>
+        <v>0.15966389151232019</v>
+      </c>
+      <c r="O20" s="35"/>
+      <c r="P20" s="40">
+        <f>NetworkingLESS!K20</f>
+        <v>163.15</v>
+      </c>
+      <c r="Q20" s="20">
+        <f>NetworkingLESS!S20</f>
+        <v>253.59</v>
+      </c>
+      <c r="R20" s="20">
+        <f>NetworkingLESS!AA20</f>
+        <v>2128.14</v>
+      </c>
+      <c r="S20" s="20">
+        <f>NetworkingLESS!AH20</f>
+        <v>18913.650000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A21" s="9">
+        <v>17</v>
+      </c>
+      <c r="B21" s="35">
+        <f>NetworkingLESS!O21</f>
+        <v>0.5750799051359109</v>
+      </c>
+      <c r="C21" s="35">
+        <f>NetworkingLESS!W21</f>
+        <v>0.55737480624537106</v>
+      </c>
+      <c r="D21" s="35"/>
+      <c r="E21" s="40">
+        <f>NetworkingLESS!K21</f>
+        <v>231.98</v>
+      </c>
+      <c r="F21" s="20">
+        <f>NetworkingLESS!S21</f>
+        <v>357.76</v>
+      </c>
+      <c r="G21" s="20">
+        <f>NetworkingLESS!AA21</f>
+        <v>2587.64</v>
+      </c>
+      <c r="K21" s="9">
+        <v>17</v>
+      </c>
+      <c r="L21" s="42">
+        <f>NetworkingLESS!P21</f>
+        <v>0.65453651067849239</v>
+      </c>
+      <c r="M21" s="42">
+        <f>NetworkingLESS!X21</f>
+        <v>0.6401421214381704</v>
+      </c>
+      <c r="N21" s="42">
+        <f>NetworkingLESS!AE21</f>
+        <v>0.18699187565604714</v>
+      </c>
+      <c r="O21" s="35"/>
+      <c r="P21" s="40">
+        <f>NetworkingLESS!K21</f>
+        <v>231.98</v>
+      </c>
+      <c r="Q21" s="20">
+        <f>NetworkingLESS!S21</f>
+        <v>357.76</v>
+      </c>
+      <c r="R21" s="20">
+        <f>NetworkingLESS!AA21</f>
+        <v>2587.64</v>
+      </c>
+      <c r="S21" s="20">
+        <f>NetworkingLESS!AH21</f>
+        <v>25256.100000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A22" s="9">
+        <v>18</v>
+      </c>
+      <c r="B22" s="35">
+        <f>NetworkingLESS!O22</f>
+        <v>0.57020981320619024</v>
+      </c>
+      <c r="C22" s="35">
+        <f>NetworkingLESS!W22</f>
+        <v>0.55230188875644814</v>
+      </c>
+      <c r="D22" s="35"/>
+      <c r="E22" s="40">
+        <f>NetworkingLESS!K22</f>
+        <v>316.45999999999998</v>
+      </c>
+      <c r="F22" s="20">
+        <f>NetworkingLESS!S22</f>
+        <v>496.71</v>
+      </c>
+      <c r="G22" s="20">
+        <f>NetworkingLESS!AA22</f>
+        <v>3047.14</v>
+      </c>
+      <c r="K22" s="9">
+        <v>18</v>
+      </c>
+      <c r="L22" s="42">
+        <f>NetworkingLESS!P22</f>
+        <v>0.66752255561420182</v>
+      </c>
+      <c r="M22" s="42">
+        <f>NetworkingLESS!X22</f>
+        <v>0.65366932876479356</v>
+      </c>
+      <c r="N22" s="42">
+        <f>NetworkingLESS!AE22</f>
+        <v>0.22641918172668052</v>
+      </c>
+      <c r="O22" s="35"/>
+      <c r="P22" s="40">
+        <f>NetworkingLESS!K22</f>
+        <v>316.45999999999998</v>
+      </c>
+      <c r="Q22" s="20">
+        <f>NetworkingLESS!S22</f>
+        <v>496.71</v>
+      </c>
+      <c r="R22" s="20">
+        <f>NetworkingLESS!AA22</f>
+        <v>3047.14</v>
+      </c>
+      <c r="S22" s="20">
+        <f>NetworkingLESS!AH22</f>
+        <v>28532.15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A23" s="9">
+        <v>19</v>
+      </c>
+      <c r="B23" s="35">
+        <f>NetworkingLESS!O23</f>
+        <v>0.60378255634382039</v>
+      </c>
+      <c r="C23" s="35">
+        <f>NetworkingLESS!W23</f>
+        <v>0.43100747729743932</v>
+      </c>
+      <c r="D23" s="35"/>
+      <c r="E23" s="40">
+        <f>NetworkingLESS!K23</f>
+        <v>415.75</v>
+      </c>
+      <c r="F23" s="20">
+        <f>NetworkingLESS!S23</f>
+        <v>653.14</v>
+      </c>
+      <c r="G23" s="20">
+        <f>NetworkingLESS!AA23</f>
+        <v>3506.64</v>
+      </c>
+      <c r="K23" s="9">
+        <v>19</v>
+      </c>
+      <c r="L23" s="42">
+        <f>NetworkingLESS!P23</f>
+        <v>0.67254756798749971</v>
+      </c>
+      <c r="M23" s="42">
+        <f>NetworkingLESS!X23</f>
+        <v>0.5297582467934957</v>
+      </c>
+      <c r="N23" s="42">
+        <f>NetworkingLESS!AE23</f>
+        <v>0.17355372092943666</v>
+      </c>
+      <c r="O23" s="35"/>
+      <c r="P23" s="40">
+        <f>NetworkingLESS!K23</f>
+        <v>415.75</v>
+      </c>
+      <c r="Q23" s="20">
+        <f>NetworkingLESS!S23</f>
+        <v>653.14</v>
+      </c>
+      <c r="R23" s="20">
+        <f>NetworkingLESS!AA23</f>
+        <v>3506.64</v>
+      </c>
+      <c r="S23" s="20">
+        <f>NetworkingLESS!AH23</f>
+        <v>33112.9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A24" s="9">
+        <v>20</v>
+      </c>
+      <c r="B24" s="35">
+        <f>NetworkingLESS!O24</f>
+        <v>0.61083766712761545</v>
+      </c>
+      <c r="C24" s="35">
+        <f>NetworkingLESS!W24</f>
+        <v>0.59462254629610678</v>
+      </c>
+      <c r="D24" s="35"/>
+      <c r="E24" s="40">
+        <f>NetworkingLESS!K24</f>
+        <v>530.86</v>
+      </c>
+      <c r="F24" s="20">
+        <f>NetworkingLESS!S24</f>
+        <v>860.19</v>
+      </c>
+      <c r="G24" s="20">
+        <f>NetworkingLESS!AA24</f>
+        <v>3966.14</v>
+      </c>
+      <c r="K24" s="9">
+        <v>20</v>
+      </c>
+      <c r="L24" s="42">
+        <f>NetworkingLESS!P24</f>
+        <v>0.67424732297659173</v>
+      </c>
+      <c r="M24" s="42">
+        <f>NetworkingLESS!X24</f>
+        <v>0.6606742749887895</v>
+      </c>
+      <c r="N24" s="42">
+        <f>NetworkingLESS!AE24</f>
+        <v>0.16293883167200007</v>
+      </c>
+      <c r="O24" s="35"/>
+      <c r="P24" s="40">
+        <f>NetworkingLESS!K24</f>
+        <v>530.86</v>
+      </c>
+      <c r="Q24" s="20">
+        <f>NetworkingLESS!S24</f>
+        <v>860.19</v>
+      </c>
+      <c r="R24" s="20">
+        <f>NetworkingLESS!AA24</f>
+        <v>3966.14</v>
+      </c>
+      <c r="S24" s="20">
+        <f>NetworkingLESS!AH24</f>
+        <v>39025.599999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A25" s="36">
+        <v>21</v>
+      </c>
+      <c r="B25" s="35">
+        <f>NetworkingLESS!O25</f>
+        <v>0.58097829271440793</v>
+      </c>
+      <c r="C25" s="35">
+        <f>NetworkingLESS!W25</f>
+        <v>0.56351904634939931</v>
+      </c>
+      <c r="D25" s="35"/>
+      <c r="E25" s="40">
+        <f>NetworkingLESS!K25</f>
+        <v>672.84</v>
+      </c>
+      <c r="F25" s="20">
+        <f>NetworkingLESS!S25</f>
+        <v>1067.24</v>
+      </c>
+      <c r="G25" s="20">
+        <f>NetworkingLESS!AA25</f>
+        <v>4425.6400000000003</v>
+      </c>
+      <c r="K25" s="36">
+        <v>21</v>
+      </c>
+      <c r="L25" s="42">
+        <f>NetworkingLESS!P25</f>
+        <v>0.63243709953478622</v>
+      </c>
+      <c r="M25" s="42">
+        <f>NetworkingLESS!X25</f>
+        <v>0.61712197117203205</v>
+      </c>
+      <c r="N25" s="42">
+        <f>NetworkingLESS!AE25</f>
+        <v>0.12280701912492008</v>
+      </c>
+      <c r="O25" s="35"/>
+      <c r="P25" s="40">
+        <f>NetworkingLESS!K25</f>
+        <v>672.84</v>
+      </c>
+      <c r="Q25" s="20">
+        <f>NetworkingLESS!S25</f>
+        <v>1067.24</v>
+      </c>
+      <c r="R25" s="20">
+        <f>NetworkingLESS!AA25</f>
+        <v>4425.6400000000003</v>
+      </c>
+      <c r="S25" s="20">
+        <f>NetworkingLESS!AH25</f>
+        <v>41087.9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="37">
+        <f>AVERAGE(B20:B25)</f>
+        <v>0.57820829659861517</v>
+      </c>
+      <c r="C26" s="37">
+        <f>AVERAGE(C20:C25)</f>
+        <v>0.53458927451225824</v>
+      </c>
+      <c r="D26" s="37"/>
+      <c r="E26" s="39">
+        <f>AVERAGE(E20:E25)</f>
+        <v>388.50666666666666</v>
+      </c>
+      <c r="F26" s="39">
+        <f>AVERAGE(F20:F25)</f>
+        <v>614.77166666666665</v>
+      </c>
+      <c r="G26" s="39">
+        <f>AVERAGE(G20:G25)</f>
+        <v>3276.89</v>
+      </c>
+      <c r="K26" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="L26" s="45">
+        <f>AVERAGE(L20:L25)</f>
+        <v>0.65082603882621637</v>
+      </c>
+      <c r="M26" s="45">
+        <f>AVERAGE(M20:M25)</f>
+        <v>0.61475285289448844</v>
+      </c>
+      <c r="N26" s="45">
+        <f>AVERAGE(N20:N25)</f>
+        <v>0.17206242010356743</v>
+      </c>
+      <c r="O26" s="37"/>
+      <c r="P26" s="39">
+        <f>AVERAGE(P20:P25)</f>
+        <v>388.50666666666666</v>
+      </c>
+      <c r="Q26" s="39">
+        <f>AVERAGE(Q20:Q25)</f>
+        <v>614.77166666666665</v>
+      </c>
+      <c r="R26" s="39">
+        <f>AVERAGE(R20:R25)</f>
+        <v>3276.89</v>
+      </c>
+      <c r="S26" s="39">
+        <f>AVERAGE(S20:S25)</f>
+        <v>30988.05</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:N2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -20248,29 +23678,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="E1" s="19" t="s">
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="E1" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="I1" s="19" t="s">
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="I1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="M1" s="19" t="s">
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="M1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="19"/>
-      <c r="P1" s="19" t="s">
+      <c r="N1" s="46"/>
+      <c r="P1" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="19"/>
+      <c r="Q1" s="46"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2">
@@ -22459,28 +25889,278 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D6B04FF-CAF6-FE40-B656-3920DD2CFD72}">
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1">
+        <v>0.1</v>
+      </c>
+      <c r="B1">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="C1">
+        <f>A1*B1</f>
+        <v>0.11599999999999999</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0.33</v>
+      </c>
+      <c r="B2">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="C2">
+        <f t="shared" ref="C2:C20" si="0">A2*B2</f>
+        <v>0.37619999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="B3">
+        <v>1.21</v>
+      </c>
+      <c r="C3">
+        <f t="shared" si="0"/>
+        <v>0.68969999999999987</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4">
+        <v>1.17</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>1.2869999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="B5">
+        <v>1.23</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>2.7552000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>8.75</v>
+      </c>
+      <c r="B6">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>9.9749999999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="B7">
+        <v>1.19</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>23.919</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>37.33</v>
+      </c>
+      <c r="B8">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>41.809600000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>60.39</v>
+      </c>
+      <c r="B9">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>68.24069999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>290.14</v>
+      </c>
+      <c r="B10">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>327.85819999999995</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>749.64</v>
+      </c>
+      <c r="B11">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>854.5895999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>1209.1400000000001</v>
+      </c>
+      <c r="B12">
+        <v>1.21</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>1463.0594000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>1668.64</v>
+      </c>
+      <c r="B13">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>1868.8768000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2128.14</v>
+      </c>
+      <c r="B14">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>2383.5167999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2587.64</v>
+      </c>
+      <c r="B15">
+        <v>1.23</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>3182.7972</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>3047.14</v>
+      </c>
+      <c r="B16">
+        <v>1.18</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>3595.6251999999995</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>3506.64</v>
+      </c>
+      <c r="B17">
+        <v>1.19</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="0"/>
+        <v>4172.9015999999992</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>3966.14</v>
+      </c>
+      <c r="B18">
+        <v>1.24</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="0"/>
+        <v>4918.0136000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>4425.6400000000003</v>
+      </c>
+      <c r="B19">
+        <v>1.17</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="0"/>
+        <v>5177.9988000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>4885.1400000000003</v>
+      </c>
+      <c r="B20">
+        <v>1.17</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="0"/>
+        <v>5715.6138000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42F1A473-994F-5D42-A9F3-FFDA207A32EE}">
   <dimension ref="A2:V18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4" style="20" customWidth="1"/>
+    <col min="3" max="3" width="4" style="19" customWidth="1"/>
     <col min="4" max="4" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4" style="20" customWidth="1"/>
+    <col min="8" max="8" width="4" style="19" customWidth="1"/>
     <col min="9" max="9" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4" style="20" customWidth="1"/>
+    <col min="13" max="13" width="4" style="19" customWidth="1"/>
     <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4" style="20" customWidth="1"/>
+    <col min="18" max="18" width="4" style="19" customWidth="1"/>
     <col min="19" max="19" width="8" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
@@ -22488,32 +26168,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="I2" s="19" t="s">
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="I2" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="N2" s="19" t="s">
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="N2" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="19"/>
-      <c r="P2" s="19"/>
-      <c r="Q2" s="19"/>
-      <c r="S2" s="19" t="s">
+      <c r="O2" s="46"/>
+      <c r="P2" s="46"/>
+      <c r="Q2" s="46"/>
+      <c r="S2" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="19"/>
-      <c r="U2" s="19"/>
-      <c r="V2" s="19"/>
+      <c r="T2" s="46"/>
+      <c r="U2" s="46"/>
+      <c r="V2" s="46"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -23386,67 +27064,92 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C03F23-5B48-E740-AE12-B3F8383D5054}">
-  <dimension ref="A2:AD26"/>
+  <dimension ref="A2:AM26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4" style="20" customWidth="1"/>
+    <col min="4" max="4" width="4" style="19" customWidth="1"/>
     <col min="5" max="5" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4" style="20" customWidth="1"/>
-    <col min="9" max="9" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.6640625" customWidth="1"/>
-    <col min="14" max="14" width="4" style="20" customWidth="1"/>
-    <col min="15" max="15" width="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="7.1640625" customWidth="1"/>
-    <col min="20" max="20" width="4" style="20" customWidth="1"/>
-    <col min="21" max="21" width="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.1640625" customWidth="1"/>
-    <col min="25" max="25" width="4" style="20" customWidth="1"/>
-    <col min="30" max="30" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.1640625" customWidth="1"/>
+    <col min="10" max="10" width="4" style="19" customWidth="1"/>
+    <col min="11" max="11" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+    <col min="14" max="14" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="8.6640625" customWidth="1"/>
+    <col min="18" max="18" width="4" style="19" customWidth="1"/>
+    <col min="19" max="19" width="8" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.83203125" customWidth="1"/>
+    <col min="22" max="22" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.6640625" customWidth="1"/>
+    <col min="24" max="25" width="7.1640625" customWidth="1"/>
+    <col min="26" max="26" width="4" style="19" customWidth="1"/>
+    <col min="27" max="27" width="8" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.83203125" customWidth="1"/>
+    <col min="30" max="30" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="7.6640625" customWidth="1"/>
+    <col min="33" max="33" width="4" style="19" customWidth="1"/>
+    <col min="34" max="34" width="8.83203125" customWidth="1"/>
+    <col min="35" max="35" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.83203125" customWidth="1"/>
+    <col min="37" max="37" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.1640625" customWidth="1"/>
+    <col min="39" max="39" width="4" style="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="E2" s="19" t="s">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="E2" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="I2" s="19" t="s">
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="18"/>
+      <c r="K2" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="18"/>
-      <c r="O2" s="19" t="s">
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18"/>
+      <c r="S2" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="19"/>
-      <c r="Q2" s="19"/>
-      <c r="R2" s="19"/>
-      <c r="S2" s="18"/>
-      <c r="U2" s="19" t="s">
+      <c r="T2" s="46"/>
+      <c r="U2" s="46"/>
+      <c r="V2" s="46"/>
+      <c r="W2" s="46"/>
+      <c r="X2" s="18"/>
+      <c r="Y2" s="18"/>
+      <c r="AA2" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="V2" s="19"/>
-      <c r="W2" s="19"/>
-      <c r="X2" s="19"/>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB2" s="46"/>
+      <c r="AC2" s="46"/>
+      <c r="AD2" s="46"/>
+      <c r="AE2" s="46"/>
+      <c r="AF2" s="18"/>
+      <c r="AH2" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI2" s="46"/>
+      <c r="AJ2" s="46"/>
+      <c r="AK2" s="46"/>
+      <c r="AL2" s="46"/>
+    </row>
+    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -23463,52 +27166,91 @@
         <v>11</v>
       </c>
       <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
         <v>14</v>
       </c>
       <c r="I3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K3" t="s">
         <v>12</v>
       </c>
-      <c r="J3" t="s">
+      <c r="L3" t="s">
         <v>11</v>
       </c>
-      <c r="K3" t="s">
-        <v>14</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" t="s">
         <v>19</v>
       </c>
-      <c r="M3" t="s">
+      <c r="O3" t="s">
         <v>20</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S3" t="s">
         <v>12</v>
       </c>
-      <c r="P3" t="s">
+      <c r="T3" t="s">
         <v>11</v>
       </c>
-      <c r="Q3" t="s">
-        <v>14</v>
-      </c>
-      <c r="R3" t="s">
+      <c r="U3" t="s">
+        <v>15</v>
+      </c>
+      <c r="V3" t="s">
         <v>19</v>
       </c>
-      <c r="S3" t="s">
+      <c r="W3" t="s">
         <v>20</v>
       </c>
-      <c r="U3" t="s">
+      <c r="X3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA3" t="s">
         <v>12</v>
       </c>
-      <c r="V3" t="s">
+      <c r="AB3" t="s">
         <v>11</v>
       </c>
-      <c r="W3" t="s">
-        <v>14</v>
-      </c>
-      <c r="X3" t="s">
+      <c r="AC3" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>0</v>
       </c>
@@ -23525,57 +27267,105 @@
         <v>450</v>
       </c>
       <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
+        <f>F4/G4</f>
+        <v>90</v>
+      </c>
+      <c r="K4">
         <v>1.87</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>450</v>
       </c>
-      <c r="K4">
+      <c r="M4" s="6">
+        <v>5</v>
+      </c>
+      <c r="N4">
+        <f t="shared" ref="N4:N19" si="0">($F4-L4)/$F4</f>
         <v>0</v>
       </c>
-      <c r="L4">
-        <f>($F4-J4)/$F4</f>
+      <c r="O4">
+        <f t="shared" ref="O4:O26" si="1">($AB4-L4)/$AB4</f>
         <v>0</v>
       </c>
-      <c r="M4">
-        <f>($V4-J4)/$V4</f>
+      <c r="P4">
+        <f t="shared" ref="P4:P26" si="2">($AI4-L4)/$AI4</f>
         <v>0</v>
       </c>
-      <c r="O4">
+      <c r="Q4">
+        <f>L4/M4</f>
+        <v>90</v>
+      </c>
+      <c r="S4">
         <v>1.86</v>
       </c>
-      <c r="P4">
+      <c r="T4">
         <v>450</v>
       </c>
-      <c r="Q4">
+      <c r="U4">
+        <v>5</v>
+      </c>
+      <c r="V4">
+        <f t="shared" ref="V4:V19" si="3">($F4-T4)/$F4</f>
         <v>0</v>
       </c>
-      <c r="R4">
-        <f>($F4-P4)/$F4</f>
+      <c r="W4">
+        <f t="shared" ref="W4:W26" si="4">($AB4-T4)/$AB4</f>
         <v>0</v>
       </c>
-      <c r="S4">
-        <f t="shared" ref="S4:S26" si="0">($V4-P4)/$V4</f>
+      <c r="X4">
+        <f t="shared" ref="X4:X26" si="5">($AI4-T4)/$AI4</f>
         <v>0</v>
       </c>
-      <c r="U4">
+      <c r="Y4">
+        <f>T4/U4</f>
+        <v>90</v>
+      </c>
+      <c r="AA4">
         <v>1.84</v>
       </c>
-      <c r="V4">
+      <c r="AB4">
         <v>450</v>
       </c>
-      <c r="W4">
+      <c r="AC4">
+        <v>5</v>
+      </c>
+      <c r="AD4">
+        <f t="shared" ref="AD4:AD19" si="6">($F4-AB4)/$F4</f>
         <v>0</v>
       </c>
-      <c r="X4">
-        <f>($F4-V4)/$F4</f>
+      <c r="AE4">
+        <f>($AI4-AB4)/$AI4</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AF4">
+        <f>AB4/AC4</f>
+        <v>90</v>
+      </c>
+      <c r="AH4" s="4">
+        <v>1.74</v>
+      </c>
+      <c r="AI4">
+        <v>450</v>
+      </c>
+      <c r="AJ4">
+        <v>5</v>
+      </c>
+      <c r="AK4" s="4">
+        <f t="shared" ref="AK4:AK19" si="7">($F4-AI4)/$F4</f>
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <f>AI4/AJ4</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -23592,57 +27382,105 @@
         <v>5390</v>
       </c>
       <c r="G5">
+        <v>97</v>
+      </c>
+      <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>4067</v>
+        <f t="shared" ref="I5:I19" si="8">F5/G5</f>
+        <v>55.567010309278352</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="L5" s="4">
-        <f t="shared" ref="L5:L19" si="1">($F5-J5)/$F5</f>
+      <c r="L5">
+        <v>4067</v>
+      </c>
+      <c r="M5" s="6">
+        <v>73</v>
+      </c>
+      <c r="N5" s="4">
+        <f t="shared" si="0"/>
         <v>0.24545454545454545</v>
       </c>
-      <c r="M5">
-        <f>($V5-J5)/$V5</f>
+      <c r="O5">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O5">
+      <c r="P5">
+        <f t="shared" si="2"/>
+        <v>0.23119092627599244</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q26" si="9">L5/M5</f>
+        <v>55.712328767123289</v>
+      </c>
+      <c r="S5">
         <v>0</v>
       </c>
-      <c r="P5">
+      <c r="T5">
         <v>4067</v>
       </c>
-      <c r="Q5">
+      <c r="U5">
+        <v>73</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="3"/>
+        <v>0.24545454545454545</v>
+      </c>
+      <c r="W5">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R5">
-        <f t="shared" ref="R5:R19" si="2">($F5-P5)/$F5</f>
+      <c r="X5">
+        <f t="shared" si="5"/>
+        <v>0.23119092627599244</v>
+      </c>
+      <c r="Y5">
+        <f t="shared" ref="Y5:Y26" si="10">T5/U5</f>
+        <v>55.712328767123289</v>
+      </c>
+      <c r="AA5">
+        <v>0.03</v>
+      </c>
+      <c r="AB5">
+        <v>4067</v>
+      </c>
+      <c r="AC5">
+        <v>73</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" si="6"/>
         <v>0.24545454545454545</v>
       </c>
-      <c r="S5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0.03</v>
-      </c>
-      <c r="V5">
-        <v>4067</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <f t="shared" ref="X5:X19" si="3">($F5-V5)/$F5</f>
-        <v>0.24545454545454545</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE5">
+        <f t="shared" ref="AE5:AE26" si="11">($AI5-AB5)/$AI5</f>
+        <v>0.23119092627599244</v>
+      </c>
+      <c r="AF5">
+        <f t="shared" ref="AF5:AF26" si="12">AB5/AC5</f>
+        <v>55.712328767123289</v>
+      </c>
+      <c r="AH5" s="4">
+        <v>3.4000000000000004</v>
+      </c>
+      <c r="AI5">
+        <v>5290</v>
+      </c>
+      <c r="AJ5">
+        <v>95</v>
+      </c>
+      <c r="AK5" s="4">
+        <f t="shared" si="7"/>
+        <v>1.8552875695732839E-2</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" ref="AL5:AL26" si="13">AI5/AJ5</f>
+        <v>55.684210526315788</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2</v>
       </c>
@@ -23659,57 +27497,105 @@
         <v>7290</v>
       </c>
       <c r="G6">
+        <v>255</v>
+      </c>
+      <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>2890</v>
+        <f t="shared" si="8"/>
+        <v>28.588235294117649</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6">
+        <v>2890</v>
+      </c>
+      <c r="M6" s="6">
+        <v>101</v>
+      </c>
+      <c r="N6" s="4">
+        <f t="shared" si="0"/>
+        <v>0.60356652949245537</v>
+      </c>
+      <c r="O6">
         <f t="shared" si="1"/>
+        <v>0.50933786078098475</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="2"/>
+        <v>0.58357348703170031</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="9"/>
+        <v>28.613861386138613</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>2890</v>
+      </c>
+      <c r="U6">
+        <v>101</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="3"/>
         <v>0.60356652949245537</v>
       </c>
-      <c r="M6">
-        <f t="shared" ref="M6:M26" si="4">($V6-J6)/$V6</f>
+      <c r="W6">
+        <f t="shared" si="4"/>
         <v>0.50933786078098475</v>
       </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>2890</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="2"/>
-        <v>0.60356652949245537</v>
-      </c>
-      <c r="S6">
-        <f t="shared" si="0"/>
-        <v>0.50933786078098475</v>
-      </c>
-      <c r="U6">
+      <c r="X6">
+        <f t="shared" si="5"/>
+        <v>0.58357348703170031</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" si="10"/>
+        <v>28.613861386138613</v>
+      </c>
+      <c r="AA6">
         <v>0.06</v>
       </c>
-      <c r="V6">
+      <c r="AB6">
         <v>5890</v>
       </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <f t="shared" si="3"/>
+      <c r="AC6">
+        <v>206</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="6"/>
         <v>0.19204389574759945</v>
       </c>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE6">
+        <f t="shared" si="11"/>
+        <v>0.15129682997118155</v>
+      </c>
+      <c r="AF6">
+        <f t="shared" si="12"/>
+        <v>28.592233009708739</v>
+      </c>
+      <c r="AH6" s="4">
+        <v>3.65</v>
+      </c>
+      <c r="AI6">
+        <v>6940</v>
+      </c>
+      <c r="AJ6">
+        <v>242</v>
+      </c>
+      <c r="AK6" s="4">
+        <f t="shared" si="7"/>
+        <v>4.8010973936899862E-2</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="13"/>
+        <v>28.677685950413224</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>3</v>
       </c>
@@ -23726,57 +27612,105 @@
         <v>24472</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>499</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>11782</v>
+        <f t="shared" si="8"/>
+        <v>49.042084168336672</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7">
+        <v>11782</v>
+      </c>
+      <c r="M7" s="6">
+        <v>240</v>
+      </c>
+      <c r="N7" s="4">
+        <f t="shared" si="0"/>
+        <v>0.51855181431840469</v>
+      </c>
+      <c r="O7">
         <f t="shared" si="1"/>
-        <v>0.51855181431840469</v>
-      </c>
-      <c r="M7">
+        <v>0.43731792349204834</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="2"/>
+        <v>0.49786907603136721</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="9"/>
+        <v>49.091666666666669</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>14632</v>
+      </c>
+      <c r="U7">
+        <v>298</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="3"/>
+        <v>0.40209218698921217</v>
+      </c>
+      <c r="W7">
         <f t="shared" si="4"/>
-        <v>0.43731792349204834</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>14632</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="2"/>
-        <v>0.40209218698921217</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="0"/>
         <v>0.30120827164621045</v>
       </c>
-      <c r="U7">
+      <c r="X7">
+        <f t="shared" si="5"/>
+        <v>0.37640640981929763</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" si="10"/>
+        <v>49.100671140939596</v>
+      </c>
+      <c r="AA7">
         <v>0.1</v>
       </c>
-      <c r="V7">
+      <c r="AB7">
         <v>20939</v>
       </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <f t="shared" si="3"/>
+      <c r="AC7">
+        <v>427</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="6"/>
         <v>0.1443690748610657</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7">
+        <f t="shared" si="11"/>
+        <v>0.10761166041595636</v>
+      </c>
+      <c r="AF7">
+        <f t="shared" si="12"/>
+        <v>49.037470725995313</v>
+      </c>
+      <c r="AH7" s="4">
+        <v>3.85</v>
+      </c>
+      <c r="AI7">
+        <v>23464</v>
+      </c>
+      <c r="AJ7">
+        <v>478</v>
+      </c>
+      <c r="AK7" s="4">
+        <f t="shared" si="7"/>
+        <v>4.1189931350114416E-2</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="13"/>
+        <v>49.087866108786613</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>4</v>
       </c>
@@ -23793,57 +27727,105 @@
         <v>29348</v>
       </c>
       <c r="G8">
+        <v>1219</v>
+      </c>
+      <c r="H8">
         <v>2</v>
       </c>
       <c r="I8">
+        <f t="shared" si="8"/>
+        <v>24.075471698113208</v>
+      </c>
+      <c r="K8">
         <v>0.02</v>
       </c>
-      <c r="J8">
+      <c r="L8">
         <v>10880</v>
       </c>
-      <c r="K8">
-        <v>2</v>
-      </c>
-      <c r="L8" s="4">
+      <c r="M8" s="6">
+        <v>452</v>
+      </c>
+      <c r="N8" s="4">
+        <f t="shared" si="0"/>
+        <v>0.62927627095543137</v>
+      </c>
+      <c r="O8">
         <f t="shared" si="1"/>
-        <v>0.62927627095543137</v>
-      </c>
-      <c r="M8">
+        <v>0.49699491447064265</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="2"/>
+        <v>0.60357077791947533</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="9"/>
+        <v>24.070796460176989</v>
+      </c>
+      <c r="S8">
+        <v>0.05</v>
+      </c>
+      <c r="T8">
+        <v>15734</v>
+      </c>
+      <c r="U8">
+        <v>654</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="3"/>
+        <v>0.46388169551587843</v>
+      </c>
+      <c r="W8">
         <f t="shared" si="4"/>
-        <v>0.49699491447064265</v>
-      </c>
-      <c r="O8">
-        <v>0.05</v>
-      </c>
-      <c r="P8">
-        <v>15734</v>
-      </c>
-      <c r="Q8">
-        <v>2</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="2"/>
-        <v>0.46388169551587843</v>
-      </c>
-      <c r="S8">
-        <f t="shared" si="0"/>
         <v>0.27258437355524734</v>
       </c>
-      <c r="U8">
+      <c r="X8">
+        <f t="shared" si="5"/>
+        <v>0.42670796137730005</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="10"/>
+        <v>24.058103975535168</v>
+      </c>
+      <c r="AA8">
         <v>0.33</v>
       </c>
-      <c r="V8">
+      <c r="AB8">
         <v>21630</v>
       </c>
-      <c r="W8">
-        <v>2</v>
-      </c>
-      <c r="X8">
-        <f t="shared" si="3"/>
+      <c r="AC8">
+        <v>898</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="6"/>
         <v>0.26298214529099084</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8">
+        <f t="shared" si="11"/>
+        <v>0.21187830205866279</v>
+      </c>
+      <c r="AF8">
+        <f t="shared" si="12"/>
+        <v>24.08685968819599</v>
+      </c>
+      <c r="AH8" s="4">
+        <v>4.95</v>
+      </c>
+      <c r="AI8">
+        <v>27445</v>
+      </c>
+      <c r="AJ8">
+        <v>1139</v>
+      </c>
+      <c r="AK8" s="4">
+        <f t="shared" si="7"/>
+        <v>6.484257871064468E-2</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="13"/>
+        <v>24.095697980684811</v>
+      </c>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>5</v>
       </c>
@@ -23860,57 +27842,105 @@
         <v>99280</v>
       </c>
       <c r="G9">
+        <v>1714</v>
+      </c>
+      <c r="H9">
         <v>4</v>
       </c>
       <c r="I9">
+        <f t="shared" si="8"/>
+        <v>57.92298716452742</v>
+      </c>
+      <c r="K9">
         <v>0.05</v>
       </c>
-      <c r="J9">
+      <c r="L9">
         <v>31563</v>
       </c>
-      <c r="K9">
-        <v>4</v>
-      </c>
-      <c r="L9" s="4">
+      <c r="M9" s="6">
+        <v>545</v>
+      </c>
+      <c r="N9" s="4">
+        <f t="shared" si="0"/>
+        <v>0.68208098307816278</v>
+      </c>
+      <c r="O9">
         <f t="shared" si="1"/>
-        <v>0.68208098307816278</v>
-      </c>
-      <c r="M9">
+        <v>0.61270016565433461</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="2"/>
+        <v>0.65739313548835288</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="9"/>
+        <v>57.913761467889906</v>
+      </c>
+      <c r="S9">
+        <v>0.09</v>
+      </c>
+      <c r="T9">
+        <v>40182</v>
+      </c>
+      <c r="U9">
+        <v>694</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="3"/>
+        <v>0.5952659145850121</v>
+      </c>
+      <c r="W9">
         <f t="shared" si="4"/>
-        <v>0.61270016565433461</v>
-      </c>
-      <c r="O9">
-        <v>0.09</v>
-      </c>
-      <c r="P9">
-        <v>40182</v>
-      </c>
-      <c r="Q9">
-        <v>4</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="2"/>
-        <v>0.5952659145850121</v>
-      </c>
-      <c r="S9">
-        <f t="shared" si="0"/>
         <v>0.50693907601693355</v>
       </c>
-      <c r="U9">
+      <c r="X9">
+        <f t="shared" si="5"/>
+        <v>0.56383648481427606</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" si="10"/>
+        <v>57.899135446685882</v>
+      </c>
+      <c r="AA9">
         <v>0.56999999999999995</v>
       </c>
-      <c r="V9">
+      <c r="AB9">
         <v>81495</v>
       </c>
-      <c r="W9">
-        <v>4</v>
-      </c>
-      <c r="X9">
-        <f t="shared" si="3"/>
+      <c r="AC9">
+        <v>1407</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="6"/>
         <v>0.17913980660757453</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9">
+        <f t="shared" si="11"/>
+        <v>0.11539630506046067</v>
+      </c>
+      <c r="AF9">
+        <f t="shared" si="12"/>
+        <v>57.921108742004265</v>
+      </c>
+      <c r="AH9" s="4">
+        <v>5.4</v>
+      </c>
+      <c r="AI9">
+        <v>92126</v>
+      </c>
+      <c r="AJ9">
+        <v>1590</v>
+      </c>
+      <c r="AK9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.2058823529411759E-2</v>
+      </c>
+      <c r="AL9">
+        <f t="shared" si="13"/>
+        <v>57.940880503144655</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>6</v>
       </c>
@@ -23927,57 +27957,105 @@
         <v>33031</v>
       </c>
       <c r="G10">
+        <v>2395</v>
+      </c>
+      <c r="H10">
         <v>12</v>
       </c>
       <c r="I10">
+        <f t="shared" si="8"/>
+        <v>13.791649269311065</v>
+      </c>
+      <c r="K10">
         <v>0.1</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>22664</v>
       </c>
-      <c r="K10">
-        <v>12</v>
-      </c>
-      <c r="L10" s="4">
+      <c r="M10" s="6">
+        <v>1643</v>
+      </c>
+      <c r="N10" s="4">
+        <f t="shared" si="0"/>
+        <v>0.31385668008840178</v>
+      </c>
+      <c r="O10">
         <f t="shared" si="1"/>
-        <v>0.31385668008840178</v>
-      </c>
-      <c r="M10">
+        <v>0.14979179952732866</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="2"/>
+        <v>0.28897254901960784</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="9"/>
+        <v>13.794278758368838</v>
+      </c>
+      <c r="S10">
+        <v>0.19</v>
+      </c>
+      <c r="T10">
+        <v>22678</v>
+      </c>
+      <c r="U10">
+        <v>1644</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="3"/>
+        <v>0.31343283582089554</v>
+      </c>
+      <c r="W10">
         <f t="shared" si="4"/>
-        <v>0.14979179952732866</v>
-      </c>
-      <c r="O10">
-        <v>0.19</v>
-      </c>
-      <c r="P10">
-        <v>22678</v>
-      </c>
-      <c r="Q10">
-        <v>12</v>
-      </c>
-      <c r="R10">
-        <f t="shared" si="2"/>
-        <v>0.31343283582089554</v>
-      </c>
-      <c r="S10">
-        <f t="shared" si="0"/>
         <v>0.14926660914581535</v>
       </c>
-      <c r="U10">
+      <c r="X10">
+        <f t="shared" si="5"/>
+        <v>0.28853333333333331</v>
+      </c>
+      <c r="Y10">
+        <f t="shared" si="10"/>
+        <v>13.79440389294404</v>
+      </c>
+      <c r="AA10">
         <v>1.1000000000000001</v>
       </c>
-      <c r="V10">
+      <c r="AB10">
         <v>26657</v>
       </c>
-      <c r="W10">
-        <v>12</v>
-      </c>
-      <c r="X10">
-        <f t="shared" si="3"/>
+      <c r="AC10">
+        <v>1933</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="6"/>
         <v>0.19297024007750296</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10">
+        <f t="shared" si="11"/>
+        <v>0.16370196078431373</v>
+      </c>
+      <c r="AF10">
+        <f t="shared" si="12"/>
+        <v>13.790481117434041</v>
+      </c>
+      <c r="AH10" s="4">
+        <v>10.149999999999999</v>
+      </c>
+      <c r="AI10">
+        <v>31875</v>
+      </c>
+      <c r="AJ10">
+        <v>2311</v>
+      </c>
+      <c r="AK10" s="4">
+        <f t="shared" si="7"/>
+        <v>3.4997426659804425E-2</v>
+      </c>
+      <c r="AL10">
+        <f t="shared" si="13"/>
+        <v>13.792730419731718</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>7</v>
       </c>
@@ -23994,57 +28072,105 @@
         <v>115483</v>
       </c>
       <c r="G11">
+        <v>4867</v>
+      </c>
+      <c r="H11">
         <v>12</v>
       </c>
       <c r="I11">
+        <f t="shared" si="8"/>
+        <v>23.727758372714199</v>
+      </c>
+      <c r="K11">
         <v>0.15</v>
       </c>
-      <c r="J11">
+      <c r="L11">
         <v>34580</v>
       </c>
-      <c r="K11">
-        <v>12</v>
-      </c>
-      <c r="L11" s="4">
+      <c r="M11" s="6">
+        <v>1457</v>
+      </c>
+      <c r="N11" s="4">
+        <f t="shared" si="0"/>
+        <v>0.70056198747867648</v>
+      </c>
+      <c r="O11">
         <f t="shared" si="1"/>
-        <v>0.70056198747867648</v>
-      </c>
-      <c r="M11">
+        <v>0.63388035997882475</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="2"/>
+        <v>0.67340385341896492</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="9"/>
+        <v>23.733699382292382</v>
+      </c>
+      <c r="S11">
+        <v>0.24</v>
+      </c>
+      <c r="T11">
+        <v>54775</v>
+      </c>
+      <c r="U11">
+        <v>2308</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="3"/>
+        <v>0.52568776356693192</v>
+      </c>
+      <c r="W11">
         <f t="shared" si="4"/>
-        <v>0.63388035997882475</v>
-      </c>
-      <c r="O11">
-        <v>0.24</v>
-      </c>
-      <c r="P11">
-        <v>54775</v>
-      </c>
-      <c r="Q11">
-        <v>12</v>
-      </c>
-      <c r="R11">
-        <f t="shared" si="2"/>
-        <v>0.52568776356693192</v>
-      </c>
-      <c r="S11">
-        <f t="shared" si="0"/>
         <v>0.4200635256749603</v>
       </c>
-      <c r="U11">
+      <c r="X11">
+        <f t="shared" si="5"/>
+        <v>0.48266905931242915</v>
+      </c>
+      <c r="Y11">
+        <f t="shared" si="10"/>
+        <v>23.732668977469672</v>
+      </c>
+      <c r="AA11">
         <v>2.2400000000000002</v>
       </c>
-      <c r="V11">
+      <c r="AB11">
         <v>94450</v>
       </c>
-      <c r="W11">
-        <v>12</v>
-      </c>
-      <c r="X11">
-        <f t="shared" si="3"/>
+      <c r="AC11">
+        <v>3981</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="6"/>
         <v>0.18213070322038741</v>
       </c>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11">
+        <f t="shared" si="11"/>
+        <v>0.10795239894219871</v>
+      </c>
+      <c r="AF11">
+        <f t="shared" si="12"/>
+        <v>23.725194674704849</v>
+      </c>
+      <c r="AH11" s="4">
+        <v>21.8</v>
+      </c>
+      <c r="AI11">
+        <v>105880</v>
+      </c>
+      <c r="AJ11">
+        <v>4462</v>
+      </c>
+      <c r="AK11" s="4">
+        <f t="shared" si="7"/>
+        <v>8.3155096421118263E-2</v>
+      </c>
+      <c r="AL11">
+        <f t="shared" si="13"/>
+        <v>23.729269385925594</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>8</v>
       </c>
@@ -24061,57 +28187,105 @@
         <v>370512</v>
       </c>
       <c r="G12">
+        <v>9406</v>
+      </c>
+      <c r="H12">
         <v>56</v>
       </c>
       <c r="I12">
+        <f t="shared" si="8"/>
+        <v>39.391027004039977</v>
+      </c>
+      <c r="K12">
         <v>0.6</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>111012</v>
       </c>
-      <c r="K12">
-        <v>56</v>
-      </c>
-      <c r="L12" s="4">
+      <c r="M12" s="6">
+        <v>3818</v>
+      </c>
+      <c r="N12" s="4">
+        <f t="shared" si="0"/>
+        <v>0.70038217385671719</v>
+      </c>
+      <c r="O12">
         <f t="shared" si="1"/>
-        <v>0.70038217385671719</v>
-      </c>
-      <c r="M12">
+        <v>0.60402636685309896</v>
+      </c>
+      <c r="P12">
+        <f t="shared" si="2"/>
+        <v>0.68408111692288431</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="9"/>
+        <v>29.075955997904661</v>
+      </c>
+      <c r="S12">
+        <v>0.97</v>
+      </c>
+      <c r="T12">
+        <v>117078</v>
+      </c>
+      <c r="U12">
+        <v>3972</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="3"/>
+        <v>0.68401023448633247</v>
+      </c>
+      <c r="W12">
         <f t="shared" si="4"/>
-        <v>0.60402636685309896</v>
-      </c>
-      <c r="O12">
-        <v>0.97</v>
-      </c>
-      <c r="P12">
-        <v>117078</v>
-      </c>
-      <c r="Q12">
-        <v>56</v>
-      </c>
-      <c r="R12">
-        <f t="shared" si="2"/>
-        <v>0.68401023448633247</v>
-      </c>
-      <c r="S12">
-        <f t="shared" si="0"/>
         <v>0.58238928204542861</v>
       </c>
-      <c r="U12">
+      <c r="X12">
+        <f t="shared" si="5"/>
+        <v>0.66681844311513572</v>
+      </c>
+      <c r="Y12">
+        <f t="shared" si="10"/>
+        <v>29.475830815709969</v>
+      </c>
+      <c r="AA12">
         <v>8.75</v>
       </c>
-      <c r="V12">
+      <c r="AB12">
         <v>280352</v>
       </c>
-      <c r="W12">
-        <v>56</v>
-      </c>
-      <c r="X12">
-        <f t="shared" si="3"/>
+      <c r="AC12">
+        <v>9117</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" si="6"/>
         <v>0.24333894718659585</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12">
+        <f t="shared" si="11"/>
+        <v>0.2021719209775921</v>
+      </c>
+      <c r="AF12">
+        <f t="shared" si="12"/>
+        <v>30.75046616211473</v>
+      </c>
+      <c r="AH12" s="4">
+        <v>79.099999999999994</v>
+      </c>
+      <c r="AI12">
+        <v>351394</v>
+      </c>
+      <c r="AJ12">
+        <v>8920</v>
+      </c>
+      <c r="AK12" s="4">
+        <f t="shared" si="7"/>
+        <v>5.1598868592650171E-2</v>
+      </c>
+      <c r="AL12">
+        <f t="shared" si="13"/>
+        <v>39.393946188340806</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>9</v>
       </c>
@@ -24128,57 +28302,105 @@
         <v>799008</v>
       </c>
       <c r="G13">
+        <v>13507</v>
+      </c>
+      <c r="H13">
         <v>122</v>
       </c>
       <c r="I13">
+        <f t="shared" si="8"/>
+        <v>59.155104760494559</v>
+      </c>
+      <c r="K13">
         <v>1.36</v>
       </c>
-      <c r="J13">
+      <c r="L13">
         <v>268814</v>
       </c>
-      <c r="K13">
-        <v>122</v>
-      </c>
-      <c r="L13" s="4">
+      <c r="M13" s="6">
+        <v>9544</v>
+      </c>
+      <c r="N13" s="4">
+        <f t="shared" si="0"/>
+        <v>0.66356532099803756</v>
+      </c>
+      <c r="O13">
         <f t="shared" si="1"/>
-        <v>0.66356532099803756</v>
-      </c>
-      <c r="M13">
+        <v>0.59456858794145684</v>
+      </c>
+      <c r="P13">
+        <f t="shared" si="2"/>
+        <v>0.63600837895403894</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="9"/>
+        <v>28.165758591785416</v>
+      </c>
+      <c r="S13">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="T13">
+        <v>268520</v>
+      </c>
+      <c r="U13">
+        <v>9439</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="3"/>
+        <v>0.66393327726380713</v>
+      </c>
+      <c r="W13">
         <f t="shared" si="4"/>
-        <v>0.59456858794145684</v>
-      </c>
-      <c r="O13">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="P13">
-        <v>268520</v>
-      </c>
-      <c r="Q13">
-        <v>122</v>
-      </c>
-      <c r="R13">
-        <f t="shared" si="2"/>
-        <v>0.66393327726380713</v>
-      </c>
-      <c r="S13">
-        <f t="shared" si="0"/>
         <v>0.59501200545373378</v>
       </c>
-      <c r="U13">
+      <c r="X13">
+        <f t="shared" si="5"/>
+        <v>0.63640647405543815</v>
+      </c>
+      <c r="Y13">
+        <f t="shared" si="10"/>
+        <v>28.447928806017586</v>
+      </c>
+      <c r="AA13">
         <v>20.100000000000001</v>
       </c>
-      <c r="V13">
+      <c r="AB13">
         <v>663032</v>
       </c>
-      <c r="W13">
-        <v>122</v>
-      </c>
-      <c r="X13">
-        <f t="shared" si="3"/>
+      <c r="AC13">
+        <v>13208</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="6"/>
         <v>0.17018102447034322</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13">
+        <f t="shared" si="11"/>
+        <v>0.1022115943167185</v>
+      </c>
+      <c r="AF13">
+        <f t="shared" si="12"/>
+        <v>50.199273167777108</v>
+      </c>
+      <c r="AH13" s="4">
+        <v>189.75</v>
+      </c>
+      <c r="AI13">
+        <v>738517</v>
+      </c>
+      <c r="AJ13">
+        <v>12484</v>
+      </c>
+      <c r="AK13" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5707627458047974E-2</v>
+      </c>
+      <c r="AL13">
+        <f t="shared" si="13"/>
+        <v>59.157081063761616</v>
+      </c>
+    </row>
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>10</v>
       </c>
@@ -24195,58 +28417,105 @@
         <v>923919</v>
       </c>
       <c r="G14">
+        <v>17566</v>
+      </c>
+      <c r="H14">
         <v>244</v>
       </c>
       <c r="I14">
+        <f t="shared" si="8"/>
+        <v>52.597005578959354</v>
+      </c>
+      <c r="K14">
         <v>2.4300000000000002</v>
       </c>
-      <c r="J14">
+      <c r="L14">
         <v>335135</v>
       </c>
-      <c r="K14">
-        <v>244</v>
-      </c>
-      <c r="L14" s="4">
+      <c r="M14" s="6">
+        <v>9372</v>
+      </c>
+      <c r="N14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.63726798561345743</v>
+      </c>
+      <c r="O14">
         <f t="shared" si="1"/>
-        <v>0.63726798561345743</v>
-      </c>
-      <c r="M14">
+        <v>0.5413946932687439</v>
+      </c>
+      <c r="P14">
+        <f t="shared" si="2"/>
+        <v>0.61640023899512164</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="9"/>
+        <v>35.759176269739648</v>
+      </c>
+      <c r="S14">
+        <v>3.88</v>
+      </c>
+      <c r="T14">
+        <v>334359</v>
+      </c>
+      <c r="U14">
+        <v>9357</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="3"/>
+        <v>0.63810788608092273</v>
+      </c>
+      <c r="W14">
         <f t="shared" si="4"/>
-        <v>0.5413946932687439</v>
-      </c>
-      <c r="O14">
-        <v>3.88</v>
-      </c>
-      <c r="P14">
-        <v>334359</v>
-      </c>
-      <c r="Q14">
-        <v>244</v>
-      </c>
-      <c r="R14">
-        <f t="shared" si="2"/>
-        <v>0.63810788608092273</v>
-      </c>
-      <c r="S14">
-        <f t="shared" si="0"/>
         <v>0.54245658688780329</v>
       </c>
-      <c r="U14">
+      <c r="X14">
+        <f t="shared" si="5"/>
+        <v>0.61728845841278857</v>
+      </c>
+      <c r="Y14">
+        <f t="shared" si="10"/>
+        <v>35.733568451426741</v>
+      </c>
+      <c r="AA14">
         <v>37.33</v>
       </c>
-      <c r="V14">
+      <c r="AB14">
         <v>730770</v>
       </c>
-      <c r="W14">
-        <v>244</v>
-      </c>
-      <c r="X14">
-        <f t="shared" si="3"/>
+      <c r="AC14">
+        <v>15894</v>
+      </c>
+      <c r="AD14">
+        <f t="shared" si="6"/>
         <v>0.20905404045159803</v>
       </c>
-      <c r="AD14" s="6"/>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14">
+        <f t="shared" si="11"/>
+        <v>0.16355141256647338</v>
+      </c>
+      <c r="AF14">
+        <f t="shared" si="12"/>
+        <v>45.97772744431861</v>
+      </c>
+      <c r="AH14" s="4">
+        <v>331.75</v>
+      </c>
+      <c r="AI14">
+        <v>873658</v>
+      </c>
+      <c r="AJ14">
+        <v>16610</v>
+      </c>
+      <c r="AK14" s="4">
+        <f t="shared" si="7"/>
+        <v>5.439979045782152E-2</v>
+      </c>
+      <c r="AL14">
+        <f t="shared" si="13"/>
+        <v>52.598314268512944</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>11</v>
       </c>
@@ -24263,58 +28532,105 @@
         <v>1079619</v>
       </c>
       <c r="G15">
+        <v>21412</v>
+      </c>
+      <c r="H15">
         <v>392</v>
       </c>
       <c r="I15">
+        <f t="shared" si="8"/>
+        <v>50.421212404259293</v>
+      </c>
+      <c r="K15">
         <v>3.8</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>316572</v>
       </c>
-      <c r="K15">
-        <v>392</v>
-      </c>
-      <c r="L15" s="4">
+      <c r="M15" s="6">
+        <v>10279</v>
+      </c>
+      <c r="N15" s="4">
+        <f t="shared" si="0"/>
+        <v>0.70677433427903735</v>
+      </c>
+      <c r="O15">
         <f t="shared" si="1"/>
-        <v>0.70677433427903735</v>
-      </c>
-      <c r="M15">
+        <v>0.6522570142426859</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="2"/>
+        <v>0.69807901759231528</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="9"/>
+        <v>30.797937542562504</v>
+      </c>
+      <c r="S15">
+        <v>6.13</v>
+      </c>
+      <c r="T15">
+        <v>315606</v>
+      </c>
+      <c r="U15">
+        <v>10259</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="3"/>
+        <v>0.70766909437496006</v>
+      </c>
+      <c r="W15">
         <f t="shared" si="4"/>
-        <v>0.6522570142426859</v>
-      </c>
-      <c r="O15">
-        <v>6.13</v>
-      </c>
-      <c r="P15">
-        <v>315606</v>
-      </c>
-      <c r="Q15">
-        <v>392</v>
-      </c>
-      <c r="R15">
-        <f t="shared" si="2"/>
-        <v>0.70766909437496006</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="0"/>
         <v>0.65331813058980936</v>
       </c>
-      <c r="U15">
+      <c r="X15">
+        <f t="shared" si="5"/>
+        <v>0.69900031091265258</v>
+      </c>
+      <c r="Y15">
+        <f t="shared" si="10"/>
+        <v>30.763817136173117</v>
+      </c>
+      <c r="AA15">
         <v>60.39</v>
       </c>
-      <c r="V15">
+      <c r="AB15">
         <v>910362</v>
       </c>
-      <c r="W15">
-        <v>392</v>
-      </c>
-      <c r="X15">
-        <f t="shared" si="3"/>
+      <c r="AC15">
+        <v>19235</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="6"/>
         <v>0.15677475109274661</v>
       </c>
-      <c r="AD15" s="6"/>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15">
+        <f t="shared" si="11"/>
+        <v>0.13176974152286161</v>
+      </c>
+      <c r="AF15">
+        <f t="shared" si="12"/>
+        <v>47.328411749415132</v>
+      </c>
+      <c r="AH15" s="4">
+        <v>541.70000000000005</v>
+      </c>
+      <c r="AI15">
+        <v>1048526</v>
+      </c>
+      <c r="AJ15">
+        <v>20795</v>
+      </c>
+      <c r="AK15" s="4">
+        <f t="shared" si="7"/>
+        <v>2.8799974805926904E-2</v>
+      </c>
+      <c r="AL15">
+        <f t="shared" si="13"/>
+        <v>50.422024525126233</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>12</v>
       </c>
@@ -24331,58 +28647,105 @@
         <v>3531509</v>
       </c>
       <c r="G16">
+        <v>39863</v>
+      </c>
+      <c r="H16">
         <v>1606</v>
       </c>
       <c r="I16">
+        <f t="shared" si="8"/>
+        <v>88.5911496876803</v>
+      </c>
+      <c r="K16">
         <v>15.53</v>
       </c>
-      <c r="J16">
+      <c r="L16">
         <v>861424</v>
       </c>
-      <c r="K16">
-        <v>1606</v>
-      </c>
-      <c r="L16" s="4">
+      <c r="M16" s="6">
+        <v>25724</v>
+      </c>
+      <c r="N16" s="4">
+        <f t="shared" si="0"/>
+        <v>0.75607481107934316</v>
+      </c>
+      <c r="O16">
         <f t="shared" si="1"/>
-        <v>0.75607481107934316</v>
-      </c>
-      <c r="M16">
+        <v>0.69484084980239957</v>
+      </c>
+      <c r="P16">
+        <f t="shared" si="2"/>
+        <v>0.74543395593003559</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="9"/>
+        <v>33.487171512983984</v>
+      </c>
+      <c r="S16">
+        <v>25.1</v>
+      </c>
+      <c r="T16">
+        <v>859044</v>
+      </c>
+      <c r="U16">
+        <v>24697</v>
+      </c>
+      <c r="V16">
+        <f t="shared" si="3"/>
+        <v>0.75674874395053215</v>
+      </c>
+      <c r="W16">
         <f t="shared" si="4"/>
-        <v>0.69484084980239957</v>
-      </c>
-      <c r="O16">
-        <v>25.1</v>
-      </c>
-      <c r="P16">
-        <v>859044</v>
-      </c>
-      <c r="Q16">
-        <v>1606</v>
-      </c>
-      <c r="R16">
-        <f t="shared" si="2"/>
-        <v>0.75674874395053215</v>
-      </c>
-      <c r="S16">
-        <f t="shared" si="0"/>
         <v>0.69568396396855958</v>
       </c>
-      <c r="U16">
+      <c r="X16">
+        <f t="shared" si="5"/>
+        <v>0.74613728806947743</v>
+      </c>
+      <c r="Y16">
+        <f t="shared" si="10"/>
+        <v>34.783334008179132</v>
+      </c>
+      <c r="AA16">
         <v>290.14</v>
       </c>
-      <c r="V16">
+      <c r="AB16">
         <v>2822868</v>
       </c>
-      <c r="W16">
-        <v>1606</v>
-      </c>
-      <c r="X16">
-        <f t="shared" si="3"/>
+      <c r="AC16">
+        <v>56864</v>
+      </c>
+      <c r="AD16">
+        <f t="shared" si="6"/>
         <v>0.20066237973625439</v>
       </c>
-      <c r="AD16" s="6"/>
-    </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE16">
+        <f t="shared" si="11"/>
+        <v>0.16579252529336042</v>
+      </c>
+      <c r="AF16">
+        <f t="shared" si="12"/>
+        <v>49.642445132245356</v>
+      </c>
+      <c r="AH16" s="4">
+        <v>2601.5499999999997</v>
+      </c>
+      <c r="AI16">
+        <v>3383892</v>
+      </c>
+      <c r="AJ16">
+        <v>38196</v>
+      </c>
+      <c r="AK16" s="4">
+        <f t="shared" si="7"/>
+        <v>4.1799978422821522E-2</v>
+      </c>
+      <c r="AL16">
+        <f t="shared" si="13"/>
+        <v>88.592836946277103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>13</v>
       </c>
@@ -24399,58 +28762,105 @@
         <v>5931296</v>
       </c>
       <c r="G17">
+        <v>57922</v>
+      </c>
+      <c r="H17">
         <v>3548</v>
       </c>
       <c r="I17">
+        <f t="shared" si="8"/>
+        <v>102.40143641448844</v>
+      </c>
+      <c r="K17">
         <v>35.65</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>1589216</v>
       </c>
-      <c r="K17">
-        <v>3548</v>
-      </c>
-      <c r="L17" s="4">
+      <c r="M17" s="6">
+        <v>36819</v>
+      </c>
+      <c r="N17" s="4">
+        <f t="shared" si="0"/>
+        <v>0.7320626048674691</v>
+      </c>
+      <c r="O17">
         <f t="shared" si="1"/>
-        <v>0.7320626048674691</v>
-      </c>
-      <c r="M17">
+        <v>0.64769768811140194</v>
+      </c>
+      <c r="P17">
+        <f t="shared" si="2"/>
+        <v>0.70412597865789006</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="9"/>
+        <v>43.162932181753987</v>
+      </c>
+      <c r="S17">
+        <v>57.41</v>
+      </c>
+      <c r="T17">
+        <v>1583008</v>
+      </c>
+      <c r="U17">
+        <v>35459</v>
+      </c>
+      <c r="V17">
+        <f t="shared" si="3"/>
+        <v>0.73310925639185764</v>
+      </c>
+      <c r="W17">
         <f t="shared" si="4"/>
-        <v>0.64769768811140194</v>
-      </c>
-      <c r="O17">
-        <v>57.41</v>
-      </c>
-      <c r="P17">
-        <v>1583008</v>
-      </c>
-      <c r="Q17">
-        <v>3548</v>
-      </c>
-      <c r="R17">
-        <f t="shared" si="2"/>
-        <v>0.73310925639185764</v>
-      </c>
-      <c r="S17">
-        <f t="shared" si="0"/>
         <v>0.64907389672760296</v>
       </c>
-      <c r="U17">
+      <c r="X17">
+        <f t="shared" si="5"/>
+        <v>0.70528175982576902</v>
+      </c>
+      <c r="Y17">
+        <f t="shared" si="10"/>
+        <v>44.643334555402014</v>
+      </c>
+      <c r="AA17">
         <v>749.64</v>
       </c>
-      <c r="V17">
+      <c r="AB17">
         <v>4510944</v>
       </c>
-      <c r="W17">
-        <v>3548</v>
-      </c>
-      <c r="X17">
-        <f t="shared" si="3"/>
+      <c r="AC17">
+        <v>84052</v>
+      </c>
+      <c r="AD17">
+        <f t="shared" si="6"/>
         <v>0.23946739464697092</v>
       </c>
-      <c r="AD17" s="6"/>
-    </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE17">
+        <f t="shared" si="11"/>
+        <v>0.16017008302895094</v>
+      </c>
+      <c r="AF17">
+        <f t="shared" si="12"/>
+        <v>53.668490934183602</v>
+      </c>
+      <c r="AH17" s="4">
+        <v>6781.25</v>
+      </c>
+      <c r="AI17">
+        <v>5371259</v>
+      </c>
+      <c r="AJ17">
+        <v>52452</v>
+      </c>
+      <c r="AK17" s="4">
+        <f t="shared" si="7"/>
+        <v>9.4420679730028642E-2</v>
+      </c>
+      <c r="AL17">
+        <f t="shared" si="13"/>
+        <v>102.40332113170136</v>
+      </c>
+    </row>
+    <row r="18" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>14</v>
       </c>
@@ -24467,57 +28877,105 @@
         <v>11862592</v>
       </c>
       <c r="G18">
+        <v>102556</v>
+      </c>
+      <c r="H18">
         <v>6100</v>
       </c>
       <c r="I18">
+        <f t="shared" si="8"/>
+        <v>115.66940988338078</v>
+      </c>
+      <c r="K18">
         <v>66.44</v>
       </c>
-      <c r="J18">
+      <c r="L18">
         <v>2744120</v>
       </c>
-      <c r="K18">
-        <v>6100</v>
-      </c>
-      <c r="L18" s="4">
+      <c r="M18" s="6">
+        <v>63724</v>
+      </c>
+      <c r="N18" s="4">
+        <f t="shared" si="0"/>
+        <v>0.76867450216613709</v>
+      </c>
+      <c r="O18">
         <f t="shared" si="1"/>
-        <v>0.76867450216613709</v>
-      </c>
-      <c r="M18">
+        <v>0.68604872530373229</v>
+      </c>
+      <c r="P18">
+        <f t="shared" si="2"/>
+        <v>0.75716407654483664</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="9"/>
+        <v>43.062582386541962</v>
+      </c>
+      <c r="S18">
+        <v>104.96</v>
+      </c>
+      <c r="T18">
+        <v>2840592</v>
+      </c>
+      <c r="U18">
+        <v>61558</v>
+      </c>
+      <c r="V18">
+        <f t="shared" si="3"/>
+        <v>0.76054204679719239</v>
+      </c>
+      <c r="W18">
         <f t="shared" si="4"/>
-        <v>0.68604872530373229</v>
-      </c>
-      <c r="O18">
-        <v>104.96</v>
-      </c>
-      <c r="P18">
-        <v>2840592</v>
-      </c>
-      <c r="Q18">
-        <v>6100</v>
-      </c>
-      <c r="R18">
-        <f t="shared" si="2"/>
-        <v>0.76054204679719239</v>
-      </c>
-      <c r="S18">
-        <f t="shared" si="0"/>
         <v>0.67501148663614552</v>
       </c>
-      <c r="U18">
+      <c r="X18">
+        <f t="shared" si="5"/>
+        <v>0.74862696183864064</v>
+      </c>
+      <c r="Y18">
+        <f t="shared" si="10"/>
+        <v>46.144968972351279</v>
+      </c>
+      <c r="AA18">
         <v>1209.1400000000001</v>
       </c>
-      <c r="V18">
+      <c r="AB18">
         <v>8740592</v>
       </c>
-      <c r="W18">
-        <v>6100</v>
-      </c>
-      <c r="X18">
-        <f t="shared" si="3"/>
+      <c r="AC18">
+        <v>125565</v>
+      </c>
+      <c r="AD18">
+        <f t="shared" si="6"/>
         <v>0.26318025605196571</v>
       </c>
-    </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE18">
+        <f t="shared" si="11"/>
+        <v>0.22651716037752964</v>
+      </c>
+      <c r="AF18">
+        <f t="shared" si="12"/>
+        <v>69.610098355433436</v>
+      </c>
+      <c r="AH18" s="4">
+        <v>11609.75</v>
+      </c>
+      <c r="AI18">
+        <v>11300305</v>
+      </c>
+      <c r="AJ18">
+        <v>97694</v>
+      </c>
+      <c r="AK18" s="4">
+        <f t="shared" si="7"/>
+        <v>4.7400011734366317E-2</v>
+      </c>
+      <c r="AL18">
+        <f t="shared" si="13"/>
+        <v>115.67040964644707</v>
+      </c>
+    </row>
+    <row r="19" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>15</v>
       </c>
@@ -24534,57 +28992,105 @@
         <v>12891294</v>
       </c>
       <c r="G19">
+        <v>110297</v>
+      </c>
+      <c r="H19">
         <v>9472</v>
       </c>
       <c r="I19">
+        <f t="shared" si="8"/>
+        <v>116.87801118797429</v>
+      </c>
+      <c r="K19">
         <v>109.15</v>
       </c>
-      <c r="J19">
+      <c r="L19">
         <v>4006876</v>
       </c>
-      <c r="K19">
-        <v>9472</v>
-      </c>
-      <c r="L19" s="4">
+      <c r="M19" s="6">
+        <v>84283</v>
+      </c>
+      <c r="N19" s="4">
+        <f t="shared" si="0"/>
+        <v>0.68917968979685051</v>
+      </c>
+      <c r="O19">
         <f t="shared" si="1"/>
-        <v>0.68917968979685051</v>
-      </c>
-      <c r="M19">
+        <v>0.61575619066907861</v>
+      </c>
+      <c r="P19">
+        <f t="shared" si="2"/>
+        <v>0.67047690055471298</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="9"/>
+        <v>47.540737752571694</v>
+      </c>
+      <c r="S19">
+        <v>168.04</v>
+      </c>
+      <c r="T19">
+        <v>3997952</v>
+      </c>
+      <c r="U19">
+        <v>83206</v>
+      </c>
+      <c r="V19">
+        <f t="shared" si="3"/>
+        <v>0.68987193993093321</v>
+      </c>
+      <c r="W19">
         <f t="shared" si="4"/>
-        <v>0.61575619066907861</v>
-      </c>
-      <c r="O19">
-        <v>168.04</v>
-      </c>
-      <c r="P19">
-        <v>3997952</v>
-      </c>
-      <c r="Q19">
-        <v>9472</v>
-      </c>
-      <c r="R19">
-        <f t="shared" si="2"/>
-        <v>0.68987193993093321</v>
-      </c>
-      <c r="S19">
-        <f t="shared" si="0"/>
         <v>0.61661196752727665</v>
       </c>
-      <c r="U19">
+      <c r="X19">
+        <f t="shared" si="5"/>
+        <v>0.6712108050078206</v>
+      </c>
+      <c r="Y19">
+        <f t="shared" si="10"/>
+        <v>48.048842631540992</v>
+      </c>
+      <c r="AA19">
         <v>1668.64</v>
       </c>
-      <c r="V19">
+      <c r="AB19">
         <v>10427952</v>
       </c>
-      <c r="W19">
-        <v>9472</v>
-      </c>
-      <c r="X19">
-        <f t="shared" si="3"/>
+      <c r="AC19">
+        <v>129221</v>
+      </c>
+      <c r="AD19">
+        <f t="shared" si="6"/>
         <v>0.19108570481753034</v>
       </c>
-    </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE19">
+        <f t="shared" si="11"/>
+        <v>0.14241142877726207</v>
+      </c>
+      <c r="AF19">
+        <f t="shared" si="12"/>
+        <v>80.698586143119158</v>
+      </c>
+      <c r="AH19" s="4">
+        <v>14829.849999999999</v>
+      </c>
+      <c r="AI19">
+        <v>12159621</v>
+      </c>
+      <c r="AJ19">
+        <v>104036</v>
+      </c>
+      <c r="AK19" s="4">
+        <f t="shared" si="7"/>
+        <v>5.6757141680268873E-2</v>
+      </c>
+      <c r="AL19">
+        <f t="shared" si="13"/>
+        <v>116.87897458572033</v>
+      </c>
+    </row>
+    <row r="20" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>16</v>
       </c>
@@ -24594,46 +29100,83 @@
       <c r="C20">
         <v>30000</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>13646</v>
       </c>
-      <c r="I20">
+      <c r="K20">
         <v>163.15</v>
       </c>
-      <c r="J20">
+      <c r="L20">
         <v>6156725</v>
       </c>
-      <c r="K20">
-        <v>13646</v>
-      </c>
-      <c r="M20">
+      <c r="M20" s="6">
+        <v>127413</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="1"/>
+        <v>0.52836154506374644</v>
+      </c>
+      <c r="P20">
+        <f t="shared" si="2"/>
+        <v>0.60366517616572668</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="9"/>
+        <v>48.321011199799081</v>
+      </c>
+      <c r="S20">
+        <v>253.59</v>
+      </c>
+      <c r="T20">
+        <v>6413256</v>
+      </c>
+      <c r="U20">
+        <v>126607</v>
+      </c>
+      <c r="W20">
         <f t="shared" si="4"/>
-        <v>0.52836154506374644</v>
-      </c>
-      <c r="O20">
-        <v>253.59</v>
-      </c>
-      <c r="P20">
-        <v>6413256</v>
-      </c>
-      <c r="Q20">
-        <v>13646</v>
-      </c>
-      <c r="S20">
-        <f t="shared" si="0"/>
         <v>0.50870988212878476</v>
       </c>
-      <c r="U20">
+      <c r="X20">
+        <f t="shared" si="5"/>
+        <v>0.58715117420964946</v>
+      </c>
+      <c r="Y20">
+        <f t="shared" si="10"/>
+        <v>50.654829511796343</v>
+      </c>
+      <c r="AA20">
         <v>2128.14</v>
       </c>
-      <c r="V20">
+      <c r="AB20">
         <v>13053908</v>
       </c>
-      <c r="W20">
-        <v>13646</v>
-      </c>
-    </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AC20">
+        <v>155867</v>
+      </c>
+      <c r="AE20">
+        <f t="shared" si="11"/>
+        <v>0.15966389151232019</v>
+      </c>
+      <c r="AF20">
+        <f t="shared" si="12"/>
+        <v>83.75029993520117</v>
+      </c>
+      <c r="AH20" s="4">
+        <v>18913.650000000001</v>
+      </c>
+      <c r="AI20">
+        <v>15534151</v>
+      </c>
+      <c r="AJ20">
+        <v>150000</v>
+      </c>
+      <c r="AL20">
+        <f t="shared" si="13"/>
+        <v>103.56100666666667</v>
+      </c>
+    </row>
+    <row r="21" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>17</v>
       </c>
@@ -24643,46 +29186,83 @@
       <c r="C21">
         <v>35000</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>18388</v>
       </c>
-      <c r="I21">
+      <c r="K21">
         <v>231.98</v>
       </c>
-      <c r="J21">
+      <c r="L21">
         <v>7832598</v>
       </c>
-      <c r="K21">
-        <v>18388</v>
-      </c>
-      <c r="M21">
+      <c r="M21" s="6">
+        <v>155445</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="1"/>
+        <v>0.5750799051359109</v>
+      </c>
+      <c r="P21">
+        <f t="shared" si="2"/>
+        <v>0.65453651067849239</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="9"/>
+        <v>50.388227347293252</v>
+      </c>
+      <c r="S21">
+        <v>357.76</v>
+      </c>
+      <c r="T21">
+        <v>8158958</v>
+      </c>
+      <c r="U21">
+        <v>154709</v>
+      </c>
+      <c r="W21">
         <f t="shared" si="4"/>
-        <v>0.5750799051359109</v>
-      </c>
-      <c r="O21">
-        <v>357.76</v>
-      </c>
-      <c r="P21">
-        <v>8158958</v>
-      </c>
-      <c r="Q21">
-        <v>18388</v>
-      </c>
-      <c r="S21">
-        <f t="shared" si="0"/>
         <v>0.55737480624537106</v>
       </c>
-      <c r="U21">
+      <c r="X21">
+        <f t="shared" si="5"/>
+        <v>0.6401421214381704</v>
+      </c>
+      <c r="Y21">
+        <f t="shared" si="10"/>
+        <v>52.737449017187103</v>
+      </c>
+      <c r="AA21">
         <v>2587.64</v>
       </c>
-      <c r="V21">
+      <c r="AB21">
         <v>18433108</v>
       </c>
-      <c r="W21">
-        <v>18388</v>
-      </c>
-    </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AC21">
+        <v>186291</v>
+      </c>
+      <c r="AE21">
+        <f t="shared" si="11"/>
+        <v>0.18699187565604714</v>
+      </c>
+      <c r="AF21">
+        <f t="shared" si="12"/>
+        <v>98.947925557326982</v>
+      </c>
+      <c r="AH21" s="4">
+        <v>25256.100000000002</v>
+      </c>
+      <c r="AI21">
+        <v>22672723</v>
+      </c>
+      <c r="AJ21">
+        <v>170660</v>
+      </c>
+      <c r="AL21">
+        <f t="shared" si="13"/>
+        <v>132.8531759053088</v>
+      </c>
+    </row>
+    <row r="22" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>18</v>
       </c>
@@ -24692,46 +29272,83 @@
       <c r="C22">
         <v>40000</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>23990</v>
       </c>
-      <c r="I22">
+      <c r="K22">
         <v>316.45999999999998</v>
       </c>
-      <c r="J22">
+      <c r="L22">
         <v>11825328</v>
       </c>
-      <c r="K22">
-        <v>23990</v>
-      </c>
-      <c r="M22">
+      <c r="M22" s="6">
+        <v>216196</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="1"/>
+        <v>0.57020981320619024</v>
+      </c>
+      <c r="P22">
+        <f t="shared" si="2"/>
+        <v>0.66752255561420182</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="9"/>
+        <v>54.697256193454088</v>
+      </c>
+      <c r="S22">
+        <v>496.71</v>
+      </c>
+      <c r="T22">
+        <v>12318050</v>
+      </c>
+      <c r="U22">
+        <v>219719</v>
+      </c>
+      <c r="W22">
         <f t="shared" si="4"/>
-        <v>0.57020981320619024</v>
-      </c>
-      <c r="O22">
-        <v>496.71</v>
-      </c>
-      <c r="P22">
-        <v>12318050</v>
-      </c>
-      <c r="Q22">
-        <v>23990</v>
-      </c>
-      <c r="S22">
-        <f t="shared" si="0"/>
         <v>0.55230188875644814</v>
       </c>
-      <c r="U22">
+      <c r="X22">
+        <f t="shared" si="5"/>
+        <v>0.65366932876479356</v>
+      </c>
+      <c r="Y22">
+        <f t="shared" si="10"/>
+        <v>56.062743777279159</v>
+      </c>
+      <c r="AA22">
         <v>3047.14</v>
       </c>
-      <c r="V22">
+      <c r="AB22">
         <v>27514188</v>
       </c>
-      <c r="W22">
-        <v>23990</v>
-      </c>
-    </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AC22">
+        <v>197895</v>
+      </c>
+      <c r="AE22">
+        <f t="shared" si="11"/>
+        <v>0.22641918172668052</v>
+      </c>
+      <c r="AF22">
+        <f t="shared" si="12"/>
+        <v>139.03427575229287</v>
+      </c>
+      <c r="AH22" s="4">
+        <v>28532.15</v>
+      </c>
+      <c r="AI22">
+        <v>35567309</v>
+      </c>
+      <c r="AJ22">
+        <v>195885</v>
+      </c>
+      <c r="AL22">
+        <f t="shared" si="13"/>
+        <v>181.57239706970927</v>
+      </c>
+    </row>
+    <row r="23" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>19</v>
       </c>
@@ -24741,46 +29358,83 @@
       <c r="C23">
         <v>45000</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>30476</v>
       </c>
-      <c r="I23">
+      <c r="K23">
         <v>415.75</v>
       </c>
-      <c r="J23">
+      <c r="L23">
         <v>25355318</v>
       </c>
-      <c r="K23">
-        <v>30476</v>
-      </c>
-      <c r="M23">
+      <c r="M23" s="6">
+        <v>420429</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="1"/>
+        <v>0.60378255634382039</v>
+      </c>
+      <c r="P23">
+        <f t="shared" si="2"/>
+        <v>0.67254756798749971</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="9"/>
+        <v>60.308204239003494</v>
+      </c>
+      <c r="S23">
+        <v>653.14</v>
+      </c>
+      <c r="T23">
+        <v>36411790</v>
+      </c>
+      <c r="U23">
+        <v>623069</v>
+      </c>
+      <c r="W23">
         <f t="shared" si="4"/>
-        <v>0.60378255634382039</v>
-      </c>
-      <c r="O23">
-        <v>653.14</v>
-      </c>
-      <c r="P23">
-        <v>36411790</v>
-      </c>
-      <c r="Q23">
-        <v>30476</v>
-      </c>
-      <c r="S23">
-        <f t="shared" si="0"/>
         <v>0.43100747729743932</v>
       </c>
-      <c r="U23">
+      <c r="X23">
+        <f t="shared" si="5"/>
+        <v>0.5297582467934957</v>
+      </c>
+      <c r="Y23">
+        <f t="shared" si="10"/>
+        <v>58.43941842717259</v>
+      </c>
+      <c r="AA23">
         <v>3506.64</v>
       </c>
-      <c r="V23">
+      <c r="AB23">
         <v>63993442</v>
       </c>
-      <c r="W23">
-        <v>30476</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AC23">
+        <v>294407</v>
+      </c>
+      <c r="AE23">
+        <f t="shared" si="11"/>
+        <v>0.17355372092943666</v>
+      </c>
+      <c r="AF23">
+        <f t="shared" si="12"/>
+        <v>217.36386023430148</v>
+      </c>
+      <c r="AH23" s="4">
+        <v>33112.9</v>
+      </c>
+      <c r="AI23">
+        <v>77432065</v>
+      </c>
+      <c r="AJ23">
+        <v>273766</v>
+      </c>
+      <c r="AL23">
+        <f t="shared" si="13"/>
+        <v>282.84032714069679</v>
+      </c>
+    </row>
+    <row r="24" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>20</v>
       </c>
@@ -24790,46 +29444,83 @@
       <c r="C24">
         <v>50000</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>37502</v>
       </c>
-      <c r="I24">
+      <c r="K24">
         <v>530.86</v>
       </c>
-      <c r="J24">
+      <c r="L24">
         <v>31567586</v>
       </c>
-      <c r="K24">
-        <v>37502</v>
-      </c>
-      <c r="M24">
+      <c r="M24" s="6">
+        <v>541163</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="1"/>
+        <v>0.61083766712761545</v>
+      </c>
+      <c r="P24">
+        <f t="shared" si="2"/>
+        <v>0.67424732297659173</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="9"/>
+        <v>58.332860894037474</v>
+      </c>
+      <c r="S24">
+        <v>860.19</v>
+      </c>
+      <c r="T24">
+        <v>32882904</v>
+      </c>
+      <c r="U24">
+        <v>559605</v>
+      </c>
+      <c r="W24">
         <f t="shared" si="4"/>
-        <v>0.61083766712761545</v>
-      </c>
-      <c r="O24">
-        <v>860.19</v>
-      </c>
-      <c r="P24">
-        <v>32882904</v>
-      </c>
-      <c r="Q24">
-        <v>37502</v>
-      </c>
-      <c r="S24">
-        <f t="shared" si="0"/>
         <v>0.59462254629610678</v>
       </c>
-      <c r="U24">
+      <c r="X24">
+        <f t="shared" si="5"/>
+        <v>0.6606742749887895</v>
+      </c>
+      <c r="Y24">
+        <f t="shared" si="10"/>
+        <v>58.760918862411877</v>
+      </c>
+      <c r="AA24">
         <v>3966.14</v>
       </c>
-      <c r="V24">
+      <c r="AB24">
         <v>81116756</v>
       </c>
-      <c r="W24">
-        <v>37502</v>
-      </c>
-    </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AC24">
+        <v>303410</v>
+      </c>
+      <c r="AE24">
+        <f t="shared" si="11"/>
+        <v>0.16293883167200007</v>
+      </c>
+      <c r="AF24">
+        <f t="shared" si="12"/>
+        <v>267.35030486800042</v>
+      </c>
+      <c r="AH24" s="4">
+        <v>39025.599999999999</v>
+      </c>
+      <c r="AI24">
+        <v>96906605</v>
+      </c>
+      <c r="AJ24">
+        <v>355000</v>
+      </c>
+      <c r="AL24">
+        <f t="shared" si="13"/>
+        <v>272.97635211267607</v>
+      </c>
+    </row>
+    <row r="25" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>21</v>
       </c>
@@ -24839,46 +29530,83 @@
       <c r="C25">
         <v>55000</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>44992</v>
       </c>
-      <c r="I25">
+      <c r="K25">
         <v>672.84</v>
       </c>
-      <c r="J25">
+      <c r="L25">
         <v>36707166</v>
       </c>
-      <c r="K25">
-        <v>44992</v>
-      </c>
-      <c r="M25">
+      <c r="M25" s="6">
+        <v>643411</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="1"/>
+        <v>0.58097829271440793</v>
+      </c>
+      <c r="P25">
+        <f t="shared" si="2"/>
+        <v>0.63243709953478622</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="9"/>
+        <v>57.050883494376066</v>
+      </c>
+      <c r="S25">
+        <v>1067.24</v>
+      </c>
+      <c r="T25">
+        <v>38236632</v>
+      </c>
+      <c r="U25">
+        <v>656499</v>
+      </c>
+      <c r="W25">
         <f t="shared" si="4"/>
-        <v>0.58097829271440793</v>
-      </c>
-      <c r="O25">
-        <v>1067.24</v>
-      </c>
-      <c r="P25">
-        <v>38236632</v>
-      </c>
-      <c r="Q25">
-        <v>44992</v>
-      </c>
-      <c r="S25">
-        <f t="shared" si="0"/>
         <v>0.56351904634939931</v>
       </c>
-      <c r="U25">
+      <c r="X25">
+        <f t="shared" si="5"/>
+        <v>0.61712197117203205</v>
+      </c>
+      <c r="Y25">
+        <f t="shared" si="10"/>
+        <v>58.243244848811649</v>
+      </c>
+      <c r="AA25">
         <v>4425.6400000000003</v>
       </c>
-      <c r="V25">
+      <c r="AB25">
         <v>87602063</v>
       </c>
-      <c r="W25">
-        <v>44992</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AC25">
+        <v>423297</v>
+      </c>
+      <c r="AE25">
+        <f t="shared" si="11"/>
+        <v>0.12280701912492008</v>
+      </c>
+      <c r="AF25">
+        <f t="shared" si="12"/>
+        <v>206.95176908884306</v>
+      </c>
+      <c r="AH25" s="4">
+        <v>41087.9</v>
+      </c>
+      <c r="AI25">
+        <v>99866352</v>
+      </c>
+      <c r="AJ25">
+        <v>342653</v>
+      </c>
+      <c r="AL25">
+        <f t="shared" si="13"/>
+        <v>291.45039442234565</v>
+      </c>
+    </row>
+    <row r="26" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>22</v>
       </c>
@@ -24888,57 +29616,96 @@
       <c r="C26">
         <v>60000</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>53644</v>
       </c>
-      <c r="I26">
+      <c r="K26">
         <v>838.03</v>
       </c>
-      <c r="J26">
+      <c r="L26">
         <v>43814448</v>
       </c>
-      <c r="K26">
-        <v>53644</v>
-      </c>
-      <c r="M26">
+      <c r="M26" s="6">
+        <v>793905</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="1"/>
+        <v>0.63567472170361794</v>
+      </c>
+      <c r="P26">
+        <f t="shared" si="2"/>
+        <v>0.70695987982414721</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="9"/>
+        <v>55.188527594611443</v>
+      </c>
+      <c r="S26">
+        <v>1874.29</v>
+      </c>
+      <c r="T26">
+        <v>45640047</v>
+      </c>
+      <c r="U26">
+        <v>789693</v>
+      </c>
+      <c r="W26">
         <f t="shared" si="4"/>
-        <v>0.63567472170361794</v>
-      </c>
-      <c r="O26">
-        <v>1874.29</v>
-      </c>
-      <c r="P26">
-        <v>45640047</v>
-      </c>
-      <c r="Q26">
-        <v>53644</v>
-      </c>
-      <c r="S26">
-        <f t="shared" si="0"/>
         <v>0.62049452672015959</v>
       </c>
-      <c r="U26">
+      <c r="X26">
+        <f t="shared" si="5"/>
+        <v>0.69474989488144256</v>
+      </c>
+      <c r="Y26">
+        <f t="shared" si="10"/>
+        <v>57.794670840440524</v>
+      </c>
+      <c r="AA26">
         <v>4885.1400000000003</v>
       </c>
-      <c r="V26">
+      <c r="AB26">
         <v>120261894</v>
       </c>
-      <c r="W26">
-        <v>53644</v>
+      <c r="AC26">
+        <v>564092</v>
+      </c>
+      <c r="AE26">
+        <f t="shared" si="11"/>
+        <v>0.19566349733915014</v>
+      </c>
+      <c r="AF26">
+        <f t="shared" si="12"/>
+        <v>213.19553193450713</v>
+      </c>
+      <c r="AH26" s="4">
+        <v>45354.6</v>
+      </c>
+      <c r="AI26">
+        <v>149516892</v>
+      </c>
+      <c r="AJ26">
+        <v>492560</v>
+      </c>
+      <c r="AL26">
+        <f t="shared" si="13"/>
+        <v>303.55061718369336</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="O2:R2"/>
-    <mergeCell ref="U2:X2"/>
+  <mergeCells count="5">
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="K2:O2"/>
+    <mergeCell ref="S2:W2"/>
+    <mergeCell ref="AA2:AE2"/>
+    <mergeCell ref="AH2:AL2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D91D38E-6269-3A4D-9F76-C5B55836BC8A}">
   <dimension ref="C5:V37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -25284,64 +30051,64 @@
       </c>
     </row>
     <row r="29" spans="3:22" x14ac:dyDescent="0.2">
-      <c r="I29" s="23" t="s">
+      <c r="I29" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="J29" s="23"/>
-      <c r="K29" s="23"/>
-      <c r="L29" s="23"/>
-      <c r="M29" s="24"/>
-      <c r="N29" s="23" t="s">
+      <c r="J29" s="47"/>
+      <c r="K29" s="47"/>
+      <c r="L29" s="47"/>
+      <c r="M29" s="21"/>
+      <c r="N29" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="O29" s="23"/>
-      <c r="P29" s="23"/>
-      <c r="Q29" s="23"/>
-      <c r="R29" s="24"/>
-      <c r="S29" s="23" t="s">
+      <c r="O29" s="47"/>
+      <c r="P29" s="47"/>
+      <c r="Q29" s="47"/>
+      <c r="R29" s="21"/>
+      <c r="S29" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="T29" s="23"/>
-      <c r="U29" s="23"/>
-      <c r="V29" s="23"/>
+      <c r="T29" s="47"/>
+      <c r="U29" s="47"/>
+      <c r="V29" s="47"/>
     </row>
     <row r="30" spans="3:22" x14ac:dyDescent="0.2">
-      <c r="I30" s="24" t="s">
+      <c r="I30" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J30" s="24" t="s">
+      <c r="J30" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="K30" s="24" t="s">
+      <c r="K30" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="L30" s="24" t="s">
+      <c r="L30" s="21" t="s">
         <v>24</v>
       </c>
       <c r="M30" s="17"/>
-      <c r="N30" s="24" t="s">
+      <c r="N30" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="O30" s="24" t="s">
+      <c r="O30" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="P30" s="24" t="s">
+      <c r="P30" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="Q30" s="24" t="s">
+      <c r="Q30" s="21" t="s">
         <v>24</v>
       </c>
       <c r="R30" s="17"/>
-      <c r="S30" s="24" t="s">
+      <c r="S30" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="T30" s="24" t="s">
+      <c r="T30" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="U30" s="24" t="s">
+      <c r="U30" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="V30" s="24" t="s">
+      <c r="V30" s="21" t="s">
         <v>24</v>
       </c>
     </row>
@@ -25574,42 +30341,42 @@
       </c>
     </row>
     <row r="37" spans="9:22" x14ac:dyDescent="0.2">
-      <c r="I37" s="25">
+      <c r="I37" s="22">
         <v>7</v>
       </c>
-      <c r="J37" s="25">
+      <c r="J37" s="22">
         <v>10</v>
       </c>
-      <c r="K37" s="25">
+      <c r="K37" s="22">
         <v>1000</v>
       </c>
-      <c r="L37" s="25">
+      <c r="L37" s="22">
         <v>12</v>
       </c>
-      <c r="M37" s="25"/>
-      <c r="N37" s="25">
+      <c r="M37" s="22"/>
+      <c r="N37" s="22">
         <v>14</v>
       </c>
-      <c r="O37" s="25">
+      <c r="O37" s="22">
         <v>10</v>
       </c>
-      <c r="P37" s="25">
+      <c r="P37" s="22">
         <v>20000</v>
       </c>
-      <c r="Q37" s="25">
+      <c r="Q37" s="22">
         <v>6100</v>
       </c>
-      <c r="R37" s="25"/>
-      <c r="S37" s="25">
+      <c r="R37" s="22"/>
+      <c r="S37" s="22">
         <v>21</v>
       </c>
-      <c r="T37" s="25">
+      <c r="T37" s="22">
         <v>10</v>
       </c>
-      <c r="U37" s="25">
+      <c r="U37" s="22">
         <v>55000</v>
       </c>
-      <c r="V37" s="25">
+      <c r="V37" s="22">
         <v>44992</v>
       </c>
     </row>
@@ -25623,1276 +30390,485 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4BCCACE-EA30-D046-B0A4-6BE1833C0F15}">
-  <dimension ref="A1:I19"/>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95737D00-8B32-3D46-AE69-173842C5D8C4}">
+  <dimension ref="E7:J30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="2.6640625" customWidth="1"/>
+    <col min="5" max="5" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="34" t="s">
+    <row r="7" spans="5:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
+      <c r="J7" s="33"/>
+    </row>
+    <row r="8" spans="5:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="E8" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-    </row>
-    <row r="3" spans="1:9" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="33"/>
-      <c r="B3" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="30" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="26">
+      <c r="F8" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" s="27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="5:10" x14ac:dyDescent="0.2">
+      <c r="E9">
         <v>1</v>
       </c>
-      <c r="B4" s="27">
-        <f>NetworkingLESS!L5</f>
-        <v>0.24545454545454545</v>
-      </c>
-      <c r="C4" s="27">
-        <f>NetworkingLESS!R5</f>
-        <v>0.24545454545454545</v>
-      </c>
-      <c r="D4" s="28">
-        <f>NetworkingLESS!X5</f>
-        <v>0.24545454545454545</v>
-      </c>
-      <c r="E4" s="28"/>
-      <c r="F4" s="22">
-        <f>NetworkingLESS!E5</f>
-        <v>0.02</v>
-      </c>
-      <c r="G4" s="22">
-        <f>NetworkingLESS!I5</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="22">
-        <f>NetworkingLESS!O5</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="22">
-        <f>NetworkingLESS!U5</f>
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="26">
+      <c r="F9" s="56">
+        <v>55.567</v>
+      </c>
+      <c r="G9" s="4">
+        <v>55.712328767123289</v>
+      </c>
+      <c r="H9" s="4">
+        <v>55.712328767123289</v>
+      </c>
+      <c r="I9" s="4">
+        <v>55.712328767123289</v>
+      </c>
+      <c r="J9" s="4">
+        <v>55.684210526315788</v>
+      </c>
+    </row>
+    <row r="10" spans="5:10" x14ac:dyDescent="0.2">
+      <c r="E10">
         <v>2</v>
       </c>
-      <c r="B5" s="27">
-        <f>NetworkingLESS!L6</f>
-        <v>0.60356652949245537</v>
-      </c>
-      <c r="C5" s="27">
-        <f>NetworkingLESS!R6</f>
-        <v>0.60356652949245537</v>
-      </c>
-      <c r="D5" s="28">
-        <f>NetworkingLESS!X6</f>
-        <v>0.19204389574759945</v>
-      </c>
-      <c r="E5" s="28"/>
-      <c r="F5" s="22">
-        <f>NetworkingLESS!E6</f>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G5" s="22">
-        <f>NetworkingLESS!I6</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="22">
-        <f>NetworkingLESS!O6</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="22">
-        <f>NetworkingLESS!U6</f>
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="26">
+      <c r="F10" s="56">
+        <v>28.588000000000001</v>
+      </c>
+      <c r="G10" s="4">
+        <v>28.613861386138613</v>
+      </c>
+      <c r="H10" s="4">
+        <v>28.613861386138613</v>
+      </c>
+      <c r="I10" s="4">
+        <v>28.592233009708739</v>
+      </c>
+      <c r="J10" s="4">
+        <v>28.677685950413224</v>
+      </c>
+    </row>
+    <row r="11" spans="5:10" x14ac:dyDescent="0.2">
+      <c r="E11">
         <v>3</v>
       </c>
-      <c r="B6" s="27">
-        <f>NetworkingLESS!L7</f>
-        <v>0.51855181431840469</v>
-      </c>
-      <c r="C6" s="27">
-        <f>NetworkingLESS!R7</f>
-        <v>0.40209218698921217</v>
-      </c>
-      <c r="D6" s="28">
-        <f>NetworkingLESS!X7</f>
-        <v>0.1443690748610657</v>
-      </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="22">
-        <f>NetworkingLESS!E7</f>
-        <v>0.1</v>
-      </c>
-      <c r="G6" s="22">
-        <f>NetworkingLESS!I7</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="22">
-        <f>NetworkingLESS!O7</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="22">
-        <f>NetworkingLESS!U7</f>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="26">
+      <c r="F11" s="56">
+        <v>49.042000000000002</v>
+      </c>
+      <c r="G11" s="4">
+        <v>49.091666666666669</v>
+      </c>
+      <c r="H11" s="4">
+        <v>49.100671140939596</v>
+      </c>
+      <c r="I11" s="4">
+        <v>49.037470725995313</v>
+      </c>
+      <c r="J11" s="4">
+        <v>49.087866108786613</v>
+      </c>
+    </row>
+    <row r="12" spans="5:10" x14ac:dyDescent="0.2">
+      <c r="E12">
         <v>4</v>
       </c>
-      <c r="B7" s="27">
-        <f>NetworkingLESS!L8</f>
-        <v>0.62927627095543137</v>
-      </c>
-      <c r="C7" s="27">
-        <f>NetworkingLESS!R8</f>
-        <v>0.46388169551587843</v>
-      </c>
-      <c r="D7" s="28">
-        <f>NetworkingLESS!X8</f>
-        <v>0.26298214529099084</v>
-      </c>
-      <c r="E7" s="28"/>
-      <c r="F7" s="22">
-        <f>NetworkingLESS!E8</f>
-        <v>0.27</v>
-      </c>
-      <c r="G7" s="22">
-        <f>NetworkingLESS!I8</f>
-        <v>0.02</v>
-      </c>
-      <c r="H7" s="22">
-        <f>NetworkingLESS!O8</f>
-        <v>0.05</v>
-      </c>
-      <c r="I7" s="22">
-        <f>NetworkingLESS!U8</f>
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="26">
+      <c r="F12" s="56">
+        <v>24.074999999999999</v>
+      </c>
+      <c r="G12" s="4">
+        <v>24.070796460176989</v>
+      </c>
+      <c r="H12" s="4">
+        <v>24.058103975535168</v>
+      </c>
+      <c r="I12" s="4">
+        <v>24.08685968819599</v>
+      </c>
+      <c r="J12" s="4">
+        <v>24.095697980684811</v>
+      </c>
+    </row>
+    <row r="13" spans="5:10" x14ac:dyDescent="0.2">
+      <c r="E13">
         <v>5</v>
       </c>
-      <c r="B8" s="27">
-        <f>NetworkingLESS!L9</f>
-        <v>0.68208098307816278</v>
-      </c>
-      <c r="C8" s="27">
-        <f>NetworkingLESS!R9</f>
-        <v>0.5952659145850121</v>
-      </c>
-      <c r="D8" s="28">
-        <f>NetworkingLESS!X9</f>
-        <v>0.17913980660757453</v>
-      </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="22">
-        <f>NetworkingLESS!E9</f>
-        <v>0.41</v>
-      </c>
-      <c r="G8" s="22">
-        <f>NetworkingLESS!I9</f>
-        <v>0.05</v>
-      </c>
-      <c r="H8" s="22">
-        <f>NetworkingLESS!O9</f>
-        <v>0.09</v>
-      </c>
-      <c r="I8" s="22">
-        <f>NetworkingLESS!U9</f>
-        <v>0.56999999999999995</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="26">
+      <c r="F13" s="56">
+        <v>57.923000000000002</v>
+      </c>
+      <c r="G13" s="4">
+        <v>57.913761467889906</v>
+      </c>
+      <c r="H13" s="4">
+        <v>57.899135446685882</v>
+      </c>
+      <c r="I13" s="4">
+        <v>57.921108742004265</v>
+      </c>
+      <c r="J13" s="4">
+        <v>57.940880503144655</v>
+      </c>
+    </row>
+    <row r="14" spans="5:10" x14ac:dyDescent="0.2">
+      <c r="E14">
         <v>6</v>
       </c>
-      <c r="B9" s="27">
-        <f>NetworkingLESS!L10</f>
-        <v>0.31385668008840178</v>
-      </c>
-      <c r="C9" s="27">
-        <f>NetworkingLESS!R10</f>
-        <v>0.31343283582089554</v>
-      </c>
-      <c r="D9" s="28">
-        <f>NetworkingLESS!X10</f>
-        <v>0.19297024007750296</v>
-      </c>
-      <c r="E9" s="28"/>
-      <c r="F9" s="22">
-        <f>NetworkingLESS!E10</f>
-        <v>0.63</v>
-      </c>
-      <c r="G9" s="22">
-        <f>NetworkingLESS!I10</f>
-        <v>0.1</v>
-      </c>
-      <c r="H9" s="22">
-        <f>NetworkingLESS!O10</f>
-        <v>0.19</v>
-      </c>
-      <c r="I9" s="22">
-        <f>NetworkingLESS!U10</f>
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="26">
+      <c r="F14" s="56">
+        <v>13.792</v>
+      </c>
+      <c r="G14" s="4">
+        <v>13.794278758368838</v>
+      </c>
+      <c r="H14" s="4">
+        <v>13.79440389294404</v>
+      </c>
+      <c r="I14" s="4">
+        <v>13.790481117434041</v>
+      </c>
+      <c r="J14" s="4">
+        <v>13.792730419731718</v>
+      </c>
+    </row>
+    <row r="15" spans="5:10" x14ac:dyDescent="0.2">
+      <c r="E15">
         <v>7</v>
       </c>
-      <c r="B10" s="27">
-        <f>NetworkingLESS!L11</f>
-        <v>0.70056198747867648</v>
-      </c>
-      <c r="C10" s="27">
-        <f>NetworkingLESS!R11</f>
-        <v>0.52568776356693192</v>
-      </c>
-      <c r="D10" s="28">
-        <f>NetworkingLESS!X11</f>
-        <v>0.18213070322038741</v>
-      </c>
-      <c r="E10" s="28"/>
-      <c r="F10" s="22">
-        <f>NetworkingLESS!E11</f>
-        <v>1.29</v>
-      </c>
-      <c r="G10" s="22">
-        <f>NetworkingLESS!I11</f>
-        <v>0.15</v>
-      </c>
-      <c r="H10" s="22">
-        <f>NetworkingLESS!O11</f>
-        <v>0.24</v>
-      </c>
-      <c r="I10" s="22">
-        <f>NetworkingLESS!U11</f>
-        <v>2.2400000000000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="26">
+      <c r="F15" s="56">
+        <v>23.728000000000002</v>
+      </c>
+      <c r="G15" s="4">
+        <v>23.733699382292382</v>
+      </c>
+      <c r="H15" s="4">
+        <v>23.732668977469672</v>
+      </c>
+      <c r="I15" s="4">
+        <v>23.725194674704849</v>
+      </c>
+      <c r="J15" s="4">
+        <v>23.729269385925594</v>
+      </c>
+    </row>
+    <row r="16" spans="5:10" x14ac:dyDescent="0.2">
+      <c r="E16">
         <v>8</v>
       </c>
-      <c r="B11" s="27">
-        <f>NetworkingLESS!L12</f>
-        <v>0.70038217385671719</v>
-      </c>
-      <c r="C11" s="27">
-        <f>NetworkingLESS!R12</f>
-        <v>0.68401023448633247</v>
-      </c>
-      <c r="D11" s="28">
-        <f>NetworkingLESS!X12</f>
-        <v>0.24333894718659585</v>
-      </c>
-      <c r="E11" s="28"/>
-      <c r="F11" s="22">
-        <f>NetworkingLESS!E12</f>
-        <v>4.26</v>
-      </c>
-      <c r="G11" s="22">
-        <f>NetworkingLESS!I12</f>
-        <v>0.6</v>
-      </c>
-      <c r="H11" s="22">
-        <f>NetworkingLESS!O12</f>
-        <v>0.97</v>
-      </c>
-      <c r="I11" s="22">
-        <f>NetworkingLESS!U12</f>
-        <v>8.75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="26">
+      <c r="F16" s="56">
+        <v>39.390999999999998</v>
+      </c>
+      <c r="G16" s="4">
+        <v>29.075955997904661</v>
+      </c>
+      <c r="H16" s="4">
+        <v>29.475830815709969</v>
+      </c>
+      <c r="I16" s="4">
+        <v>30.75046616211473</v>
+      </c>
+      <c r="J16" s="4">
+        <v>39.393946188340806</v>
+      </c>
+    </row>
+    <row r="17" spans="5:10" x14ac:dyDescent="0.2">
+      <c r="E17">
         <v>9</v>
       </c>
-      <c r="B12" s="27">
-        <f>NetworkingLESS!L13</f>
-        <v>0.66356532099803756</v>
-      </c>
-      <c r="C12" s="27">
-        <f>NetworkingLESS!R13</f>
-        <v>0.66393327726380713</v>
-      </c>
-      <c r="D12" s="28">
-        <f>NetworkingLESS!X13</f>
-        <v>0.17018102447034322</v>
-      </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="22">
-        <f>NetworkingLESS!E13</f>
-        <v>11.3</v>
-      </c>
-      <c r="G12" s="22">
-        <f>NetworkingLESS!I13</f>
-        <v>1.36</v>
-      </c>
-      <c r="H12" s="22">
-        <f>NetworkingLESS!O13</f>
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="I12" s="22">
-        <f>NetworkingLESS!U13</f>
-        <v>20.100000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="26">
+      <c r="F17" s="56">
+        <v>59.155000000000001</v>
+      </c>
+      <c r="G17" s="4">
+        <v>28.165758591785416</v>
+      </c>
+      <c r="H17" s="4">
+        <v>28.447928806017586</v>
+      </c>
+      <c r="I17" s="4">
+        <v>50.199273167777108</v>
+      </c>
+      <c r="J17" s="4">
+        <v>59.157081063761616</v>
+      </c>
+    </row>
+    <row r="18" spans="5:10" x14ac:dyDescent="0.2">
+      <c r="E18">
         <v>10</v>
       </c>
-      <c r="B13" s="27">
-        <f>NetworkingLESS!L14</f>
-        <v>0.63726798561345743</v>
-      </c>
-      <c r="C13" s="27">
-        <f>NetworkingLESS!R14</f>
-        <v>0.63810788608092273</v>
-      </c>
-      <c r="D13" s="28">
-        <f>NetworkingLESS!X14</f>
-        <v>0.20905404045159803</v>
-      </c>
-      <c r="E13" s="28"/>
-      <c r="F13" s="22">
-        <f>NetworkingLESS!E14</f>
-        <v>24.03</v>
-      </c>
-      <c r="G13" s="22">
-        <f>NetworkingLESS!I14</f>
-        <v>2.4300000000000002</v>
-      </c>
-      <c r="H13" s="22">
-        <f>NetworkingLESS!O14</f>
-        <v>3.88</v>
-      </c>
-      <c r="I13" s="22">
-        <f>NetworkingLESS!U14</f>
-        <v>37.33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="26">
+      <c r="F18" s="56">
+        <v>52.597000000000001</v>
+      </c>
+      <c r="G18" s="4">
+        <v>35.759176269739648</v>
+      </c>
+      <c r="H18" s="4">
+        <v>35.733568451426741</v>
+      </c>
+      <c r="I18" s="4">
+        <v>45.97772744431861</v>
+      </c>
+      <c r="J18" s="4">
+        <v>52.598314268512944</v>
+      </c>
+    </row>
+    <row r="19" spans="5:10" x14ac:dyDescent="0.2">
+      <c r="E19">
         <v>11</v>
       </c>
-      <c r="B14" s="27">
-        <f>NetworkingLESS!L15</f>
-        <v>0.70677433427903735</v>
-      </c>
-      <c r="C14" s="27">
-        <f>NetworkingLESS!R15</f>
-        <v>0.70766909437496006</v>
-      </c>
-      <c r="D14" s="28">
-        <f>NetworkingLESS!X15</f>
-        <v>0.15677475109274661</v>
-      </c>
-      <c r="E14" s="28"/>
-      <c r="F14" s="22">
-        <f>NetworkingLESS!E15</f>
-        <v>43.93</v>
-      </c>
-      <c r="G14" s="22">
-        <f>NetworkingLESS!I15</f>
-        <v>3.8</v>
-      </c>
-      <c r="H14" s="22">
-        <f>NetworkingLESS!O15</f>
-        <v>6.13</v>
-      </c>
-      <c r="I14" s="22">
-        <f>NetworkingLESS!U15</f>
-        <v>60.39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="26">
+      <c r="F19" s="56">
+        <v>50.420999999999999</v>
+      </c>
+      <c r="G19" s="4">
+        <v>30.797937542562504</v>
+      </c>
+      <c r="H19" s="4">
+        <v>30.763817136173117</v>
+      </c>
+      <c r="I19" s="4">
+        <v>47.328411749415132</v>
+      </c>
+      <c r="J19" s="4">
+        <v>50.422024525126233</v>
+      </c>
+    </row>
+    <row r="20" spans="5:10" x14ac:dyDescent="0.2">
+      <c r="E20">
         <v>12</v>
       </c>
-      <c r="B15" s="27">
-        <f>NetworkingLESS!L16</f>
-        <v>0.75607481107934316</v>
-      </c>
-      <c r="C15" s="27">
-        <f>NetworkingLESS!R16</f>
-        <v>0.75674874395053215</v>
-      </c>
-      <c r="D15" s="28">
-        <f>NetworkingLESS!X16</f>
-        <v>0.20066237973625439</v>
-      </c>
-      <c r="E15" s="28"/>
-      <c r="F15" s="22">
-        <f>NetworkingLESS!E16</f>
-        <v>309.95999999999998</v>
-      </c>
-      <c r="G15" s="22">
-        <f>NetworkingLESS!I16</f>
-        <v>15.53</v>
-      </c>
-      <c r="H15" s="22">
-        <f>NetworkingLESS!O16</f>
-        <v>25.1</v>
-      </c>
-      <c r="I15" s="22">
-        <f>NetworkingLESS!U16</f>
-        <v>290.14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="26">
+      <c r="F20" s="56">
+        <v>88.590999999999994</v>
+      </c>
+      <c r="G20" s="4">
+        <v>33.487171512983984</v>
+      </c>
+      <c r="H20" s="4">
+        <v>34.783334008179132</v>
+      </c>
+      <c r="I20" s="4">
+        <v>49.642445132245356</v>
+      </c>
+      <c r="J20" s="4">
+        <v>88.592836946277103</v>
+      </c>
+    </row>
+    <row r="21" spans="5:10" x14ac:dyDescent="0.2">
+      <c r="E21">
         <v>13</v>
       </c>
-      <c r="B16" s="27">
-        <f>NetworkingLESS!L17</f>
-        <v>0.7320626048674691</v>
-      </c>
-      <c r="C16" s="27">
-        <f>NetworkingLESS!R17</f>
-        <v>0.73310925639185764</v>
-      </c>
-      <c r="D16" s="28">
-        <f>NetworkingLESS!X17</f>
-        <v>0.23946739464697092</v>
-      </c>
-      <c r="E16" s="28"/>
-      <c r="F16" s="22">
-        <f>NetworkingLESS!E17</f>
-        <v>1732.32</v>
-      </c>
-      <c r="G16" s="22">
-        <f>NetworkingLESS!I17</f>
-        <v>35.65</v>
-      </c>
-      <c r="H16" s="22">
-        <f>NetworkingLESS!O17</f>
-        <v>57.41</v>
-      </c>
-      <c r="I16" s="22">
-        <f>NetworkingLESS!U17</f>
-        <v>749.64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" s="26">
+      <c r="F21" s="56">
+        <v>102.4</v>
+      </c>
+      <c r="G21" s="4">
+        <v>43.162932181753987</v>
+      </c>
+      <c r="H21" s="4">
+        <v>44.643334555402014</v>
+      </c>
+      <c r="I21" s="4">
+        <v>53.668490934183602</v>
+      </c>
+      <c r="J21" s="4">
+        <v>102.40332113170136</v>
+      </c>
+    </row>
+    <row r="22" spans="5:10" x14ac:dyDescent="0.2">
+      <c r="E22">
         <v>14</v>
       </c>
-      <c r="B17" s="27">
-        <f>NetworkingLESS!L18</f>
-        <v>0.76867450216613709</v>
-      </c>
-      <c r="C17" s="27">
-        <f>NetworkingLESS!R18</f>
-        <v>0.76054204679719239</v>
-      </c>
-      <c r="D17" s="28">
-        <f>NetworkingLESS!X18</f>
-        <v>0.26318025605196571</v>
-      </c>
-      <c r="E17" s="28"/>
-      <c r="F17" s="22">
-        <f>NetworkingLESS!E18</f>
-        <v>9234.91</v>
-      </c>
-      <c r="G17" s="22">
-        <f>NetworkingLESS!I18</f>
-        <v>66.44</v>
-      </c>
-      <c r="H17" s="22">
-        <f>NetworkingLESS!O18</f>
-        <v>104.96</v>
-      </c>
-      <c r="I17" s="22">
-        <f>NetworkingLESS!U18</f>
-        <v>1209.1400000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="25">
+      <c r="F22" s="56">
+        <v>115.67</v>
+      </c>
+      <c r="G22" s="4">
+        <v>43.062582386541962</v>
+      </c>
+      <c r="H22" s="4">
+        <v>46.144968972351279</v>
+      </c>
+      <c r="I22" s="4">
+        <v>69.610098355433436</v>
+      </c>
+      <c r="J22" s="4">
+        <v>115.67040964644707</v>
+      </c>
+    </row>
+    <row r="23" spans="5:10" x14ac:dyDescent="0.2">
+      <c r="E23">
         <v>15</v>
       </c>
-      <c r="B18" s="27">
-        <f>NetworkingLESS!L19</f>
-        <v>0.68917968979685051</v>
-      </c>
-      <c r="C18" s="27">
-        <f>NetworkingLESS!R19</f>
-        <v>0.68987193993093321</v>
-      </c>
-      <c r="D18" s="28">
-        <f>NetworkingLESS!X19</f>
-        <v>0.19108570481753034</v>
-      </c>
-      <c r="E18" s="28"/>
-      <c r="F18" s="22">
-        <f>NetworkingLESS!E19</f>
-        <v>50792.01</v>
-      </c>
-      <c r="G18" s="22">
-        <f>NetworkingLESS!I19</f>
-        <v>109.15</v>
-      </c>
-      <c r="H18" s="22">
-        <f>NetworkingLESS!O19</f>
-        <v>168.04</v>
-      </c>
-      <c r="I18" s="22">
-        <f>NetworkingLESS!U19</f>
-        <v>1668.64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="35">
-        <f t="shared" ref="B19:I19" si="0">AVERAGE(B4:B18)</f>
-        <v>0.62315534890154178</v>
-      </c>
-      <c r="C19" s="35">
-        <f t="shared" si="0"/>
-        <v>0.58555826338009809</v>
-      </c>
-      <c r="D19" s="35">
-        <f t="shared" si="0"/>
-        <v>0.2048556606475781</v>
-      </c>
-      <c r="E19" s="35"/>
-      <c r="F19" s="36">
-        <f t="shared" si="0"/>
-        <v>4143.7006666666666</v>
-      </c>
-      <c r="G19" s="36">
-        <f t="shared" si="0"/>
-        <v>15.685333333333334</v>
-      </c>
-      <c r="H19" s="36">
-        <f t="shared" si="0"/>
-        <v>24.616</v>
-      </c>
-      <c r="I19" s="36">
-        <f t="shared" si="0"/>
-        <v>269.90400000000005</v>
+      <c r="F23" s="56">
+        <v>116.88</v>
+      </c>
+      <c r="G23" s="4">
+        <v>47.540737752571694</v>
+      </c>
+      <c r="H23" s="4">
+        <v>48.048842631540992</v>
+      </c>
+      <c r="I23" s="4">
+        <v>80.698586143119158</v>
+      </c>
+      <c r="J23" s="4">
+        <v>116.87897458572033</v>
+      </c>
+    </row>
+    <row r="24" spans="5:10" x14ac:dyDescent="0.2">
+      <c r="E24">
+        <v>16</v>
+      </c>
+      <c r="F24" s="57" t="s">
+        <v>44</v>
+      </c>
+      <c r="G24" s="4">
+        <v>48.321011199799081</v>
+      </c>
+      <c r="H24" s="4">
+        <v>50.654829511796343</v>
+      </c>
+      <c r="I24" s="4">
+        <v>83.75029993520117</v>
+      </c>
+      <c r="J24" s="4">
+        <v>103.56100666666667</v>
+      </c>
+    </row>
+    <row r="25" spans="5:10" x14ac:dyDescent="0.2">
+      <c r="E25">
+        <v>17</v>
+      </c>
+      <c r="F25" s="57" t="s">
+        <v>44</v>
+      </c>
+      <c r="G25" s="4">
+        <v>50.388227347293252</v>
+      </c>
+      <c r="H25" s="4">
+        <v>52.737449017187103</v>
+      </c>
+      <c r="I25" s="4">
+        <v>98.947925557326982</v>
+      </c>
+      <c r="J25" s="4">
+        <v>132.8531759053088</v>
+      </c>
+    </row>
+    <row r="26" spans="5:10" x14ac:dyDescent="0.2">
+      <c r="E26">
+        <v>18</v>
+      </c>
+      <c r="F26" s="57" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" s="4">
+        <v>54.697256193454088</v>
+      </c>
+      <c r="H26" s="4">
+        <v>56.062743777279159</v>
+      </c>
+      <c r="I26" s="4">
+        <v>139.03427575229287</v>
+      </c>
+      <c r="J26" s="4">
+        <v>181.57239706970927</v>
+      </c>
+    </row>
+    <row r="27" spans="5:10" x14ac:dyDescent="0.2">
+      <c r="E27">
+        <v>19</v>
+      </c>
+      <c r="F27" s="57" t="s">
+        <v>44</v>
+      </c>
+      <c r="G27" s="4">
+        <v>60.308204239003494</v>
+      </c>
+      <c r="H27" s="4">
+        <v>58.43941842717259</v>
+      </c>
+      <c r="I27" s="4">
+        <v>217.36386023430148</v>
+      </c>
+      <c r="J27" s="4">
+        <v>282.84032714069679</v>
+      </c>
+    </row>
+    <row r="28" spans="5:10" x14ac:dyDescent="0.2">
+      <c r="E28">
+        <v>20</v>
+      </c>
+      <c r="F28" s="57" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" s="4">
+        <v>58.332860894037474</v>
+      </c>
+      <c r="H28" s="4">
+        <v>58.760918862411877</v>
+      </c>
+      <c r="I28" s="4">
+        <v>267.35030486800042</v>
+      </c>
+      <c r="J28" s="4">
+        <v>272.97635211267607</v>
+      </c>
+    </row>
+    <row r="29" spans="5:10" x14ac:dyDescent="0.2">
+      <c r="E29">
+        <v>21</v>
+      </c>
+      <c r="F29" s="57" t="s">
+        <v>44</v>
+      </c>
+      <c r="G29" s="4">
+        <v>57.050883494376066</v>
+      </c>
+      <c r="H29" s="4">
+        <v>58.243244848811649</v>
+      </c>
+      <c r="I29" s="4">
+        <v>206.95176908884306</v>
+      </c>
+      <c r="J29" s="4">
+        <v>291.45039442234565</v>
+      </c>
+    </row>
+    <row r="30" spans="5:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E30" s="33">
+        <v>22</v>
+      </c>
+      <c r="F30" s="58" t="s">
+        <v>44</v>
+      </c>
+      <c r="G30" s="59">
+        <v>55.188527594611443</v>
+      </c>
+      <c r="H30" s="59">
+        <v>57.794670840440524</v>
+      </c>
+      <c r="I30" s="59">
+        <v>213.19553193450713</v>
+      </c>
+      <c r="J30" s="59">
+        <v>303.55061718369336</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="F2:I2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D29F935A-7EB1-C14F-935D-FC60577D8149}">
-  <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="3.33203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9"/>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-    </row>
-    <row r="3" spans="1:7" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="48"/>
-      <c r="B3" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="31" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="51">
-        <v>1</v>
-      </c>
-      <c r="B4" s="44">
-        <f>NetworkingLESS!M5</f>
-        <v>0</v>
-      </c>
-      <c r="C4" s="44">
-        <f>NetworkingLESS!S5</f>
-        <v>0</v>
-      </c>
-      <c r="D4" s="29"/>
-      <c r="E4" s="53">
-        <f>NetworkingLESS!I5</f>
-        <v>0</v>
-      </c>
-      <c r="F4" s="22">
-        <f>NetworkingLESS!O5</f>
-        <v>0</v>
-      </c>
-      <c r="G4" s="22">
-        <f>NetworkingLESS!U5</f>
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="9">
-        <v>2</v>
-      </c>
-      <c r="B5" s="44">
-        <f>NetworkingLESS!M6</f>
-        <v>0.50933786078098475</v>
-      </c>
-      <c r="C5" s="44">
-        <f>NetworkingLESS!S6</f>
-        <v>0.50933786078098475</v>
-      </c>
-      <c r="D5" s="29"/>
-      <c r="E5" s="53">
-        <f>NetworkingLESS!I6</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="22">
-        <f>NetworkingLESS!O6</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="22">
-        <f>NetworkingLESS!U6</f>
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="9">
-        <v>3</v>
-      </c>
-      <c r="B6" s="44">
-        <f>NetworkingLESS!M7</f>
-        <v>0.43731792349204834</v>
-      </c>
-      <c r="C6" s="44">
-        <f>NetworkingLESS!S7</f>
-        <v>0.30120827164621045</v>
-      </c>
-      <c r="D6" s="29"/>
-      <c r="E6" s="53">
-        <f>NetworkingLESS!I7</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="22">
-        <f>NetworkingLESS!O7</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="22">
-        <f>NetworkingLESS!U7</f>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="9">
-        <v>4</v>
-      </c>
-      <c r="B7" s="44">
-        <f>NetworkingLESS!M8</f>
-        <v>0.49699491447064265</v>
-      </c>
-      <c r="C7" s="44">
-        <f>NetworkingLESS!S8</f>
-        <v>0.27258437355524734</v>
-      </c>
-      <c r="D7" s="29"/>
-      <c r="E7" s="53">
-        <f>NetworkingLESS!I8</f>
-        <v>0.02</v>
-      </c>
-      <c r="F7" s="22">
-        <f>NetworkingLESS!O8</f>
-        <v>0.05</v>
-      </c>
-      <c r="G7" s="22">
-        <f>NetworkingLESS!U8</f>
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="9">
-        <v>5</v>
-      </c>
-      <c r="B8" s="44">
-        <f>NetworkingLESS!M9</f>
-        <v>0.61270016565433461</v>
-      </c>
-      <c r="C8" s="44">
-        <f>NetworkingLESS!S9</f>
-        <v>0.50693907601693355</v>
-      </c>
-      <c r="D8" s="29"/>
-      <c r="E8" s="53">
-        <f>NetworkingLESS!I9</f>
-        <v>0.05</v>
-      </c>
-      <c r="F8" s="22">
-        <f>NetworkingLESS!O9</f>
-        <v>0.09</v>
-      </c>
-      <c r="G8" s="22">
-        <f>NetworkingLESS!U9</f>
-        <v>0.56999999999999995</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="50">
-        <v>6</v>
-      </c>
-      <c r="B9" s="44">
-        <f>NetworkingLESS!M10</f>
-        <v>0.14979179952732866</v>
-      </c>
-      <c r="C9" s="44">
-        <f>NetworkingLESS!S10</f>
-        <v>0.14926660914581535</v>
-      </c>
-      <c r="D9" s="29"/>
-      <c r="E9" s="53">
-        <f>NetworkingLESS!I10</f>
-        <v>0.1</v>
-      </c>
-      <c r="F9" s="22">
-        <f>NetworkingLESS!O10</f>
-        <v>0.19</v>
-      </c>
-      <c r="G9" s="22">
-        <f>NetworkingLESS!U10</f>
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="50">
-        <v>7</v>
-      </c>
-      <c r="B10" s="44">
-        <f>NetworkingLESS!M11</f>
-        <v>0.63388035997882475</v>
-      </c>
-      <c r="C10" s="44">
-        <f>NetworkingLESS!S11</f>
-        <v>0.4200635256749603</v>
-      </c>
-      <c r="D10" s="29"/>
-      <c r="E10" s="53">
-        <f>NetworkingLESS!I11</f>
-        <v>0.15</v>
-      </c>
-      <c r="F10" s="22">
-        <f>NetworkingLESS!O11</f>
-        <v>0.24</v>
-      </c>
-      <c r="G10" s="22">
-        <f>NetworkingLESS!U11</f>
-        <v>2.2400000000000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="50">
-        <v>8</v>
-      </c>
-      <c r="B11" s="44">
-        <f>NetworkingLESS!M12</f>
-        <v>0.60402636685309896</v>
-      </c>
-      <c r="C11" s="44">
-        <f>NetworkingLESS!S12</f>
-        <v>0.58238928204542861</v>
-      </c>
-      <c r="D11" s="29"/>
-      <c r="E11" s="53">
-        <f>NetworkingLESS!I12</f>
-        <v>0.6</v>
-      </c>
-      <c r="F11" s="22">
-        <f>NetworkingLESS!O12</f>
-        <v>0.97</v>
-      </c>
-      <c r="G11" s="22">
-        <f>NetworkingLESS!U12</f>
-        <v>8.75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="50">
-        <v>9</v>
-      </c>
-      <c r="B12" s="44">
-        <f>NetworkingLESS!M13</f>
-        <v>0.59456858794145684</v>
-      </c>
-      <c r="C12" s="44">
-        <f>NetworkingLESS!S13</f>
-        <v>0.59501200545373378</v>
-      </c>
-      <c r="D12" s="29"/>
-      <c r="E12" s="53">
-        <f>NetworkingLESS!I13</f>
-        <v>1.36</v>
-      </c>
-      <c r="F12" s="22">
-        <f>NetworkingLESS!O13</f>
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="G12" s="22">
-        <f>NetworkingLESS!U13</f>
-        <v>20.100000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="50">
-        <v>10</v>
-      </c>
-      <c r="B13" s="44">
-        <f>NetworkingLESS!M14</f>
-        <v>0.5413946932687439</v>
-      </c>
-      <c r="C13" s="44">
-        <f>NetworkingLESS!S14</f>
-        <v>0.54245658688780329</v>
-      </c>
-      <c r="D13" s="29"/>
-      <c r="E13" s="53">
-        <f>NetworkingLESS!I14</f>
-        <v>2.4300000000000002</v>
-      </c>
-      <c r="F13" s="22">
-        <f>NetworkingLESS!O14</f>
-        <v>3.88</v>
-      </c>
-      <c r="G13" s="22">
-        <f>NetworkingLESS!U14</f>
-        <v>37.33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="50">
-        <v>11</v>
-      </c>
-      <c r="B14" s="44">
-        <f>NetworkingLESS!M15</f>
-        <v>0.6522570142426859</v>
-      </c>
-      <c r="C14" s="44">
-        <f>NetworkingLESS!S15</f>
-        <v>0.65331813058980936</v>
-      </c>
-      <c r="D14" s="29"/>
-      <c r="E14" s="53">
-        <f>NetworkingLESS!I15</f>
-        <v>3.8</v>
-      </c>
-      <c r="F14" s="22">
-        <f>NetworkingLESS!O15</f>
-        <v>6.13</v>
-      </c>
-      <c r="G14" s="22">
-        <f>NetworkingLESS!U15</f>
-        <v>60.39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="50">
-        <v>12</v>
-      </c>
-      <c r="B15" s="44">
-        <f>NetworkingLESS!M16</f>
-        <v>0.69484084980239957</v>
-      </c>
-      <c r="C15" s="44">
-        <f>NetworkingLESS!S16</f>
-        <v>0.69568396396855958</v>
-      </c>
-      <c r="D15" s="29"/>
-      <c r="E15" s="53">
-        <f>NetworkingLESS!I16</f>
-        <v>15.53</v>
-      </c>
-      <c r="F15" s="22">
-        <f>NetworkingLESS!O16</f>
-        <v>25.1</v>
-      </c>
-      <c r="G15" s="22">
-        <f>NetworkingLESS!U16</f>
-        <v>290.14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="50">
-        <v>13</v>
-      </c>
-      <c r="B16" s="44">
-        <f>NetworkingLESS!M17</f>
-        <v>0.64769768811140194</v>
-      </c>
-      <c r="C16" s="44">
-        <f>NetworkingLESS!S17</f>
-        <v>0.64907389672760296</v>
-      </c>
-      <c r="D16" s="29"/>
-      <c r="E16" s="53">
-        <f>NetworkingLESS!I17</f>
-        <v>35.65</v>
-      </c>
-      <c r="F16" s="22">
-        <f>NetworkingLESS!O17</f>
-        <v>57.41</v>
-      </c>
-      <c r="G16" s="22">
-        <f>NetworkingLESS!U17</f>
-        <v>749.64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="9">
-        <v>14</v>
-      </c>
-      <c r="B17" s="44">
-        <f>NetworkingLESS!M18</f>
-        <v>0.68604872530373229</v>
-      </c>
-      <c r="C17" s="44">
-        <f>NetworkingLESS!S18</f>
-        <v>0.67501148663614552</v>
-      </c>
-      <c r="D17" s="29"/>
-      <c r="E17" s="53">
-        <f>NetworkingLESS!I18</f>
-        <v>66.44</v>
-      </c>
-      <c r="F17" s="22">
-        <f>NetworkingLESS!O18</f>
-        <v>104.96</v>
-      </c>
-      <c r="G17" s="22">
-        <f>NetworkingLESS!U18</f>
-        <v>1209.1400000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="50">
-        <v>15</v>
-      </c>
-      <c r="B18" s="44">
-        <f>NetworkingLESS!M19</f>
-        <v>0.61575619066907861</v>
-      </c>
-      <c r="C18" s="44">
-        <f>NetworkingLESS!S19</f>
-        <v>0.61661196752727665</v>
-      </c>
-      <c r="D18" s="29"/>
-      <c r="E18" s="53">
-        <f>NetworkingLESS!I19</f>
-        <v>109.15</v>
-      </c>
-      <c r="F18" s="22">
-        <f>NetworkingLESS!O19</f>
-        <v>168.04</v>
-      </c>
-      <c r="G18" s="22">
-        <f>NetworkingLESS!U19</f>
-        <v>1668.64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="54" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="46">
-        <f>AVERAGE(B4:B18)</f>
-        <v>0.52510754267311743</v>
-      </c>
-      <c r="C19" s="46">
-        <f>AVERAGE(C4:C18)</f>
-        <v>0.47793046911043408</v>
-      </c>
-      <c r="D19" s="46"/>
-      <c r="E19" s="52">
-        <f>AVERAGE(E4:E18)</f>
-        <v>15.685333333333334</v>
-      </c>
-      <c r="F19" s="52">
-        <f>AVERAGE(F4:F18)</f>
-        <v>24.616</v>
-      </c>
-      <c r="G19" s="52">
-        <f>AVERAGE(G4:G18)</f>
-        <v>269.90400000000005</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="50">
-        <v>16</v>
-      </c>
-      <c r="B20" s="44">
-        <f>NetworkingLESS!M20</f>
-        <v>0.52836154506374644</v>
-      </c>
-      <c r="C20" s="44">
-        <f>NetworkingLESS!S20</f>
-        <v>0.50870988212878476</v>
-      </c>
-      <c r="D20" s="44"/>
-      <c r="E20" s="53">
-        <f>NetworkingLESS!I20</f>
-        <v>163.15</v>
-      </c>
-      <c r="F20" s="22">
-        <f>NetworkingLESS!O20</f>
-        <v>253.59</v>
-      </c>
-      <c r="G20" s="22">
-        <f>NetworkingLESS!U20</f>
-        <v>2128.14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="50">
-        <v>17</v>
-      </c>
-      <c r="B21" s="44">
-        <f>NetworkingLESS!M21</f>
-        <v>0.5750799051359109</v>
-      </c>
-      <c r="C21" s="44">
-        <f>NetworkingLESS!S21</f>
-        <v>0.55737480624537106</v>
-      </c>
-      <c r="D21" s="44"/>
-      <c r="E21" s="53">
-        <f>NetworkingLESS!I21</f>
-        <v>231.98</v>
-      </c>
-      <c r="F21" s="22">
-        <f>NetworkingLESS!O21</f>
-        <v>357.76</v>
-      </c>
-      <c r="G21" s="22">
-        <f>NetworkingLESS!U21</f>
-        <v>2587.64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="50">
-        <v>18</v>
-      </c>
-      <c r="B22" s="44">
-        <f>NetworkingLESS!M22</f>
-        <v>0.57020981320619024</v>
-      </c>
-      <c r="C22" s="44">
-        <f>NetworkingLESS!S22</f>
-        <v>0.55230188875644814</v>
-      </c>
-      <c r="D22" s="44"/>
-      <c r="E22" s="53">
-        <f>NetworkingLESS!I22</f>
-        <v>316.45999999999998</v>
-      </c>
-      <c r="F22" s="22">
-        <f>NetworkingLESS!O22</f>
-        <v>496.71</v>
-      </c>
-      <c r="G22" s="22">
-        <f>NetworkingLESS!U22</f>
-        <v>3047.14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="50">
-        <v>19</v>
-      </c>
-      <c r="B23" s="44">
-        <f>NetworkingLESS!M23</f>
-        <v>0.60378255634382039</v>
-      </c>
-      <c r="C23" s="44">
-        <f>NetworkingLESS!S23</f>
-        <v>0.43100747729743932</v>
-      </c>
-      <c r="D23" s="44"/>
-      <c r="E23" s="53">
-        <f>NetworkingLESS!I23</f>
-        <v>415.75</v>
-      </c>
-      <c r="F23" s="22">
-        <f>NetworkingLESS!O23</f>
-        <v>653.14</v>
-      </c>
-      <c r="G23" s="22">
-        <f>NetworkingLESS!U23</f>
-        <v>3506.64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="9">
-        <v>20</v>
-      </c>
-      <c r="B24" s="44">
-        <f>NetworkingLESS!M24</f>
-        <v>0.61083766712761545</v>
-      </c>
-      <c r="C24" s="44">
-        <f>NetworkingLESS!S24</f>
-        <v>0.59462254629610678</v>
-      </c>
-      <c r="D24" s="44"/>
-      <c r="E24" s="53">
-        <f>NetworkingLESS!I24</f>
-        <v>530.86</v>
-      </c>
-      <c r="F24" s="22">
-        <f>NetworkingLESS!O24</f>
-        <v>860.19</v>
-      </c>
-      <c r="G24" s="22">
-        <f>NetworkingLESS!U24</f>
-        <v>3966.14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="45">
-        <v>21</v>
-      </c>
-      <c r="B25" s="44">
-        <f>NetworkingLESS!M25</f>
-        <v>0.58097829271440793</v>
-      </c>
-      <c r="C25" s="44">
-        <f>NetworkingLESS!S25</f>
-        <v>0.56351904634939931</v>
-      </c>
-      <c r="D25" s="44"/>
-      <c r="E25" s="53">
-        <f>NetworkingLESS!I25</f>
-        <v>672.84</v>
-      </c>
-      <c r="F25" s="22">
-        <f>NetworkingLESS!O25</f>
-        <v>1067.24</v>
-      </c>
-      <c r="G25" s="22">
-        <f>NetworkingLESS!U25</f>
-        <v>4425.6400000000003</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="42" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="46">
-        <f>AVERAGE(B20:B25)</f>
-        <v>0.57820829659861517</v>
-      </c>
-      <c r="C26" s="46">
-        <f>AVERAGE(C20:C25)</f>
-        <v>0.53458927451225824</v>
-      </c>
-      <c r="D26" s="46"/>
-      <c r="E26" s="52">
-        <f>AVERAGE(E20:E25)</f>
-        <v>388.50666666666666</v>
-      </c>
-      <c r="F26" s="52">
-        <f>AVERAGE(F20:F25)</f>
-        <v>614.77166666666665</v>
-      </c>
-      <c r="G26" s="52">
-        <f>AVERAGE(G20:G25)</f>
-        <v>3276.89</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:G2"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/All_perf.xlsx
+++ b/All_perf.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10329"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ttdkoc/Documents/dev/workspaces/python/copt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918BE3DF-5DF5-4943-91DA-9F177CA705BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED7288C-5F95-D54B-9213-6266013E6BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20440" activeTab="8" xr2:uid="{544C10BC-9448-4CAA-97CB-C174D9523FCA}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20440" activeTab="6" xr2:uid="{544C10BC-9448-4CAA-97CB-C174D9523FCA}"/>
   </bookViews>
   <sheets>
     <sheet name="loose channel" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="52">
   <si>
     <t>Exact</t>
   </si>
@@ -198,6 +198,15 @@
   <si>
     <t>SA+Agg+
 Grdy©</t>
+  </si>
+  <si>
+    <t>Exact/NO - NET</t>
+  </si>
+  <si>
+    <t>Net Ratio</t>
+  </si>
+  <si>
+    <t>SA+Greed With Alg-C/NO - NET</t>
   </si>
 </sst>
 </file>
@@ -497,6 +506,14 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -527,14 +544,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -1384,7 +1393,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-TR"/>
+          <a:endParaRPr lang="tr-TR"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -16910,27 +16919,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="F1" s="46" t="s">
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="F1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="J1" s="46" t="s">
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="J1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="N1" s="46" t="s">
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="N1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="O1" s="46"/>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="46"/>
+      <c r="O1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
     </row>
     <row r="2" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B2">
@@ -18881,41 +18890,41 @@
       <c r="V1" s="33"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
       <c r="E2" s="32"/>
-      <c r="F2" s="50" t="s">
+      <c r="F2" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="L2" s="48" t="s">
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="L2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="51" t="s">
+      <c r="M2" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
       <c r="Q2" s="32"/>
-      <c r="R2" s="50" t="s">
+      <c r="R2" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
-      <c r="U2" s="50"/>
-      <c r="V2" s="50"/>
+      <c r="S2" s="54"/>
+      <c r="T2" s="54"/>
+      <c r="U2" s="54"/>
+      <c r="V2" s="54"/>
     </row>
     <row r="3" spans="1:22" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="49"/>
+      <c r="A3" s="53"/>
       <c r="B3" s="26" t="s">
         <v>31</v>
       </c>
@@ -18938,7 +18947,7 @@
       <c r="I3" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="L3" s="49"/>
+      <c r="L3" s="53"/>
       <c r="M3" s="27" t="s">
         <v>37</v>
       </c>
@@ -20163,24 +20172,24 @@
       <c r="I25" s="33"/>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A26" s="48" t="s">
+      <c r="A26" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B26" s="52" t="s">
+      <c r="B26" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="52"/>
-      <c r="D26" s="52"/>
+      <c r="C26" s="56"/>
+      <c r="D26" s="56"/>
       <c r="E26" s="32"/>
-      <c r="F26" s="50" t="s">
+      <c r="F26" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="G26" s="50"/>
-      <c r="H26" s="50"/>
-      <c r="I26" s="50"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
     </row>
     <row r="27" spans="1:22" ht="32" x14ac:dyDescent="0.2">
-      <c r="A27" s="49"/>
+      <c r="A27" s="53"/>
       <c r="B27" s="26" t="s">
         <v>31</v>
       </c>
@@ -20798,37 +20807,37 @@
       <c r="S1" s="34"/>
     </row>
     <row r="2" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="51"/>
+      <c r="C2" s="55"/>
       <c r="D2" s="32"/>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="K2" s="53" t="s">
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="K2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="55" t="s">
+      <c r="L2" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
       <c r="O2" s="32"/>
-      <c r="P2" s="51" t="s">
+      <c r="P2" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="55"/>
+      <c r="S2" s="55"/>
     </row>
     <row r="3" spans="1:19" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="54"/>
+      <c r="A3" s="58"/>
       <c r="B3" s="27" t="s">
         <v>31</v>
       </c>
@@ -20845,7 +20854,7 @@
       <c r="G3" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="K3" s="54"/>
+      <c r="K3" s="58"/>
       <c r="L3" s="27" t="s">
         <v>37</v>
       </c>
@@ -23678,29 +23687,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="E1" s="46" t="s">
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="E1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="I1" s="46" t="s">
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="I1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="M1" s="46" t="s">
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="M1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="46"/>
-      <c r="P1" s="46" t="s">
+      <c r="N1" s="50"/>
+      <c r="P1" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="46"/>
+      <c r="Q1" s="50"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2">
@@ -26168,30 +26177,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="D2" s="46" t="s">
+      <c r="D2" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="I2" s="46" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="I2" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="N2" s="46" t="s">
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="N2" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="46"/>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="46"/>
-      <c r="S2" s="46" t="s">
+      <c r="O2" s="50"/>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="50"/>
+      <c r="S2" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="46"/>
-      <c r="U2" s="46"/>
-      <c r="V2" s="46"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="50"/>
+      <c r="V2" s="50"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -27066,7 +27075,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C03F23-5B48-E740-AE12-B3F8383D5054}">
-  <dimension ref="A2:AM26"/>
+  <dimension ref="A2:AS27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
@@ -27105,51 +27114,65 @@
     <col min="37" max="37" width="7.1640625" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="6.1640625" customWidth="1"/>
     <col min="39" max="39" width="4" style="19" customWidth="1"/>
+    <col min="40" max="40" width="18" customWidth="1"/>
+    <col min="41" max="41" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="4" style="19" customWidth="1"/>
+    <col min="43" max="43" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="E2" s="46" t="s">
+    <row r="2" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="E2" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
       <c r="I2" s="18"/>
-      <c r="K2" s="46" t="s">
+      <c r="K2" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="50"/>
       <c r="P2" s="18"/>
       <c r="Q2" s="18"/>
-      <c r="S2" s="46" t="s">
+      <c r="S2" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="T2" s="46"/>
-      <c r="U2" s="46"/>
-      <c r="V2" s="46"/>
-      <c r="W2" s="46"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="50"/>
+      <c r="V2" s="50"/>
+      <c r="W2" s="50"/>
       <c r="X2" s="18"/>
       <c r="Y2" s="18"/>
-      <c r="AA2" s="46" t="s">
+      <c r="AA2" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="AB2" s="46"/>
-      <c r="AC2" s="46"/>
-      <c r="AD2" s="46"/>
-      <c r="AE2" s="46"/>
+      <c r="AB2" s="50"/>
+      <c r="AC2" s="50"/>
+      <c r="AD2" s="50"/>
+      <c r="AE2" s="50"/>
       <c r="AF2" s="18"/>
-      <c r="AH2" s="46" t="s">
+      <c r="AH2" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="AI2" s="46"/>
-      <c r="AJ2" s="46"/>
-      <c r="AK2" s="46"/>
-      <c r="AL2" s="46"/>
-    </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="50"/>
+      <c r="AK2" s="50"/>
+      <c r="AL2" s="50"/>
+      <c r="AN2" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO2" s="50"/>
+      <c r="AQ2" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="AR2" s="50"/>
+    </row>
+    <row r="3" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -27249,8 +27272,20 @@
       <c r="AL3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AN3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>0</v>
       </c>
@@ -27365,7 +27400,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -27385,7 +27420,7 @@
         <v>97</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <f t="shared" ref="I5:I19" si="8">F5/G5</f>
@@ -27479,8 +27514,22 @@
         <f t="shared" ref="AL5:AL26" si="13">AI5/AJ5</f>
         <v>55.684210526315788</v>
       </c>
-    </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AN5">
+        <v>4263</v>
+      </c>
+      <c r="AO5" s="4">
+        <f>F5/AN5</f>
+        <v>1.264367816091954</v>
+      </c>
+      <c r="AQ5">
+        <v>4851</v>
+      </c>
+      <c r="AR5" s="4">
+        <f>AI5/AQ5</f>
+        <v>1.090496804782519</v>
+      </c>
+    </row>
+    <row r="6" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2</v>
       </c>
@@ -27500,7 +27549,7 @@
         <v>255</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <f t="shared" si="8"/>
@@ -27594,8 +27643,22 @@
         <f t="shared" si="13"/>
         <v>28.677685950413224</v>
       </c>
-    </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AN6">
+        <v>3290</v>
+      </c>
+      <c r="AO6" s="4">
+        <f>F6/AN6</f>
+        <v>2.2158054711246202</v>
+      </c>
+      <c r="AQ6">
+        <v>3170</v>
+      </c>
+      <c r="AR6" s="4">
+        <f t="shared" ref="AR6:AR26" si="14">AI6/AQ6</f>
+        <v>2.189274447949527</v>
+      </c>
+    </row>
+    <row r="7" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>3</v>
       </c>
@@ -27615,7 +27678,7 @@
         <v>499</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7">
         <f t="shared" si="8"/>
@@ -27709,8 +27772,22 @@
         <f t="shared" si="13"/>
         <v>49.087866108786613</v>
       </c>
-    </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AN7">
+        <v>12316</v>
+      </c>
+      <c r="AO7" s="4">
+        <f>F7/AN7</f>
+        <v>1.9870087690808704</v>
+      </c>
+      <c r="AQ7">
+        <v>7659</v>
+      </c>
+      <c r="AR7" s="4">
+        <f t="shared" si="14"/>
+        <v>3.0635853244548898</v>
+      </c>
+    </row>
+    <row r="8" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>4</v>
       </c>
@@ -27824,8 +27901,22 @@
         <f t="shared" si="13"/>
         <v>24.095697980684811</v>
       </c>
-    </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AN8">
+        <v>17578</v>
+      </c>
+      <c r="AO8" s="4">
+        <f>F8/AN8</f>
+        <v>1.6695869837296622</v>
+      </c>
+      <c r="AQ8">
+        <v>8318</v>
+      </c>
+      <c r="AR8" s="4">
+        <f t="shared" si="14"/>
+        <v>3.2994710266891079</v>
+      </c>
+    </row>
+    <row r="9" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>5</v>
       </c>
@@ -27939,8 +28030,22 @@
         <f t="shared" si="13"/>
         <v>57.940880503144655</v>
       </c>
-    </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AN9">
+        <v>43100</v>
+      </c>
+      <c r="AO9" s="4">
+        <f>F9/AN9</f>
+        <v>2.3034802784222737</v>
+      </c>
+      <c r="AQ9">
+        <v>32504</v>
+      </c>
+      <c r="AR9" s="4">
+        <f t="shared" si="14"/>
+        <v>2.8342973172532613</v>
+      </c>
+    </row>
+    <row r="10" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>6</v>
       </c>
@@ -28054,8 +28159,22 @@
         <f t="shared" si="13"/>
         <v>13.792730419731718</v>
       </c>
-    </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AN10">
+        <v>23591</v>
+      </c>
+      <c r="AO10" s="4">
+        <f>F10/AN10</f>
+        <v>1.4001526005680132</v>
+      </c>
+      <c r="AQ10">
+        <v>17749</v>
+      </c>
+      <c r="AR10" s="4">
+        <f t="shared" si="14"/>
+        <v>1.7958758239900841</v>
+      </c>
+    </row>
+    <row r="11" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>7</v>
       </c>
@@ -28169,8 +28288,22 @@
         <f t="shared" si="13"/>
         <v>23.729269385925594</v>
       </c>
-    </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AN11">
+        <v>60450</v>
+      </c>
+      <c r="AO11" s="4">
+        <f>F11/AN11</f>
+        <v>1.9103887510339124</v>
+      </c>
+      <c r="AQ11">
+        <v>22396</v>
+      </c>
+      <c r="AR11" s="4">
+        <f t="shared" si="14"/>
+        <v>4.7276299339167709</v>
+      </c>
+    </row>
+    <row r="12" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>8</v>
       </c>
@@ -28284,8 +28417,22 @@
         <f t="shared" si="13"/>
         <v>39.393946188340806</v>
       </c>
-    </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AN12">
+        <v>168828</v>
+      </c>
+      <c r="AO12" s="4">
+        <f>F12/AN12</f>
+        <v>2.194612268107186</v>
+      </c>
+      <c r="AQ12">
+        <v>109494</v>
+      </c>
+      <c r="AR12" s="4">
+        <f t="shared" si="14"/>
+        <v>3.20925347507626</v>
+      </c>
+    </row>
+    <row r="13" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>9</v>
       </c>
@@ -28399,8 +28546,22 @@
         <f t="shared" si="13"/>
         <v>59.157081063761616</v>
       </c>
-    </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AN13">
+        <v>478828</v>
+      </c>
+      <c r="AO13" s="4">
+        <f>F13/AN13</f>
+        <v>1.6686743465294427</v>
+      </c>
+      <c r="AQ13">
+        <v>226956</v>
+      </c>
+      <c r="AR13" s="4">
+        <f t="shared" si="14"/>
+        <v>3.2540095877615043</v>
+      </c>
+    </row>
+    <row r="14" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>10</v>
       </c>
@@ -28514,8 +28675,23 @@
         <f t="shared" si="13"/>
         <v>52.598314268512944</v>
       </c>
-    </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AN14">
+        <v>420398</v>
+      </c>
+      <c r="AO14" s="4">
+        <f>F14/AN14</f>
+        <v>2.1977245372242495</v>
+      </c>
+      <c r="AQ14">
+        <v>390761</v>
+      </c>
+      <c r="AR14" s="4">
+        <f t="shared" si="14"/>
+        <v>2.2357860687223137</v>
+      </c>
+      <c r="AS14" s="6"/>
+    </row>
+    <row r="15" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>11</v>
       </c>
@@ -28629,8 +28805,23 @@
         <f t="shared" si="13"/>
         <v>50.422024525126233</v>
       </c>
-    </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AN15">
+        <v>444705</v>
+      </c>
+      <c r="AO15" s="4">
+        <f>F15/AN15</f>
+        <v>2.4277194994434512</v>
+      </c>
+      <c r="AQ15">
+        <v>549158</v>
+      </c>
+      <c r="AR15" s="4">
+        <f t="shared" si="14"/>
+        <v>1.9093339257554292</v>
+      </c>
+      <c r="AS15" s="6"/>
+    </row>
+    <row r="16" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>12</v>
       </c>
@@ -28744,8 +28935,23 @@
         <f t="shared" si="13"/>
         <v>88.592836946277103</v>
       </c>
-    </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AN16">
+        <v>882776</v>
+      </c>
+      <c r="AO16" s="4">
+        <f>F16/AN16</f>
+        <v>4.000458780030268</v>
+      </c>
+      <c r="AQ16">
+        <v>985185</v>
+      </c>
+      <c r="AR16" s="4">
+        <f t="shared" si="14"/>
+        <v>3.4347782396199698</v>
+      </c>
+      <c r="AS16" s="6"/>
+    </row>
+    <row r="17" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>13</v>
       </c>
@@ -28859,8 +29065,23 @@
         <f t="shared" si="13"/>
         <v>102.40332113170136</v>
       </c>
-    </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AN17">
+        <v>1143696</v>
+      </c>
+      <c r="AO17" s="4">
+        <f>F17/AN17</f>
+        <v>5.1860774191743264</v>
+      </c>
+      <c r="AQ17">
+        <v>2504407</v>
+      </c>
+      <c r="AR17" s="4">
+        <f t="shared" si="14"/>
+        <v>2.144722882502724</v>
+      </c>
+      <c r="AS17" s="6"/>
+    </row>
+    <row r="18" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>14</v>
       </c>
@@ -28974,8 +29195,23 @@
         <f t="shared" si="13"/>
         <v>115.67040964644707</v>
       </c>
-    </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AN18">
+        <v>1690024</v>
+      </c>
+      <c r="AO18" s="4">
+        <f>F18/AN18</f>
+        <v>7.0191855263593892</v>
+      </c>
+      <c r="AQ18">
+        <v>4855080</v>
+      </c>
+      <c r="AR18" s="4">
+        <f t="shared" si="14"/>
+        <v>2.3275218945928802</v>
+      </c>
+      <c r="AS18" s="6"/>
+    </row>
+    <row r="19" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>15</v>
       </c>
@@ -29089,8 +29325,23 @@
         <f t="shared" si="13"/>
         <v>116.87897458572033</v>
       </c>
-    </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AN19">
+        <v>4196220</v>
+      </c>
+      <c r="AO19" s="4">
+        <f>F19/AN19</f>
+        <v>3.0721206228462759</v>
+      </c>
+      <c r="AQ19">
+        <v>2798271</v>
+      </c>
+      <c r="AR19" s="4">
+        <f t="shared" si="14"/>
+        <v>4.3454050733470773</v>
+      </c>
+      <c r="AS19" s="6"/>
+    </row>
+    <row r="20" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>16</v>
       </c>
@@ -29175,8 +29426,20 @@
         <f t="shared" si="13"/>
         <v>103.56100666666667</v>
       </c>
-    </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AO20" s="4">
+        <f>AVERAGE(AO5:AO19)</f>
+        <v>2.7011575779843926</v>
+      </c>
+      <c r="AQ20">
+        <v>6135807</v>
+      </c>
+      <c r="AR20" s="4">
+        <f>AI20/AQ20</f>
+        <v>2.5317209292925935</v>
+      </c>
+      <c r="AS20" s="6"/>
+    </row>
+    <row r="21" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>17</v>
       </c>
@@ -29261,8 +29524,16 @@
         <f t="shared" si="13"/>
         <v>132.8531759053088</v>
       </c>
-    </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AQ21">
+        <v>7276898</v>
+      </c>
+      <c r="AR21" s="4">
+        <f t="shared" si="14"/>
+        <v>3.1157126291999697</v>
+      </c>
+      <c r="AS21" s="6"/>
+    </row>
+    <row r="22" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>18</v>
       </c>
@@ -29347,8 +29618,16 @@
         <f t="shared" si="13"/>
         <v>181.57239706970927</v>
       </c>
-    </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AQ22">
+        <v>18914981</v>
+      </c>
+      <c r="AR22" s="4">
+        <f t="shared" si="14"/>
+        <v>1.8803777281087408</v>
+      </c>
+      <c r="AS22" s="6"/>
+    </row>
+    <row r="23" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>19</v>
       </c>
@@ -29433,8 +29712,16 @@
         <f t="shared" si="13"/>
         <v>282.84032714069679</v>
       </c>
-    </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AQ23">
+        <v>13045096</v>
+      </c>
+      <c r="AR23" s="4">
+        <f t="shared" si="14"/>
+        <v>5.9357221288367672</v>
+      </c>
+      <c r="AS23" s="6"/>
+    </row>
+    <row r="24" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>20</v>
       </c>
@@ -29519,8 +29806,16 @@
         <f t="shared" si="13"/>
         <v>272.97635211267607</v>
       </c>
-    </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AQ24">
+        <v>28218359</v>
+      </c>
+      <c r="AR24" s="4">
+        <f t="shared" si="14"/>
+        <v>3.4341686913827978</v>
+      </c>
+      <c r="AS24" s="6"/>
+    </row>
+    <row r="25" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>21</v>
       </c>
@@ -29605,8 +29900,16 @@
         <f t="shared" si="13"/>
         <v>291.45039442234565</v>
       </c>
-    </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AQ25">
+        <v>46782944</v>
+      </c>
+      <c r="AR25" s="4">
+        <f t="shared" si="14"/>
+        <v>2.1346743804750723</v>
+      </c>
+      <c r="AS25" s="6"/>
+    </row>
+    <row r="26" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>22</v>
       </c>
@@ -29691,9 +29994,25 @@
         <f t="shared" si="13"/>
         <v>303.55061718369336</v>
       </c>
+      <c r="AQ26">
+        <v>91294378</v>
+      </c>
+      <c r="AR26" s="4">
+        <f t="shared" si="14"/>
+        <v>1.6377447908128582</v>
+      </c>
+      <c r="AS26" s="6"/>
+    </row>
+    <row r="27" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AR27" s="4">
+        <f>AVERAGE(AR5:AR26)</f>
+        <v>2.842343777478324</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="AN2:AO2"/>
+    <mergeCell ref="AQ2:AR2"/>
     <mergeCell ref="E2:H2"/>
     <mergeCell ref="K2:O2"/>
     <mergeCell ref="S2:W2"/>
@@ -30051,26 +30370,26 @@
       </c>
     </row>
     <row r="29" spans="3:22" x14ac:dyDescent="0.2">
-      <c r="I29" s="47" t="s">
+      <c r="I29" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47"/>
+      <c r="J29" s="51"/>
+      <c r="K29" s="51"/>
+      <c r="L29" s="51"/>
       <c r="M29" s="21"/>
-      <c r="N29" s="47" t="s">
+      <c r="N29" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="O29" s="47"/>
-      <c r="P29" s="47"/>
-      <c r="Q29" s="47"/>
+      <c r="O29" s="51"/>
+      <c r="P29" s="51"/>
+      <c r="Q29" s="51"/>
       <c r="R29" s="21"/>
-      <c r="S29" s="47" t="s">
+      <c r="S29" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="T29" s="47"/>
-      <c r="U29" s="47"/>
-      <c r="V29" s="47"/>
+      <c r="T29" s="51"/>
+      <c r="U29" s="51"/>
+      <c r="V29" s="51"/>
     </row>
     <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="I30" s="21" t="s">
@@ -30432,7 +30751,7 @@
       <c r="E9">
         <v>1</v>
       </c>
-      <c r="F9" s="56">
+      <c r="F9" s="46">
         <v>55.567</v>
       </c>
       <c r="G9" s="4">
@@ -30452,7 +30771,7 @@
       <c r="E10">
         <v>2</v>
       </c>
-      <c r="F10" s="56">
+      <c r="F10" s="46">
         <v>28.588000000000001</v>
       </c>
       <c r="G10" s="4">
@@ -30472,7 +30791,7 @@
       <c r="E11">
         <v>3</v>
       </c>
-      <c r="F11" s="56">
+      <c r="F11" s="46">
         <v>49.042000000000002</v>
       </c>
       <c r="G11" s="4">
@@ -30492,7 +30811,7 @@
       <c r="E12">
         <v>4</v>
       </c>
-      <c r="F12" s="56">
+      <c r="F12" s="46">
         <v>24.074999999999999</v>
       </c>
       <c r="G12" s="4">
@@ -30512,7 +30831,7 @@
       <c r="E13">
         <v>5</v>
       </c>
-      <c r="F13" s="56">
+      <c r="F13" s="46">
         <v>57.923000000000002</v>
       </c>
       <c r="G13" s="4">
@@ -30532,7 +30851,7 @@
       <c r="E14">
         <v>6</v>
       </c>
-      <c r="F14" s="56">
+      <c r="F14" s="46">
         <v>13.792</v>
       </c>
       <c r="G14" s="4">
@@ -30552,7 +30871,7 @@
       <c r="E15">
         <v>7</v>
       </c>
-      <c r="F15" s="56">
+      <c r="F15" s="46">
         <v>23.728000000000002</v>
       </c>
       <c r="G15" s="4">
@@ -30572,7 +30891,7 @@
       <c r="E16">
         <v>8</v>
       </c>
-      <c r="F16" s="56">
+      <c r="F16" s="46">
         <v>39.390999999999998</v>
       </c>
       <c r="G16" s="4">
@@ -30592,7 +30911,7 @@
       <c r="E17">
         <v>9</v>
       </c>
-      <c r="F17" s="56">
+      <c r="F17" s="46">
         <v>59.155000000000001</v>
       </c>
       <c r="G17" s="4">
@@ -30612,7 +30931,7 @@
       <c r="E18">
         <v>10</v>
       </c>
-      <c r="F18" s="56">
+      <c r="F18" s="46">
         <v>52.597000000000001</v>
       </c>
       <c r="G18" s="4">
@@ -30632,7 +30951,7 @@
       <c r="E19">
         <v>11</v>
       </c>
-      <c r="F19" s="56">
+      <c r="F19" s="46">
         <v>50.420999999999999</v>
       </c>
       <c r="G19" s="4">
@@ -30652,7 +30971,7 @@
       <c r="E20">
         <v>12</v>
       </c>
-      <c r="F20" s="56">
+      <c r="F20" s="46">
         <v>88.590999999999994</v>
       </c>
       <c r="G20" s="4">
@@ -30672,7 +30991,7 @@
       <c r="E21">
         <v>13</v>
       </c>
-      <c r="F21" s="56">
+      <c r="F21" s="46">
         <v>102.4</v>
       </c>
       <c r="G21" s="4">
@@ -30692,7 +31011,7 @@
       <c r="E22">
         <v>14</v>
       </c>
-      <c r="F22" s="56">
+      <c r="F22" s="46">
         <v>115.67</v>
       </c>
       <c r="G22" s="4">
@@ -30712,7 +31031,7 @@
       <c r="E23">
         <v>15</v>
       </c>
-      <c r="F23" s="56">
+      <c r="F23" s="46">
         <v>116.88</v>
       </c>
       <c r="G23" s="4">
@@ -30732,7 +31051,7 @@
       <c r="E24">
         <v>16</v>
       </c>
-      <c r="F24" s="57" t="s">
+      <c r="F24" s="47" t="s">
         <v>44</v>
       </c>
       <c r="G24" s="4">
@@ -30752,7 +31071,7 @@
       <c r="E25">
         <v>17</v>
       </c>
-      <c r="F25" s="57" t="s">
+      <c r="F25" s="47" t="s">
         <v>44</v>
       </c>
       <c r="G25" s="4">
@@ -30772,7 +31091,7 @@
       <c r="E26">
         <v>18</v>
       </c>
-      <c r="F26" s="57" t="s">
+      <c r="F26" s="47" t="s">
         <v>44</v>
       </c>
       <c r="G26" s="4">
@@ -30792,7 +31111,7 @@
       <c r="E27">
         <v>19</v>
       </c>
-      <c r="F27" s="57" t="s">
+      <c r="F27" s="47" t="s">
         <v>44</v>
       </c>
       <c r="G27" s="4">
@@ -30812,7 +31131,7 @@
       <c r="E28">
         <v>20</v>
       </c>
-      <c r="F28" s="57" t="s">
+      <c r="F28" s="47" t="s">
         <v>44</v>
       </c>
       <c r="G28" s="4">
@@ -30832,7 +31151,7 @@
       <c r="E29">
         <v>21</v>
       </c>
-      <c r="F29" s="57" t="s">
+      <c r="F29" s="47" t="s">
         <v>44</v>
       </c>
       <c r="G29" s="4">
@@ -30852,19 +31171,19 @@
       <c r="E30" s="33">
         <v>22</v>
       </c>
-      <c r="F30" s="58" t="s">
+      <c r="F30" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="G30" s="59">
+      <c r="G30" s="49">
         <v>55.188527594611443</v>
       </c>
-      <c r="H30" s="59">
+      <c r="H30" s="49">
         <v>57.794670840440524</v>
       </c>
-      <c r="I30" s="59">
+      <c r="I30" s="49">
         <v>213.19553193450713</v>
       </c>
-      <c r="J30" s="59">
+      <c r="J30" s="49">
         <v>303.55061718369336</v>
       </c>
     </row>

--- a/All_perf.xlsx
+++ b/All_perf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ttdkoc/Documents/dev/workspaces/python/copt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B4A9399-45C5-D24B-BA30-CFCCA95CA6CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265735EE-7CAB-0144-AB66-DBF457F72EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20440" activeTab="5" xr2:uid="{544C10BC-9448-4CAA-97CB-C174D9523FCA}"/>
   </bookViews>
@@ -19,11 +19,12 @@
     <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
     <sheet name="NetworkingEXX" sheetId="5" r:id="rId5"/>
     <sheet name="NetworkingLESS" sheetId="7" r:id="rId6"/>
-    <sheet name="TestInstances" sheetId="8" r:id="rId7"/>
-    <sheet name="OV over DM" sheetId="13" r:id="rId8"/>
-    <sheet name="OvGap" sheetId="9" r:id="rId9"/>
-    <sheet name="IntraGap" sheetId="10" r:id="rId10"/>
-    <sheet name="Net Effect" sheetId="15" r:id="rId11"/>
+    <sheet name="Sheet2" sheetId="16" r:id="rId7"/>
+    <sheet name="TestInstances" sheetId="8" r:id="rId8"/>
+    <sheet name="OV over DM" sheetId="13" r:id="rId9"/>
+    <sheet name="OvGap" sheetId="9" r:id="rId10"/>
+    <sheet name="IntraGap" sheetId="10" r:id="rId11"/>
+    <sheet name="Net Effect" sheetId="15" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="64">
   <si>
     <t>Exact</t>
   </si>
@@ -223,6 +224,27 @@
   <si>
     <t>Objective Value No Net</t>
   </si>
+  <si>
+    <t>Net Optimized</t>
+  </si>
+  <si>
+    <t>No Net Optimized</t>
+  </si>
+  <si>
+    <t>No Net Opt/ Net Applied</t>
+  </si>
+  <si>
+    <t>Edges</t>
+  </si>
+  <si>
+    <t>Net Opt Success</t>
+  </si>
+  <si>
+    <t>MaxDegree</t>
+  </si>
+  <si>
+    <t>AverageDegre</t>
+  </si>
 </sst>
 </file>
 
@@ -235,7 +257,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,6 +282,12 @@
     <font>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -459,7 +487,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -568,6 +596,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -18882,6 +18913,1925 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4BCCACE-EA30-D046-B0A4-6BE1833C0F15}">
+  <dimension ref="A1:V43"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="5" max="5" width="2.6640625" customWidth="1"/>
+    <col min="13" max="15" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="2.83203125" customWidth="1"/>
+    <col min="18" max="18" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="33"/>
+      <c r="V1" s="33"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A2" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="L2" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="59" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="S2" s="58"/>
+      <c r="T2" s="58"/>
+      <c r="U2" s="58"/>
+      <c r="V2" s="58"/>
+    </row>
+    <row r="3" spans="1:22" ht="32" x14ac:dyDescent="0.2">
+      <c r="A3" s="57"/>
+      <c r="B3" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="27"/>
+      <c r="F3" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="57"/>
+      <c r="M3" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="O3" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="P3" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="S3" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="T3" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="U3" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="V3" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="23">
+        <f>NetworkingLESS!N5</f>
+        <v>0.24545454545454545</v>
+      </c>
+      <c r="C4" s="23">
+        <f>NetworkingLESS!V5</f>
+        <v>0.24545454545454545</v>
+      </c>
+      <c r="D4" s="24">
+        <f>NetworkingLESS!AD5</f>
+        <v>0.24545454545454545</v>
+      </c>
+      <c r="E4" s="24"/>
+      <c r="F4" s="20">
+        <f>NetworkingLESS!E5</f>
+        <v>0.02</v>
+      </c>
+      <c r="G4" s="20">
+        <f>NetworkingLESS!K5</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="20">
+        <f>NetworkingLESS!S5</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="20">
+        <f>NetworkingLESS!AA5</f>
+        <v>0.03</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4" s="2">
+        <f>NetworkingLESS!N5</f>
+        <v>0.24545454545454545</v>
+      </c>
+      <c r="N4" s="2">
+        <f>NetworkingLESS!V5</f>
+        <v>0.24545454545454545</v>
+      </c>
+      <c r="O4" s="43">
+        <f>NetworkingLESS!AD5</f>
+        <v>0.24545454545454545</v>
+      </c>
+      <c r="P4" s="43">
+        <f>NetworkingLESS!AK4</f>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="20">
+        <f>NetworkingLESS!E5</f>
+        <v>0.02</v>
+      </c>
+      <c r="S4" s="20">
+        <f>NetworkingLESS!K5</f>
+        <v>0</v>
+      </c>
+      <c r="T4" s="20">
+        <f>NetworkingLESS!S5</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="20">
+        <f>NetworkingLESS!AA5</f>
+        <v>0.03</v>
+      </c>
+      <c r="V4" s="20">
+        <f>NetworkingLESS!AH5</f>
+        <v>3.4000000000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" s="23">
+        <f>NetworkingLESS!N6</f>
+        <v>0.60356652949245537</v>
+      </c>
+      <c r="C5" s="23">
+        <f>NetworkingLESS!V6</f>
+        <v>0.60356652949245537</v>
+      </c>
+      <c r="D5" s="24">
+        <f>NetworkingLESS!AD6</f>
+        <v>0.19204389574759945</v>
+      </c>
+      <c r="E5" s="24"/>
+      <c r="F5" s="20">
+        <f>NetworkingLESS!E6</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G5" s="20">
+        <f>NetworkingLESS!K6</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="20">
+        <f>NetworkingLESS!S6</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="20">
+        <f>NetworkingLESS!AA6</f>
+        <v>0.06</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5" s="2">
+        <f>NetworkingLESS!N6</f>
+        <v>0.60356652949245537</v>
+      </c>
+      <c r="N5" s="2">
+        <f>NetworkingLESS!V6</f>
+        <v>0.60356652949245537</v>
+      </c>
+      <c r="O5" s="43">
+        <f>NetworkingLESS!AD6</f>
+        <v>0.19204389574759945</v>
+      </c>
+      <c r="P5" s="43">
+        <f>NetworkingLESS!AK5</f>
+        <v>1.8552875695732839E-2</v>
+      </c>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="20">
+        <f>NetworkingLESS!E6</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="S5" s="20">
+        <f>NetworkingLESS!K6</f>
+        <v>0</v>
+      </c>
+      <c r="T5" s="20">
+        <f>NetworkingLESS!S6</f>
+        <v>0</v>
+      </c>
+      <c r="U5" s="20">
+        <f>NetworkingLESS!AA6</f>
+        <v>0.06</v>
+      </c>
+      <c r="V5" s="20">
+        <f>NetworkingLESS!AH6</f>
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" s="23">
+        <f>NetworkingLESS!N7</f>
+        <v>0.51855181431840469</v>
+      </c>
+      <c r="C6" s="23">
+        <f>NetworkingLESS!V7</f>
+        <v>0.40209218698921217</v>
+      </c>
+      <c r="D6" s="24">
+        <f>NetworkingLESS!AD7</f>
+        <v>0.1443690748610657</v>
+      </c>
+      <c r="E6" s="24"/>
+      <c r="F6" s="20">
+        <f>NetworkingLESS!E7</f>
+        <v>0.1</v>
+      </c>
+      <c r="G6" s="20">
+        <f>NetworkingLESS!K7</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="20">
+        <f>NetworkingLESS!S7</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="20">
+        <f>NetworkingLESS!AA7</f>
+        <v>0.1</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6" s="2">
+        <f>NetworkingLESS!N7</f>
+        <v>0.51855181431840469</v>
+      </c>
+      <c r="N6" s="2">
+        <f>NetworkingLESS!V7</f>
+        <v>0.40209218698921217</v>
+      </c>
+      <c r="O6" s="43">
+        <f>NetworkingLESS!AD7</f>
+        <v>0.1443690748610657</v>
+      </c>
+      <c r="P6" s="43">
+        <f>NetworkingLESS!AK6</f>
+        <v>4.8010973936899862E-2</v>
+      </c>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="20">
+        <f>NetworkingLESS!E7</f>
+        <v>0.1</v>
+      </c>
+      <c r="S6" s="20">
+        <f>NetworkingLESS!K7</f>
+        <v>0</v>
+      </c>
+      <c r="T6" s="20">
+        <f>NetworkingLESS!S7</f>
+        <v>0</v>
+      </c>
+      <c r="U6" s="20">
+        <f>NetworkingLESS!AA7</f>
+        <v>0.1</v>
+      </c>
+      <c r="V6" s="20">
+        <f>NetworkingLESS!AH7</f>
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" s="23">
+        <f>NetworkingLESS!N8</f>
+        <v>0.62927627095543137</v>
+      </c>
+      <c r="C7" s="23">
+        <f>NetworkingLESS!V8</f>
+        <v>0.46388169551587843</v>
+      </c>
+      <c r="D7" s="24">
+        <f>NetworkingLESS!AD8</f>
+        <v>0.26298214529099084</v>
+      </c>
+      <c r="E7" s="24"/>
+      <c r="F7" s="20">
+        <f>NetworkingLESS!E8</f>
+        <v>0.27</v>
+      </c>
+      <c r="G7" s="20">
+        <f>NetworkingLESS!K8</f>
+        <v>0.02</v>
+      </c>
+      <c r="H7" s="20">
+        <f>NetworkingLESS!S8</f>
+        <v>0.05</v>
+      </c>
+      <c r="I7" s="20">
+        <f>NetworkingLESS!AA8</f>
+        <v>0.33</v>
+      </c>
+      <c r="L7">
+        <v>4</v>
+      </c>
+      <c r="M7" s="2">
+        <f>NetworkingLESS!N8</f>
+        <v>0.62927627095543137</v>
+      </c>
+      <c r="N7" s="2">
+        <f>NetworkingLESS!V8</f>
+        <v>0.46388169551587843</v>
+      </c>
+      <c r="O7" s="43">
+        <f>NetworkingLESS!AD8</f>
+        <v>0.26298214529099084</v>
+      </c>
+      <c r="P7" s="43">
+        <f>NetworkingLESS!AK7</f>
+        <v>4.1189931350114416E-2</v>
+      </c>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="20">
+        <f>NetworkingLESS!E8</f>
+        <v>0.27</v>
+      </c>
+      <c r="S7" s="20">
+        <f>NetworkingLESS!K8</f>
+        <v>0.02</v>
+      </c>
+      <c r="T7" s="20">
+        <f>NetworkingLESS!S8</f>
+        <v>0.05</v>
+      </c>
+      <c r="U7" s="20">
+        <f>NetworkingLESS!AA8</f>
+        <v>0.33</v>
+      </c>
+      <c r="V7" s="20">
+        <f>NetworkingLESS!AH8</f>
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" s="23">
+        <f>NetworkingLESS!N9</f>
+        <v>0.68208098307816278</v>
+      </c>
+      <c r="C8" s="23">
+        <f>NetworkingLESS!V9</f>
+        <v>0.5952659145850121</v>
+      </c>
+      <c r="D8" s="24">
+        <f>NetworkingLESS!AD9</f>
+        <v>0.17913980660757453</v>
+      </c>
+      <c r="E8" s="24"/>
+      <c r="F8" s="20">
+        <f>NetworkingLESS!E9</f>
+        <v>0.41</v>
+      </c>
+      <c r="G8" s="20">
+        <f>NetworkingLESS!K9</f>
+        <v>0.05</v>
+      </c>
+      <c r="H8" s="20">
+        <f>NetworkingLESS!S9</f>
+        <v>0.09</v>
+      </c>
+      <c r="I8" s="20">
+        <f>NetworkingLESS!AA9</f>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="L8">
+        <v>5</v>
+      </c>
+      <c r="M8" s="2">
+        <f>NetworkingLESS!N9</f>
+        <v>0.68208098307816278</v>
+      </c>
+      <c r="N8" s="2">
+        <f>NetworkingLESS!V9</f>
+        <v>0.5952659145850121</v>
+      </c>
+      <c r="O8" s="43">
+        <f>NetworkingLESS!AD9</f>
+        <v>0.17913980660757453</v>
+      </c>
+      <c r="P8" s="43">
+        <f>NetworkingLESS!AK8</f>
+        <v>6.484257871064468E-2</v>
+      </c>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="20">
+        <f>NetworkingLESS!E9</f>
+        <v>0.41</v>
+      </c>
+      <c r="S8" s="20">
+        <f>NetworkingLESS!K9</f>
+        <v>0.05</v>
+      </c>
+      <c r="T8" s="20">
+        <f>NetworkingLESS!S9</f>
+        <v>0.09</v>
+      </c>
+      <c r="U8" s="20">
+        <f>NetworkingLESS!AA9</f>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="V8" s="20">
+        <f>NetworkingLESS!AH9</f>
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" s="23">
+        <f>NetworkingLESS!N10</f>
+        <v>0.31385668008840178</v>
+      </c>
+      <c r="C9" s="23">
+        <f>NetworkingLESS!V10</f>
+        <v>0.31343283582089554</v>
+      </c>
+      <c r="D9" s="24">
+        <f>NetworkingLESS!AD10</f>
+        <v>0.19297024007750296</v>
+      </c>
+      <c r="E9" s="24"/>
+      <c r="F9" s="20">
+        <f>NetworkingLESS!E10</f>
+        <v>0.63</v>
+      </c>
+      <c r="G9" s="20">
+        <f>NetworkingLESS!K10</f>
+        <v>0.1</v>
+      </c>
+      <c r="H9" s="20">
+        <f>NetworkingLESS!S10</f>
+        <v>0.19</v>
+      </c>
+      <c r="I9" s="20">
+        <f>NetworkingLESS!AA10</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L9">
+        <v>6</v>
+      </c>
+      <c r="M9" s="2">
+        <f>NetworkingLESS!N10</f>
+        <v>0.31385668008840178</v>
+      </c>
+      <c r="N9" s="2">
+        <f>NetworkingLESS!V10</f>
+        <v>0.31343283582089554</v>
+      </c>
+      <c r="O9" s="43">
+        <f>NetworkingLESS!AD10</f>
+        <v>0.19297024007750296</v>
+      </c>
+      <c r="P9" s="43">
+        <f>NetworkingLESS!AK9</f>
+        <v>7.2058823529411759E-2</v>
+      </c>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="20">
+        <f>NetworkingLESS!E10</f>
+        <v>0.63</v>
+      </c>
+      <c r="S9" s="20">
+        <f>NetworkingLESS!K10</f>
+        <v>0.1</v>
+      </c>
+      <c r="T9" s="20">
+        <f>NetworkingLESS!S10</f>
+        <v>0.19</v>
+      </c>
+      <c r="U9" s="20">
+        <f>NetworkingLESS!AA10</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="V9" s="20">
+        <f>NetworkingLESS!AH10</f>
+        <v>10.149999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" s="23">
+        <f>NetworkingLESS!N11</f>
+        <v>0.70056198747867648</v>
+      </c>
+      <c r="C10" s="23">
+        <f>NetworkingLESS!V11</f>
+        <v>0.52568776356693192</v>
+      </c>
+      <c r="D10" s="24">
+        <f>NetworkingLESS!AD11</f>
+        <v>0.18213070322038741</v>
+      </c>
+      <c r="E10" s="24"/>
+      <c r="F10" s="20">
+        <f>NetworkingLESS!E11</f>
+        <v>1.29</v>
+      </c>
+      <c r="G10" s="20">
+        <f>NetworkingLESS!K11</f>
+        <v>0.15</v>
+      </c>
+      <c r="H10" s="20">
+        <f>NetworkingLESS!S11</f>
+        <v>0.24</v>
+      </c>
+      <c r="I10" s="20">
+        <f>NetworkingLESS!AA11</f>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="L10">
+        <v>7</v>
+      </c>
+      <c r="M10" s="2">
+        <f>NetworkingLESS!N11</f>
+        <v>0.70056198747867648</v>
+      </c>
+      <c r="N10" s="2">
+        <f>NetworkingLESS!V11</f>
+        <v>0.52568776356693192</v>
+      </c>
+      <c r="O10" s="43">
+        <f>NetworkingLESS!AD11</f>
+        <v>0.18213070322038741</v>
+      </c>
+      <c r="P10" s="43">
+        <f>NetworkingLESS!AK10</f>
+        <v>3.4997426659804425E-2</v>
+      </c>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="20">
+        <f>NetworkingLESS!E11</f>
+        <v>1.29</v>
+      </c>
+      <c r="S10" s="20">
+        <f>NetworkingLESS!K11</f>
+        <v>0.15</v>
+      </c>
+      <c r="T10" s="20">
+        <f>NetworkingLESS!S11</f>
+        <v>0.24</v>
+      </c>
+      <c r="U10" s="20">
+        <f>NetworkingLESS!AA11</f>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="V10" s="20">
+        <f>NetworkingLESS!AH11</f>
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" s="23">
+        <f>NetworkingLESS!N12</f>
+        <v>0.70038217385671719</v>
+      </c>
+      <c r="C11" s="23">
+        <f>NetworkingLESS!V12</f>
+        <v>0.68401023448633247</v>
+      </c>
+      <c r="D11" s="24">
+        <f>NetworkingLESS!AD12</f>
+        <v>0.24333894718659585</v>
+      </c>
+      <c r="E11" s="24"/>
+      <c r="F11" s="20">
+        <f>NetworkingLESS!E12</f>
+        <v>4.26</v>
+      </c>
+      <c r="G11" s="20">
+        <f>NetworkingLESS!K12</f>
+        <v>0.6</v>
+      </c>
+      <c r="H11" s="20">
+        <f>NetworkingLESS!S12</f>
+        <v>0.97</v>
+      </c>
+      <c r="I11" s="20">
+        <f>NetworkingLESS!AA12</f>
+        <v>8.75</v>
+      </c>
+      <c r="L11">
+        <v>8</v>
+      </c>
+      <c r="M11" s="2">
+        <f>NetworkingLESS!N12</f>
+        <v>0.70038217385671719</v>
+      </c>
+      <c r="N11" s="2">
+        <f>NetworkingLESS!V12</f>
+        <v>0.68401023448633247</v>
+      </c>
+      <c r="O11" s="43">
+        <f>NetworkingLESS!AD12</f>
+        <v>0.24333894718659585</v>
+      </c>
+      <c r="P11" s="43">
+        <f>NetworkingLESS!AK11</f>
+        <v>8.3155096421118263E-2</v>
+      </c>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="20">
+        <f>NetworkingLESS!E12</f>
+        <v>4.26</v>
+      </c>
+      <c r="S11" s="20">
+        <f>NetworkingLESS!K12</f>
+        <v>0.6</v>
+      </c>
+      <c r="T11" s="20">
+        <f>NetworkingLESS!S12</f>
+        <v>0.97</v>
+      </c>
+      <c r="U11" s="20">
+        <f>NetworkingLESS!AA12</f>
+        <v>8.75</v>
+      </c>
+      <c r="V11" s="20">
+        <f>NetworkingLESS!AH12</f>
+        <v>79.099999999999994</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" s="23">
+        <f>NetworkingLESS!N13</f>
+        <v>0.66356532099803756</v>
+      </c>
+      <c r="C12" s="23">
+        <f>NetworkingLESS!V13</f>
+        <v>0.66393327726380713</v>
+      </c>
+      <c r="D12" s="24">
+        <f>NetworkingLESS!AD13</f>
+        <v>0.17018102447034322</v>
+      </c>
+      <c r="E12" s="24"/>
+      <c r="F12" s="20">
+        <f>NetworkingLESS!E13</f>
+        <v>11.3</v>
+      </c>
+      <c r="G12" s="20">
+        <f>NetworkingLESS!K13</f>
+        <v>1.36</v>
+      </c>
+      <c r="H12" s="20">
+        <f>NetworkingLESS!S13</f>
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="I12" s="20">
+        <f>NetworkingLESS!AA13</f>
+        <v>20.100000000000001</v>
+      </c>
+      <c r="L12">
+        <v>9</v>
+      </c>
+      <c r="M12" s="2">
+        <f>NetworkingLESS!N13</f>
+        <v>0.66356532099803756</v>
+      </c>
+      <c r="N12" s="2">
+        <f>NetworkingLESS!V13</f>
+        <v>0.66393327726380713</v>
+      </c>
+      <c r="O12" s="43">
+        <f>NetworkingLESS!AD13</f>
+        <v>0.17018102447034322</v>
+      </c>
+      <c r="P12" s="43">
+        <f>NetworkingLESS!AK12</f>
+        <v>5.1598868592650171E-2</v>
+      </c>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="20">
+        <f>NetworkingLESS!E13</f>
+        <v>11.3</v>
+      </c>
+      <c r="S12" s="20">
+        <f>NetworkingLESS!K13</f>
+        <v>1.36</v>
+      </c>
+      <c r="T12" s="20">
+        <f>NetworkingLESS!S13</f>
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="U12" s="20">
+        <f>NetworkingLESS!AA13</f>
+        <v>20.100000000000001</v>
+      </c>
+      <c r="V12" s="20">
+        <f>NetworkingLESS!AH13</f>
+        <v>189.75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" s="23">
+        <f>NetworkingLESS!N14</f>
+        <v>0.63726798561345743</v>
+      </c>
+      <c r="C13" s="23">
+        <f>NetworkingLESS!V14</f>
+        <v>0.63810788608092273</v>
+      </c>
+      <c r="D13" s="24">
+        <f>NetworkingLESS!AD14</f>
+        <v>0.20905404045159803</v>
+      </c>
+      <c r="E13" s="24"/>
+      <c r="F13" s="20">
+        <f>NetworkingLESS!E14</f>
+        <v>24.03</v>
+      </c>
+      <c r="G13" s="20">
+        <f>NetworkingLESS!K14</f>
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="H13" s="20">
+        <f>NetworkingLESS!S14</f>
+        <v>3.88</v>
+      </c>
+      <c r="I13" s="20">
+        <f>NetworkingLESS!AA14</f>
+        <v>37.33</v>
+      </c>
+      <c r="L13">
+        <v>10</v>
+      </c>
+      <c r="M13" s="2">
+        <f>NetworkingLESS!N14</f>
+        <v>0.63726798561345743</v>
+      </c>
+      <c r="N13" s="2">
+        <f>NetworkingLESS!V14</f>
+        <v>0.63810788608092273</v>
+      </c>
+      <c r="O13" s="43">
+        <f>NetworkingLESS!AD14</f>
+        <v>0.20905404045159803</v>
+      </c>
+      <c r="P13" s="43">
+        <f>NetworkingLESS!AK13</f>
+        <v>7.5707627458047974E-2</v>
+      </c>
+      <c r="Q13" s="24"/>
+      <c r="R13" s="20">
+        <f>NetworkingLESS!E14</f>
+        <v>24.03</v>
+      </c>
+      <c r="S13" s="20">
+        <f>NetworkingLESS!K14</f>
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="T13" s="20">
+        <f>NetworkingLESS!S14</f>
+        <v>3.88</v>
+      </c>
+      <c r="U13" s="20">
+        <f>NetworkingLESS!AA14</f>
+        <v>37.33</v>
+      </c>
+      <c r="V13" s="20">
+        <f>NetworkingLESS!AH14</f>
+        <v>331.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" s="23">
+        <f>NetworkingLESS!N15</f>
+        <v>0.70677433427903735</v>
+      </c>
+      <c r="C14" s="23">
+        <f>NetworkingLESS!V15</f>
+        <v>0.70766909437496006</v>
+      </c>
+      <c r="D14" s="24">
+        <f>NetworkingLESS!AD15</f>
+        <v>0.15677475109274661</v>
+      </c>
+      <c r="E14" s="24"/>
+      <c r="F14" s="20">
+        <f>NetworkingLESS!E15</f>
+        <v>43.93</v>
+      </c>
+      <c r="G14" s="20">
+        <f>NetworkingLESS!K15</f>
+        <v>3.8</v>
+      </c>
+      <c r="H14" s="20">
+        <f>NetworkingLESS!S15</f>
+        <v>6.13</v>
+      </c>
+      <c r="I14" s="20">
+        <f>NetworkingLESS!AA15</f>
+        <v>60.39</v>
+      </c>
+      <c r="L14">
+        <v>11</v>
+      </c>
+      <c r="M14" s="2">
+        <f>NetworkingLESS!N15</f>
+        <v>0.70677433427903735</v>
+      </c>
+      <c r="N14" s="2">
+        <f>NetworkingLESS!V15</f>
+        <v>0.70766909437496006</v>
+      </c>
+      <c r="O14" s="43">
+        <f>NetworkingLESS!AD15</f>
+        <v>0.15677475109274661</v>
+      </c>
+      <c r="P14" s="43">
+        <f>NetworkingLESS!AK14</f>
+        <v>5.439979045782152E-2</v>
+      </c>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="20">
+        <f>NetworkingLESS!E15</f>
+        <v>43.93</v>
+      </c>
+      <c r="S14" s="20">
+        <f>NetworkingLESS!K15</f>
+        <v>3.8</v>
+      </c>
+      <c r="T14" s="20">
+        <f>NetworkingLESS!S15</f>
+        <v>6.13</v>
+      </c>
+      <c r="U14" s="20">
+        <f>NetworkingLESS!AA15</f>
+        <v>60.39</v>
+      </c>
+      <c r="V14" s="20">
+        <f>NetworkingLESS!AH15</f>
+        <v>541.70000000000005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" s="23">
+        <f>NetworkingLESS!N16</f>
+        <v>0.75607481107934316</v>
+      </c>
+      <c r="C15" s="23">
+        <f>NetworkingLESS!V16</f>
+        <v>0.75674874395053215</v>
+      </c>
+      <c r="D15" s="24">
+        <f>NetworkingLESS!AD16</f>
+        <v>0.20066237973625439</v>
+      </c>
+      <c r="E15" s="24"/>
+      <c r="F15" s="20">
+        <f>NetworkingLESS!E16</f>
+        <v>309.95999999999998</v>
+      </c>
+      <c r="G15" s="20">
+        <f>NetworkingLESS!K16</f>
+        <v>15.53</v>
+      </c>
+      <c r="H15" s="20">
+        <f>NetworkingLESS!S16</f>
+        <v>25.1</v>
+      </c>
+      <c r="I15" s="20">
+        <f>NetworkingLESS!AA16</f>
+        <v>290.14</v>
+      </c>
+      <c r="L15">
+        <v>12</v>
+      </c>
+      <c r="M15" s="2">
+        <f>NetworkingLESS!N16</f>
+        <v>0.75607481107934316</v>
+      </c>
+      <c r="N15" s="2">
+        <f>NetworkingLESS!V16</f>
+        <v>0.75674874395053215</v>
+      </c>
+      <c r="O15" s="43">
+        <f>NetworkingLESS!AD16</f>
+        <v>0.20066237973625439</v>
+      </c>
+      <c r="P15" s="43">
+        <f>NetworkingLESS!AK15</f>
+        <v>2.8799974805926904E-2</v>
+      </c>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="20">
+        <f>NetworkingLESS!E16</f>
+        <v>309.95999999999998</v>
+      </c>
+      <c r="S15" s="20">
+        <f>NetworkingLESS!K16</f>
+        <v>15.53</v>
+      </c>
+      <c r="T15" s="20">
+        <f>NetworkingLESS!S16</f>
+        <v>25.1</v>
+      </c>
+      <c r="U15" s="20">
+        <f>NetworkingLESS!AA16</f>
+        <v>290.14</v>
+      </c>
+      <c r="V15" s="20">
+        <f>NetworkingLESS!AH16</f>
+        <v>2601.5499999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" s="23">
+        <f>NetworkingLESS!N17</f>
+        <v>0.7320626048674691</v>
+      </c>
+      <c r="C16" s="23">
+        <f>NetworkingLESS!V17</f>
+        <v>0.73310925639185764</v>
+      </c>
+      <c r="D16" s="24">
+        <f>NetworkingLESS!AD17</f>
+        <v>0.23946739464697092</v>
+      </c>
+      <c r="E16" s="24"/>
+      <c r="F16" s="20">
+        <f>NetworkingLESS!E17</f>
+        <v>1732.32</v>
+      </c>
+      <c r="G16" s="20">
+        <f>NetworkingLESS!K17</f>
+        <v>35.65</v>
+      </c>
+      <c r="H16" s="20">
+        <f>NetworkingLESS!S17</f>
+        <v>57.41</v>
+      </c>
+      <c r="I16" s="20">
+        <f>NetworkingLESS!AA17</f>
+        <v>749.64</v>
+      </c>
+      <c r="L16">
+        <v>13</v>
+      </c>
+      <c r="M16" s="2">
+        <f>NetworkingLESS!N17</f>
+        <v>0.7320626048674691</v>
+      </c>
+      <c r="N16" s="2">
+        <f>NetworkingLESS!V17</f>
+        <v>0.73310925639185764</v>
+      </c>
+      <c r="O16" s="43">
+        <f>NetworkingLESS!AD17</f>
+        <v>0.23946739464697092</v>
+      </c>
+      <c r="P16" s="43">
+        <f>NetworkingLESS!AK16</f>
+        <v>4.1799978422821522E-2</v>
+      </c>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="20">
+        <f>NetworkingLESS!E17</f>
+        <v>1732.32</v>
+      </c>
+      <c r="S16" s="20">
+        <f>NetworkingLESS!K17</f>
+        <v>35.65</v>
+      </c>
+      <c r="T16" s="20">
+        <f>NetworkingLESS!S17</f>
+        <v>57.41</v>
+      </c>
+      <c r="U16" s="20">
+        <f>NetworkingLESS!AA17</f>
+        <v>749.64</v>
+      </c>
+      <c r="V16" s="20">
+        <f>NetworkingLESS!AH17</f>
+        <v>6781.25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" s="23">
+        <f>NetworkingLESS!N18</f>
+        <v>0.76867450216613709</v>
+      </c>
+      <c r="C17" s="23">
+        <f>NetworkingLESS!V18</f>
+        <v>0.76054204679719239</v>
+      </c>
+      <c r="D17" s="24">
+        <f>NetworkingLESS!AD18</f>
+        <v>0.26318025605196571</v>
+      </c>
+      <c r="E17" s="24"/>
+      <c r="F17" s="20">
+        <f>NetworkingLESS!E18</f>
+        <v>9234.91</v>
+      </c>
+      <c r="G17" s="20">
+        <f>NetworkingLESS!K18</f>
+        <v>66.44</v>
+      </c>
+      <c r="H17" s="20">
+        <f>NetworkingLESS!S18</f>
+        <v>104.96</v>
+      </c>
+      <c r="I17" s="20">
+        <f>NetworkingLESS!AA18</f>
+        <v>1209.1400000000001</v>
+      </c>
+      <c r="L17">
+        <v>14</v>
+      </c>
+      <c r="M17" s="2">
+        <f>NetworkingLESS!N18</f>
+        <v>0.76867450216613709</v>
+      </c>
+      <c r="N17" s="2">
+        <f>NetworkingLESS!V18</f>
+        <v>0.76054204679719239</v>
+      </c>
+      <c r="O17" s="43">
+        <f>NetworkingLESS!AD18</f>
+        <v>0.26318025605196571</v>
+      </c>
+      <c r="P17" s="43">
+        <f>NetworkingLESS!AK17</f>
+        <v>9.4420679730028642E-2</v>
+      </c>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="20">
+        <f>NetworkingLESS!E18</f>
+        <v>9234.91</v>
+      </c>
+      <c r="S17" s="20">
+        <f>NetworkingLESS!K18</f>
+        <v>66.44</v>
+      </c>
+      <c r="T17" s="20">
+        <f>NetworkingLESS!S18</f>
+        <v>104.96</v>
+      </c>
+      <c r="U17" s="20">
+        <f>NetworkingLESS!AA18</f>
+        <v>1209.1400000000001</v>
+      </c>
+      <c r="V17" s="20">
+        <f>NetworkingLESS!AH18</f>
+        <v>11609.75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A18" s="22">
+        <v>15</v>
+      </c>
+      <c r="B18" s="23">
+        <f>NetworkingLESS!N19</f>
+        <v>0.68917968979685051</v>
+      </c>
+      <c r="C18" s="23">
+        <f>NetworkingLESS!V19</f>
+        <v>0.68987193993093321</v>
+      </c>
+      <c r="D18" s="24">
+        <f>NetworkingLESS!AD19</f>
+        <v>0.19108570481753034</v>
+      </c>
+      <c r="E18" s="24"/>
+      <c r="F18" s="20">
+        <f>NetworkingLESS!E19</f>
+        <v>50792.01</v>
+      </c>
+      <c r="G18" s="20">
+        <f>NetworkingLESS!K19</f>
+        <v>109.15</v>
+      </c>
+      <c r="H18" s="20">
+        <f>NetworkingLESS!S19</f>
+        <v>168.04</v>
+      </c>
+      <c r="I18" s="20">
+        <f>NetworkingLESS!AA19</f>
+        <v>1668.64</v>
+      </c>
+      <c r="L18" s="22">
+        <v>15</v>
+      </c>
+      <c r="M18" s="2">
+        <f>NetworkingLESS!N19</f>
+        <v>0.68917968979685051</v>
+      </c>
+      <c r="N18" s="2">
+        <f>NetworkingLESS!V19</f>
+        <v>0.68987193993093321</v>
+      </c>
+      <c r="O18" s="43">
+        <f>NetworkingLESS!AD19</f>
+        <v>0.19108570481753034</v>
+      </c>
+      <c r="P18" s="43">
+        <f>NetworkingLESS!AK18</f>
+        <v>4.7400011734366317E-2</v>
+      </c>
+      <c r="Q18" s="24"/>
+      <c r="R18" s="20">
+        <f>NetworkingLESS!E19</f>
+        <v>50792.01</v>
+      </c>
+      <c r="S18" s="20">
+        <f>NetworkingLESS!K19</f>
+        <v>109.15</v>
+      </c>
+      <c r="T18" s="20">
+        <f>NetworkingLESS!S19</f>
+        <v>168.04</v>
+      </c>
+      <c r="U18" s="20">
+        <f>NetworkingLESS!AA19</f>
+        <v>1668.64</v>
+      </c>
+      <c r="V18" s="20">
+        <f>NetworkingLESS!AH19</f>
+        <v>14829.849999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="29">
+        <f t="shared" ref="B19:I19" si="0">AVERAGE(B4:B18)</f>
+        <v>0.62315534890154178</v>
+      </c>
+      <c r="C19" s="29">
+        <f t="shared" si="0"/>
+        <v>0.58555826338009809</v>
+      </c>
+      <c r="D19" s="29">
+        <f t="shared" si="0"/>
+        <v>0.2048556606475781</v>
+      </c>
+      <c r="E19" s="29"/>
+      <c r="F19" s="30">
+        <f t="shared" si="0"/>
+        <v>4143.7006666666666</v>
+      </c>
+      <c r="G19" s="30">
+        <f t="shared" si="0"/>
+        <v>15.685333333333334</v>
+      </c>
+      <c r="H19" s="30">
+        <f t="shared" si="0"/>
+        <v>24.616</v>
+      </c>
+      <c r="I19" s="30">
+        <f t="shared" si="0"/>
+        <v>269.90400000000005</v>
+      </c>
+      <c r="L19" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="M19" s="44">
+        <f t="shared" ref="M19:O19" si="1">AVERAGE(M4:M18)</f>
+        <v>0.62315534890154178</v>
+      </c>
+      <c r="N19" s="44">
+        <f t="shared" si="1"/>
+        <v>0.58555826338009809</v>
+      </c>
+      <c r="O19" s="44">
+        <f t="shared" si="1"/>
+        <v>0.2048556606475781</v>
+      </c>
+      <c r="P19" s="44">
+        <f>AVERAGE(P4:P18)</f>
+        <v>5.0462309167025966E-2</v>
+      </c>
+      <c r="Q19" s="29"/>
+      <c r="R19" s="30">
+        <f t="shared" ref="R19:V19" si="2">AVERAGE(R4:R18)</f>
+        <v>4143.7006666666666</v>
+      </c>
+      <c r="S19" s="30">
+        <f t="shared" si="2"/>
+        <v>15.685333333333334</v>
+      </c>
+      <c r="T19" s="30">
+        <f t="shared" si="2"/>
+        <v>24.616</v>
+      </c>
+      <c r="U19" s="30">
+        <f t="shared" si="2"/>
+        <v>269.90400000000005</v>
+      </c>
+      <c r="V19" s="30">
+        <f t="shared" si="2"/>
+        <v>2467.8599999999997</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="33"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A26" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="58"/>
+      <c r="H26" s="58"/>
+      <c r="I26" s="58"/>
+    </row>
+    <row r="27" spans="1:22" ht="32" x14ac:dyDescent="0.2">
+      <c r="A27" s="57"/>
+      <c r="B27" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" s="27"/>
+      <c r="F27" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="G27" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="H27" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="26" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>1</v>
+      </c>
+      <c r="B28" s="23">
+        <f>NetworkingLESS!N5</f>
+        <v>0.24545454545454545</v>
+      </c>
+      <c r="C28" s="23">
+        <f>NetworkingLESS!V5</f>
+        <v>0.24545454545454545</v>
+      </c>
+      <c r="D28" s="24">
+        <f>NetworkingLESS!AD5</f>
+        <v>0.24545454545454545</v>
+      </c>
+      <c r="E28" s="24"/>
+      <c r="F28" s="20">
+        <f>NetworkingLESS!E5</f>
+        <v>0.02</v>
+      </c>
+      <c r="G28" s="20">
+        <f>NetworkingLESS!K5</f>
+        <v>0</v>
+      </c>
+      <c r="H28" s="20">
+        <f>NetworkingLESS!S5</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="20">
+        <f>NetworkingLESS!AA5</f>
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29" s="23">
+        <f>NetworkingLESS!N6</f>
+        <v>0.60356652949245537</v>
+      </c>
+      <c r="C29" s="23">
+        <f>NetworkingLESS!V6</f>
+        <v>0.60356652949245537</v>
+      </c>
+      <c r="D29" s="24">
+        <f>NetworkingLESS!AD6</f>
+        <v>0.19204389574759945</v>
+      </c>
+      <c r="E29" s="24"/>
+      <c r="F29" s="20">
+        <f>NetworkingLESS!E6</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G29" s="20">
+        <f>NetworkingLESS!K6</f>
+        <v>0</v>
+      </c>
+      <c r="H29" s="20">
+        <f>NetworkingLESS!S6</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="20">
+        <f>NetworkingLESS!AA6</f>
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>3</v>
+      </c>
+      <c r="B30" s="23">
+        <f>NetworkingLESS!N7</f>
+        <v>0.51855181431840469</v>
+      </c>
+      <c r="C30" s="23">
+        <f>NetworkingLESS!V7</f>
+        <v>0.40209218698921217</v>
+      </c>
+      <c r="D30" s="24">
+        <f>NetworkingLESS!AD7</f>
+        <v>0.1443690748610657</v>
+      </c>
+      <c r="E30" s="24"/>
+      <c r="F30" s="20">
+        <f>NetworkingLESS!E7</f>
+        <v>0.1</v>
+      </c>
+      <c r="G30" s="20">
+        <f>NetworkingLESS!K7</f>
+        <v>0</v>
+      </c>
+      <c r="H30" s="20">
+        <f>NetworkingLESS!S7</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="20">
+        <f>NetworkingLESS!AA7</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31" s="23">
+        <f>NetworkingLESS!N8</f>
+        <v>0.62927627095543137</v>
+      </c>
+      <c r="C31" s="23">
+        <f>NetworkingLESS!V8</f>
+        <v>0.46388169551587843</v>
+      </c>
+      <c r="D31" s="24">
+        <f>NetworkingLESS!AD8</f>
+        <v>0.26298214529099084</v>
+      </c>
+      <c r="E31" s="24"/>
+      <c r="F31" s="20">
+        <f>NetworkingLESS!E8</f>
+        <v>0.27</v>
+      </c>
+      <c r="G31" s="20">
+        <f>NetworkingLESS!K8</f>
+        <v>0.02</v>
+      </c>
+      <c r="H31" s="20">
+        <f>NetworkingLESS!S8</f>
+        <v>0.05</v>
+      </c>
+      <c r="I31" s="20">
+        <f>NetworkingLESS!AA8</f>
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>5</v>
+      </c>
+      <c r="B32" s="23">
+        <f>NetworkingLESS!N9</f>
+        <v>0.68208098307816278</v>
+      </c>
+      <c r="C32" s="23">
+        <f>NetworkingLESS!V9</f>
+        <v>0.5952659145850121</v>
+      </c>
+      <c r="D32" s="24">
+        <f>NetworkingLESS!AD9</f>
+        <v>0.17913980660757453</v>
+      </c>
+      <c r="E32" s="24"/>
+      <c r="F32" s="20">
+        <f>NetworkingLESS!E9</f>
+        <v>0.41</v>
+      </c>
+      <c r="G32" s="20">
+        <f>NetworkingLESS!K9</f>
+        <v>0.05</v>
+      </c>
+      <c r="H32" s="20">
+        <f>NetworkingLESS!S9</f>
+        <v>0.09</v>
+      </c>
+      <c r="I32" s="20">
+        <f>NetworkingLESS!AA9</f>
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>6</v>
+      </c>
+      <c r="B33" s="23">
+        <f>NetworkingLESS!N10</f>
+        <v>0.31385668008840178</v>
+      </c>
+      <c r="C33" s="23">
+        <f>NetworkingLESS!V10</f>
+        <v>0.31343283582089554</v>
+      </c>
+      <c r="D33" s="24">
+        <f>NetworkingLESS!AD10</f>
+        <v>0.19297024007750296</v>
+      </c>
+      <c r="E33" s="24"/>
+      <c r="F33" s="20">
+        <f>NetworkingLESS!E10</f>
+        <v>0.63</v>
+      </c>
+      <c r="G33" s="20">
+        <f>NetworkingLESS!K10</f>
+        <v>0.1</v>
+      </c>
+      <c r="H33" s="20">
+        <f>NetworkingLESS!S10</f>
+        <v>0.19</v>
+      </c>
+      <c r="I33" s="20">
+        <f>NetworkingLESS!AA10</f>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>7</v>
+      </c>
+      <c r="B34" s="23">
+        <f>NetworkingLESS!N11</f>
+        <v>0.70056198747867648</v>
+      </c>
+      <c r="C34" s="23">
+        <f>NetworkingLESS!V11</f>
+        <v>0.52568776356693192</v>
+      </c>
+      <c r="D34" s="24">
+        <f>NetworkingLESS!AD11</f>
+        <v>0.18213070322038741</v>
+      </c>
+      <c r="E34" s="24"/>
+      <c r="F34" s="20">
+        <f>NetworkingLESS!E11</f>
+        <v>1.29</v>
+      </c>
+      <c r="G34" s="20">
+        <f>NetworkingLESS!K11</f>
+        <v>0.15</v>
+      </c>
+      <c r="H34" s="20">
+        <f>NetworkingLESS!S11</f>
+        <v>0.24</v>
+      </c>
+      <c r="I34" s="20">
+        <f>NetworkingLESS!AA11</f>
+        <v>2.2400000000000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>8</v>
+      </c>
+      <c r="B35" s="23">
+        <f>NetworkingLESS!N12</f>
+        <v>0.70038217385671719</v>
+      </c>
+      <c r="C35" s="23">
+        <f>NetworkingLESS!V12</f>
+        <v>0.68401023448633247</v>
+      </c>
+      <c r="D35" s="24">
+        <f>NetworkingLESS!AD12</f>
+        <v>0.24333894718659585</v>
+      </c>
+      <c r="E35" s="24"/>
+      <c r="F35" s="20">
+        <f>NetworkingLESS!E12</f>
+        <v>4.26</v>
+      </c>
+      <c r="G35" s="20">
+        <f>NetworkingLESS!K12</f>
+        <v>0.6</v>
+      </c>
+      <c r="H35" s="20">
+        <f>NetworkingLESS!S12</f>
+        <v>0.97</v>
+      </c>
+      <c r="I35" s="20">
+        <f>NetworkingLESS!AA12</f>
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>9</v>
+      </c>
+      <c r="B36" s="23">
+        <f>NetworkingLESS!N13</f>
+        <v>0.66356532099803756</v>
+      </c>
+      <c r="C36" s="23">
+        <f>NetworkingLESS!V13</f>
+        <v>0.66393327726380713</v>
+      </c>
+      <c r="D36" s="24">
+        <f>NetworkingLESS!AD13</f>
+        <v>0.17018102447034322</v>
+      </c>
+      <c r="E36" s="24"/>
+      <c r="F36" s="20">
+        <f>NetworkingLESS!E13</f>
+        <v>11.3</v>
+      </c>
+      <c r="G36" s="20">
+        <f>NetworkingLESS!K13</f>
+        <v>1.36</v>
+      </c>
+      <c r="H36" s="20">
+        <f>NetworkingLESS!S13</f>
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="I36" s="20">
+        <f>NetworkingLESS!AA13</f>
+        <v>20.100000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>10</v>
+      </c>
+      <c r="B37" s="23">
+        <f>NetworkingLESS!N14</f>
+        <v>0.63726798561345743</v>
+      </c>
+      <c r="C37" s="23">
+        <f>NetworkingLESS!V14</f>
+        <v>0.63810788608092273</v>
+      </c>
+      <c r="D37" s="24">
+        <f>NetworkingLESS!AD14</f>
+        <v>0.20905404045159803</v>
+      </c>
+      <c r="E37" s="24"/>
+      <c r="F37" s="20">
+        <f>NetworkingLESS!E14</f>
+        <v>24.03</v>
+      </c>
+      <c r="G37" s="20">
+        <f>NetworkingLESS!K14</f>
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="H37" s="20">
+        <f>NetworkingLESS!S14</f>
+        <v>3.88</v>
+      </c>
+      <c r="I37" s="20">
+        <f>NetworkingLESS!AA14</f>
+        <v>37.33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>11</v>
+      </c>
+      <c r="B38" s="23">
+        <f>NetworkingLESS!N15</f>
+        <v>0.70677433427903735</v>
+      </c>
+      <c r="C38" s="23">
+        <f>NetworkingLESS!V15</f>
+        <v>0.70766909437496006</v>
+      </c>
+      <c r="D38" s="24">
+        <f>NetworkingLESS!AD15</f>
+        <v>0.15677475109274661</v>
+      </c>
+      <c r="E38" s="24"/>
+      <c r="F38" s="20">
+        <f>NetworkingLESS!E15</f>
+        <v>43.93</v>
+      </c>
+      <c r="G38" s="20">
+        <f>NetworkingLESS!K15</f>
+        <v>3.8</v>
+      </c>
+      <c r="H38" s="20">
+        <f>NetworkingLESS!S15</f>
+        <v>6.13</v>
+      </c>
+      <c r="I38" s="20">
+        <f>NetworkingLESS!AA15</f>
+        <v>60.39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>12</v>
+      </c>
+      <c r="B39" s="23">
+        <f>NetworkingLESS!N16</f>
+        <v>0.75607481107934316</v>
+      </c>
+      <c r="C39" s="23">
+        <f>NetworkingLESS!V16</f>
+        <v>0.75674874395053215</v>
+      </c>
+      <c r="D39" s="24">
+        <f>NetworkingLESS!AD16</f>
+        <v>0.20066237973625439</v>
+      </c>
+      <c r="E39" s="24"/>
+      <c r="F39" s="20">
+        <f>NetworkingLESS!E16</f>
+        <v>309.95999999999998</v>
+      </c>
+      <c r="G39" s="20">
+        <f>NetworkingLESS!K16</f>
+        <v>15.53</v>
+      </c>
+      <c r="H39" s="20">
+        <f>NetworkingLESS!S16</f>
+        <v>25.1</v>
+      </c>
+      <c r="I39" s="20">
+        <f>NetworkingLESS!AA16</f>
+        <v>290.14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>13</v>
+      </c>
+      <c r="B40" s="23">
+        <f>NetworkingLESS!N17</f>
+        <v>0.7320626048674691</v>
+      </c>
+      <c r="C40" s="23">
+        <f>NetworkingLESS!V17</f>
+        <v>0.73310925639185764</v>
+      </c>
+      <c r="D40" s="24">
+        <f>NetworkingLESS!AD17</f>
+        <v>0.23946739464697092</v>
+      </c>
+      <c r="E40" s="24"/>
+      <c r="F40" s="20">
+        <f>NetworkingLESS!E17</f>
+        <v>1732.32</v>
+      </c>
+      <c r="G40" s="20">
+        <f>NetworkingLESS!K17</f>
+        <v>35.65</v>
+      </c>
+      <c r="H40" s="20">
+        <f>NetworkingLESS!S17</f>
+        <v>57.41</v>
+      </c>
+      <c r="I40" s="20">
+        <f>NetworkingLESS!AA17</f>
+        <v>749.64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>14</v>
+      </c>
+      <c r="B41" s="23">
+        <f>NetworkingLESS!N18</f>
+        <v>0.76867450216613709</v>
+      </c>
+      <c r="C41" s="23">
+        <f>NetworkingLESS!V18</f>
+        <v>0.76054204679719239</v>
+      </c>
+      <c r="D41" s="24">
+        <f>NetworkingLESS!AD18</f>
+        <v>0.26318025605196571</v>
+      </c>
+      <c r="E41" s="24"/>
+      <c r="F41" s="20">
+        <f>NetworkingLESS!E18</f>
+        <v>9234.91</v>
+      </c>
+      <c r="G41" s="20">
+        <f>NetworkingLESS!K18</f>
+        <v>66.44</v>
+      </c>
+      <c r="H41" s="20">
+        <f>NetworkingLESS!S18</f>
+        <v>104.96</v>
+      </c>
+      <c r="I41" s="20">
+        <f>NetworkingLESS!AA18</f>
+        <v>1209.1400000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A42" s="22">
+        <v>15</v>
+      </c>
+      <c r="B42" s="23">
+        <f>NetworkingLESS!N19</f>
+        <v>0.68917968979685051</v>
+      </c>
+      <c r="C42" s="23">
+        <f>NetworkingLESS!V19</f>
+        <v>0.68987193993093321</v>
+      </c>
+      <c r="D42" s="24">
+        <f>NetworkingLESS!AD19</f>
+        <v>0.19108570481753034</v>
+      </c>
+      <c r="E42" s="24"/>
+      <c r="F42" s="20">
+        <f>NetworkingLESS!E19</f>
+        <v>50792.01</v>
+      </c>
+      <c r="G42" s="20">
+        <f>NetworkingLESS!K19</f>
+        <v>109.15</v>
+      </c>
+      <c r="H42" s="20">
+        <f>NetworkingLESS!S19</f>
+        <v>168.04</v>
+      </c>
+      <c r="I42" s="20">
+        <f>NetworkingLESS!AA19</f>
+        <v>1668.64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B43" s="29">
+        <f t="shared" ref="B43:D43" si="3">AVERAGE(B28:B42)</f>
+        <v>0.62315534890154178</v>
+      </c>
+      <c r="C43" s="29">
+        <f t="shared" si="3"/>
+        <v>0.58555826338009809</v>
+      </c>
+      <c r="D43" s="29">
+        <f t="shared" si="3"/>
+        <v>0.2048556606475781</v>
+      </c>
+      <c r="E43" s="29"/>
+      <c r="F43" s="30">
+        <f t="shared" ref="F43:I43" si="4">AVERAGE(F28:F42)</f>
+        <v>4143.7006666666666</v>
+      </c>
+      <c r="G43" s="30">
+        <f t="shared" si="4"/>
+        <v>15.685333333333334</v>
+      </c>
+      <c r="H43" s="30">
+        <f t="shared" si="4"/>
+        <v>24.616</v>
+      </c>
+      <c r="I43" s="30">
+        <f t="shared" si="4"/>
+        <v>269.90400000000005</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="R2:V2"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="F2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D29F935A-7EB1-C14F-935D-FC60577D8149}">
   <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -20333,7 +22283,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AECD3073-CA55-8949-9F2C-A8E081473853}">
   <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -20367,14 +22317,14 @@
         <v>1</v>
       </c>
       <c r="B3" s="50">
-        <f>NetworkingLESS!AP5</f>
+        <f>NetworkingLESS!AR5</f>
         <v>1.264367816091954</v>
       </c>
       <c r="D3" s="38">
         <v>1</v>
       </c>
       <c r="E3" s="52">
-        <f>NetworkingLESS!AS5</f>
+        <f>NetworkingLESS!AU5</f>
         <v>1.090496804782519</v>
       </c>
     </row>
@@ -20383,14 +22333,14 @@
         <v>2</v>
       </c>
       <c r="B4" s="50">
-        <f>NetworkingLESS!AP6</f>
+        <f>NetworkingLESS!AR6</f>
         <v>1.1815235008103728</v>
       </c>
       <c r="D4" s="9">
         <v>2</v>
       </c>
       <c r="E4" s="52">
-        <f>NetworkingLESS!AS6</f>
+        <f>NetworkingLESS!AU6</f>
         <v>2.189274447949527</v>
       </c>
     </row>
@@ -20399,14 +22349,14 @@
         <v>3</v>
       </c>
       <c r="B5" s="50">
-        <f>NetworkingLESS!AP7</f>
+        <f>NetworkingLESS!AR7</f>
         <v>1.9870087690808704</v>
       </c>
       <c r="D5" s="9">
         <v>3</v>
       </c>
       <c r="E5" s="52">
-        <f>NetworkingLESS!AS7</f>
+        <f>NetworkingLESS!AU7</f>
         <v>3.0635853244548898</v>
       </c>
     </row>
@@ -20415,14 +22365,14 @@
         <v>4</v>
       </c>
       <c r="B6" s="50">
-        <f>NetworkingLESS!AP8</f>
+        <f>NetworkingLESS!AR8</f>
         <v>1.6695869837296622</v>
       </c>
       <c r="D6" s="9">
         <v>4</v>
       </c>
       <c r="E6" s="52">
-        <f>NetworkingLESS!AS8</f>
+        <f>NetworkingLESS!AU8</f>
         <v>3.2994710266891079</v>
       </c>
     </row>
@@ -20431,14 +22381,14 @@
         <v>5</v>
       </c>
       <c r="B7" s="50">
-        <f>NetworkingLESS!AP9</f>
+        <f>NetworkingLESS!AR9</f>
         <v>2.3034802784222737</v>
       </c>
       <c r="D7" s="9">
         <v>5</v>
       </c>
       <c r="E7" s="52">
-        <f>NetworkingLESS!AS9</f>
+        <f>NetworkingLESS!AU9</f>
         <v>2.8342973172532613</v>
       </c>
     </row>
@@ -20447,14 +22397,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="50">
-        <f>NetworkingLESS!AP10</f>
+        <f>NetworkingLESS!AR10</f>
         <v>1.4001526005680132</v>
       </c>
       <c r="D8" s="9">
         <v>6</v>
       </c>
       <c r="E8" s="52">
-        <f>NetworkingLESS!AS10</f>
+        <f>NetworkingLESS!AU10</f>
         <v>1.7958758239900841</v>
       </c>
     </row>
@@ -20463,14 +22413,14 @@
         <v>7</v>
       </c>
       <c r="B9" s="50">
-        <f>NetworkingLESS!AP11</f>
+        <f>NetworkingLESS!AR11</f>
         <v>1.9103887510339124</v>
       </c>
       <c r="D9" s="9">
         <v>7</v>
       </c>
       <c r="E9" s="52">
-        <f>NetworkingLESS!AS11</f>
+        <f>NetworkingLESS!AU11</f>
         <v>4.7276299339167709</v>
       </c>
     </row>
@@ -20479,14 +22429,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="50">
-        <f>NetworkingLESS!AP12</f>
+        <f>NetworkingLESS!AR12</f>
         <v>2.194612268107186</v>
       </c>
       <c r="D10" s="9">
         <v>8</v>
       </c>
       <c r="E10" s="52">
-        <f>NetworkingLESS!AS12</f>
+        <f>NetworkingLESS!AU12</f>
         <v>3.20925347507626</v>
       </c>
     </row>
@@ -20495,14 +22445,14 @@
         <v>9</v>
       </c>
       <c r="B11" s="50">
-        <f>NetworkingLESS!AP13</f>
+        <f>NetworkingLESS!AR13</f>
         <v>1.6686743465294427</v>
       </c>
       <c r="D11" s="9">
         <v>9</v>
       </c>
       <c r="E11" s="52">
-        <f>NetworkingLESS!AS13</f>
+        <f>NetworkingLESS!AU13</f>
         <v>3.2540095877615043</v>
       </c>
     </row>
@@ -20511,14 +22461,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="50">
-        <f>NetworkingLESS!AP14</f>
+        <f>NetworkingLESS!AR14</f>
         <v>2.1977245372242495</v>
       </c>
       <c r="D12" s="9">
         <v>10</v>
       </c>
       <c r="E12" s="52">
-        <f>NetworkingLESS!AS14</f>
+        <f>NetworkingLESS!AU14</f>
         <v>2.2357860687223137</v>
       </c>
     </row>
@@ -20527,14 +22477,14 @@
         <v>11</v>
       </c>
       <c r="B13" s="50">
-        <f>NetworkingLESS!AP15</f>
+        <f>NetworkingLESS!AR15</f>
         <v>2.4277194994434512</v>
       </c>
       <c r="D13" s="9">
         <v>11</v>
       </c>
       <c r="E13" s="52">
-        <f>NetworkingLESS!AS15</f>
+        <f>NetworkingLESS!AU15</f>
         <v>1.9093339257554292</v>
       </c>
     </row>
@@ -20543,14 +22493,14 @@
         <v>12</v>
       </c>
       <c r="B14" s="50">
-        <f>NetworkingLESS!AP16</f>
+        <f>NetworkingLESS!AR16</f>
         <v>4.000458780030268</v>
       </c>
       <c r="D14" s="9">
         <v>12</v>
       </c>
       <c r="E14" s="52">
-        <f>NetworkingLESS!AS16</f>
+        <f>NetworkingLESS!AU16</f>
         <v>3.4347782396199698</v>
       </c>
     </row>
@@ -20559,14 +22509,14 @@
         <v>13</v>
       </c>
       <c r="B15" s="50">
-        <f>NetworkingLESS!AP17</f>
+        <f>NetworkingLESS!AR17</f>
         <v>5.1860774191743264</v>
       </c>
       <c r="D15" s="9">
         <v>13</v>
       </c>
       <c r="E15" s="52">
-        <f>NetworkingLESS!AS17</f>
+        <f>NetworkingLESS!AU17</f>
         <v>2.144722882502724</v>
       </c>
     </row>
@@ -20575,14 +22525,14 @@
         <v>14</v>
       </c>
       <c r="B16" s="50">
-        <f>NetworkingLESS!AP18</f>
+        <f>NetworkingLESS!AR18</f>
         <v>7.0191855263593892</v>
       </c>
       <c r="D16" s="9">
         <v>14</v>
       </c>
       <c r="E16" s="52">
-        <f>NetworkingLESS!AS18</f>
+        <f>NetworkingLESS!AU18</f>
         <v>2.3275218945928802</v>
       </c>
     </row>
@@ -20591,14 +22541,14 @@
         <v>15</v>
       </c>
       <c r="B17" s="50">
-        <f>NetworkingLESS!AP19</f>
+        <f>NetworkingLESS!AR19</f>
         <v>3.0721206228462759</v>
       </c>
       <c r="D17" s="9">
         <v>15</v>
       </c>
       <c r="E17" s="52">
-        <f>NetworkingLESS!AS19</f>
+        <f>NetworkingLESS!AU19</f>
         <v>4.3454050733470773</v>
       </c>
     </row>
@@ -20614,7 +22564,7 @@
         <v>16</v>
       </c>
       <c r="E18" s="52">
-        <f>NetworkingLESS!AS20</f>
+        <f>NetworkingLESS!AU20</f>
         <v>2.5317209292925935</v>
       </c>
     </row>
@@ -20625,7 +22575,7 @@
         <v>17</v>
       </c>
       <c r="E19" s="52">
-        <f>NetworkingLESS!AS21</f>
+        <f>NetworkingLESS!AU21</f>
         <v>3.1157126291999697</v>
       </c>
     </row>
@@ -20636,7 +22586,7 @@
         <v>18</v>
       </c>
       <c r="E20" s="52">
-        <f>NetworkingLESS!AS22</f>
+        <f>NetworkingLESS!AU22</f>
         <v>1.8803777281087408</v>
       </c>
     </row>
@@ -20647,7 +22597,7 @@
         <v>19</v>
       </c>
       <c r="E21" s="52">
-        <f>NetworkingLESS!AS23</f>
+        <f>NetworkingLESS!AU23</f>
         <v>5.9357221288367672</v>
       </c>
     </row>
@@ -20658,7 +22608,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="52">
-        <f>NetworkingLESS!AS24</f>
+        <f>NetworkingLESS!AU24</f>
         <v>3.4341686913827978</v>
       </c>
     </row>
@@ -20669,7 +22619,7 @@
         <v>21</v>
       </c>
       <c r="E23" s="52">
-        <f>NetworkingLESS!AS25</f>
+        <f>NetworkingLESS!AU25</f>
         <v>2.1346743804750723</v>
       </c>
     </row>
@@ -25297,7 +27247,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C03F23-5B48-E740-AE12-B3F8383D5054}">
-  <dimension ref="A2:AT26"/>
+  <dimension ref="A2:AV26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
@@ -25338,14 +27288,16 @@
     <col min="39" max="39" width="4" style="19" customWidth="1"/>
     <col min="40" max="40" width="18" customWidth="1"/>
     <col min="41" max="41" width="22.6640625" customWidth="1"/>
-    <col min="42" max="42" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="4" style="19" customWidth="1"/>
-    <col min="44" max="44" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="10" customWidth="1"/>
+    <col min="43" max="43" width="11.5" customWidth="1"/>
+    <col min="44" max="44" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="4" style="19" customWidth="1"/>
+    <col min="46" max="46" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:48" x14ac:dyDescent="0.2">
       <c r="E2" s="54" t="s">
         <v>0</v>
       </c>
@@ -25391,12 +27343,14 @@
       </c>
       <c r="AO2" s="54"/>
       <c r="AP2" s="54"/>
-      <c r="AR2" s="54" t="s">
+      <c r="AQ2" s="54"/>
+      <c r="AR2" s="54"/>
+      <c r="AT2" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="AS2" s="54"/>
-    </row>
-    <row r="3" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="AU2" s="54"/>
+    </row>
+    <row r="3" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -25503,16 +27457,22 @@
         <v>55</v>
       </c>
       <c r="AP3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>63</v>
+      </c>
+      <c r="AR3" t="s">
         <v>50</v>
       </c>
-      <c r="AR3" t="s">
+      <c r="AT3" t="s">
         <v>11</v>
       </c>
-      <c r="AS3" t="s">
+      <c r="AU3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>0</v>
       </c>
@@ -25627,7 +27587,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -25747,19 +27707,25 @@
       <c r="AO5">
         <v>4263</v>
       </c>
-      <c r="AP5" s="4">
+      <c r="AP5">
+        <v>1</v>
+      </c>
+      <c r="AQ5" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="AR5" s="4">
         <f>F5/AO5</f>
         <v>1.264367816091954</v>
       </c>
-      <c r="AR5">
+      <c r="AT5">
         <v>4851</v>
       </c>
-      <c r="AS5" s="4">
-        <f>AI5/AR5</f>
+      <c r="AU5" s="4">
+        <f>AI5/AT5</f>
         <v>1.090496804782519</v>
       </c>
     </row>
-    <row r="6" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2</v>
       </c>
@@ -25879,19 +27845,25 @@
       <c r="AO6">
         <v>6170</v>
       </c>
-      <c r="AP6" s="4">
+      <c r="AP6">
+        <v>1</v>
+      </c>
+      <c r="AQ6" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="AR6" s="4">
         <f>F6/AO6</f>
         <v>1.1815235008103728</v>
       </c>
-      <c r="AR6">
+      <c r="AT6">
         <v>3170</v>
       </c>
-      <c r="AS6" s="4">
-        <f>AI6/AR6</f>
+      <c r="AU6" s="4">
+        <f>AI6/AT6</f>
         <v>2.189274447949527</v>
       </c>
     </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>3</v>
       </c>
@@ -26011,19 +27983,25 @@
       <c r="AO7">
         <v>12316</v>
       </c>
-      <c r="AP7" s="4">
+      <c r="AP7">
+        <v>3</v>
+      </c>
+      <c r="AQ7" s="4">
+        <v>0.26</v>
+      </c>
+      <c r="AR7" s="4">
         <f>F7/AO7</f>
         <v>1.9870087690808704</v>
       </c>
-      <c r="AR7">
+      <c r="AT7">
         <v>7659</v>
       </c>
-      <c r="AS7" s="4">
-        <f>AI7/AR7</f>
+      <c r="AU7" s="4">
+        <f>AI7/AT7</f>
         <v>3.0635853244548898</v>
       </c>
     </row>
-    <row r="8" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>4</v>
       </c>
@@ -26143,19 +28121,25 @@
       <c r="AO8">
         <v>17578</v>
       </c>
-      <c r="AP8" s="4">
+      <c r="AP8">
+        <v>4</v>
+      </c>
+      <c r="AQ8" s="4">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="AR8" s="4">
         <f>F8/AO8</f>
         <v>1.6695869837296622</v>
       </c>
-      <c r="AR8">
+      <c r="AT8">
         <v>8318</v>
       </c>
-      <c r="AS8" s="4">
-        <f>AI8/AR8</f>
+      <c r="AU8" s="4">
+        <f>AI8/AT8</f>
         <v>3.2994710266891079</v>
       </c>
     </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>5</v>
       </c>
@@ -26275,19 +28259,25 @@
       <c r="AO9">
         <v>43100</v>
       </c>
-      <c r="AP9" s="4">
+      <c r="AP9">
+        <v>5</v>
+      </c>
+      <c r="AQ9" s="4">
+        <v>0.88</v>
+      </c>
+      <c r="AR9" s="4">
         <f>F9/AO9</f>
         <v>2.3034802784222737</v>
       </c>
-      <c r="AR9">
+      <c r="AT9">
         <v>32504</v>
       </c>
-      <c r="AS9" s="4">
-        <f>AI9/AR9</f>
+      <c r="AU9" s="4">
+        <f>AI9/AT9</f>
         <v>2.8342973172532613</v>
       </c>
     </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>6</v>
       </c>
@@ -26407,19 +28397,25 @@
       <c r="AO10">
         <v>23591</v>
       </c>
-      <c r="AP10" s="4">
+      <c r="AP10">
+        <v>8</v>
+      </c>
+      <c r="AQ10" s="4">
+        <v>1.28</v>
+      </c>
+      <c r="AR10" s="4">
         <f>F10/AO10</f>
         <v>1.4001526005680132</v>
       </c>
-      <c r="AR10">
+      <c r="AT10">
         <v>17749</v>
       </c>
-      <c r="AS10" s="4">
-        <f>AI10/AR10</f>
+      <c r="AU10" s="4">
+        <f>AI10/AT10</f>
         <v>1.7958758239900841</v>
       </c>
     </row>
-    <row r="11" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>7</v>
       </c>
@@ -26539,19 +28535,25 @@
       <c r="AO11">
         <v>60450</v>
       </c>
-      <c r="AP11" s="4">
+      <c r="AP11">
+        <v>8</v>
+      </c>
+      <c r="AQ11" s="4">
+        <v>1.28</v>
+      </c>
+      <c r="AR11" s="4">
         <f>F11/AO11</f>
         <v>1.9103887510339124</v>
       </c>
-      <c r="AR11">
+      <c r="AT11">
         <v>22396</v>
       </c>
-      <c r="AS11" s="4">
-        <f>AI11/AR11</f>
+      <c r="AU11" s="4">
+        <f>AI11/AT11</f>
         <v>4.7276299339167709</v>
       </c>
     </row>
-    <row r="12" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>8</v>
       </c>
@@ -26671,19 +28673,25 @@
       <c r="AO12">
         <v>168828</v>
       </c>
-      <c r="AP12" s="4">
+      <c r="AP12">
+        <v>10</v>
+      </c>
+      <c r="AQ12" s="4">
+        <v>2.36</v>
+      </c>
+      <c r="AR12" s="4">
         <f>F12/AO12</f>
         <v>2.194612268107186</v>
       </c>
-      <c r="AR12">
+      <c r="AT12">
         <v>109494</v>
       </c>
-      <c r="AS12" s="4">
-        <f>AI12/AR12</f>
+      <c r="AU12" s="4">
+        <f>AI12/AT12</f>
         <v>3.20925347507626</v>
       </c>
     </row>
-    <row r="13" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>9</v>
       </c>
@@ -26803,19 +28811,25 @@
       <c r="AO13">
         <v>478828</v>
       </c>
-      <c r="AP13" s="4">
+      <c r="AP13">
+        <v>12</v>
+      </c>
+      <c r="AQ13" s="4">
+        <v>3.59</v>
+      </c>
+      <c r="AR13" s="4">
         <f>F13/AO13</f>
         <v>1.6686743465294427</v>
       </c>
-      <c r="AR13">
+      <c r="AT13">
         <v>226956</v>
       </c>
-      <c r="AS13" s="4">
-        <f>AI13/AR13</f>
+      <c r="AU13" s="4">
+        <f>AI13/AT13</f>
         <v>3.2540095877615043</v>
       </c>
     </row>
-    <row r="14" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>10</v>
       </c>
@@ -26935,20 +28949,26 @@
       <c r="AO14">
         <v>420398</v>
       </c>
-      <c r="AP14" s="4">
+      <c r="AP14">
+        <v>15</v>
+      </c>
+      <c r="AQ14" s="4">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="AR14" s="4">
         <f>F14/AO14</f>
         <v>2.1977245372242495</v>
       </c>
-      <c r="AR14">
+      <c r="AT14">
         <v>390761</v>
       </c>
-      <c r="AS14" s="4">
-        <f>AI14/AR14</f>
+      <c r="AU14" s="4">
+        <f>AI14/AT14</f>
         <v>2.2357860687223137</v>
       </c>
-      <c r="AT14" s="6"/>
-    </row>
-    <row r="15" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="AV14" s="6"/>
+    </row>
+    <row r="15" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>11</v>
       </c>
@@ -27068,20 +29088,26 @@
       <c r="AO15">
         <v>444705</v>
       </c>
-      <c r="AP15" s="4">
+      <c r="AP15">
+        <v>17</v>
+      </c>
+      <c r="AQ15" s="4">
+        <v>5.98</v>
+      </c>
+      <c r="AR15" s="4">
         <f>F15/AO15</f>
         <v>2.4277194994434512</v>
       </c>
-      <c r="AR15">
+      <c r="AT15">
         <v>549158</v>
       </c>
-      <c r="AS15" s="4">
-        <f>AI15/AR15</f>
+      <c r="AU15" s="4">
+        <f>AI15/AT15</f>
         <v>1.9093339257554292</v>
       </c>
-      <c r="AT15" s="6"/>
-    </row>
-    <row r="16" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="AV15" s="6"/>
+    </row>
+    <row r="16" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>12</v>
       </c>
@@ -27201,20 +29227,26 @@
       <c r="AO16">
         <v>882776</v>
       </c>
-      <c r="AP16" s="4">
+      <c r="AP16">
+        <v>27</v>
+      </c>
+      <c r="AQ16" s="4">
+        <v>11.98</v>
+      </c>
+      <c r="AR16" s="4">
         <f>F16/AO16</f>
         <v>4.000458780030268</v>
       </c>
-      <c r="AR16">
+      <c r="AT16">
         <v>985185</v>
       </c>
-      <c r="AS16" s="4">
-        <f>AI16/AR16</f>
+      <c r="AU16" s="4">
+        <f>AI16/AT16</f>
         <v>3.4347782396199698</v>
       </c>
-      <c r="AT16" s="6"/>
-    </row>
-    <row r="17" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="AV16" s="6"/>
+    </row>
+    <row r="17" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>13</v>
       </c>
@@ -27334,20 +29366,26 @@
       <c r="AO17">
         <v>1143696</v>
       </c>
-      <c r="AP17" s="4">
+      <c r="AP17">
+        <v>36</v>
+      </c>
+      <c r="AQ17" s="4">
+        <v>17.989999999999998</v>
+      </c>
+      <c r="AR17" s="4">
         <f>F17/AO17</f>
         <v>5.1860774191743264</v>
       </c>
-      <c r="AR17">
+      <c r="AT17">
         <v>2504407</v>
       </c>
-      <c r="AS17" s="4">
-        <f>AI17/AR17</f>
+      <c r="AU17" s="4">
+        <f>AI17/AT17</f>
         <v>2.144722882502724</v>
       </c>
-      <c r="AT17" s="6"/>
-    </row>
-    <row r="18" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="AV17" s="6"/>
+    </row>
+    <row r="18" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>14</v>
       </c>
@@ -27467,20 +29505,26 @@
       <c r="AO18">
         <v>1690024</v>
       </c>
-      <c r="AP18" s="4">
+      <c r="AP18">
+        <v>45</v>
+      </c>
+      <c r="AQ18" s="4">
+        <v>23.99</v>
+      </c>
+      <c r="AR18" s="4">
         <f>F18/AO18</f>
         <v>7.0191855263593892</v>
       </c>
-      <c r="AR18">
+      <c r="AT18">
         <v>4855080</v>
       </c>
-      <c r="AS18" s="4">
-        <f>AI18/AR18</f>
+      <c r="AU18" s="4">
+        <f>AI18/AT18</f>
         <v>2.3275218945928802</v>
       </c>
-      <c r="AT18" s="6"/>
-    </row>
-    <row r="19" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="AV18" s="6"/>
+    </row>
+    <row r="19" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>15</v>
       </c>
@@ -27600,20 +29644,26 @@
       <c r="AO19">
         <v>4196220</v>
       </c>
-      <c r="AP19" s="4">
+      <c r="AP19">
+        <v>55</v>
+      </c>
+      <c r="AQ19" s="4">
+        <v>30.06</v>
+      </c>
+      <c r="AR19" s="4">
         <f>F19/AO19</f>
         <v>3.0721206228462759</v>
       </c>
-      <c r="AR19">
+      <c r="AT19">
         <v>2798271</v>
       </c>
-      <c r="AS19" s="4">
-        <f>AI19/AR19</f>
+      <c r="AU19" s="4">
+        <f>AI19/AT19</f>
         <v>4.3454050733470773</v>
       </c>
-      <c r="AT19" s="6"/>
-    </row>
-    <row r="20" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="AV19" s="6"/>
+    </row>
+    <row r="20" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>16</v>
       </c>
@@ -27701,20 +29751,21 @@
       <c r="AO20" t="s">
         <v>52</v>
       </c>
-      <c r="AP20" s="4">
-        <f>AVERAGE(AP5:AP19)</f>
+      <c r="AQ20" s="66"/>
+      <c r="AR20" s="4">
+        <f>AVERAGE(AR5:AR19)</f>
         <v>2.6322054466301097</v>
       </c>
-      <c r="AR20">
+      <c r="AT20">
         <v>6135807</v>
       </c>
-      <c r="AS20" s="4">
-        <f>AI20/AR20</f>
+      <c r="AU20" s="4">
+        <f>AI20/AT20</f>
         <v>2.5317209292925935</v>
       </c>
-      <c r="AT20" s="6"/>
-    </row>
-    <row r="21" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="AV20" s="6"/>
+    </row>
+    <row r="21" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>17</v>
       </c>
@@ -27799,16 +29850,17 @@
         <f t="shared" si="13"/>
         <v>132.8531759053088</v>
       </c>
-      <c r="AR21">
+      <c r="AQ21" s="66"/>
+      <c r="AT21">
         <v>7276898</v>
       </c>
-      <c r="AS21" s="4">
-        <f>AI21/AR21</f>
+      <c r="AU21" s="4">
+        <f>AI21/AT21</f>
         <v>3.1157126291999697</v>
       </c>
-      <c r="AT21" s="6"/>
-    </row>
-    <row r="22" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="AV21" s="6"/>
+    </row>
+    <row r="22" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>18</v>
       </c>
@@ -27893,16 +29945,17 @@
         <f t="shared" si="13"/>
         <v>181.57239706970927</v>
       </c>
-      <c r="AR22">
+      <c r="AQ22" s="66"/>
+      <c r="AT22">
         <v>18914981</v>
       </c>
-      <c r="AS22" s="4">
-        <f>AI22/AR22</f>
+      <c r="AU22" s="4">
+        <f>AI22/AT22</f>
         <v>1.8803777281087408</v>
       </c>
-      <c r="AT22" s="6"/>
-    </row>
-    <row r="23" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="AV22" s="6"/>
+    </row>
+    <row r="23" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>19</v>
       </c>
@@ -27987,16 +30040,17 @@
         <f t="shared" si="13"/>
         <v>282.84032714069679</v>
       </c>
-      <c r="AR23">
+      <c r="AQ23" s="66"/>
+      <c r="AT23">
         <v>13045096</v>
       </c>
-      <c r="AS23" s="4">
-        <f>AI23/AR23</f>
+      <c r="AU23" s="4">
+        <f>AI23/AT23</f>
         <v>5.9357221288367672</v>
       </c>
-      <c r="AT23" s="6"/>
-    </row>
-    <row r="24" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="AV23" s="6"/>
+    </row>
+    <row r="24" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>20</v>
       </c>
@@ -28081,16 +30135,17 @@
         <f t="shared" si="13"/>
         <v>272.97635211267607</v>
       </c>
-      <c r="AR24">
+      <c r="AQ24" s="66"/>
+      <c r="AT24">
         <v>28218359</v>
       </c>
-      <c r="AS24" s="4">
-        <f>AI24/AR24</f>
+      <c r="AU24" s="4">
+        <f>AI24/AT24</f>
         <v>3.4341686913827978</v>
       </c>
-      <c r="AT24" s="6"/>
-    </row>
-    <row r="25" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="AV24" s="6"/>
+    </row>
+    <row r="25" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>21</v>
       </c>
@@ -28175,16 +30230,17 @@
         <f t="shared" si="13"/>
         <v>291.45039442234565</v>
       </c>
-      <c r="AR25">
+      <c r="AQ25" s="66"/>
+      <c r="AT25">
         <v>46782944</v>
       </c>
-      <c r="AS25" s="4">
-        <f>AI25/AR25</f>
+      <c r="AU25" s="4">
+        <f>AI25/AT25</f>
         <v>2.1346743804750723</v>
       </c>
-      <c r="AT25" s="6"/>
-    </row>
-    <row r="26" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="AV25" s="6"/>
+    </row>
+    <row r="26" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>22</v>
       </c>
@@ -28269,24 +30325,25 @@
         <f t="shared" si="13"/>
         <v>303.55061718369336</v>
       </c>
-      <c r="AR26" t="s">
+      <c r="AQ26" s="66"/>
+      <c r="AT26" t="s">
         <v>52</v>
       </c>
-      <c r="AS26" s="4">
-        <f ca="1">AVERAGE(AS5:AS26)</f>
+      <c r="AU26" s="4">
+        <f ca="1">AVERAGE(AU5:AU26)</f>
         <v>2.8997056339862035</v>
       </c>
-      <c r="AT26" s="6"/>
+      <c r="AV26" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="AR2:AS2"/>
+    <mergeCell ref="AT2:AU2"/>
     <mergeCell ref="E2:H2"/>
     <mergeCell ref="K2:O2"/>
     <mergeCell ref="S2:W2"/>
     <mergeCell ref="AA2:AE2"/>
     <mergeCell ref="AH2:AL2"/>
-    <mergeCell ref="AN2:AP2"/>
+    <mergeCell ref="AN2:AR2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -28294,6 +30351,346 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA590A30-06BD-EE47-BF61-4C8D60D0B521}">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5" customWidth="1"/>
+    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="64">
+        <v>7</v>
+      </c>
+      <c r="B2" s="64">
+        <v>4</v>
+      </c>
+      <c r="C2" s="64">
+        <v>6</v>
+      </c>
+      <c r="D2" s="64">
+        <v>3</v>
+      </c>
+      <c r="E2" s="65">
+        <f>A2/C2</f>
+        <v>1.1666666666666667</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="64">
+        <v>8</v>
+      </c>
+      <c r="B3" s="64">
+        <v>4</v>
+      </c>
+      <c r="C3" s="64">
+        <v>6</v>
+      </c>
+      <c r="D3" s="64">
+        <v>4</v>
+      </c>
+      <c r="E3" s="65">
+        <f t="shared" ref="E3:E18" si="0">A3/C3</f>
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="64">
+        <v>9</v>
+      </c>
+      <c r="B4" s="64">
+        <v>4</v>
+      </c>
+      <c r="C4" s="64">
+        <v>8</v>
+      </c>
+      <c r="D4" s="64">
+        <v>7</v>
+      </c>
+      <c r="E4" s="65">
+        <f t="shared" si="0"/>
+        <v>1.125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="64">
+        <v>11</v>
+      </c>
+      <c r="B5" s="64">
+        <v>4</v>
+      </c>
+      <c r="C5" s="64">
+        <v>10</v>
+      </c>
+      <c r="D5" s="64">
+        <v>10</v>
+      </c>
+      <c r="E5" s="65">
+        <f t="shared" si="0"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="64">
+        <v>13</v>
+      </c>
+      <c r="B6" s="64">
+        <v>4</v>
+      </c>
+      <c r="C6" s="64">
+        <v>10</v>
+      </c>
+      <c r="D6" s="64">
+        <v>13</v>
+      </c>
+      <c r="E6" s="65">
+        <f t="shared" si="0"/>
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="64">
+        <v>14</v>
+      </c>
+      <c r="B7" s="64">
+        <v>4</v>
+      </c>
+      <c r="C7" s="64">
+        <v>11</v>
+      </c>
+      <c r="D7" s="64">
+        <v>15</v>
+      </c>
+      <c r="E7" s="65">
+        <f t="shared" si="0"/>
+        <v>1.2727272727272727</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="64">
+        <v>14</v>
+      </c>
+      <c r="B8" s="64">
+        <v>4</v>
+      </c>
+      <c r="C8" s="64">
+        <v>11</v>
+      </c>
+      <c r="D8" s="64">
+        <v>15</v>
+      </c>
+      <c r="E8" s="65">
+        <f t="shared" si="0"/>
+        <v>1.2727272727272727</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="64">
+        <v>16</v>
+      </c>
+      <c r="B9" s="64">
+        <v>4</v>
+      </c>
+      <c r="C9" s="64">
+        <v>11</v>
+      </c>
+      <c r="D9" s="64">
+        <v>18</v>
+      </c>
+      <c r="E9" s="65">
+        <f t="shared" si="0"/>
+        <v>1.4545454545454546</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="64">
+        <v>16</v>
+      </c>
+      <c r="B10" s="64">
+        <v>4</v>
+      </c>
+      <c r="C10" s="64">
+        <v>12</v>
+      </c>
+      <c r="D10" s="64">
+        <v>20</v>
+      </c>
+      <c r="E10" s="65">
+        <f t="shared" si="0"/>
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="64">
+        <v>16</v>
+      </c>
+      <c r="B11" s="64">
+        <v>4</v>
+      </c>
+      <c r="C11" s="64">
+        <v>14</v>
+      </c>
+      <c r="D11" s="64">
+        <v>22</v>
+      </c>
+      <c r="E11" s="65">
+        <f t="shared" si="0"/>
+        <v>1.1428571428571428</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="64">
+        <v>19</v>
+      </c>
+      <c r="B12" s="64">
+        <v>4</v>
+      </c>
+      <c r="C12" s="64">
+        <v>16</v>
+      </c>
+      <c r="D12" s="64">
+        <v>36</v>
+      </c>
+      <c r="E12" s="65">
+        <f t="shared" si="0"/>
+        <v>1.1875</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="64">
+        <v>20</v>
+      </c>
+      <c r="B13" s="64">
+        <v>4</v>
+      </c>
+      <c r="C13" s="64">
+        <v>19</v>
+      </c>
+      <c r="D13" s="64">
+        <v>60</v>
+      </c>
+      <c r="E13" s="65">
+        <f t="shared" si="0"/>
+        <v>1.0526315789473684</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="64">
+        <v>20</v>
+      </c>
+      <c r="B14" s="64">
+        <v>4</v>
+      </c>
+      <c r="C14" s="64">
+        <v>20</v>
+      </c>
+      <c r="D14" s="64">
+        <v>80</v>
+      </c>
+      <c r="E14" s="65">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="64">
+        <v>20</v>
+      </c>
+      <c r="B15" s="64">
+        <v>4</v>
+      </c>
+      <c r="C15" s="64">
+        <v>20</v>
+      </c>
+      <c r="D15" s="64">
+        <v>102</v>
+      </c>
+      <c r="E15" s="65">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="64">
+        <v>20</v>
+      </c>
+      <c r="B16" s="64">
+        <v>4</v>
+      </c>
+      <c r="C16" s="64">
+        <v>20</v>
+      </c>
+      <c r="D16" s="64">
+        <v>120</v>
+      </c>
+      <c r="E16" s="65">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="64">
+        <v>20</v>
+      </c>
+      <c r="B17" s="64">
+        <v>4</v>
+      </c>
+      <c r="C17" s="64">
+        <v>20</v>
+      </c>
+      <c r="D17" s="64">
+        <v>130</v>
+      </c>
+      <c r="E17" s="65">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="64">
+        <v>20</v>
+      </c>
+      <c r="B18" s="64">
+        <v>4</v>
+      </c>
+      <c r="C18" s="64">
+        <v>20</v>
+      </c>
+      <c r="D18" s="64">
+        <v>154</v>
+      </c>
+      <c r="E18" s="65">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D91D38E-6269-3A4D-9F76-C5B55836BC8A}">
   <dimension ref="C5:V37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -28978,7 +31375,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95737D00-8B32-3D46-AE69-173842C5D8C4}">
   <dimension ref="E7:J30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -29459,1923 +31856,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4BCCACE-EA30-D046-B0A4-6BE1833C0F15}">
-  <dimension ref="A1:V43"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="5" max="5" width="2.6640625" customWidth="1"/>
-    <col min="13" max="15" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="2.83203125" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A2" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="60" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="L2" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="59" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-      <c r="U2" s="58"/>
-      <c r="V2" s="58"/>
-    </row>
-    <row r="3" spans="1:22" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="57"/>
-      <c r="B3" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="27"/>
-      <c r="F3" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" s="57"/>
-      <c r="M3" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="N3" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="O3" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="P3" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q3" s="27"/>
-      <c r="R3" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="S3" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="T3" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="U3" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="V3" s="27" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" s="23">
-        <f>NetworkingLESS!N5</f>
-        <v>0.24545454545454545</v>
-      </c>
-      <c r="C4" s="23">
-        <f>NetworkingLESS!V5</f>
-        <v>0.24545454545454545</v>
-      </c>
-      <c r="D4" s="24">
-        <f>NetworkingLESS!AD5</f>
-        <v>0.24545454545454545</v>
-      </c>
-      <c r="E4" s="24"/>
-      <c r="F4" s="20">
-        <f>NetworkingLESS!E5</f>
-        <v>0.02</v>
-      </c>
-      <c r="G4" s="20">
-        <f>NetworkingLESS!K5</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="20">
-        <f>NetworkingLESS!S5</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="20">
-        <f>NetworkingLESS!AA5</f>
-        <v>0.03</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4" s="2">
-        <f>NetworkingLESS!N5</f>
-        <v>0.24545454545454545</v>
-      </c>
-      <c r="N4" s="2">
-        <f>NetworkingLESS!V5</f>
-        <v>0.24545454545454545</v>
-      </c>
-      <c r="O4" s="43">
-        <f>NetworkingLESS!AD5</f>
-        <v>0.24545454545454545</v>
-      </c>
-      <c r="P4" s="43">
-        <f>NetworkingLESS!AK4</f>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="24"/>
-      <c r="R4" s="20">
-        <f>NetworkingLESS!E5</f>
-        <v>0.02</v>
-      </c>
-      <c r="S4" s="20">
-        <f>NetworkingLESS!K5</f>
-        <v>0</v>
-      </c>
-      <c r="T4" s="20">
-        <f>NetworkingLESS!S5</f>
-        <v>0</v>
-      </c>
-      <c r="U4" s="20">
-        <f>NetworkingLESS!AA5</f>
-        <v>0.03</v>
-      </c>
-      <c r="V4" s="20">
-        <f>NetworkingLESS!AH5</f>
-        <v>3.4000000000000004</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" s="23">
-        <f>NetworkingLESS!N6</f>
-        <v>0.60356652949245537</v>
-      </c>
-      <c r="C5" s="23">
-        <f>NetworkingLESS!V6</f>
-        <v>0.60356652949245537</v>
-      </c>
-      <c r="D5" s="24">
-        <f>NetworkingLESS!AD6</f>
-        <v>0.19204389574759945</v>
-      </c>
-      <c r="E5" s="24"/>
-      <c r="F5" s="20">
-        <f>NetworkingLESS!E6</f>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G5" s="20">
-        <f>NetworkingLESS!K6</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="20">
-        <f>NetworkingLESS!S6</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="20">
-        <f>NetworkingLESS!AA6</f>
-        <v>0.06</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5" s="2">
-        <f>NetworkingLESS!N6</f>
-        <v>0.60356652949245537</v>
-      </c>
-      <c r="N5" s="2">
-        <f>NetworkingLESS!V6</f>
-        <v>0.60356652949245537</v>
-      </c>
-      <c r="O5" s="43">
-        <f>NetworkingLESS!AD6</f>
-        <v>0.19204389574759945</v>
-      </c>
-      <c r="P5" s="43">
-        <f>NetworkingLESS!AK5</f>
-        <v>1.8552875695732839E-2</v>
-      </c>
-      <c r="Q5" s="24"/>
-      <c r="R5" s="20">
-        <f>NetworkingLESS!E6</f>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="S5" s="20">
-        <f>NetworkingLESS!K6</f>
-        <v>0</v>
-      </c>
-      <c r="T5" s="20">
-        <f>NetworkingLESS!S6</f>
-        <v>0</v>
-      </c>
-      <c r="U5" s="20">
-        <f>NetworkingLESS!AA6</f>
-        <v>0.06</v>
-      </c>
-      <c r="V5" s="20">
-        <f>NetworkingLESS!AH6</f>
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>3</v>
-      </c>
-      <c r="B6" s="23">
-        <f>NetworkingLESS!N7</f>
-        <v>0.51855181431840469</v>
-      </c>
-      <c r="C6" s="23">
-        <f>NetworkingLESS!V7</f>
-        <v>0.40209218698921217</v>
-      </c>
-      <c r="D6" s="24">
-        <f>NetworkingLESS!AD7</f>
-        <v>0.1443690748610657</v>
-      </c>
-      <c r="E6" s="24"/>
-      <c r="F6" s="20">
-        <f>NetworkingLESS!E7</f>
-        <v>0.1</v>
-      </c>
-      <c r="G6" s="20">
-        <f>NetworkingLESS!K7</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="20">
-        <f>NetworkingLESS!S7</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="20">
-        <f>NetworkingLESS!AA7</f>
-        <v>0.1</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6" s="2">
-        <f>NetworkingLESS!N7</f>
-        <v>0.51855181431840469</v>
-      </c>
-      <c r="N6" s="2">
-        <f>NetworkingLESS!V7</f>
-        <v>0.40209218698921217</v>
-      </c>
-      <c r="O6" s="43">
-        <f>NetworkingLESS!AD7</f>
-        <v>0.1443690748610657</v>
-      </c>
-      <c r="P6" s="43">
-        <f>NetworkingLESS!AK6</f>
-        <v>4.8010973936899862E-2</v>
-      </c>
-      <c r="Q6" s="24"/>
-      <c r="R6" s="20">
-        <f>NetworkingLESS!E7</f>
-        <v>0.1</v>
-      </c>
-      <c r="S6" s="20">
-        <f>NetworkingLESS!K7</f>
-        <v>0</v>
-      </c>
-      <c r="T6" s="20">
-        <f>NetworkingLESS!S7</f>
-        <v>0</v>
-      </c>
-      <c r="U6" s="20">
-        <f>NetworkingLESS!AA7</f>
-        <v>0.1</v>
-      </c>
-      <c r="V6" s="20">
-        <f>NetworkingLESS!AH7</f>
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>4</v>
-      </c>
-      <c r="B7" s="23">
-        <f>NetworkingLESS!N8</f>
-        <v>0.62927627095543137</v>
-      </c>
-      <c r="C7" s="23">
-        <f>NetworkingLESS!V8</f>
-        <v>0.46388169551587843</v>
-      </c>
-      <c r="D7" s="24">
-        <f>NetworkingLESS!AD8</f>
-        <v>0.26298214529099084</v>
-      </c>
-      <c r="E7" s="24"/>
-      <c r="F7" s="20">
-        <f>NetworkingLESS!E8</f>
-        <v>0.27</v>
-      </c>
-      <c r="G7" s="20">
-        <f>NetworkingLESS!K8</f>
-        <v>0.02</v>
-      </c>
-      <c r="H7" s="20">
-        <f>NetworkingLESS!S8</f>
-        <v>0.05</v>
-      </c>
-      <c r="I7" s="20">
-        <f>NetworkingLESS!AA8</f>
-        <v>0.33</v>
-      </c>
-      <c r="L7">
-        <v>4</v>
-      </c>
-      <c r="M7" s="2">
-        <f>NetworkingLESS!N8</f>
-        <v>0.62927627095543137</v>
-      </c>
-      <c r="N7" s="2">
-        <f>NetworkingLESS!V8</f>
-        <v>0.46388169551587843</v>
-      </c>
-      <c r="O7" s="43">
-        <f>NetworkingLESS!AD8</f>
-        <v>0.26298214529099084</v>
-      </c>
-      <c r="P7" s="43">
-        <f>NetworkingLESS!AK7</f>
-        <v>4.1189931350114416E-2</v>
-      </c>
-      <c r="Q7" s="24"/>
-      <c r="R7" s="20">
-        <f>NetworkingLESS!E8</f>
-        <v>0.27</v>
-      </c>
-      <c r="S7" s="20">
-        <f>NetworkingLESS!K8</f>
-        <v>0.02</v>
-      </c>
-      <c r="T7" s="20">
-        <f>NetworkingLESS!S8</f>
-        <v>0.05</v>
-      </c>
-      <c r="U7" s="20">
-        <f>NetworkingLESS!AA8</f>
-        <v>0.33</v>
-      </c>
-      <c r="V7" s="20">
-        <f>NetworkingLESS!AH8</f>
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>5</v>
-      </c>
-      <c r="B8" s="23">
-        <f>NetworkingLESS!N9</f>
-        <v>0.68208098307816278</v>
-      </c>
-      <c r="C8" s="23">
-        <f>NetworkingLESS!V9</f>
-        <v>0.5952659145850121</v>
-      </c>
-      <c r="D8" s="24">
-        <f>NetworkingLESS!AD9</f>
-        <v>0.17913980660757453</v>
-      </c>
-      <c r="E8" s="24"/>
-      <c r="F8" s="20">
-        <f>NetworkingLESS!E9</f>
-        <v>0.41</v>
-      </c>
-      <c r="G8" s="20">
-        <f>NetworkingLESS!K9</f>
-        <v>0.05</v>
-      </c>
-      <c r="H8" s="20">
-        <f>NetworkingLESS!S9</f>
-        <v>0.09</v>
-      </c>
-      <c r="I8" s="20">
-        <f>NetworkingLESS!AA9</f>
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="L8">
-        <v>5</v>
-      </c>
-      <c r="M8" s="2">
-        <f>NetworkingLESS!N9</f>
-        <v>0.68208098307816278</v>
-      </c>
-      <c r="N8" s="2">
-        <f>NetworkingLESS!V9</f>
-        <v>0.5952659145850121</v>
-      </c>
-      <c r="O8" s="43">
-        <f>NetworkingLESS!AD9</f>
-        <v>0.17913980660757453</v>
-      </c>
-      <c r="P8" s="43">
-        <f>NetworkingLESS!AK8</f>
-        <v>6.484257871064468E-2</v>
-      </c>
-      <c r="Q8" s="24"/>
-      <c r="R8" s="20">
-        <f>NetworkingLESS!E9</f>
-        <v>0.41</v>
-      </c>
-      <c r="S8" s="20">
-        <f>NetworkingLESS!K9</f>
-        <v>0.05</v>
-      </c>
-      <c r="T8" s="20">
-        <f>NetworkingLESS!S9</f>
-        <v>0.09</v>
-      </c>
-      <c r="U8" s="20">
-        <f>NetworkingLESS!AA9</f>
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="V8" s="20">
-        <f>NetworkingLESS!AH9</f>
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>6</v>
-      </c>
-      <c r="B9" s="23">
-        <f>NetworkingLESS!N10</f>
-        <v>0.31385668008840178</v>
-      </c>
-      <c r="C9" s="23">
-        <f>NetworkingLESS!V10</f>
-        <v>0.31343283582089554</v>
-      </c>
-      <c r="D9" s="24">
-        <f>NetworkingLESS!AD10</f>
-        <v>0.19297024007750296</v>
-      </c>
-      <c r="E9" s="24"/>
-      <c r="F9" s="20">
-        <f>NetworkingLESS!E10</f>
-        <v>0.63</v>
-      </c>
-      <c r="G9" s="20">
-        <f>NetworkingLESS!K10</f>
-        <v>0.1</v>
-      </c>
-      <c r="H9" s="20">
-        <f>NetworkingLESS!S10</f>
-        <v>0.19</v>
-      </c>
-      <c r="I9" s="20">
-        <f>NetworkingLESS!AA10</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="L9">
-        <v>6</v>
-      </c>
-      <c r="M9" s="2">
-        <f>NetworkingLESS!N10</f>
-        <v>0.31385668008840178</v>
-      </c>
-      <c r="N9" s="2">
-        <f>NetworkingLESS!V10</f>
-        <v>0.31343283582089554</v>
-      </c>
-      <c r="O9" s="43">
-        <f>NetworkingLESS!AD10</f>
-        <v>0.19297024007750296</v>
-      </c>
-      <c r="P9" s="43">
-        <f>NetworkingLESS!AK9</f>
-        <v>7.2058823529411759E-2</v>
-      </c>
-      <c r="Q9" s="24"/>
-      <c r="R9" s="20">
-        <f>NetworkingLESS!E10</f>
-        <v>0.63</v>
-      </c>
-      <c r="S9" s="20">
-        <f>NetworkingLESS!K10</f>
-        <v>0.1</v>
-      </c>
-      <c r="T9" s="20">
-        <f>NetworkingLESS!S10</f>
-        <v>0.19</v>
-      </c>
-      <c r="U9" s="20">
-        <f>NetworkingLESS!AA10</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="V9" s="20">
-        <f>NetworkingLESS!AH10</f>
-        <v>10.149999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>7</v>
-      </c>
-      <c r="B10" s="23">
-        <f>NetworkingLESS!N11</f>
-        <v>0.70056198747867648</v>
-      </c>
-      <c r="C10" s="23">
-        <f>NetworkingLESS!V11</f>
-        <v>0.52568776356693192</v>
-      </c>
-      <c r="D10" s="24">
-        <f>NetworkingLESS!AD11</f>
-        <v>0.18213070322038741</v>
-      </c>
-      <c r="E10" s="24"/>
-      <c r="F10" s="20">
-        <f>NetworkingLESS!E11</f>
-        <v>1.29</v>
-      </c>
-      <c r="G10" s="20">
-        <f>NetworkingLESS!K11</f>
-        <v>0.15</v>
-      </c>
-      <c r="H10" s="20">
-        <f>NetworkingLESS!S11</f>
-        <v>0.24</v>
-      </c>
-      <c r="I10" s="20">
-        <f>NetworkingLESS!AA11</f>
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="L10">
-        <v>7</v>
-      </c>
-      <c r="M10" s="2">
-        <f>NetworkingLESS!N11</f>
-        <v>0.70056198747867648</v>
-      </c>
-      <c r="N10" s="2">
-        <f>NetworkingLESS!V11</f>
-        <v>0.52568776356693192</v>
-      </c>
-      <c r="O10" s="43">
-        <f>NetworkingLESS!AD11</f>
-        <v>0.18213070322038741</v>
-      </c>
-      <c r="P10" s="43">
-        <f>NetworkingLESS!AK10</f>
-        <v>3.4997426659804425E-2</v>
-      </c>
-      <c r="Q10" s="24"/>
-      <c r="R10" s="20">
-        <f>NetworkingLESS!E11</f>
-        <v>1.29</v>
-      </c>
-      <c r="S10" s="20">
-        <f>NetworkingLESS!K11</f>
-        <v>0.15</v>
-      </c>
-      <c r="T10" s="20">
-        <f>NetworkingLESS!S11</f>
-        <v>0.24</v>
-      </c>
-      <c r="U10" s="20">
-        <f>NetworkingLESS!AA11</f>
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="V10" s="20">
-        <f>NetworkingLESS!AH11</f>
-        <v>21.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>8</v>
-      </c>
-      <c r="B11" s="23">
-        <f>NetworkingLESS!N12</f>
-        <v>0.70038217385671719</v>
-      </c>
-      <c r="C11" s="23">
-        <f>NetworkingLESS!V12</f>
-        <v>0.68401023448633247</v>
-      </c>
-      <c r="D11" s="24">
-        <f>NetworkingLESS!AD12</f>
-        <v>0.24333894718659585</v>
-      </c>
-      <c r="E11" s="24"/>
-      <c r="F11" s="20">
-        <f>NetworkingLESS!E12</f>
-        <v>4.26</v>
-      </c>
-      <c r="G11" s="20">
-        <f>NetworkingLESS!K12</f>
-        <v>0.6</v>
-      </c>
-      <c r="H11" s="20">
-        <f>NetworkingLESS!S12</f>
-        <v>0.97</v>
-      </c>
-      <c r="I11" s="20">
-        <f>NetworkingLESS!AA12</f>
-        <v>8.75</v>
-      </c>
-      <c r="L11">
-        <v>8</v>
-      </c>
-      <c r="M11" s="2">
-        <f>NetworkingLESS!N12</f>
-        <v>0.70038217385671719</v>
-      </c>
-      <c r="N11" s="2">
-        <f>NetworkingLESS!V12</f>
-        <v>0.68401023448633247</v>
-      </c>
-      <c r="O11" s="43">
-        <f>NetworkingLESS!AD12</f>
-        <v>0.24333894718659585</v>
-      </c>
-      <c r="P11" s="43">
-        <f>NetworkingLESS!AK11</f>
-        <v>8.3155096421118263E-2</v>
-      </c>
-      <c r="Q11" s="24"/>
-      <c r="R11" s="20">
-        <f>NetworkingLESS!E12</f>
-        <v>4.26</v>
-      </c>
-      <c r="S11" s="20">
-        <f>NetworkingLESS!K12</f>
-        <v>0.6</v>
-      </c>
-      <c r="T11" s="20">
-        <f>NetworkingLESS!S12</f>
-        <v>0.97</v>
-      </c>
-      <c r="U11" s="20">
-        <f>NetworkingLESS!AA12</f>
-        <v>8.75</v>
-      </c>
-      <c r="V11" s="20">
-        <f>NetworkingLESS!AH12</f>
-        <v>79.099999999999994</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>9</v>
-      </c>
-      <c r="B12" s="23">
-        <f>NetworkingLESS!N13</f>
-        <v>0.66356532099803756</v>
-      </c>
-      <c r="C12" s="23">
-        <f>NetworkingLESS!V13</f>
-        <v>0.66393327726380713</v>
-      </c>
-      <c r="D12" s="24">
-        <f>NetworkingLESS!AD13</f>
-        <v>0.17018102447034322</v>
-      </c>
-      <c r="E12" s="24"/>
-      <c r="F12" s="20">
-        <f>NetworkingLESS!E13</f>
-        <v>11.3</v>
-      </c>
-      <c r="G12" s="20">
-        <f>NetworkingLESS!K13</f>
-        <v>1.36</v>
-      </c>
-      <c r="H12" s="20">
-        <f>NetworkingLESS!S13</f>
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="I12" s="20">
-        <f>NetworkingLESS!AA13</f>
-        <v>20.100000000000001</v>
-      </c>
-      <c r="L12">
-        <v>9</v>
-      </c>
-      <c r="M12" s="2">
-        <f>NetworkingLESS!N13</f>
-        <v>0.66356532099803756</v>
-      </c>
-      <c r="N12" s="2">
-        <f>NetworkingLESS!V13</f>
-        <v>0.66393327726380713</v>
-      </c>
-      <c r="O12" s="43">
-        <f>NetworkingLESS!AD13</f>
-        <v>0.17018102447034322</v>
-      </c>
-      <c r="P12" s="43">
-        <f>NetworkingLESS!AK12</f>
-        <v>5.1598868592650171E-2</v>
-      </c>
-      <c r="Q12" s="24"/>
-      <c r="R12" s="20">
-        <f>NetworkingLESS!E13</f>
-        <v>11.3</v>
-      </c>
-      <c r="S12" s="20">
-        <f>NetworkingLESS!K13</f>
-        <v>1.36</v>
-      </c>
-      <c r="T12" s="20">
-        <f>NetworkingLESS!S13</f>
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="U12" s="20">
-        <f>NetworkingLESS!AA13</f>
-        <v>20.100000000000001</v>
-      </c>
-      <c r="V12" s="20">
-        <f>NetworkingLESS!AH13</f>
-        <v>189.75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>10</v>
-      </c>
-      <c r="B13" s="23">
-        <f>NetworkingLESS!N14</f>
-        <v>0.63726798561345743</v>
-      </c>
-      <c r="C13" s="23">
-        <f>NetworkingLESS!V14</f>
-        <v>0.63810788608092273</v>
-      </c>
-      <c r="D13" s="24">
-        <f>NetworkingLESS!AD14</f>
-        <v>0.20905404045159803</v>
-      </c>
-      <c r="E13" s="24"/>
-      <c r="F13" s="20">
-        <f>NetworkingLESS!E14</f>
-        <v>24.03</v>
-      </c>
-      <c r="G13" s="20">
-        <f>NetworkingLESS!K14</f>
-        <v>2.4300000000000002</v>
-      </c>
-      <c r="H13" s="20">
-        <f>NetworkingLESS!S14</f>
-        <v>3.88</v>
-      </c>
-      <c r="I13" s="20">
-        <f>NetworkingLESS!AA14</f>
-        <v>37.33</v>
-      </c>
-      <c r="L13">
-        <v>10</v>
-      </c>
-      <c r="M13" s="2">
-        <f>NetworkingLESS!N14</f>
-        <v>0.63726798561345743</v>
-      </c>
-      <c r="N13" s="2">
-        <f>NetworkingLESS!V14</f>
-        <v>0.63810788608092273</v>
-      </c>
-      <c r="O13" s="43">
-        <f>NetworkingLESS!AD14</f>
-        <v>0.20905404045159803</v>
-      </c>
-      <c r="P13" s="43">
-        <f>NetworkingLESS!AK13</f>
-        <v>7.5707627458047974E-2</v>
-      </c>
-      <c r="Q13" s="24"/>
-      <c r="R13" s="20">
-        <f>NetworkingLESS!E14</f>
-        <v>24.03</v>
-      </c>
-      <c r="S13" s="20">
-        <f>NetworkingLESS!K14</f>
-        <v>2.4300000000000002</v>
-      </c>
-      <c r="T13" s="20">
-        <f>NetworkingLESS!S14</f>
-        <v>3.88</v>
-      </c>
-      <c r="U13" s="20">
-        <f>NetworkingLESS!AA14</f>
-        <v>37.33</v>
-      </c>
-      <c r="V13" s="20">
-        <f>NetworkingLESS!AH14</f>
-        <v>331.75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>11</v>
-      </c>
-      <c r="B14" s="23">
-        <f>NetworkingLESS!N15</f>
-        <v>0.70677433427903735</v>
-      </c>
-      <c r="C14" s="23">
-        <f>NetworkingLESS!V15</f>
-        <v>0.70766909437496006</v>
-      </c>
-      <c r="D14" s="24">
-        <f>NetworkingLESS!AD15</f>
-        <v>0.15677475109274661</v>
-      </c>
-      <c r="E14" s="24"/>
-      <c r="F14" s="20">
-        <f>NetworkingLESS!E15</f>
-        <v>43.93</v>
-      </c>
-      <c r="G14" s="20">
-        <f>NetworkingLESS!K15</f>
-        <v>3.8</v>
-      </c>
-      <c r="H14" s="20">
-        <f>NetworkingLESS!S15</f>
-        <v>6.13</v>
-      </c>
-      <c r="I14" s="20">
-        <f>NetworkingLESS!AA15</f>
-        <v>60.39</v>
-      </c>
-      <c r="L14">
-        <v>11</v>
-      </c>
-      <c r="M14" s="2">
-        <f>NetworkingLESS!N15</f>
-        <v>0.70677433427903735</v>
-      </c>
-      <c r="N14" s="2">
-        <f>NetworkingLESS!V15</f>
-        <v>0.70766909437496006</v>
-      </c>
-      <c r="O14" s="43">
-        <f>NetworkingLESS!AD15</f>
-        <v>0.15677475109274661</v>
-      </c>
-      <c r="P14" s="43">
-        <f>NetworkingLESS!AK14</f>
-        <v>5.439979045782152E-2</v>
-      </c>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="20">
-        <f>NetworkingLESS!E15</f>
-        <v>43.93</v>
-      </c>
-      <c r="S14" s="20">
-        <f>NetworkingLESS!K15</f>
-        <v>3.8</v>
-      </c>
-      <c r="T14" s="20">
-        <f>NetworkingLESS!S15</f>
-        <v>6.13</v>
-      </c>
-      <c r="U14" s="20">
-        <f>NetworkingLESS!AA15</f>
-        <v>60.39</v>
-      </c>
-      <c r="V14" s="20">
-        <f>NetworkingLESS!AH15</f>
-        <v>541.70000000000005</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>12</v>
-      </c>
-      <c r="B15" s="23">
-        <f>NetworkingLESS!N16</f>
-        <v>0.75607481107934316</v>
-      </c>
-      <c r="C15" s="23">
-        <f>NetworkingLESS!V16</f>
-        <v>0.75674874395053215</v>
-      </c>
-      <c r="D15" s="24">
-        <f>NetworkingLESS!AD16</f>
-        <v>0.20066237973625439</v>
-      </c>
-      <c r="E15" s="24"/>
-      <c r="F15" s="20">
-        <f>NetworkingLESS!E16</f>
-        <v>309.95999999999998</v>
-      </c>
-      <c r="G15" s="20">
-        <f>NetworkingLESS!K16</f>
-        <v>15.53</v>
-      </c>
-      <c r="H15" s="20">
-        <f>NetworkingLESS!S16</f>
-        <v>25.1</v>
-      </c>
-      <c r="I15" s="20">
-        <f>NetworkingLESS!AA16</f>
-        <v>290.14</v>
-      </c>
-      <c r="L15">
-        <v>12</v>
-      </c>
-      <c r="M15" s="2">
-        <f>NetworkingLESS!N16</f>
-        <v>0.75607481107934316</v>
-      </c>
-      <c r="N15" s="2">
-        <f>NetworkingLESS!V16</f>
-        <v>0.75674874395053215</v>
-      </c>
-      <c r="O15" s="43">
-        <f>NetworkingLESS!AD16</f>
-        <v>0.20066237973625439</v>
-      </c>
-      <c r="P15" s="43">
-        <f>NetworkingLESS!AK15</f>
-        <v>2.8799974805926904E-2</v>
-      </c>
-      <c r="Q15" s="24"/>
-      <c r="R15" s="20">
-        <f>NetworkingLESS!E16</f>
-        <v>309.95999999999998</v>
-      </c>
-      <c r="S15" s="20">
-        <f>NetworkingLESS!K16</f>
-        <v>15.53</v>
-      </c>
-      <c r="T15" s="20">
-        <f>NetworkingLESS!S16</f>
-        <v>25.1</v>
-      </c>
-      <c r="U15" s="20">
-        <f>NetworkingLESS!AA16</f>
-        <v>290.14</v>
-      </c>
-      <c r="V15" s="20">
-        <f>NetworkingLESS!AH16</f>
-        <v>2601.5499999999997</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>13</v>
-      </c>
-      <c r="B16" s="23">
-        <f>NetworkingLESS!N17</f>
-        <v>0.7320626048674691</v>
-      </c>
-      <c r="C16" s="23">
-        <f>NetworkingLESS!V17</f>
-        <v>0.73310925639185764</v>
-      </c>
-      <c r="D16" s="24">
-        <f>NetworkingLESS!AD17</f>
-        <v>0.23946739464697092</v>
-      </c>
-      <c r="E16" s="24"/>
-      <c r="F16" s="20">
-        <f>NetworkingLESS!E17</f>
-        <v>1732.32</v>
-      </c>
-      <c r="G16" s="20">
-        <f>NetworkingLESS!K17</f>
-        <v>35.65</v>
-      </c>
-      <c r="H16" s="20">
-        <f>NetworkingLESS!S17</f>
-        <v>57.41</v>
-      </c>
-      <c r="I16" s="20">
-        <f>NetworkingLESS!AA17</f>
-        <v>749.64</v>
-      </c>
-      <c r="L16">
-        <v>13</v>
-      </c>
-      <c r="M16" s="2">
-        <f>NetworkingLESS!N17</f>
-        <v>0.7320626048674691</v>
-      </c>
-      <c r="N16" s="2">
-        <f>NetworkingLESS!V17</f>
-        <v>0.73310925639185764</v>
-      </c>
-      <c r="O16" s="43">
-        <f>NetworkingLESS!AD17</f>
-        <v>0.23946739464697092</v>
-      </c>
-      <c r="P16" s="43">
-        <f>NetworkingLESS!AK16</f>
-        <v>4.1799978422821522E-2</v>
-      </c>
-      <c r="Q16" s="24"/>
-      <c r="R16" s="20">
-        <f>NetworkingLESS!E17</f>
-        <v>1732.32</v>
-      </c>
-      <c r="S16" s="20">
-        <f>NetworkingLESS!K17</f>
-        <v>35.65</v>
-      </c>
-      <c r="T16" s="20">
-        <f>NetworkingLESS!S17</f>
-        <v>57.41</v>
-      </c>
-      <c r="U16" s="20">
-        <f>NetworkingLESS!AA17</f>
-        <v>749.64</v>
-      </c>
-      <c r="V16" s="20">
-        <f>NetworkingLESS!AH17</f>
-        <v>6781.25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>14</v>
-      </c>
-      <c r="B17" s="23">
-        <f>NetworkingLESS!N18</f>
-        <v>0.76867450216613709</v>
-      </c>
-      <c r="C17" s="23">
-        <f>NetworkingLESS!V18</f>
-        <v>0.76054204679719239</v>
-      </c>
-      <c r="D17" s="24">
-        <f>NetworkingLESS!AD18</f>
-        <v>0.26318025605196571</v>
-      </c>
-      <c r="E17" s="24"/>
-      <c r="F17" s="20">
-        <f>NetworkingLESS!E18</f>
-        <v>9234.91</v>
-      </c>
-      <c r="G17" s="20">
-        <f>NetworkingLESS!K18</f>
-        <v>66.44</v>
-      </c>
-      <c r="H17" s="20">
-        <f>NetworkingLESS!S18</f>
-        <v>104.96</v>
-      </c>
-      <c r="I17" s="20">
-        <f>NetworkingLESS!AA18</f>
-        <v>1209.1400000000001</v>
-      </c>
-      <c r="L17">
-        <v>14</v>
-      </c>
-      <c r="M17" s="2">
-        <f>NetworkingLESS!N18</f>
-        <v>0.76867450216613709</v>
-      </c>
-      <c r="N17" s="2">
-        <f>NetworkingLESS!V18</f>
-        <v>0.76054204679719239</v>
-      </c>
-      <c r="O17" s="43">
-        <f>NetworkingLESS!AD18</f>
-        <v>0.26318025605196571</v>
-      </c>
-      <c r="P17" s="43">
-        <f>NetworkingLESS!AK17</f>
-        <v>9.4420679730028642E-2</v>
-      </c>
-      <c r="Q17" s="24"/>
-      <c r="R17" s="20">
-        <f>NetworkingLESS!E18</f>
-        <v>9234.91</v>
-      </c>
-      <c r="S17" s="20">
-        <f>NetworkingLESS!K18</f>
-        <v>66.44</v>
-      </c>
-      <c r="T17" s="20">
-        <f>NetworkingLESS!S18</f>
-        <v>104.96</v>
-      </c>
-      <c r="U17" s="20">
-        <f>NetworkingLESS!AA18</f>
-        <v>1209.1400000000001</v>
-      </c>
-      <c r="V17" s="20">
-        <f>NetworkingLESS!AH18</f>
-        <v>11609.75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A18" s="22">
-        <v>15</v>
-      </c>
-      <c r="B18" s="23">
-        <f>NetworkingLESS!N19</f>
-        <v>0.68917968979685051</v>
-      </c>
-      <c r="C18" s="23">
-        <f>NetworkingLESS!V19</f>
-        <v>0.68987193993093321</v>
-      </c>
-      <c r="D18" s="24">
-        <f>NetworkingLESS!AD19</f>
-        <v>0.19108570481753034</v>
-      </c>
-      <c r="E18" s="24"/>
-      <c r="F18" s="20">
-        <f>NetworkingLESS!E19</f>
-        <v>50792.01</v>
-      </c>
-      <c r="G18" s="20">
-        <f>NetworkingLESS!K19</f>
-        <v>109.15</v>
-      </c>
-      <c r="H18" s="20">
-        <f>NetworkingLESS!S19</f>
-        <v>168.04</v>
-      </c>
-      <c r="I18" s="20">
-        <f>NetworkingLESS!AA19</f>
-        <v>1668.64</v>
-      </c>
-      <c r="L18" s="22">
-        <v>15</v>
-      </c>
-      <c r="M18" s="2">
-        <f>NetworkingLESS!N19</f>
-        <v>0.68917968979685051</v>
-      </c>
-      <c r="N18" s="2">
-        <f>NetworkingLESS!V19</f>
-        <v>0.68987193993093321</v>
-      </c>
-      <c r="O18" s="43">
-        <f>NetworkingLESS!AD19</f>
-        <v>0.19108570481753034</v>
-      </c>
-      <c r="P18" s="43">
-        <f>NetworkingLESS!AK18</f>
-        <v>4.7400011734366317E-2</v>
-      </c>
-      <c r="Q18" s="24"/>
-      <c r="R18" s="20">
-        <f>NetworkingLESS!E19</f>
-        <v>50792.01</v>
-      </c>
-      <c r="S18" s="20">
-        <f>NetworkingLESS!K19</f>
-        <v>109.15</v>
-      </c>
-      <c r="T18" s="20">
-        <f>NetworkingLESS!S19</f>
-        <v>168.04</v>
-      </c>
-      <c r="U18" s="20">
-        <f>NetworkingLESS!AA19</f>
-        <v>1668.64</v>
-      </c>
-      <c r="V18" s="20">
-        <f>NetworkingLESS!AH19</f>
-        <v>14829.849999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="29">
-        <f t="shared" ref="B19:I19" si="0">AVERAGE(B4:B18)</f>
-        <v>0.62315534890154178</v>
-      </c>
-      <c r="C19" s="29">
-        <f t="shared" si="0"/>
-        <v>0.58555826338009809</v>
-      </c>
-      <c r="D19" s="29">
-        <f t="shared" si="0"/>
-        <v>0.2048556606475781</v>
-      </c>
-      <c r="E19" s="29"/>
-      <c r="F19" s="30">
-        <f t="shared" si="0"/>
-        <v>4143.7006666666666</v>
-      </c>
-      <c r="G19" s="30">
-        <f t="shared" si="0"/>
-        <v>15.685333333333334</v>
-      </c>
-      <c r="H19" s="30">
-        <f t="shared" si="0"/>
-        <v>24.616</v>
-      </c>
-      <c r="I19" s="30">
-        <f t="shared" si="0"/>
-        <v>269.90400000000005</v>
-      </c>
-      <c r="L19" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="M19" s="44">
-        <f t="shared" ref="M19:O19" si="1">AVERAGE(M4:M18)</f>
-        <v>0.62315534890154178</v>
-      </c>
-      <c r="N19" s="44">
-        <f t="shared" si="1"/>
-        <v>0.58555826338009809</v>
-      </c>
-      <c r="O19" s="44">
-        <f t="shared" si="1"/>
-        <v>0.2048556606475781</v>
-      </c>
-      <c r="P19" s="44">
-        <f>AVERAGE(P4:P18)</f>
-        <v>5.0462309167025966E-2</v>
-      </c>
-      <c r="Q19" s="29"/>
-      <c r="R19" s="30">
-        <f t="shared" ref="R19:V19" si="2">AVERAGE(R4:R18)</f>
-        <v>4143.7006666666666</v>
-      </c>
-      <c r="S19" s="30">
-        <f t="shared" si="2"/>
-        <v>15.685333333333334</v>
-      </c>
-      <c r="T19" s="30">
-        <f t="shared" si="2"/>
-        <v>24.616</v>
-      </c>
-      <c r="U19" s="30">
-        <f t="shared" si="2"/>
-        <v>269.90400000000005</v>
-      </c>
-      <c r="V19" s="30">
-        <f t="shared" si="2"/>
-        <v>2467.8599999999997</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="33"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A26" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="B26" s="60" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="60"/>
-      <c r="D26" s="60"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
-    </row>
-    <row r="27" spans="1:22" ht="32" x14ac:dyDescent="0.2">
-      <c r="A27" s="57"/>
-      <c r="B27" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="E27" s="27"/>
-      <c r="F27" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="G27" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="H27" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="26" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>1</v>
-      </c>
-      <c r="B28" s="23">
-        <f>NetworkingLESS!N5</f>
-        <v>0.24545454545454545</v>
-      </c>
-      <c r="C28" s="23">
-        <f>NetworkingLESS!V5</f>
-        <v>0.24545454545454545</v>
-      </c>
-      <c r="D28" s="24">
-        <f>NetworkingLESS!AD5</f>
-        <v>0.24545454545454545</v>
-      </c>
-      <c r="E28" s="24"/>
-      <c r="F28" s="20">
-        <f>NetworkingLESS!E5</f>
-        <v>0.02</v>
-      </c>
-      <c r="G28" s="20">
-        <f>NetworkingLESS!K5</f>
-        <v>0</v>
-      </c>
-      <c r="H28" s="20">
-        <f>NetworkingLESS!S5</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="20">
-        <f>NetworkingLESS!AA5</f>
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>2</v>
-      </c>
-      <c r="B29" s="23">
-        <f>NetworkingLESS!N6</f>
-        <v>0.60356652949245537</v>
-      </c>
-      <c r="C29" s="23">
-        <f>NetworkingLESS!V6</f>
-        <v>0.60356652949245537</v>
-      </c>
-      <c r="D29" s="24">
-        <f>NetworkingLESS!AD6</f>
-        <v>0.19204389574759945</v>
-      </c>
-      <c r="E29" s="24"/>
-      <c r="F29" s="20">
-        <f>NetworkingLESS!E6</f>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G29" s="20">
-        <f>NetworkingLESS!K6</f>
-        <v>0</v>
-      </c>
-      <c r="H29" s="20">
-        <f>NetworkingLESS!S6</f>
-        <v>0</v>
-      </c>
-      <c r="I29" s="20">
-        <f>NetworkingLESS!AA6</f>
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>3</v>
-      </c>
-      <c r="B30" s="23">
-        <f>NetworkingLESS!N7</f>
-        <v>0.51855181431840469</v>
-      </c>
-      <c r="C30" s="23">
-        <f>NetworkingLESS!V7</f>
-        <v>0.40209218698921217</v>
-      </c>
-      <c r="D30" s="24">
-        <f>NetworkingLESS!AD7</f>
-        <v>0.1443690748610657</v>
-      </c>
-      <c r="E30" s="24"/>
-      <c r="F30" s="20">
-        <f>NetworkingLESS!E7</f>
-        <v>0.1</v>
-      </c>
-      <c r="G30" s="20">
-        <f>NetworkingLESS!K7</f>
-        <v>0</v>
-      </c>
-      <c r="H30" s="20">
-        <f>NetworkingLESS!S7</f>
-        <v>0</v>
-      </c>
-      <c r="I30" s="20">
-        <f>NetworkingLESS!AA7</f>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>4</v>
-      </c>
-      <c r="B31" s="23">
-        <f>NetworkingLESS!N8</f>
-        <v>0.62927627095543137</v>
-      </c>
-      <c r="C31" s="23">
-        <f>NetworkingLESS!V8</f>
-        <v>0.46388169551587843</v>
-      </c>
-      <c r="D31" s="24">
-        <f>NetworkingLESS!AD8</f>
-        <v>0.26298214529099084</v>
-      </c>
-      <c r="E31" s="24"/>
-      <c r="F31" s="20">
-        <f>NetworkingLESS!E8</f>
-        <v>0.27</v>
-      </c>
-      <c r="G31" s="20">
-        <f>NetworkingLESS!K8</f>
-        <v>0.02</v>
-      </c>
-      <c r="H31" s="20">
-        <f>NetworkingLESS!S8</f>
-        <v>0.05</v>
-      </c>
-      <c r="I31" s="20">
-        <f>NetworkingLESS!AA8</f>
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>5</v>
-      </c>
-      <c r="B32" s="23">
-        <f>NetworkingLESS!N9</f>
-        <v>0.68208098307816278</v>
-      </c>
-      <c r="C32" s="23">
-        <f>NetworkingLESS!V9</f>
-        <v>0.5952659145850121</v>
-      </c>
-      <c r="D32" s="24">
-        <f>NetworkingLESS!AD9</f>
-        <v>0.17913980660757453</v>
-      </c>
-      <c r="E32" s="24"/>
-      <c r="F32" s="20">
-        <f>NetworkingLESS!E9</f>
-        <v>0.41</v>
-      </c>
-      <c r="G32" s="20">
-        <f>NetworkingLESS!K9</f>
-        <v>0.05</v>
-      </c>
-      <c r="H32" s="20">
-        <f>NetworkingLESS!S9</f>
-        <v>0.09</v>
-      </c>
-      <c r="I32" s="20">
-        <f>NetworkingLESS!AA9</f>
-        <v>0.56999999999999995</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>6</v>
-      </c>
-      <c r="B33" s="23">
-        <f>NetworkingLESS!N10</f>
-        <v>0.31385668008840178</v>
-      </c>
-      <c r="C33" s="23">
-        <f>NetworkingLESS!V10</f>
-        <v>0.31343283582089554</v>
-      </c>
-      <c r="D33" s="24">
-        <f>NetworkingLESS!AD10</f>
-        <v>0.19297024007750296</v>
-      </c>
-      <c r="E33" s="24"/>
-      <c r="F33" s="20">
-        <f>NetworkingLESS!E10</f>
-        <v>0.63</v>
-      </c>
-      <c r="G33" s="20">
-        <f>NetworkingLESS!K10</f>
-        <v>0.1</v>
-      </c>
-      <c r="H33" s="20">
-        <f>NetworkingLESS!S10</f>
-        <v>0.19</v>
-      </c>
-      <c r="I33" s="20">
-        <f>NetworkingLESS!AA10</f>
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>7</v>
-      </c>
-      <c r="B34" s="23">
-        <f>NetworkingLESS!N11</f>
-        <v>0.70056198747867648</v>
-      </c>
-      <c r="C34" s="23">
-        <f>NetworkingLESS!V11</f>
-        <v>0.52568776356693192</v>
-      </c>
-      <c r="D34" s="24">
-        <f>NetworkingLESS!AD11</f>
-        <v>0.18213070322038741</v>
-      </c>
-      <c r="E34" s="24"/>
-      <c r="F34" s="20">
-        <f>NetworkingLESS!E11</f>
-        <v>1.29</v>
-      </c>
-      <c r="G34" s="20">
-        <f>NetworkingLESS!K11</f>
-        <v>0.15</v>
-      </c>
-      <c r="H34" s="20">
-        <f>NetworkingLESS!S11</f>
-        <v>0.24</v>
-      </c>
-      <c r="I34" s="20">
-        <f>NetworkingLESS!AA11</f>
-        <v>2.2400000000000002</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>8</v>
-      </c>
-      <c r="B35" s="23">
-        <f>NetworkingLESS!N12</f>
-        <v>0.70038217385671719</v>
-      </c>
-      <c r="C35" s="23">
-        <f>NetworkingLESS!V12</f>
-        <v>0.68401023448633247</v>
-      </c>
-      <c r="D35" s="24">
-        <f>NetworkingLESS!AD12</f>
-        <v>0.24333894718659585</v>
-      </c>
-      <c r="E35" s="24"/>
-      <c r="F35" s="20">
-        <f>NetworkingLESS!E12</f>
-        <v>4.26</v>
-      </c>
-      <c r="G35" s="20">
-        <f>NetworkingLESS!K12</f>
-        <v>0.6</v>
-      </c>
-      <c r="H35" s="20">
-        <f>NetworkingLESS!S12</f>
-        <v>0.97</v>
-      </c>
-      <c r="I35" s="20">
-        <f>NetworkingLESS!AA12</f>
-        <v>8.75</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>9</v>
-      </c>
-      <c r="B36" s="23">
-        <f>NetworkingLESS!N13</f>
-        <v>0.66356532099803756</v>
-      </c>
-      <c r="C36" s="23">
-        <f>NetworkingLESS!V13</f>
-        <v>0.66393327726380713</v>
-      </c>
-      <c r="D36" s="24">
-        <f>NetworkingLESS!AD13</f>
-        <v>0.17018102447034322</v>
-      </c>
-      <c r="E36" s="24"/>
-      <c r="F36" s="20">
-        <f>NetworkingLESS!E13</f>
-        <v>11.3</v>
-      </c>
-      <c r="G36" s="20">
-        <f>NetworkingLESS!K13</f>
-        <v>1.36</v>
-      </c>
-      <c r="H36" s="20">
-        <f>NetworkingLESS!S13</f>
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="I36" s="20">
-        <f>NetworkingLESS!AA13</f>
-        <v>20.100000000000001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>10</v>
-      </c>
-      <c r="B37" s="23">
-        <f>NetworkingLESS!N14</f>
-        <v>0.63726798561345743</v>
-      </c>
-      <c r="C37" s="23">
-        <f>NetworkingLESS!V14</f>
-        <v>0.63810788608092273</v>
-      </c>
-      <c r="D37" s="24">
-        <f>NetworkingLESS!AD14</f>
-        <v>0.20905404045159803</v>
-      </c>
-      <c r="E37" s="24"/>
-      <c r="F37" s="20">
-        <f>NetworkingLESS!E14</f>
-        <v>24.03</v>
-      </c>
-      <c r="G37" s="20">
-        <f>NetworkingLESS!K14</f>
-        <v>2.4300000000000002</v>
-      </c>
-      <c r="H37" s="20">
-        <f>NetworkingLESS!S14</f>
-        <v>3.88</v>
-      </c>
-      <c r="I37" s="20">
-        <f>NetworkingLESS!AA14</f>
-        <v>37.33</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>11</v>
-      </c>
-      <c r="B38" s="23">
-        <f>NetworkingLESS!N15</f>
-        <v>0.70677433427903735</v>
-      </c>
-      <c r="C38" s="23">
-        <f>NetworkingLESS!V15</f>
-        <v>0.70766909437496006</v>
-      </c>
-      <c r="D38" s="24">
-        <f>NetworkingLESS!AD15</f>
-        <v>0.15677475109274661</v>
-      </c>
-      <c r="E38" s="24"/>
-      <c r="F38" s="20">
-        <f>NetworkingLESS!E15</f>
-        <v>43.93</v>
-      </c>
-      <c r="G38" s="20">
-        <f>NetworkingLESS!K15</f>
-        <v>3.8</v>
-      </c>
-      <c r="H38" s="20">
-        <f>NetworkingLESS!S15</f>
-        <v>6.13</v>
-      </c>
-      <c r="I38" s="20">
-        <f>NetworkingLESS!AA15</f>
-        <v>60.39</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>12</v>
-      </c>
-      <c r="B39" s="23">
-        <f>NetworkingLESS!N16</f>
-        <v>0.75607481107934316</v>
-      </c>
-      <c r="C39" s="23">
-        <f>NetworkingLESS!V16</f>
-        <v>0.75674874395053215</v>
-      </c>
-      <c r="D39" s="24">
-        <f>NetworkingLESS!AD16</f>
-        <v>0.20066237973625439</v>
-      </c>
-      <c r="E39" s="24"/>
-      <c r="F39" s="20">
-        <f>NetworkingLESS!E16</f>
-        <v>309.95999999999998</v>
-      </c>
-      <c r="G39" s="20">
-        <f>NetworkingLESS!K16</f>
-        <v>15.53</v>
-      </c>
-      <c r="H39" s="20">
-        <f>NetworkingLESS!S16</f>
-        <v>25.1</v>
-      </c>
-      <c r="I39" s="20">
-        <f>NetworkingLESS!AA16</f>
-        <v>290.14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>13</v>
-      </c>
-      <c r="B40" s="23">
-        <f>NetworkingLESS!N17</f>
-        <v>0.7320626048674691</v>
-      </c>
-      <c r="C40" s="23">
-        <f>NetworkingLESS!V17</f>
-        <v>0.73310925639185764</v>
-      </c>
-      <c r="D40" s="24">
-        <f>NetworkingLESS!AD17</f>
-        <v>0.23946739464697092</v>
-      </c>
-      <c r="E40" s="24"/>
-      <c r="F40" s="20">
-        <f>NetworkingLESS!E17</f>
-        <v>1732.32</v>
-      </c>
-      <c r="G40" s="20">
-        <f>NetworkingLESS!K17</f>
-        <v>35.65</v>
-      </c>
-      <c r="H40" s="20">
-        <f>NetworkingLESS!S17</f>
-        <v>57.41</v>
-      </c>
-      <c r="I40" s="20">
-        <f>NetworkingLESS!AA17</f>
-        <v>749.64</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A41">
-        <v>14</v>
-      </c>
-      <c r="B41" s="23">
-        <f>NetworkingLESS!N18</f>
-        <v>0.76867450216613709</v>
-      </c>
-      <c r="C41" s="23">
-        <f>NetworkingLESS!V18</f>
-        <v>0.76054204679719239</v>
-      </c>
-      <c r="D41" s="24">
-        <f>NetworkingLESS!AD18</f>
-        <v>0.26318025605196571</v>
-      </c>
-      <c r="E41" s="24"/>
-      <c r="F41" s="20">
-        <f>NetworkingLESS!E18</f>
-        <v>9234.91</v>
-      </c>
-      <c r="G41" s="20">
-        <f>NetworkingLESS!K18</f>
-        <v>66.44</v>
-      </c>
-      <c r="H41" s="20">
-        <f>NetworkingLESS!S18</f>
-        <v>104.96</v>
-      </c>
-      <c r="I41" s="20">
-        <f>NetworkingLESS!AA18</f>
-        <v>1209.1400000000001</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A42" s="22">
-        <v>15</v>
-      </c>
-      <c r="B42" s="23">
-        <f>NetworkingLESS!N19</f>
-        <v>0.68917968979685051</v>
-      </c>
-      <c r="C42" s="23">
-        <f>NetworkingLESS!V19</f>
-        <v>0.68987193993093321</v>
-      </c>
-      <c r="D42" s="24">
-        <f>NetworkingLESS!AD19</f>
-        <v>0.19108570481753034</v>
-      </c>
-      <c r="E42" s="24"/>
-      <c r="F42" s="20">
-        <f>NetworkingLESS!E19</f>
-        <v>50792.01</v>
-      </c>
-      <c r="G42" s="20">
-        <f>NetworkingLESS!K19</f>
-        <v>109.15</v>
-      </c>
-      <c r="H42" s="20">
-        <f>NetworkingLESS!S19</f>
-        <v>168.04</v>
-      </c>
-      <c r="I42" s="20">
-        <f>NetworkingLESS!AA19</f>
-        <v>1668.64</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="B43" s="29">
-        <f t="shared" ref="B43:D43" si="3">AVERAGE(B28:B42)</f>
-        <v>0.62315534890154178</v>
-      </c>
-      <c r="C43" s="29">
-        <f t="shared" si="3"/>
-        <v>0.58555826338009809</v>
-      </c>
-      <c r="D43" s="29">
-        <f t="shared" si="3"/>
-        <v>0.2048556606475781</v>
-      </c>
-      <c r="E43" s="29"/>
-      <c r="F43" s="30">
-        <f t="shared" ref="F43:I43" si="4">AVERAGE(F28:F42)</f>
-        <v>4143.7006666666666</v>
-      </c>
-      <c r="G43" s="30">
-        <f t="shared" si="4"/>
-        <v>15.685333333333334</v>
-      </c>
-      <c r="H43" s="30">
-        <f t="shared" si="4"/>
-        <v>24.616</v>
-      </c>
-      <c r="I43" s="30">
-        <f t="shared" si="4"/>
-        <v>269.90400000000005</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="R2:V2"/>
-    <mergeCell ref="M2:P2"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="F2:I2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
 </file>
--- a/All_perf.xlsx
+++ b/All_perf.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ttdkoc/Documents/dev/workspaces/python/copt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265735EE-7CAB-0144-AB66-DBF457F72EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71037805-A046-C24C-9E92-E4F1F848206F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20440" activeTab="5" xr2:uid="{544C10BC-9448-4CAA-97CB-C174D9523FCA}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="20440" activeTab="2" xr2:uid="{544C10BC-9448-4CAA-97CB-C174D9523FCA}"/>
   </bookViews>
   <sheets>
     <sheet name="loose channel" sheetId="1" r:id="rId1"/>
@@ -566,6 +566,9 @@
     <xf numFmtId="166" fontId="2" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -596,9 +599,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -1338,6 +1338,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1345,7 +1346,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1589,85 +1589,85 @@
                   <c:v>0.10525560351552343</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.20000462791558682</c:v>
+                  <c:v>0.10727508330248056</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.35472885437637436</c:v>
+                  <c:v>6.1454720739024964E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.50163430795561958</c:v>
+                  <c:v>6.1152636738890959E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.46020790640631387</c:v>
+                  <c:v>5.6746249768906083E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.26550806425441364</c:v>
+                  <c:v>0.11914073032261653</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.37953348558489974</c:v>
+                  <c:v>4.7842126837266498E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.35491829220810273</c:v>
+                  <c:v>0.14354737926473884</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.15329169218185035</c:v>
+                  <c:v>0.11147304376893077</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.38633736860884577</c:v>
+                  <c:v>6.928407170574917E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.35240157428264218</c:v>
+                  <c:v>0.13566570746596543</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.34310710656208393</c:v>
+                  <c:v>5.0376914516441433E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.47172184799406869</c:v>
+                  <c:v>6.6880368988717631E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.16030826518645427</c:v>
+                  <c:v>8.4443165977031845E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.35971716965630196</c:v>
+                  <c:v>3.9451474538658111E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.20139719094233494</c:v>
+                  <c:v>7.4947247928898508E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.1885541644366191</c:v>
+                  <c:v>0.10761940929141713</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.24546127240293561</c:v>
+                  <c:v>8.5283061160062373E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.38591075669314467</c:v>
+                  <c:v>9.6819929349237249E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.33200818085749706</c:v>
+                  <c:v>7.900422856258138E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.2975080678153868</c:v>
+                  <c:v>7.2615525069536127E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.19686953712114605</c:v>
+                  <c:v>9.5677297746248974E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0.17033591029572154</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.21596418572951082</c:v>
+                  <c:v>0.13163459668615074</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.23937372997215967</c:v>
+                  <c:v>0.12257501684480773</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.22070574009966351</c:v>
+                  <c:v>0.11231338426822614</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.30047371569192333</c:v>
+                  <c:v>9.8033637732355697E-2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.48119227099294576</c:v>
+                  <c:v>0.1017248772600066</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2058,6 +2058,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2065,7 +2066,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2550,6 +2550,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2557,7 +2558,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2956,85 +2956,85 @@
                   <c:v>0.10525560351552343</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.20000462791558682</c:v>
+                  <c:v>0.10727508330248056</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.35472885437637436</c:v>
+                  <c:v>6.1454720739024964E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.50163430795561958</c:v>
+                  <c:v>6.1152636738890959E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.46020790640631387</c:v>
+                  <c:v>5.6746249768906083E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.26550806425441364</c:v>
+                  <c:v>0.11914073032261653</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.37953348558489974</c:v>
+                  <c:v>4.7842126837266498E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.35491829220810273</c:v>
+                  <c:v>0.14354737926473884</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.15329169218185035</c:v>
+                  <c:v>0.11147304376893077</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.38633736860884577</c:v>
+                  <c:v>6.928407170574917E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.35240157428264218</c:v>
+                  <c:v>0.13566570746596543</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.34310710656208393</c:v>
+                  <c:v>5.0376914516441433E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.47172184799406869</c:v>
+                  <c:v>6.6880368988717631E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.16030826518645427</c:v>
+                  <c:v>8.4443165977031845E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.35971716965630196</c:v>
+                  <c:v>3.9451474538658111E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.20139719094233494</c:v>
+                  <c:v>7.4947247928898508E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.1885541644366191</c:v>
+                  <c:v>0.10761940929141713</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.24546127240293561</c:v>
+                  <c:v>8.5283061160062373E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.38591075669314467</c:v>
+                  <c:v>9.6819929349237249E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.33200818085749706</c:v>
+                  <c:v>7.900422856258138E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.2975080678153868</c:v>
+                  <c:v>7.2615525069536127E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.19686953712114605</c:v>
+                  <c:v>9.5677297746248974E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0.17033591029572154</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.21596418572951082</c:v>
+                  <c:v>0.13163459668615074</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.23937372997215967</c:v>
+                  <c:v>0.12257501684480773</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.22070574009966351</c:v>
+                  <c:v>0.11231338426822614</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.30047371569192333</c:v>
+                  <c:v>9.8033637732355697E-2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.48119227099294576</c:v>
+                  <c:v>0.1017248772600066</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3205,6 +3205,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3212,7 +3213,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3949,6 +3949,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3956,7 +3957,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4933,6 +4933,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4940,7 +4941,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5822,6 +5822,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5829,7 +5830,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6537,6 +6537,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6544,7 +6545,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7455,6 +7455,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7462,7 +7463,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8278,6 +8278,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8285,7 +8286,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8933,6 +8933,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8940,7 +8941,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9488,6 +9488,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -9495,7 +9496,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -16976,27 +16976,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="F1" s="54" t="s">
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="F1" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="J1" s="54" t="s">
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="J1" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="N1" s="54" t="s">
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="N1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="O1" s="54"/>
-      <c r="Q1" s="54"/>
-      <c r="R1" s="54"/>
+      <c r="O1" s="57"/>
+      <c r="Q1" s="57"/>
+      <c r="R1" s="57"/>
     </row>
     <row r="2" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B2">
@@ -18947,41 +18947,41 @@
       <c r="V1" s="33"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
       <c r="E2" s="32"/>
-      <c r="F2" s="58" t="s">
+      <c r="F2" s="61" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="L2" s="56" t="s">
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="L2" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="59" t="s">
+      <c r="M2" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
       <c r="Q2" s="32"/>
-      <c r="R2" s="58" t="s">
+      <c r="R2" s="61" t="s">
         <v>28</v>
       </c>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-      <c r="U2" s="58"/>
-      <c r="V2" s="58"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="61"/>
     </row>
     <row r="3" spans="1:22" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="57"/>
+      <c r="A3" s="60"/>
       <c r="B3" s="26" t="s">
         <v>31</v>
       </c>
@@ -19004,7 +19004,7 @@
       <c r="I3" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="L3" s="57"/>
+      <c r="L3" s="60"/>
       <c r="M3" s="27" t="s">
         <v>37</v>
       </c>
@@ -20229,24 +20229,24 @@
       <c r="I25" s="33"/>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A26" s="56" t="s">
+      <c r="A26" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="B26" s="60" t="s">
+      <c r="B26" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="60"/>
-      <c r="D26" s="60"/>
+      <c r="C26" s="63"/>
+      <c r="D26" s="63"/>
       <c r="E26" s="32"/>
-      <c r="F26" s="58" t="s">
+      <c r="F26" s="61" t="s">
         <v>28</v>
       </c>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="61"/>
     </row>
     <row r="27" spans="1:22" ht="32" x14ac:dyDescent="0.2">
-      <c r="A27" s="57"/>
+      <c r="A27" s="60"/>
       <c r="B27" s="26" t="s">
         <v>31</v>
       </c>
@@ -20864,37 +20864,37 @@
       <c r="Q1" s="34"/>
     </row>
     <row r="2" spans="1:17" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="59"/>
+      <c r="C2" s="62"/>
       <c r="D2" s="32"/>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="I2" s="61" t="s">
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="I2" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="63" t="s">
+      <c r="J2" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
       <c r="M2" s="32"/>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
     </row>
     <row r="3" spans="1:17" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="62"/>
+      <c r="A3" s="65"/>
       <c r="B3" s="27" t="s">
         <v>31</v>
       </c>
@@ -20911,7 +20911,7 @@
       <c r="G3" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="62"/>
+      <c r="I3" s="65"/>
       <c r="J3" s="27" t="s">
         <v>37</v>
       </c>
@@ -24109,29 +24109,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="E1" s="54" t="s">
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="E1" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="I1" s="54" t="s">
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="I1" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="M1" s="54" t="s">
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="M1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="54"/>
-      <c r="P1" s="54" t="s">
+      <c r="N1" s="57"/>
+      <c r="P1" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="54"/>
+      <c r="Q1" s="57"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2">
@@ -24177,7 +24177,7 @@
       <c r="P2" s="9">
         <v>1</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="Q2">
         <v>90</v>
       </c>
       <c r="R2">
@@ -24230,7 +24230,7 @@
       <c r="P3" s="9">
         <v>2</v>
       </c>
-      <c r="Q3" s="4">
+      <c r="Q3">
         <v>2604</v>
       </c>
       <c r="R3">
@@ -24283,12 +24283,12 @@
       <c r="P4" s="9">
         <v>3</v>
       </c>
-      <c r="Q4" s="4">
-        <v>8300</v>
+      <c r="Q4">
+        <v>5390</v>
       </c>
       <c r="R4">
         <f t="shared" si="3"/>
-        <v>0.35060240963855421</v>
+        <v>0</v>
       </c>
       <c r="S4" s="4"/>
     </row>
@@ -24336,12 +24336,12 @@
       <c r="P5" s="9">
         <v>4</v>
       </c>
-      <c r="Q5" s="4">
-        <v>15048</v>
+      <c r="Q5">
+        <v>7524</v>
       </c>
       <c r="R5">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S5" s="4"/>
     </row>
@@ -24389,12 +24389,12 @@
       <c r="P6" s="9">
         <v>5</v>
       </c>
-      <c r="Q6" s="4">
-        <v>41650</v>
+      <c r="Q6">
+        <v>8330</v>
       </c>
       <c r="R6">
         <f t="shared" si="3"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S6" s="4"/>
     </row>
@@ -24442,12 +24442,12 @@
       <c r="P7" s="9">
         <v>6</v>
       </c>
-      <c r="Q7" s="4">
-        <v>195700</v>
+      <c r="Q7">
+        <v>33950</v>
       </c>
       <c r="R7">
         <f t="shared" si="3"/>
-        <v>0.82652018395503324</v>
+        <v>0</v>
       </c>
       <c r="S7" s="4"/>
     </row>
@@ -24495,12 +24495,12 @@
       <c r="P8" s="9">
         <v>7</v>
       </c>
-      <c r="Q8" s="4">
-        <v>74664</v>
+      <c r="Q8">
+        <v>20090</v>
       </c>
       <c r="R8">
         <f t="shared" si="3"/>
-        <v>0.73092789028179583</v>
+        <v>0</v>
       </c>
       <c r="S8" s="4"/>
     </row>
@@ -24548,12 +24548,12 @@
       <c r="P9" s="9">
         <v>8</v>
       </c>
-      <c r="Q9" s="4">
-        <v>270520</v>
+      <c r="Q9">
+        <v>31200</v>
       </c>
       <c r="R9">
         <f t="shared" si="3"/>
-        <v>0.88466656809108379</v>
+        <v>0</v>
       </c>
       <c r="S9" s="4"/>
     </row>
@@ -24601,12 +24601,12 @@
       <c r="P10" s="9">
         <v>9</v>
       </c>
-      <c r="Q10" s="4">
-        <v>705516</v>
+      <c r="Q10">
+        <v>54120</v>
       </c>
       <c r="R10">
         <f t="shared" si="3"/>
-        <v>0.92329018760736825</v>
+        <v>0</v>
       </c>
       <c r="S10" s="4"/>
     </row>
@@ -24654,12 +24654,12 @@
       <c r="P11" s="9">
         <v>10</v>
       </c>
-      <c r="Q11" s="4">
-        <v>1672862</v>
+      <c r="Q11">
+        <v>120540</v>
       </c>
       <c r="R11">
         <f t="shared" si="3"/>
-        <v>0.92794384713144296</v>
+        <v>0</v>
       </c>
       <c r="S11" s="4"/>
     </row>
@@ -24707,12 +24707,12 @@
       <c r="P12" s="9">
         <v>11</v>
       </c>
-      <c r="Q12" s="4">
-        <v>1161046</v>
+      <c r="Q12">
+        <v>170720</v>
       </c>
       <c r="R12">
         <f t="shared" si="3"/>
-        <v>0.85296017556582604</v>
+        <v>0</v>
       </c>
       <c r="S12" s="4"/>
     </row>
@@ -24760,12 +24760,12 @@
       <c r="P13" s="9">
         <v>12</v>
       </c>
-      <c r="Q13" s="4">
-        <v>1982340</v>
+      <c r="Q13">
+        <v>134550</v>
       </c>
       <c r="R13">
         <f t="shared" si="3"/>
-        <v>0.93212566966312538</v>
+        <v>0</v>
       </c>
       <c r="S13" s="4"/>
     </row>
@@ -24813,12 +24813,12 @@
       <c r="P14" s="9">
         <v>13</v>
       </c>
-      <c r="Q14" s="4">
-        <v>4244663</v>
+      <c r="Q14">
+        <v>319600</v>
       </c>
       <c r="R14">
         <f t="shared" si="3"/>
-        <v>0.92470544775875019</v>
+        <v>0</v>
       </c>
       <c r="S14" s="4"/>
     </row>
@@ -24866,12 +24866,12 @@
       <c r="P15" s="9">
         <v>14</v>
       </c>
-      <c r="Q15" s="4">
-        <v>6378160</v>
+      <c r="Q15">
+        <v>564000</v>
       </c>
       <c r="R15">
         <f t="shared" si="3"/>
-        <v>0.91157324369410608</v>
+        <v>0</v>
       </c>
       <c r="S15" s="4"/>
     </row>
@@ -24919,12 +24919,12 @@
       <c r="P16" s="9">
         <v>15</v>
       </c>
-      <c r="Q16" s="4">
-        <v>4565882</v>
+      <c r="Q16">
+        <v>481600</v>
       </c>
       <c r="R16">
         <f t="shared" si="3"/>
-        <v>0.89452202225112254</v>
+        <v>0</v>
       </c>
       <c r="S16" s="4"/>
     </row>
@@ -24972,12 +24972,12 @@
       <c r="P17" s="9">
         <v>16</v>
       </c>
-      <c r="Q17" s="4">
-        <v>14814516</v>
+      <c r="Q17">
+        <v>970000</v>
       </c>
       <c r="R17">
         <f t="shared" si="3"/>
-        <v>0.93452367934261238</v>
+        <v>0</v>
       </c>
       <c r="S17" s="4"/>
     </row>
@@ -25025,12 +25025,12 @@
       <c r="P18" s="9">
         <v>17</v>
       </c>
-      <c r="Q18" s="4">
-        <v>11077403</v>
+      <c r="Q18">
+        <v>772200</v>
       </c>
       <c r="R18">
         <f t="shared" si="3"/>
-        <v>0.93029052026002845</v>
+        <v>0</v>
       </c>
       <c r="S18" s="4"/>
     </row>
@@ -25042,7 +25042,7 @@
         <v>860252</v>
       </c>
       <c r="C19" s="2">
-        <f t="shared" si="0"/>
+        <f>(Q19-B19)/Q19</f>
         <v>0.10525560351552343</v>
       </c>
       <c r="D19" s="1"/>
@@ -25053,7 +25053,7 @@
         <v>780472</v>
       </c>
       <c r="G19" s="2">
-        <f t="shared" si="1"/>
+        <f>(Q19-F19)/Q19</f>
         <v>0.18823443756825628</v>
       </c>
       <c r="H19" s="1"/>
@@ -25066,23 +25066,23 @@
       <c r="M19" s="17">
         <v>18</v>
       </c>
-      <c r="N19" s="17">
-        <v>961450</v>
-      </c>
+      <c r="N19" s="17"/>
       <c r="O19" s="8"/>
       <c r="P19" s="9"/>
-      <c r="Q19" s="4"/>
+      <c r="Q19" s="17">
+        <v>961450</v>
+      </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>864315</v>
+        <v>964500</v>
       </c>
       <c r="C20" s="2">
-        <f t="shared" si="0"/>
-        <v>0.20000462791558682</v>
+        <f t="shared" ref="C20:C46" si="4">(Q20-B20)/Q20</f>
+        <v>0.10727508330248056</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20">
@@ -25092,7 +25092,7 @@
         <v>792367</v>
       </c>
       <c r="G20" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="G20:G46" si="5">(Q20-F20)/Q20</f>
         <v>0.26659848204368752</v>
       </c>
       <c r="H20" s="1"/>
@@ -25105,11 +25105,10 @@
       <c r="M20">
         <v>19</v>
       </c>
-      <c r="N20">
+      <c r="O20" s="8"/>
+      <c r="Q20">
         <v>1080400</v>
       </c>
-      <c r="O20" s="8"/>
-      <c r="Q20" s="4"/>
       <c r="R20" s="5"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.2">
@@ -25117,11 +25116,11 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>659953</v>
+        <v>959900</v>
       </c>
       <c r="C21" s="2">
-        <f t="shared" si="0"/>
-        <v>0.35472885437637436</v>
+        <f t="shared" si="4"/>
+        <v>6.1454720739024964E-2</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21">
@@ -25131,7 +25130,7 @@
         <v>597265</v>
       </c>
       <c r="G21" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.41602224584039355</v>
       </c>
       <c r="H21" s="1"/>
@@ -25144,12 +25143,11 @@
       <c r="M21">
         <v>20</v>
       </c>
-      <c r="N21">
-        <v>1022753</v>
-      </c>
       <c r="O21" s="8"/>
       <c r="P21" s="7"/>
-      <c r="Q21" s="4"/>
+      <c r="Q21">
+        <v>1022753</v>
+      </c>
       <c r="R21" s="5"/>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.2">
@@ -25157,11 +25155,11 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>1019719</v>
+        <v>1921000</v>
       </c>
       <c r="C22" s="2">
-        <f t="shared" si="0"/>
-        <v>0.50163430795561958</v>
+        <f t="shared" si="4"/>
+        <v>6.1152636738890959E-2</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22">
@@ -25171,7 +25169,7 @@
         <v>883314</v>
       </c>
       <c r="G22" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.56829931294553704</v>
       </c>
       <c r="H22" s="1"/>
@@ -25184,11 +25182,10 @@
       <c r="M22">
         <v>21</v>
       </c>
-      <c r="N22">
+      <c r="O22" s="8"/>
+      <c r="Q22">
         <v>2046126</v>
       </c>
-      <c r="O22" s="8"/>
-      <c r="Q22" s="4"/>
       <c r="R22" s="5"/>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.2">
@@ -25196,11 +25193,11 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>1658427</v>
+        <v>2898000</v>
       </c>
       <c r="C23" s="2">
-        <f t="shared" si="0"/>
-        <v>0.46020790640631387</v>
+        <f t="shared" si="4"/>
+        <v>5.6746249768906083E-2</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23">
@@ -25210,7 +25207,7 @@
         <v>1599535</v>
       </c>
       <c r="G23" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.47937633285856013</v>
       </c>
       <c r="H23" s="1"/>
@@ -25223,11 +25220,10 @@
       <c r="M23">
         <v>22</v>
       </c>
-      <c r="N23">
+      <c r="O23" s="8"/>
+      <c r="Q23">
         <v>3072344</v>
       </c>
-      <c r="O23" s="8"/>
-      <c r="Q23" s="4"/>
       <c r="R23" s="5"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.2">
@@ -25235,11 +25231,11 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>3010147</v>
+        <v>3610000</v>
       </c>
       <c r="C24" s="2">
-        <f t="shared" si="0"/>
-        <v>0.26550806425441364</v>
+        <f t="shared" si="4"/>
+        <v>0.11914073032261653</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24">
@@ -25249,7 +25245,7 @@
         <v>2662337</v>
       </c>
       <c r="G24" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.35037556081576843</v>
       </c>
       <c r="H24" s="1"/>
@@ -25262,11 +25258,10 @@
       <c r="M24">
         <v>23</v>
       </c>
-      <c r="N24">
+      <c r="O24" s="8"/>
+      <c r="Q24">
         <v>4098271</v>
       </c>
-      <c r="O24" s="8"/>
-      <c r="Q24" s="4"/>
       <c r="R24" s="5"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.2">
@@ -25274,11 +25269,11 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>3178712</v>
+        <v>4878000</v>
       </c>
       <c r="C25" s="2">
-        <f t="shared" si="0"/>
-        <v>0.37953348558489974</v>
+        <f t="shared" si="4"/>
+        <v>4.7842126837266498E-2</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25">
@@ -25288,7 +25283,7 @@
         <v>2729581</v>
       </c>
       <c r="G25" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.4672013038980305</v>
       </c>
       <c r="H25" s="1"/>
@@ -25301,11 +25296,10 @@
       <c r="M25">
         <v>24</v>
       </c>
-      <c r="N25">
+      <c r="O25" s="8"/>
+      <c r="Q25">
         <v>5123100</v>
       </c>
-      <c r="O25" s="8"/>
-      <c r="Q25" s="4"/>
       <c r="R25" s="5"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.2">
@@ -25313,11 +25307,11 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>3966361</v>
+        <v>5266000</v>
       </c>
       <c r="C26" s="2">
-        <f t="shared" si="0"/>
-        <v>0.35491829220810273</v>
+        <f t="shared" si="4"/>
+        <v>0.14354737926473884</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26">
@@ -25327,7 +25321,7 @@
         <v>3466977</v>
       </c>
       <c r="G26" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.4361371937563856</v>
       </c>
       <c r="H26" s="1"/>
@@ -25340,11 +25334,10 @@
       <c r="M26">
         <v>25</v>
       </c>
-      <c r="N26">
+      <c r="O26" s="8"/>
+      <c r="Q26">
         <v>6148618</v>
       </c>
-      <c r="O26" s="8"/>
-      <c r="Q26" s="4"/>
       <c r="R26" s="5"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.2">
@@ -25352,11 +25345,11 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>6074144</v>
+        <v>6374144</v>
       </c>
       <c r="C27" s="2">
-        <f t="shared" si="0"/>
-        <v>0.15329169218185035</v>
+        <f t="shared" si="4"/>
+        <v>0.11147304376893077</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27">
@@ -25366,7 +25359,7 @@
         <v>4286262</v>
       </c>
       <c r="G27" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.4025143880544752</v>
       </c>
       <c r="H27" s="1"/>
@@ -25379,11 +25372,10 @@
       <c r="M27">
         <v>26</v>
       </c>
-      <c r="N27">
+      <c r="O27" s="8"/>
+      <c r="Q27">
         <v>7173833</v>
       </c>
-      <c r="O27" s="8"/>
-      <c r="Q27" s="4"/>
       <c r="R27" s="5"/>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.2">
@@ -25391,11 +25383,11 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>5032349</v>
+        <v>7632349</v>
       </c>
       <c r="C28" s="2">
-        <f t="shared" si="0"/>
-        <v>0.38633736860884577</v>
+        <f t="shared" si="4"/>
+        <v>6.928407170574917E-2</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28">
@@ -25405,7 +25397,7 @@
         <v>4495396</v>
       </c>
       <c r="G28" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.451815337428849</v>
       </c>
       <c r="H28" s="1"/>
@@ -25418,11 +25410,10 @@
       <c r="M28">
         <v>27</v>
       </c>
-      <c r="N28">
+      <c r="O28" s="8"/>
+      <c r="Q28">
         <v>8200514</v>
       </c>
-      <c r="O28" s="8"/>
-      <c r="Q28" s="4"/>
       <c r="R28" s="5"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.2">
@@ -25430,11 +25421,11 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>5975923</v>
+        <v>7975923</v>
       </c>
       <c r="C29" s="2">
-        <f t="shared" si="0"/>
-        <v>0.35240157428264218</v>
+        <f t="shared" si="4"/>
+        <v>0.13566570746596543</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29">
@@ -25444,7 +25435,7 @@
         <v>5502254</v>
       </c>
       <c r="G29" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.40373210493223644</v>
       </c>
       <c r="H29" s="1"/>
@@ -25457,11 +25448,10 @@
       <c r="M29">
         <v>28</v>
       </c>
-      <c r="N29">
+      <c r="O29" s="8"/>
+      <c r="Q29">
         <v>9227822</v>
       </c>
-      <c r="O29" s="8"/>
-      <c r="Q29" s="4"/>
       <c r="R29" s="5"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.2">
@@ -25469,11 +25459,11 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>6732065</v>
+        <v>9732065</v>
       </c>
       <c r="C30" s="2">
-        <f t="shared" si="0"/>
-        <v>0.34310710656208393</v>
+        <f t="shared" si="4"/>
+        <v>5.0376914516441433E-2</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30">
@@ -25483,7 +25473,7 @@
         <v>6276007</v>
       </c>
       <c r="G30" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.38760775520340113</v>
       </c>
       <c r="H30" s="1"/>
@@ -25496,11 +25486,10 @@
       <c r="M30">
         <v>29</v>
       </c>
-      <c r="N30">
+      <c r="O30" s="8"/>
+      <c r="Q30">
         <v>10248345</v>
       </c>
-      <c r="O30" s="8"/>
-      <c r="Q30" s="4"/>
       <c r="R30" s="5"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.2">
@@ -25508,11 +25497,11 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>10439210</v>
+        <v>18439210</v>
       </c>
       <c r="C31" s="2">
-        <f t="shared" si="0"/>
-        <v>0.47172184799406869</v>
+        <f t="shared" si="4"/>
+        <v>6.6880368988717631E-2</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31">
@@ -25522,7 +25511,7 @@
         <v>8988744</v>
       </c>
       <c r="G31" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.54512294807994055</v>
       </c>
       <c r="H31" s="1"/>
@@ -25535,11 +25524,10 @@
       <c r="M31">
         <v>30</v>
       </c>
-      <c r="N31">
+      <c r="O31" s="8"/>
+      <c r="Q31">
         <v>19760821</v>
       </c>
-      <c r="O31" s="8"/>
-      <c r="Q31" s="4"/>
       <c r="R31" s="5"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.2">
@@ -25547,11 +25535,11 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>33204665</v>
+        <v>36204665</v>
       </c>
       <c r="C32" s="2">
-        <f t="shared" si="0"/>
-        <v>0.16030826518645427</v>
+        <f t="shared" si="4"/>
+        <v>8.4443165977031845E-2</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32">
@@ -25561,7 +25549,7 @@
         <v>31267376</v>
       </c>
       <c r="G32" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.20929913924722857</v>
       </c>
       <c r="H32" s="1"/>
@@ -25574,11 +25562,10 @@
       <c r="M32">
         <v>31</v>
       </c>
-      <c r="N32">
+      <c r="O32" s="8"/>
+      <c r="Q32">
         <v>39543875</v>
       </c>
-      <c r="O32" s="8"/>
-      <c r="Q32" s="4"/>
       <c r="R32" s="5"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.2">
@@ -25586,11 +25573,11 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>37985254</v>
+        <v>56985254</v>
       </c>
       <c r="C33" s="2">
-        <f t="shared" si="0"/>
-        <v>0.35971716965630196</v>
+        <f t="shared" si="4"/>
+        <v>3.9451474538658111E-2</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33">
@@ -25600,7 +25587,7 @@
         <v>34041448</v>
       </c>
       <c r="G33" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.42619431544573011</v>
       </c>
       <c r="H33" s="1"/>
@@ -25613,11 +25600,10 @@
       <c r="M33">
         <v>32</v>
       </c>
-      <c r="N33">
+      <c r="O33" s="8"/>
+      <c r="Q33">
         <v>59325742</v>
       </c>
-      <c r="O33" s="8"/>
-      <c r="Q33" s="4"/>
       <c r="R33" s="5"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.2">
@@ -25625,11 +25611,11 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>63155648</v>
+        <v>73155648</v>
       </c>
       <c r="C34" s="2">
-        <f t="shared" si="0"/>
-        <v>0.20139719094233494</v>
+        <f t="shared" si="4"/>
+        <v>7.4947247928898508E-2</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34">
@@ -25639,7 +25625,7 @@
         <v>60638550</v>
       </c>
       <c r="G34" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.23322588080825843</v>
       </c>
       <c r="H34" s="1"/>
@@ -25652,11 +25638,10 @@
       <c r="M34">
         <v>33</v>
       </c>
-      <c r="N34">
+      <c r="O34" s="8"/>
+      <c r="Q34">
         <v>79082677</v>
       </c>
-      <c r="O34" s="8"/>
-      <c r="Q34" s="4"/>
       <c r="R34" s="5"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.2">
@@ -25664,11 +25649,11 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>80207405</v>
+        <v>88207405</v>
       </c>
       <c r="C35" s="2">
-        <f t="shared" si="0"/>
-        <v>0.1885541644366191</v>
+        <f t="shared" si="4"/>
+        <v>0.10761940929141713</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35">
@@ -25678,7 +25663,7 @@
         <v>73959964</v>
       </c>
       <c r="G35" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.25175855288900606</v>
       </c>
       <c r="H35" s="1"/>
@@ -25691,11 +25676,10 @@
       <c r="M35">
         <v>34</v>
       </c>
-      <c r="N35">
+      <c r="O35" s="8"/>
+      <c r="Q35">
         <v>98845051</v>
       </c>
-      <c r="O35" s="8"/>
-      <c r="Q35" s="4"/>
       <c r="R35" s="5"/>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.2">
@@ -25703,11 +25687,11 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>89501785</v>
+        <v>108501785</v>
       </c>
       <c r="C36" s="2">
-        <f t="shared" si="0"/>
-        <v>0.24546127240293561</v>
+        <f t="shared" si="4"/>
+        <v>8.5283061160062373E-2</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36">
@@ -25717,7 +25701,7 @@
         <v>87873858</v>
       </c>
       <c r="G36" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.25918540055525019</v>
       </c>
       <c r="H36" s="1"/>
@@ -25730,11 +25714,10 @@
       <c r="M36">
         <v>35</v>
       </c>
-      <c r="N36">
+      <c r="O36" s="8"/>
+      <c r="Q36">
         <v>118617881</v>
       </c>
-      <c r="O36" s="8"/>
-      <c r="Q36" s="4"/>
       <c r="R36" s="5"/>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.2">
@@ -25742,11 +25725,11 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>84968347</v>
+        <v>124968347</v>
       </c>
       <c r="C37" s="2">
-        <f t="shared" si="0"/>
-        <v>0.38591075669314467</v>
+        <f t="shared" si="4"/>
+        <v>9.6819929349237249E-2</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37">
@@ -25756,7 +25739,7 @@
         <v>76948539</v>
       </c>
       <c r="G37" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.44387207993962685</v>
       </c>
       <c r="H37" s="1"/>
@@ -25769,11 +25752,10 @@
       <c r="M37">
         <v>36</v>
       </c>
-      <c r="N37">
+      <c r="O37" s="8"/>
+      <c r="Q37">
         <v>138364819</v>
       </c>
-      <c r="O37" s="8"/>
-      <c r="Q37" s="4"/>
       <c r="R37" s="5"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.2">
@@ -25781,11 +25763,11 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>105609705</v>
+        <v>145609705</v>
       </c>
       <c r="C38" s="2">
-        <f t="shared" si="0"/>
-        <v>0.33200818085749706</v>
+        <f t="shared" si="4"/>
+        <v>7.900422856258138E-2</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38">
@@ -25795,7 +25777,7 @@
         <v>87270834</v>
       </c>
       <c r="G38" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.44800335194816238</v>
       </c>
       <c r="H38" s="1"/>
@@ -25808,11 +25790,10 @@
       <c r="M38">
         <v>37</v>
       </c>
-      <c r="N38">
+      <c r="O38" s="8"/>
+      <c r="Q38">
         <v>158100297</v>
       </c>
-      <c r="O38" s="8"/>
-      <c r="Q38" s="4"/>
       <c r="R38" s="5"/>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.2">
@@ -25820,11 +25801,11 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>124947031</v>
+        <v>164947000</v>
       </c>
       <c r="C39" s="2">
-        <f t="shared" si="0"/>
-        <v>0.2975080678153868</v>
+        <f t="shared" si="4"/>
+        <v>7.2615525069536127E-2</v>
       </c>
       <c r="D39" s="1"/>
       <c r="E39">
@@ -25834,7 +25815,7 @@
         <v>110088127</v>
       </c>
       <c r="G39" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.38104955013444791</v>
       </c>
       <c r="H39" s="1"/>
@@ -25847,11 +25828,10 @@
       <c r="M39">
         <v>38</v>
       </c>
-      <c r="N39">
+      <c r="O39" s="8"/>
+      <c r="Q39">
         <v>177862585</v>
       </c>
-      <c r="O39" s="8"/>
-      <c r="Q39" s="4"/>
       <c r="R39" s="5"/>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.2">
@@ -25859,11 +25839,11 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>158733608</v>
+        <v>178733608</v>
       </c>
       <c r="C40" s="2">
-        <f t="shared" si="0"/>
-        <v>0.19686953712114605</v>
+        <f t="shared" si="4"/>
+        <v>9.5677297746248974E-2</v>
       </c>
       <c r="D40" s="1"/>
       <c r="E40">
@@ -25873,7 +25853,7 @@
         <v>157173483</v>
       </c>
       <c r="G40" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.20476316424388413</v>
       </c>
       <c r="H40" s="1"/>
@@ -25886,11 +25866,10 @@
       <c r="M40">
         <v>39</v>
       </c>
-      <c r="N40">
+      <c r="O40" s="8"/>
+      <c r="Q40">
         <v>197643615</v>
       </c>
-      <c r="O40" s="8"/>
-      <c r="Q40" s="4"/>
       <c r="R40" s="5"/>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.2">
@@ -25901,7 +25880,7 @@
         <v>168746330</v>
       </c>
       <c r="C41" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0.17033591029572154</v>
       </c>
       <c r="D41" s="1"/>
@@ -25912,7 +25891,7 @@
         <v>168583488</v>
       </c>
       <c r="G41" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.17113654495068334</v>
       </c>
       <c r="H41" s="1"/>
@@ -25925,11 +25904,10 @@
       <c r="M41">
         <v>40</v>
       </c>
-      <c r="N41">
+      <c r="O41" s="8"/>
+      <c r="Q41">
         <v>203391146</v>
       </c>
-      <c r="O41" s="8"/>
-      <c r="Q41" s="4"/>
       <c r="R41" s="5"/>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.2">
@@ -25937,11 +25915,11 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>185945603</v>
+        <v>205945603</v>
       </c>
       <c r="C42" s="2">
-        <f t="shared" si="0"/>
-        <v>0.21596418572951082</v>
+        <f t="shared" si="4"/>
+        <v>0.13163459668615074</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42">
@@ -25951,7 +25929,7 @@
         <v>156500038</v>
       </c>
       <c r="G42" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.3401208055094882</v>
       </c>
       <c r="H42" s="1"/>
@@ -25964,11 +25942,10 @@
       <c r="M42">
         <v>41</v>
       </c>
-      <c r="N42">
+      <c r="O42" s="8"/>
+      <c r="Q42">
         <v>237164680</v>
       </c>
-      <c r="O42" s="8"/>
-      <c r="Q42" s="4"/>
       <c r="R42" s="5"/>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.2">
@@ -25976,11 +25953,11 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>195368489</v>
+        <v>225368489</v>
       </c>
       <c r="C43" s="2">
-        <f t="shared" si="0"/>
-        <v>0.23937372997215967</v>
+        <f t="shared" si="4"/>
+        <v>0.12257501684480773</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43">
@@ -25990,7 +25967,7 @@
         <v>181832457</v>
       </c>
       <c r="G43" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.29207343392051488</v>
       </c>
       <c r="H43" s="1"/>
@@ -26003,11 +25980,10 @@
       <c r="M43">
         <v>42</v>
       </c>
-      <c r="N43">
+      <c r="O43" s="8"/>
+      <c r="Q43">
         <v>256852145</v>
       </c>
-      <c r="O43" s="8"/>
-      <c r="Q43" s="4"/>
       <c r="R43" s="5"/>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.2">
@@ -26015,11 +25991,11 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>215687053</v>
+        <v>245687053</v>
       </c>
       <c r="C44" s="2">
-        <f t="shared" si="0"/>
-        <v>0.22070574009966351</v>
+        <f t="shared" si="4"/>
+        <v>0.11231338426822614</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44">
@@ -26029,7 +26005,7 @@
         <v>195977949</v>
       </c>
       <c r="G44" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.29191628056255703</v>
       </c>
       <c r="H44" s="1"/>
@@ -26042,11 +26018,10 @@
       <c r="M44">
         <v>43</v>
       </c>
-      <c r="N44">
+      <c r="O44" s="8"/>
+      <c r="Q44">
         <v>276772285</v>
       </c>
-      <c r="O44" s="8"/>
-      <c r="Q44" s="4"/>
       <c r="R44" s="5"/>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.2">
@@ -26054,11 +26029,11 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>207328322</v>
+        <v>267328300</v>
       </c>
       <c r="C45" s="2">
-        <f t="shared" si="0"/>
-        <v>0.30047371569192333</v>
+        <f t="shared" si="4"/>
+        <v>9.8033637732355697E-2</v>
       </c>
       <c r="D45" s="1"/>
       <c r="E45">
@@ -26068,7 +26043,7 @@
         <v>186623585</v>
       </c>
       <c r="G45" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.37033155084666863</v>
       </c>
       <c r="H45" s="1"/>
@@ -26081,11 +26056,10 @@
       <c r="M45">
         <v>44</v>
       </c>
-      <c r="N45">
+      <c r="O45" s="8"/>
+      <c r="Q45">
         <v>296383891</v>
       </c>
-      <c r="O45" s="8"/>
-      <c r="Q45" s="4"/>
       <c r="R45" s="5"/>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.2">
@@ -26093,11 +26067,11 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>164063971</v>
+        <v>284063971</v>
       </c>
       <c r="C46" s="2">
-        <f t="shared" si="0"/>
-        <v>0.48119227099294576</v>
+        <f t="shared" si="4"/>
+        <v>0.1017248772600066</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46">
@@ -26107,7 +26081,7 @@
         <v>150825577</v>
       </c>
       <c r="G46" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.52305509489619395</v>
       </c>
       <c r="H46" s="1"/>
@@ -26120,11 +26094,10 @@
       <c r="M46">
         <v>45</v>
       </c>
-      <c r="N46">
+      <c r="O46" s="8"/>
+      <c r="Q46">
         <v>316232704</v>
       </c>
-      <c r="O46" s="8"/>
-      <c r="Q46" s="4"/>
       <c r="R46" s="5"/>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.2">
@@ -26349,30 +26322,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="D2" s="54" t="s">
+      <c r="D2" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="I2" s="54" t="s">
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="I2" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="N2" s="54" t="s">
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="N2" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="54"/>
-      <c r="P2" s="54"/>
-      <c r="Q2" s="54"/>
-      <c r="S2" s="54" t="s">
+      <c r="O2" s="57"/>
+      <c r="P2" s="57"/>
+      <c r="Q2" s="57"/>
+      <c r="S2" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="54"/>
-      <c r="U2" s="54"/>
-      <c r="V2" s="54"/>
+      <c r="T2" s="57"/>
+      <c r="U2" s="57"/>
+      <c r="V2" s="57"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -27298,57 +27271,57 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="E2" s="54" t="s">
+      <c r="E2" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
       <c r="I2" s="18"/>
-      <c r="K2" s="54" t="s">
+      <c r="K2" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="57"/>
       <c r="P2" s="18"/>
       <c r="Q2" s="18"/>
-      <c r="S2" s="54" t="s">
+      <c r="S2" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="T2" s="54"/>
-      <c r="U2" s="54"/>
-      <c r="V2" s="54"/>
-      <c r="W2" s="54"/>
+      <c r="T2" s="57"/>
+      <c r="U2" s="57"/>
+      <c r="V2" s="57"/>
+      <c r="W2" s="57"/>
       <c r="X2" s="18"/>
       <c r="Y2" s="18"/>
-      <c r="AA2" s="54" t="s">
+      <c r="AA2" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="AB2" s="54"/>
-      <c r="AC2" s="54"/>
-      <c r="AD2" s="54"/>
-      <c r="AE2" s="54"/>
+      <c r="AB2" s="57"/>
+      <c r="AC2" s="57"/>
+      <c r="AD2" s="57"/>
+      <c r="AE2" s="57"/>
       <c r="AF2" s="18"/>
-      <c r="AH2" s="54" t="s">
+      <c r="AH2" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="AI2" s="54"/>
-      <c r="AJ2" s="54"/>
-      <c r="AK2" s="54"/>
-      <c r="AL2" s="54"/>
-      <c r="AN2" s="54" t="s">
+      <c r="AI2" s="57"/>
+      <c r="AJ2" s="57"/>
+      <c r="AK2" s="57"/>
+      <c r="AL2" s="57"/>
+      <c r="AN2" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="AO2" s="54"/>
-      <c r="AP2" s="54"/>
-      <c r="AQ2" s="54"/>
-      <c r="AR2" s="54"/>
-      <c r="AT2" s="54" t="s">
+      <c r="AO2" s="57"/>
+      <c r="AP2" s="57"/>
+      <c r="AQ2" s="57"/>
+      <c r="AR2" s="57"/>
+      <c r="AT2" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="AU2" s="54"/>
+      <c r="AU2" s="57"/>
     </row>
     <row r="3" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -27714,14 +27687,14 @@
         <v>0.1</v>
       </c>
       <c r="AR5" s="4">
-        <f>F5/AO5</f>
+        <f t="shared" ref="AR5:AR19" si="14">F5/AO5</f>
         <v>1.264367816091954</v>
       </c>
       <c r="AT5">
         <v>4851</v>
       </c>
       <c r="AU5" s="4">
-        <f>AI5/AT5</f>
+        <f t="shared" ref="AU5:AU25" si="15">AI5/AT5</f>
         <v>1.090496804782519</v>
       </c>
     </row>
@@ -27852,14 +27825,14 @@
         <v>0.1</v>
       </c>
       <c r="AR6" s="4">
-        <f>F6/AO6</f>
+        <f t="shared" si="14"/>
         <v>1.1815235008103728</v>
       </c>
       <c r="AT6">
         <v>3170</v>
       </c>
       <c r="AU6" s="4">
-        <f>AI6/AT6</f>
+        <f t="shared" si="15"/>
         <v>2.189274447949527</v>
       </c>
     </row>
@@ -27990,14 +27963,14 @@
         <v>0.26</v>
       </c>
       <c r="AR7" s="4">
-        <f>F7/AO7</f>
+        <f t="shared" si="14"/>
         <v>1.9870087690808704</v>
       </c>
       <c r="AT7">
         <v>7659</v>
       </c>
       <c r="AU7" s="4">
-        <f>AI7/AT7</f>
+        <f t="shared" si="15"/>
         <v>3.0635853244548898</v>
       </c>
     </row>
@@ -28128,14 +28101,14 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="AR8" s="4">
-        <f>F8/AO8</f>
+        <f t="shared" si="14"/>
         <v>1.6695869837296622</v>
       </c>
       <c r="AT8">
         <v>8318</v>
       </c>
       <c r="AU8" s="4">
-        <f>AI8/AT8</f>
+        <f t="shared" si="15"/>
         <v>3.2994710266891079</v>
       </c>
     </row>
@@ -28266,14 +28239,14 @@
         <v>0.88</v>
       </c>
       <c r="AR9" s="4">
-        <f>F9/AO9</f>
+        <f t="shared" si="14"/>
         <v>2.3034802784222737</v>
       </c>
       <c r="AT9">
         <v>32504</v>
       </c>
       <c r="AU9" s="4">
-        <f>AI9/AT9</f>
+        <f t="shared" si="15"/>
         <v>2.8342973172532613</v>
       </c>
     </row>
@@ -28404,14 +28377,14 @@
         <v>1.28</v>
       </c>
       <c r="AR10" s="4">
-        <f>F10/AO10</f>
+        <f t="shared" si="14"/>
         <v>1.4001526005680132</v>
       </c>
       <c r="AT10">
         <v>17749</v>
       </c>
       <c r="AU10" s="4">
-        <f>AI10/AT10</f>
+        <f t="shared" si="15"/>
         <v>1.7958758239900841</v>
       </c>
     </row>
@@ -28542,14 +28515,14 @@
         <v>1.28</v>
       </c>
       <c r="AR11" s="4">
-        <f>F11/AO11</f>
+        <f t="shared" si="14"/>
         <v>1.9103887510339124</v>
       </c>
       <c r="AT11">
         <v>22396</v>
       </c>
       <c r="AU11" s="4">
-        <f>AI11/AT11</f>
+        <f t="shared" si="15"/>
         <v>4.7276299339167709</v>
       </c>
     </row>
@@ -28680,14 +28653,14 @@
         <v>2.36</v>
       </c>
       <c r="AR12" s="4">
-        <f>F12/AO12</f>
+        <f t="shared" si="14"/>
         <v>2.194612268107186</v>
       </c>
       <c r="AT12">
         <v>109494</v>
       </c>
       <c r="AU12" s="4">
-        <f>AI12/AT12</f>
+        <f t="shared" si="15"/>
         <v>3.20925347507626</v>
       </c>
     </row>
@@ -28818,14 +28791,14 @@
         <v>3.59</v>
       </c>
       <c r="AR13" s="4">
-        <f>F13/AO13</f>
+        <f t="shared" si="14"/>
         <v>1.6686743465294427</v>
       </c>
       <c r="AT13">
         <v>226956</v>
       </c>
       <c r="AU13" s="4">
-        <f>AI13/AT13</f>
+        <f t="shared" si="15"/>
         <v>3.2540095877615043</v>
       </c>
     </row>
@@ -28956,14 +28929,14 @@
         <v>4.8099999999999996</v>
       </c>
       <c r="AR14" s="4">
-        <f>F14/AO14</f>
+        <f t="shared" si="14"/>
         <v>2.1977245372242495</v>
       </c>
       <c r="AT14">
         <v>390761</v>
       </c>
       <c r="AU14" s="4">
-        <f>AI14/AT14</f>
+        <f t="shared" si="15"/>
         <v>2.2357860687223137</v>
       </c>
       <c r="AV14" s="6"/>
@@ -29095,14 +29068,14 @@
         <v>5.98</v>
       </c>
       <c r="AR15" s="4">
-        <f>F15/AO15</f>
+        <f t="shared" si="14"/>
         <v>2.4277194994434512</v>
       </c>
       <c r="AT15">
         <v>549158</v>
       </c>
       <c r="AU15" s="4">
-        <f>AI15/AT15</f>
+        <f t="shared" si="15"/>
         <v>1.9093339257554292</v>
       </c>
       <c r="AV15" s="6"/>
@@ -29234,14 +29207,14 @@
         <v>11.98</v>
       </c>
       <c r="AR16" s="4">
-        <f>F16/AO16</f>
+        <f t="shared" si="14"/>
         <v>4.000458780030268</v>
       </c>
       <c r="AT16">
         <v>985185</v>
       </c>
       <c r="AU16" s="4">
-        <f>AI16/AT16</f>
+        <f t="shared" si="15"/>
         <v>3.4347782396199698</v>
       </c>
       <c r="AV16" s="6"/>
@@ -29373,14 +29346,14 @@
         <v>17.989999999999998</v>
       </c>
       <c r="AR17" s="4">
-        <f>F17/AO17</f>
+        <f t="shared" si="14"/>
         <v>5.1860774191743264</v>
       </c>
       <c r="AT17">
         <v>2504407</v>
       </c>
       <c r="AU17" s="4">
-        <f>AI17/AT17</f>
+        <f t="shared" si="15"/>
         <v>2.144722882502724</v>
       </c>
       <c r="AV17" s="6"/>
@@ -29512,14 +29485,14 @@
         <v>23.99</v>
       </c>
       <c r="AR18" s="4">
-        <f>F18/AO18</f>
+        <f t="shared" si="14"/>
         <v>7.0191855263593892</v>
       </c>
       <c r="AT18">
         <v>4855080</v>
       </c>
       <c r="AU18" s="4">
-        <f>AI18/AT18</f>
+        <f t="shared" si="15"/>
         <v>2.3275218945928802</v>
       </c>
       <c r="AV18" s="6"/>
@@ -29651,14 +29624,14 @@
         <v>30.06</v>
       </c>
       <c r="AR19" s="4">
-        <f>F19/AO19</f>
+        <f t="shared" si="14"/>
         <v>3.0721206228462759</v>
       </c>
       <c r="AT19">
         <v>2798271</v>
       </c>
       <c r="AU19" s="4">
-        <f>AI19/AT19</f>
+        <f t="shared" si="15"/>
         <v>4.3454050733470773</v>
       </c>
       <c r="AV19" s="6"/>
@@ -29751,7 +29724,7 @@
       <c r="AO20" t="s">
         <v>52</v>
       </c>
-      <c r="AQ20" s="66"/>
+      <c r="AQ20" s="56"/>
       <c r="AR20" s="4">
         <f>AVERAGE(AR5:AR19)</f>
         <v>2.6322054466301097</v>
@@ -29760,7 +29733,7 @@
         <v>6135807</v>
       </c>
       <c r="AU20" s="4">
-        <f>AI20/AT20</f>
+        <f t="shared" si="15"/>
         <v>2.5317209292925935</v>
       </c>
       <c r="AV20" s="6"/>
@@ -29850,12 +29823,12 @@
         <f t="shared" si="13"/>
         <v>132.8531759053088</v>
       </c>
-      <c r="AQ21" s="66"/>
+      <c r="AQ21" s="56"/>
       <c r="AT21">
         <v>7276898</v>
       </c>
       <c r="AU21" s="4">
-        <f>AI21/AT21</f>
+        <f t="shared" si="15"/>
         <v>3.1157126291999697</v>
       </c>
       <c r="AV21" s="6"/>
@@ -29945,12 +29918,12 @@
         <f t="shared" si="13"/>
         <v>181.57239706970927</v>
       </c>
-      <c r="AQ22" s="66"/>
+      <c r="AQ22" s="56"/>
       <c r="AT22">
         <v>18914981</v>
       </c>
       <c r="AU22" s="4">
-        <f>AI22/AT22</f>
+        <f t="shared" si="15"/>
         <v>1.8803777281087408</v>
       </c>
       <c r="AV22" s="6"/>
@@ -30040,12 +30013,12 @@
         <f t="shared" si="13"/>
         <v>282.84032714069679</v>
       </c>
-      <c r="AQ23" s="66"/>
+      <c r="AQ23" s="56"/>
       <c r="AT23">
         <v>13045096</v>
       </c>
       <c r="AU23" s="4">
-        <f>AI23/AT23</f>
+        <f t="shared" si="15"/>
         <v>5.9357221288367672</v>
       </c>
       <c r="AV23" s="6"/>
@@ -30135,12 +30108,12 @@
         <f t="shared" si="13"/>
         <v>272.97635211267607</v>
       </c>
-      <c r="AQ24" s="66"/>
+      <c r="AQ24" s="56"/>
       <c r="AT24">
         <v>28218359</v>
       </c>
       <c r="AU24" s="4">
-        <f>AI24/AT24</f>
+        <f t="shared" si="15"/>
         <v>3.4341686913827978</v>
       </c>
       <c r="AV24" s="6"/>
@@ -30230,12 +30203,12 @@
         <f t="shared" si="13"/>
         <v>291.45039442234565</v>
       </c>
-      <c r="AQ25" s="66"/>
+      <c r="AQ25" s="56"/>
       <c r="AT25">
         <v>46782944</v>
       </c>
       <c r="AU25" s="4">
-        <f>AI25/AT25</f>
+        <f t="shared" si="15"/>
         <v>2.1346743804750723</v>
       </c>
       <c r="AV25" s="6"/>
@@ -30325,7 +30298,7 @@
         <f t="shared" si="13"/>
         <v>303.55061718369336</v>
       </c>
-      <c r="AQ26" s="66"/>
+      <c r="AQ26" s="56"/>
       <c r="AT26" t="s">
         <v>52</v>
       </c>
@@ -30380,307 +30353,307 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="64">
+      <c r="A2" s="54">
         <v>7</v>
       </c>
-      <c r="B2" s="64">
+      <c r="B2" s="54">
         <v>4</v>
       </c>
-      <c r="C2" s="64">
+      <c r="C2" s="54">
         <v>6</v>
       </c>
-      <c r="D2" s="64">
+      <c r="D2" s="54">
         <v>3</v>
       </c>
-      <c r="E2" s="65">
+      <c r="E2" s="55">
         <f>A2/C2</f>
         <v>1.1666666666666667</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="64">
+      <c r="A3" s="54">
         <v>8</v>
       </c>
-      <c r="B3" s="64">
+      <c r="B3" s="54">
         <v>4</v>
       </c>
-      <c r="C3" s="64">
+      <c r="C3" s="54">
         <v>6</v>
       </c>
-      <c r="D3" s="64">
+      <c r="D3" s="54">
         <v>4</v>
       </c>
-      <c r="E3" s="65">
+      <c r="E3" s="55">
         <f t="shared" ref="E3:E18" si="0">A3/C3</f>
         <v>1.3333333333333333</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="64">
+      <c r="A4" s="54">
         <v>9</v>
       </c>
-      <c r="B4" s="64">
+      <c r="B4" s="54">
         <v>4</v>
       </c>
-      <c r="C4" s="64">
+      <c r="C4" s="54">
         <v>8</v>
       </c>
-      <c r="D4" s="64">
+      <c r="D4" s="54">
         <v>7</v>
       </c>
-      <c r="E4" s="65">
+      <c r="E4" s="55">
         <f t="shared" si="0"/>
         <v>1.125</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="64">
+      <c r="A5" s="54">
         <v>11</v>
       </c>
-      <c r="B5" s="64">
+      <c r="B5" s="54">
         <v>4</v>
       </c>
-      <c r="C5" s="64">
+      <c r="C5" s="54">
         <v>10</v>
       </c>
-      <c r="D5" s="64">
+      <c r="D5" s="54">
         <v>10</v>
       </c>
-      <c r="E5" s="65">
+      <c r="E5" s="55">
         <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="64">
+      <c r="A6" s="54">
         <v>13</v>
       </c>
-      <c r="B6" s="64">
+      <c r="B6" s="54">
         <v>4</v>
       </c>
-      <c r="C6" s="64">
+      <c r="C6" s="54">
         <v>10</v>
       </c>
-      <c r="D6" s="64">
+      <c r="D6" s="54">
         <v>13</v>
       </c>
-      <c r="E6" s="65">
+      <c r="E6" s="55">
         <f t="shared" si="0"/>
         <v>1.3</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="64">
+      <c r="A7" s="54">
         <v>14</v>
       </c>
-      <c r="B7" s="64">
+      <c r="B7" s="54">
         <v>4</v>
       </c>
-      <c r="C7" s="64">
+      <c r="C7" s="54">
         <v>11</v>
       </c>
-      <c r="D7" s="64">
+      <c r="D7" s="54">
         <v>15</v>
       </c>
-      <c r="E7" s="65">
+      <c r="E7" s="55">
         <f t="shared" si="0"/>
         <v>1.2727272727272727</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="64">
+      <c r="A8" s="54">
         <v>14</v>
       </c>
-      <c r="B8" s="64">
+      <c r="B8" s="54">
         <v>4</v>
       </c>
-      <c r="C8" s="64">
+      <c r="C8" s="54">
         <v>11</v>
       </c>
-      <c r="D8" s="64">
+      <c r="D8" s="54">
         <v>15</v>
       </c>
-      <c r="E8" s="65">
+      <c r="E8" s="55">
         <f t="shared" si="0"/>
         <v>1.2727272727272727</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="64">
+      <c r="A9" s="54">
         <v>16</v>
       </c>
-      <c r="B9" s="64">
+      <c r="B9" s="54">
         <v>4</v>
       </c>
-      <c r="C9" s="64">
+      <c r="C9" s="54">
         <v>11</v>
       </c>
-      <c r="D9" s="64">
+      <c r="D9" s="54">
         <v>18</v>
       </c>
-      <c r="E9" s="65">
+      <c r="E9" s="55">
         <f t="shared" si="0"/>
         <v>1.4545454545454546</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="64">
+      <c r="A10" s="54">
         <v>16</v>
       </c>
-      <c r="B10" s="64">
+      <c r="B10" s="54">
         <v>4</v>
       </c>
-      <c r="C10" s="64">
+      <c r="C10" s="54">
         <v>12</v>
       </c>
-      <c r="D10" s="64">
+      <c r="D10" s="54">
         <v>20</v>
       </c>
-      <c r="E10" s="65">
+      <c r="E10" s="55">
         <f t="shared" si="0"/>
         <v>1.3333333333333333</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="64">
+      <c r="A11" s="54">
         <v>16</v>
       </c>
-      <c r="B11" s="64">
+      <c r="B11" s="54">
         <v>4</v>
       </c>
-      <c r="C11" s="64">
+      <c r="C11" s="54">
         <v>14</v>
       </c>
-      <c r="D11" s="64">
+      <c r="D11" s="54">
         <v>22</v>
       </c>
-      <c r="E11" s="65">
+      <c r="E11" s="55">
         <f t="shared" si="0"/>
         <v>1.1428571428571428</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="64">
+      <c r="A12" s="54">
         <v>19</v>
       </c>
-      <c r="B12" s="64">
+      <c r="B12" s="54">
         <v>4</v>
       </c>
-      <c r="C12" s="64">
+      <c r="C12" s="54">
         <v>16</v>
       </c>
-      <c r="D12" s="64">
+      <c r="D12" s="54">
         <v>36</v>
       </c>
-      <c r="E12" s="65">
+      <c r="E12" s="55">
         <f t="shared" si="0"/>
         <v>1.1875</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="64">
+      <c r="A13" s="54">
         <v>20</v>
       </c>
-      <c r="B13" s="64">
+      <c r="B13" s="54">
         <v>4</v>
       </c>
-      <c r="C13" s="64">
+      <c r="C13" s="54">
         <v>19</v>
       </c>
-      <c r="D13" s="64">
+      <c r="D13" s="54">
         <v>60</v>
       </c>
-      <c r="E13" s="65">
+      <c r="E13" s="55">
         <f t="shared" si="0"/>
         <v>1.0526315789473684</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="64">
+      <c r="A14" s="54">
         <v>20</v>
       </c>
-      <c r="B14" s="64">
+      <c r="B14" s="54">
         <v>4</v>
       </c>
-      <c r="C14" s="64">
+      <c r="C14" s="54">
         <v>20</v>
       </c>
-      <c r="D14" s="64">
+      <c r="D14" s="54">
         <v>80</v>
       </c>
-      <c r="E14" s="65">
+      <c r="E14" s="55">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="64">
+      <c r="A15" s="54">
         <v>20</v>
       </c>
-      <c r="B15" s="64">
+      <c r="B15" s="54">
         <v>4</v>
       </c>
-      <c r="C15" s="64">
+      <c r="C15" s="54">
         <v>20</v>
       </c>
-      <c r="D15" s="64">
+      <c r="D15" s="54">
         <v>102</v>
       </c>
-      <c r="E15" s="65">
+      <c r="E15" s="55">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="64">
+      <c r="A16" s="54">
         <v>20</v>
       </c>
-      <c r="B16" s="64">
+      <c r="B16" s="54">
         <v>4</v>
       </c>
-      <c r="C16" s="64">
+      <c r="C16" s="54">
         <v>20</v>
       </c>
-      <c r="D16" s="64">
+      <c r="D16" s="54">
         <v>120</v>
       </c>
-      <c r="E16" s="65">
+      <c r="E16" s="55">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="64">
+      <c r="A17" s="54">
         <v>20</v>
       </c>
-      <c r="B17" s="64">
+      <c r="B17" s="54">
         <v>4</v>
       </c>
-      <c r="C17" s="64">
+      <c r="C17" s="54">
         <v>20</v>
       </c>
-      <c r="D17" s="64">
+      <c r="D17" s="54">
         <v>130</v>
       </c>
-      <c r="E17" s="65">
+      <c r="E17" s="55">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="64">
+      <c r="A18" s="54">
         <v>20</v>
       </c>
-      <c r="B18" s="64">
+      <c r="B18" s="54">
         <v>4</v>
       </c>
-      <c r="C18" s="64">
+      <c r="C18" s="54">
         <v>20</v>
       </c>
-      <c r="D18" s="64">
+      <c r="D18" s="54">
         <v>154</v>
       </c>
-      <c r="E18" s="65">
+      <c r="E18" s="55">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -31036,26 +31009,26 @@
       </c>
     </row>
     <row r="29" spans="3:22" x14ac:dyDescent="0.2">
-      <c r="I29" s="55" t="s">
+      <c r="I29" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="J29" s="55"/>
-      <c r="K29" s="55"/>
-      <c r="L29" s="55"/>
+      <c r="J29" s="58"/>
+      <c r="K29" s="58"/>
+      <c r="L29" s="58"/>
       <c r="M29" s="21"/>
-      <c r="N29" s="55" t="s">
+      <c r="N29" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="O29" s="55"/>
-      <c r="P29" s="55"/>
-      <c r="Q29" s="55"/>
+      <c r="O29" s="58"/>
+      <c r="P29" s="58"/>
+      <c r="Q29" s="58"/>
       <c r="R29" s="21"/>
-      <c r="S29" s="55" t="s">
+      <c r="S29" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="T29" s="55"/>
-      <c r="U29" s="55"/>
-      <c r="V29" s="55"/>
+      <c r="T29" s="58"/>
+      <c r="U29" s="58"/>
+      <c r="V29" s="58"/>
     </row>
     <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="I30" s="21" t="s">
